--- a/config/company_urls_jc.xlsx
+++ b/config/company_urls_jc.xlsx
@@ -7203,7 +7203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1983"/>
+  <dimension ref="A1:H2009"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -58946,9 +58946,6 @@
           <t>investor_relations: change detected</t>
         </is>
       </c>
-      <c r="F1918" t="inlineStr"/>
-      <c r="G1918" t="inlineStr"/>
-      <c r="H1918" t="inlineStr"/>
     </row>
     <row r="1919">
       <c r="A1919" t="inlineStr">
@@ -58976,9 +58973,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F1919" t="inlineStr"/>
-      <c r="G1919" t="inlineStr"/>
-      <c r="H1919" t="inlineStr"/>
     </row>
     <row r="1920">
       <c r="A1920" t="inlineStr">
@@ -59006,9 +59000,6 @@
           <t>[ROUTINE] Insider trade — Schlachet Amir (CEO) sold 24,999 shares @ $38.24 ($955.9K) on 2026-09-02</t>
         </is>
       </c>
-      <c r="F1920" t="inlineStr"/>
-      <c r="G1920" t="inlineStr"/>
-      <c r="H1920" t="inlineStr"/>
     </row>
     <row r="1921">
       <c r="A1921" t="inlineStr">
@@ -59036,9 +59027,6 @@
           <t>[ROUTINE] Insider trade — Zarmi Sigal (Director) sold 350 shares @ $97.44 ($34.1K) on 2026-09-01</t>
         </is>
       </c>
-      <c r="F1921" t="inlineStr"/>
-      <c r="G1921" t="inlineStr"/>
-      <c r="H1921" t="inlineStr"/>
     </row>
     <row r="1922">
       <c r="A1922" t="inlineStr">
@@ -59066,9 +59054,6 @@
           <t>[ROUTINE] Insider trade — Sine Jared F. (Chief Strategy &amp; Legal Officer) sold 4,163 shares @ $101.72 ($423.4K) on 2026-09-01</t>
         </is>
       </c>
-      <c r="F1922" t="inlineStr"/>
-      <c r="G1922" t="inlineStr"/>
-      <c r="H1922" t="inlineStr"/>
     </row>
     <row r="1923">
       <c r="A1923" t="inlineStr">
@@ -59096,9 +59081,6 @@
           <t>[ROUTINE] Insider trade — Palitwanon Phontip (Chief Accounting Officer) sold 530 shares @ $101.19 ($53.6K) on 2026-09-02</t>
         </is>
       </c>
-      <c r="F1923" t="inlineStr"/>
-      <c r="G1923" t="inlineStr"/>
-      <c r="H1923" t="inlineStr"/>
     </row>
     <row r="1924">
       <c r="A1924" t="inlineStr">
@@ -59126,9 +59108,6 @@
           <t>[ROUTINE] Insider trade — McCaffrey Mark (Chief Financial Officer) sold 5,873 shares @ $100.91 ($592.6K) on 2026-09-02</t>
         </is>
       </c>
-      <c r="F1924" t="inlineStr"/>
-      <c r="G1924" t="inlineStr"/>
-      <c r="H1924" t="inlineStr"/>
     </row>
     <row r="1925">
       <c r="A1925" t="inlineStr">
@@ -59156,9 +59135,6 @@
           <t>[ROUTINE] Insider trade — Bhutani Amanpal Singh (Chief Executive Officer) sold 12,694 shares @ $99.86 ($1.27M) on 2026-09-01</t>
         </is>
       </c>
-      <c r="F1925" t="inlineStr"/>
-      <c r="G1925" t="inlineStr"/>
-      <c r="H1925" t="inlineStr"/>
     </row>
     <row r="1926">
       <c r="A1926" t="inlineStr">
@@ -59186,9 +59162,6 @@
           <t>terms: change detected</t>
         </is>
       </c>
-      <c r="F1926" t="inlineStr"/>
-      <c r="G1926" t="inlineStr"/>
-      <c r="H1926" t="inlineStr"/>
     </row>
     <row r="1927">
       <c r="A1927" t="inlineStr">
@@ -59216,9 +59189,6 @@
           <t>[ROUTINE] Insider trade — Colburn Richard Edward III (Chief Product &amp; Tech Officer) sold 2,913 shares @ $82.11 ($239.2K) on 2026-09-03</t>
         </is>
       </c>
-      <c r="F1927" t="inlineStr"/>
-      <c r="G1927" t="inlineStr"/>
-      <c r="H1927" t="inlineStr"/>
     </row>
     <row r="1928">
       <c r="A1928" t="inlineStr">
@@ -59246,9 +59216,6 @@
           <t>[ROUTINE] Insider trade — Frederick R Wilson (Director) sold 20,000 shares @ $81.86 ($1.64M) on 2026-09-01</t>
         </is>
       </c>
-      <c r="F1928" t="inlineStr"/>
-      <c r="G1928" t="inlineStr"/>
-      <c r="H1928" t="inlineStr"/>
     </row>
     <row r="1929">
       <c r="A1929" t="inlineStr">
@@ -59276,9 +59243,6 @@
           <t>[ROUTINE] Insider trade — Silverman Josh (Director) sold 13,367 shares @ $82.11 ($1.10M) on 2026-09-01</t>
         </is>
       </c>
-      <c r="F1929" t="inlineStr"/>
-      <c r="G1929" t="inlineStr"/>
-      <c r="H1929" t="inlineStr"/>
     </row>
     <row r="1930">
       <c r="A1930" t="inlineStr">
@@ -59306,9 +59270,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Colburn Richard Edward III (Officer) plans to sell 2,913 shares (~$244.5K) on/after 09/03/2026</t>
         </is>
       </c>
-      <c r="F1930" t="inlineStr"/>
-      <c r="G1930" t="inlineStr"/>
-      <c r="H1930" t="inlineStr"/>
     </row>
     <row r="1931">
       <c r="A1931" t="inlineStr">
@@ -59336,9 +59297,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Silverman Josh (Officer) plans to sell 1,671 shares (~$140.4K) on/after 09/03/2026</t>
         </is>
       </c>
-      <c r="F1931" t="inlineStr"/>
-      <c r="G1931" t="inlineStr"/>
-      <c r="H1931" t="inlineStr"/>
     </row>
     <row r="1932">
       <c r="A1932" t="inlineStr">
@@ -59366,9 +59324,6 @@
           <t>[ROUTINE] Insider trade — Hu Da-Wai (General Counsel &amp; Secretary) 445 shares withheld for taxes (vest event) on 2026-09-01</t>
         </is>
       </c>
-      <c r="F1932" t="inlineStr"/>
-      <c r="G1932" t="inlineStr"/>
-      <c r="H1932" t="inlineStr"/>
     </row>
     <row r="1933">
       <c r="A1933" t="inlineStr">
@@ -59396,9 +59351,6 @@
           <t>[ROUTINE] Insider trade — Billings William G. (Chief Accounting Officer) 625 shares withheld for taxes (vest event) on 2026-09-01</t>
         </is>
       </c>
-      <c r="F1933" t="inlineStr"/>
-      <c r="G1933" t="inlineStr"/>
-      <c r="H1933" t="inlineStr"/>
     </row>
     <row r="1934">
       <c r="A1934" t="inlineStr">
@@ -59426,9 +59378,6 @@
           <t>[ROUTINE] Insider trade — Deppe Christopher S. (Chief Financial Officer) 1,541 shares withheld for taxes (vest event) on 2026-09-01</t>
         </is>
       </c>
-      <c r="F1934" t="inlineStr"/>
-      <c r="G1934" t="inlineStr"/>
-      <c r="H1934" t="inlineStr"/>
     </row>
     <row r="1935">
       <c r="A1935" t="inlineStr">
@@ -59456,9 +59405,6 @@
           <t>[ROUTINE] Insider trade — Singh Sumit (Chief Executive Officer) 8,840 shares withheld for taxes (vest event) on 2026-09-01</t>
         </is>
       </c>
-      <c r="F1935" t="inlineStr"/>
-      <c r="G1935" t="inlineStr"/>
-      <c r="H1935" t="inlineStr"/>
     </row>
     <row r="1936">
       <c r="A1936" t="inlineStr">
@@ -59486,9 +59432,6 @@
           <t>[ROUTINE] Insider trade — Fang Andy (Director) sold 15,000 shares @ $228.31 ($3.42M) on 2026-09-01</t>
         </is>
       </c>
-      <c r="F1936" t="inlineStr"/>
-      <c r="G1936" t="inlineStr"/>
-      <c r="H1936" t="inlineStr"/>
     </row>
     <row r="1937">
       <c r="A1937" t="inlineStr">
@@ -59516,9 +59459,6 @@
           <t>[ROUTINE] Insider trade — Inukonda Ravi (CHIEF FINANCIAL OFFICER) sold 16,044 shares @ $228.55 ($3.67M) on 2026-09-01</t>
         </is>
       </c>
-      <c r="F1937" t="inlineStr"/>
-      <c r="G1937" t="inlineStr"/>
-      <c r="H1937" t="inlineStr"/>
     </row>
     <row r="1938">
       <c r="A1938" t="inlineStr">
@@ -59546,9 +59486,6 @@
           <t>[ROUTINE] Insider trade — Xu Tony (CHIEF EXECUTIVE OFFICER) sold 16,667 shares @ $230.00 ($3.83M) on 2026-09-01</t>
         </is>
       </c>
-      <c r="F1938" t="inlineStr"/>
-      <c r="G1938" t="inlineStr"/>
-      <c r="H1938" t="inlineStr"/>
     </row>
     <row r="1939">
       <c r="A1939" t="inlineStr">
@@ -59576,9 +59513,6 @@
           <t>9 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F1939" t="inlineStr"/>
-      <c r="G1939" t="inlineStr"/>
-      <c r="H1939" t="inlineStr"/>
     </row>
     <row r="1940">
       <c r="A1940" t="inlineStr">
@@ -59606,9 +59540,6 @@
           <t>pricing: change detected</t>
         </is>
       </c>
-      <c r="F1940" t="inlineStr"/>
-      <c r="G1940" t="inlineStr"/>
-      <c r="H1940" t="inlineStr"/>
     </row>
     <row r="1941">
       <c r="A1941" t="inlineStr">
@@ -59636,9 +59567,6 @@
           <t>management_team: change detected</t>
         </is>
       </c>
-      <c r="F1941" t="inlineStr"/>
-      <c r="G1941" t="inlineStr"/>
-      <c r="H1941" t="inlineStr"/>
     </row>
     <row r="1942">
       <c r="A1942" t="inlineStr">
@@ -59666,9 +59594,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F1942" t="inlineStr"/>
-      <c r="G1942" t="inlineStr"/>
-      <c r="H1942" t="inlineStr"/>
     </row>
     <row r="1943">
       <c r="A1943" t="inlineStr">
@@ -59696,9 +59621,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F1943" t="inlineStr"/>
-      <c r="G1943" t="inlineStr"/>
-      <c r="H1943" t="inlineStr"/>
     </row>
     <row r="1944">
       <c r="A1944" t="inlineStr">
@@ -59726,9 +59648,6 @@
           <t>[ROUTINE] Insider trade — Rascoff Spencer M (Chief Executive Officer) 16,014 shares withheld for taxes (vest event) on 2026-09-01</t>
         </is>
       </c>
-      <c r="F1944" t="inlineStr"/>
-      <c r="G1944" t="inlineStr"/>
-      <c r="H1944" t="inlineStr"/>
     </row>
     <row r="1945">
       <c r="A1945" t="inlineStr">
@@ -59756,9 +59675,6 @@
           <t>[ROUTINE] Insider trade — Ann Mcdaniel (Director) sold 3,531 shares @ $42.43 ($149.8K) on 2026-09-02</t>
         </is>
       </c>
-      <c r="F1945" t="inlineStr"/>
-      <c r="G1945" t="inlineStr"/>
-      <c r="H1945" t="inlineStr"/>
     </row>
     <row r="1946">
       <c r="A1946" t="inlineStr">
@@ -59786,9 +59702,6 @@
           <t>[ROUTINE] Insider trade — Eigenmann Philip D (Chief Accounting Officer) 1,795 shares withheld for taxes (vest event) on 2026-09-01</t>
         </is>
       </c>
-      <c r="F1946" t="inlineStr"/>
-      <c r="G1946" t="inlineStr"/>
-      <c r="H1946" t="inlineStr"/>
     </row>
     <row r="1947">
       <c r="A1947" t="inlineStr">
@@ -59816,9 +59729,6 @@
           <t>[ROUTINE] Insider trade — Edgett Sean (Chief Legal Officer and Sec.) 5,274 shares withheld for taxes (vest event) on 2026-09-01</t>
         </is>
       </c>
-      <c r="F1947" t="inlineStr"/>
-      <c r="G1947" t="inlineStr"/>
-      <c r="H1947" t="inlineStr"/>
     </row>
     <row r="1948">
       <c r="A1948" t="inlineStr">
@@ -59846,9 +59756,6 @@
           <t>[ROUTINE] Insider trade — Bailey Steven Richard Jr. (Chief Financial Officer) 5,276 shares withheld for taxes (vest event) on 2026-09-01</t>
         </is>
       </c>
-      <c r="F1948" t="inlineStr"/>
-      <c r="G1948" t="inlineStr"/>
-      <c r="H1948" t="inlineStr"/>
     </row>
     <row r="1949">
       <c r="A1949" t="inlineStr">
@@ -59876,9 +59783,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Cormier Thielke Claire (Director) plans to sell 1,187 shares (~$42.4K) on/after 09/03/2026</t>
         </is>
       </c>
-      <c r="F1949" t="inlineStr"/>
-      <c r="G1949" t="inlineStr"/>
-      <c r="H1949" t="inlineStr"/>
     </row>
     <row r="1950">
       <c r="A1950" t="inlineStr">
@@ -59906,9 +59810,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Erik C Blachford (Director) plans to sell 792 shares (~$28.3K) on/after 09/03/2026</t>
         </is>
       </c>
-      <c r="F1950" t="inlineStr"/>
-      <c r="G1950" t="inlineStr"/>
-      <c r="H1950" t="inlineStr"/>
     </row>
     <row r="1951">
       <c r="A1951" t="inlineStr">
@@ -59936,9 +59837,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F1951" t="inlineStr"/>
-      <c r="G1951" t="inlineStr"/>
-      <c r="H1951" t="inlineStr"/>
     </row>
     <row r="1952">
       <c r="A1952" t="inlineStr">
@@ -59966,9 +59864,6 @@
           <t>investor_relations: change detected</t>
         </is>
       </c>
-      <c r="F1952" t="inlineStr"/>
-      <c r="G1952" t="inlineStr"/>
-      <c r="H1952" t="inlineStr"/>
     </row>
     <row r="1953">
       <c r="A1953" t="inlineStr">
@@ -59996,9 +59891,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — M Eisen Anthony (Director) plans to sell 6,000 shares (~$501.4K) on/after 09/03/2026</t>
         </is>
       </c>
-      <c r="F1953" t="inlineStr"/>
-      <c r="G1953" t="inlineStr"/>
-      <c r="H1953" t="inlineStr"/>
     </row>
     <row r="1954">
       <c r="A1954" t="inlineStr">
@@ -60026,9 +59918,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Nene Irrevocable Trust (Director) plans to sell 21,124 shares (~$1.03M) on/after 09/03/2026</t>
         </is>
       </c>
-      <c r="F1954" t="inlineStr"/>
-      <c r="G1954" t="inlineStr"/>
-      <c r="H1954" t="inlineStr"/>
     </row>
     <row r="1955">
       <c r="A1955" t="inlineStr">
@@ -60056,9 +59945,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Ilio Irrevocable Trust (Director) plans to sell 21,124 shares (~$1.03M) on/after 09/03/2026</t>
         </is>
       </c>
-      <c r="F1955" t="inlineStr"/>
-      <c r="G1955" t="inlineStr"/>
-      <c r="H1955" t="inlineStr"/>
     </row>
     <row r="1956">
       <c r="A1956" t="inlineStr">
@@ -60086,9 +59972,6 @@
           <t>pricing: change detected</t>
         </is>
       </c>
-      <c r="F1956" t="inlineStr"/>
-      <c r="G1956" t="inlineStr"/>
-      <c r="H1956" t="inlineStr"/>
     </row>
     <row r="1957">
       <c r="A1957" t="inlineStr">
@@ -60116,9 +59999,6 @@
           <t>[ROUTINE] Insider trade — Webster Aaron (EVP, Global Chief Risk Officer) 2,097 shares withheld for taxes (vest event) on 2026-09-01</t>
         </is>
       </c>
-      <c r="F1957" t="inlineStr"/>
-      <c r="G1957" t="inlineStr"/>
-      <c r="H1957" t="inlineStr"/>
     </row>
     <row r="1958">
       <c r="A1958" t="inlineStr">
@@ -60146,9 +60026,6 @@
           <t>[ROUTINE] Insider trade — Natali Chris (SVP, Chief Accounting Officer) 390 shares withheld for taxes (vest event) on 2026-09-01</t>
         </is>
       </c>
-      <c r="F1958" t="inlineStr"/>
-      <c r="G1958" t="inlineStr"/>
-      <c r="H1958" t="inlineStr"/>
     </row>
     <row r="1959">
       <c r="A1959" t="inlineStr">
@@ -60176,9 +60053,6 @@
           <t>[ROUTINE] Insider trade — Miller Jamie S (Chief Fin &amp; Op Officer) 3,785 shares withheld for taxes (vest event) on 2026-09-01</t>
         </is>
       </c>
-      <c r="F1959" t="inlineStr"/>
-      <c r="G1959" t="inlineStr"/>
-      <c r="H1959" t="inlineStr"/>
     </row>
     <row r="1960">
       <c r="A1960" t="inlineStr">
@@ -60206,9 +60080,6 @@
           <t>[ROUTINE] Insider trade — Kereere Suzan (President, Global Markets) 3,524 shares withheld for taxes (vest event) on 2026-09-01</t>
         </is>
       </c>
-      <c r="F1960" t="inlineStr"/>
-      <c r="G1960" t="inlineStr"/>
-      <c r="H1960" t="inlineStr"/>
     </row>
     <row r="1961">
       <c r="A1961" t="inlineStr">
@@ -60236,9 +60107,6 @@
           <t>[ROUTINE] Insider trade — Keller Frank (Pres., Checkout Sol. &amp; Paypal) 5,709 shares withheld for taxes (vest event) on 2026-09-01</t>
         </is>
       </c>
-      <c r="F1961" t="inlineStr"/>
-      <c r="G1961" t="inlineStr"/>
-      <c r="H1961" t="inlineStr"/>
     </row>
     <row r="1962">
       <c r="A1962" t="inlineStr">
@@ -60266,9 +60134,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Kereere Suzan (Officer) plans to sell 3,379 shares (~$184.7K) on/after 09/03/2026</t>
         </is>
       </c>
-      <c r="F1962" t="inlineStr"/>
-      <c r="G1962" t="inlineStr"/>
-      <c r="H1962" t="inlineStr"/>
     </row>
     <row r="1963">
       <c r="A1963" t="inlineStr">
@@ -60296,9 +60161,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Keller Frank (Officer) plans to sell 4,612 shares (~$252.1K) on/after 09/03/2026</t>
         </is>
       </c>
-      <c r="F1963" t="inlineStr"/>
-      <c r="G1963" t="inlineStr"/>
-      <c r="H1963" t="inlineStr"/>
     </row>
     <row r="1964">
       <c r="A1964" t="inlineStr">
@@ -60326,9 +60188,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Natali Christopher (Officer) plans to sell 552 shares (~$30.2K) on/after 09/03/2026</t>
         </is>
       </c>
-      <c r="F1964" t="inlineStr"/>
-      <c r="G1964" t="inlineStr"/>
-      <c r="H1964" t="inlineStr"/>
     </row>
     <row r="1965">
       <c r="A1965" t="inlineStr">
@@ -60356,9 +60215,6 @@
           <t>13 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F1965" t="inlineStr"/>
-      <c r="G1965" t="inlineStr"/>
-      <c r="H1965" t="inlineStr"/>
     </row>
     <row r="1966">
       <c r="A1966" t="inlineStr">
@@ -60386,9 +60242,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F1966" t="inlineStr"/>
-      <c r="G1966" t="inlineStr"/>
-      <c r="H1966" t="inlineStr"/>
     </row>
     <row r="1967">
       <c r="A1967" t="inlineStr">
@@ -60416,9 +60269,6 @@
           <t>[ROUTINE] Insider trade — Adkins Katherine (Chief Legal Officer) sold 83,328 shares @ $73.04 ($6.09M) on 2026-09-01</t>
         </is>
       </c>
-      <c r="F1967" t="inlineStr"/>
-      <c r="G1967" t="inlineStr"/>
-      <c r="H1967" t="inlineStr"/>
     </row>
     <row r="1968">
       <c r="A1968" t="inlineStr">
@@ -60446,9 +60296,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Adkins Katherine (Officer) plans to sell 41,664 shares (~$3.09M) on/after 09/03/2026</t>
         </is>
       </c>
-      <c r="F1968" t="inlineStr"/>
-      <c r="G1968" t="inlineStr"/>
-      <c r="H1968" t="inlineStr"/>
     </row>
     <row r="1969">
       <c r="A1969" t="inlineStr">
@@ -60476,9 +60323,6 @@
           <t>[ROUTINE] Insider trade — O'Hare Robert (Chief Financial Officer) sold 21,631 shares @ $72.26 ($1.56M) on 2026-09-01</t>
         </is>
       </c>
-      <c r="F1969" t="inlineStr"/>
-      <c r="G1969" t="inlineStr"/>
-      <c r="H1969" t="inlineStr"/>
     </row>
     <row r="1970">
       <c r="A1970" t="inlineStr">
@@ -60506,9 +60350,6 @@
           <t>[ROUTINE] Insider trade — Michalek Libor (President) 5,784 shares withheld for taxes (vest event) on 2026-09-01</t>
         </is>
       </c>
-      <c r="F1970" t="inlineStr"/>
-      <c r="G1970" t="inlineStr"/>
-      <c r="H1970" t="inlineStr"/>
     </row>
     <row r="1971">
       <c r="A1971" t="inlineStr">
@@ -60536,9 +60377,6 @@
           <t>[ROUTINE] Insider trade — Linford Michael (President) 4,662 shares withheld for taxes (vest event) on 2026-09-01</t>
         </is>
       </c>
-      <c r="F1971" t="inlineStr"/>
-      <c r="G1971" t="inlineStr"/>
-      <c r="H1971" t="inlineStr"/>
     </row>
     <row r="1972">
       <c r="A1972" t="inlineStr">
@@ -60566,9 +60404,6 @@
           <t>[ROUTINE] Insider trade — Jiyane Siphelele (Chief Accounting Officer) 3,558 shares withheld for taxes (vest event) on 2026-09-01</t>
         </is>
       </c>
-      <c r="F1972" t="inlineStr"/>
-      <c r="G1972" t="inlineStr"/>
-      <c r="H1972" t="inlineStr"/>
     </row>
     <row r="1973">
       <c r="A1973" t="inlineStr">
@@ -60596,9 +60431,6 @@
           <t>1 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F1973" t="inlineStr"/>
-      <c r="G1973" t="inlineStr"/>
-      <c r="H1973" t="inlineStr"/>
     </row>
     <row r="1974">
       <c r="A1974" t="inlineStr">
@@ -60626,9 +60458,6 @@
           <t>[ROUTINE] Insider trade — Bazzano Dara (Chief Accounting Officer) 2,504 shares withheld for taxes (vest event) on 2026-09-01</t>
         </is>
       </c>
-      <c r="F1974" t="inlineStr"/>
-      <c r="G1974" t="inlineStr"/>
-      <c r="H1974" t="inlineStr"/>
     </row>
     <row r="1975">
       <c r="A1975" t="inlineStr">
@@ -60656,9 +60485,6 @@
           <t>[ROUTINE] Insider trade — Verma Shiv (Chief Financial Officer) 16,956 shares withheld for taxes (vest event) on 2026-09-01</t>
         </is>
       </c>
-      <c r="F1975" t="inlineStr"/>
-      <c r="G1975" t="inlineStr"/>
-      <c r="H1975" t="inlineStr"/>
     </row>
     <row r="1976">
       <c r="A1976" t="inlineStr">
@@ -60686,9 +60512,6 @@
           <t>[ROUTINE] Insider trade — Quirk Steven M. (Chief Brokerage Officer) 31,533 shares withheld for taxes (vest event) on 2026-09-01</t>
         </is>
       </c>
-      <c r="F1976" t="inlineStr"/>
-      <c r="G1976" t="inlineStr"/>
-      <c r="H1976" t="inlineStr"/>
     </row>
     <row r="1977">
       <c r="A1977" t="inlineStr">
@@ -60716,9 +60539,6 @@
           <t>[ROUTINE] Insider trade — Gallagher Daniel Martin Jr (Chief Legal Officer) 54,309 shares withheld for taxes (vest event) on 2026-09-01</t>
         </is>
       </c>
-      <c r="F1977" t="inlineStr"/>
-      <c r="G1977" t="inlineStr"/>
-      <c r="H1977" t="inlineStr"/>
     </row>
     <row r="1978">
       <c r="A1978" t="inlineStr">
@@ -60746,9 +60566,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Martin Gallagher Daniel (Officer) plans to sell 30,000 shares (~$3.21M) on/after 09/03/2026</t>
         </is>
       </c>
-      <c r="F1978" t="inlineStr"/>
-      <c r="G1978" t="inlineStr"/>
-      <c r="H1978" t="inlineStr"/>
     </row>
     <row r="1979">
       <c r="A1979" t="inlineStr">
@@ -60776,9 +60593,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Quirk Steven (Officer) plans to sell 24,416 shares (~$2.61M) on/after 09/03/2026</t>
         </is>
       </c>
-      <c r="F1979" t="inlineStr"/>
-      <c r="G1979" t="inlineStr"/>
-      <c r="H1979" t="inlineStr"/>
     </row>
     <row r="1980">
       <c r="A1980" t="inlineStr">
@@ -60806,9 +60620,6 @@
           <t>1 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F1980" t="inlineStr"/>
-      <c r="G1980" t="inlineStr"/>
-      <c r="H1980" t="inlineStr"/>
     </row>
     <row r="1981">
       <c r="A1981" t="inlineStr">
@@ -60836,9 +60647,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F1981" t="inlineStr"/>
-      <c r="G1981" t="inlineStr"/>
-      <c r="H1981" t="inlineStr"/>
     </row>
     <row r="1982">
       <c r="A1982" t="inlineStr">
@@ -60866,9 +60674,6 @@
           <t>investor_relations: change detected</t>
         </is>
       </c>
-      <c r="F1982" t="inlineStr"/>
-      <c r="G1982" t="inlineStr"/>
-      <c r="H1982" t="inlineStr"/>
     </row>
     <row r="1983">
       <c r="A1983" t="inlineStr">
@@ -60896,9 +60701,741 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F1983" t="inlineStr"/>
-      <c r="G1983" t="inlineStr"/>
-      <c r="H1983" t="inlineStr"/>
+    </row>
+    <row r="1984">
+      <c r="A1984" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B1984" t="inlineStr">
+        <is>
+          <t>LYFT</t>
+        </is>
+      </c>
+      <c r="C1984" t="inlineStr">
+        <is>
+          <t>Lyft, Inc.</t>
+        </is>
+      </c>
+      <c r="D1984" t="inlineStr">
+        <is>
+          <t>https://www.lyft.com/blog</t>
+        </is>
+      </c>
+      <c r="E1984" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1985">
+      <c r="A1985" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B1985" t="inlineStr">
+        <is>
+          <t>EXPE</t>
+        </is>
+      </c>
+      <c r="C1985" t="inlineStr">
+        <is>
+          <t>Expedia Group, Inc.</t>
+        </is>
+      </c>
+      <c r="D1985" t="inlineStr">
+        <is>
+          <t>https://careers.expediagroup.com</t>
+        </is>
+      </c>
+      <c r="E1985" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1986">
+      <c r="A1986" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B1986" t="inlineStr">
+        <is>
+          <t>ABNB</t>
+        </is>
+      </c>
+      <c r="C1986" t="inlineStr">
+        <is>
+          <t>Airbnb, Inc.</t>
+        </is>
+      </c>
+      <c r="D1986" t="inlineStr">
+        <is>
+          <t>https://careers.airbnb.com</t>
+        </is>
+      </c>
+      <c r="E1986" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1987">
+      <c r="A1987" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B1987" t="inlineStr">
+        <is>
+          <t>RDDT</t>
+        </is>
+      </c>
+      <c r="C1987" t="inlineStr">
+        <is>
+          <t>Reddit, Inc.</t>
+        </is>
+      </c>
+      <c r="D1987" t="inlineStr">
+        <is>
+          <t>https://redditinc.com/careers</t>
+        </is>
+      </c>
+      <c r="E1987" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1988">
+      <c r="A1988" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B1988" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="C1988" t="inlineStr">
+        <is>
+          <t>Unity Software Inc.</t>
+        </is>
+      </c>
+      <c r="D1988" t="inlineStr">
+        <is>
+          <t>https://careers.unity.com</t>
+        </is>
+      </c>
+      <c r="E1988" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1989">
+      <c r="A1989" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B1989" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="C1989" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="D1989" t="inlineStr">
+        <is>
+          <t>https://about.netflix.com/newsroom</t>
+        </is>
+      </c>
+      <c r="E1989" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1990">
+      <c r="A1990" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B1990" t="inlineStr">
+        <is>
+          <t>SPOT</t>
+        </is>
+      </c>
+      <c r="C1990" t="inlineStr">
+        <is>
+          <t>Spotify Technology S.A.</t>
+        </is>
+      </c>
+      <c r="D1990" t="inlineStr">
+        <is>
+          <t>https://www.spotify.com/premium</t>
+        </is>
+      </c>
+      <c r="E1990" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1991">
+      <c r="A1991" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B1991" t="inlineStr">
+        <is>
+          <t>SPOT</t>
+        </is>
+      </c>
+      <c r="C1991" t="inlineStr">
+        <is>
+          <t>Spotify Technology S.A.</t>
+        </is>
+      </c>
+      <c r="D1991" t="inlineStr">
+        <is>
+          <t>https://www.lifeatspotify.com</t>
+        </is>
+      </c>
+      <c r="E1991" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1992">
+      <c r="A1992" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B1992" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="C1992" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="D1992" t="inlineStr">
+        <is>
+          <t>https://www.disneyplus.com/welcome</t>
+        </is>
+      </c>
+      <c r="E1992" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1993">
+      <c r="A1993" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B1993" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="C1993" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="D1993" t="inlineStr">
+        <is>
+          <t>https://jobs.disneycareers.com</t>
+        </is>
+      </c>
+      <c r="E1993" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1994">
+      <c r="A1994" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B1994" t="inlineStr">
+        <is>
+          <t>FOXA</t>
+        </is>
+      </c>
+      <c r="C1994" t="inlineStr">
+        <is>
+          <t>Fox Corporation</t>
+        </is>
+      </c>
+      <c r="D1994" t="inlineStr">
+        <is>
+          <t>https://foxcareers.com</t>
+        </is>
+      </c>
+      <c r="E1994" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1995">
+      <c r="A1995" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B1995" t="inlineStr">
+        <is>
+          <t>LYV</t>
+        </is>
+      </c>
+      <c r="C1995" t="inlineStr">
+        <is>
+          <t>Live Nation Entertainment, Inc.</t>
+        </is>
+      </c>
+      <c r="D1995" t="inlineStr">
+        <is>
+          <t>https://investors.livenationentertainment.com</t>
+        </is>
+      </c>
+      <c r="E1995" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1996">
+      <c r="A1996" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B1996" t="inlineStr">
+        <is>
+          <t>STUB</t>
+        </is>
+      </c>
+      <c r="C1996" t="inlineStr">
+        <is>
+          <t>StubHub Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="D1996" t="inlineStr">
+        <is>
+          <t>https://www.stubhub.com/careers/</t>
+        </is>
+      </c>
+      <c r="E1996" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1997">
+      <c r="A1997" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B1997" t="inlineStr">
+        <is>
+          <t>TTWO</t>
+        </is>
+      </c>
+      <c r="C1997" t="inlineStr">
+        <is>
+          <t>Take-Two Interactive Software, Inc.</t>
+        </is>
+      </c>
+      <c r="D1997" t="inlineStr">
+        <is>
+          <t>https://ir.take2games.com</t>
+        </is>
+      </c>
+      <c r="E1997" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1998">
+      <c r="A1998" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B1998" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="C1998" t="inlineStr">
+        <is>
+          <t>Electronic Arts Inc.</t>
+        </is>
+      </c>
+      <c r="D1998" t="inlineStr">
+        <is>
+          <t>https://ir.ea.com</t>
+        </is>
+      </c>
+      <c r="E1998" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1999">
+      <c r="A1999" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B1999" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C1999" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D1999" t="inlineStr">
+        <is>
+          <t>https://www.shopify.com/careers</t>
+        </is>
+      </c>
+      <c r="E1999" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F1999" t="inlineStr"/>
+      <c r="G1999" t="inlineStr"/>
+      <c r="H1999" t="inlineStr"/>
+    </row>
+    <row r="2000">
+      <c r="A2000" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B2000" t="inlineStr">
+        <is>
+          <t>EBAY</t>
+        </is>
+      </c>
+      <c r="C2000" t="inlineStr">
+        <is>
+          <t>eBay Inc.</t>
+        </is>
+      </c>
+      <c r="D2000" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/help/policies/member-behaviour-policies/user-agreement?id=4259</t>
+        </is>
+      </c>
+      <c r="E2000" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+      <c r="F2000" t="inlineStr"/>
+      <c r="G2000" t="inlineStr"/>
+      <c r="H2000" t="inlineStr"/>
+    </row>
+    <row r="2001">
+      <c r="A2001" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B2001" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C2001" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D2001" t="inlineStr">
+        <is>
+          <t>https://www.instacart.com/instacart-plus</t>
+        </is>
+      </c>
+      <c r="E2001" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+      <c r="F2001" t="inlineStr"/>
+      <c r="G2001" t="inlineStr"/>
+      <c r="H2001" t="inlineStr"/>
+    </row>
+    <row r="2002">
+      <c r="A2002" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B2002" t="inlineStr">
+        <is>
+          <t>DUOL</t>
+        </is>
+      </c>
+      <c r="C2002" t="inlineStr">
+        <is>
+          <t>Duolingo Inc.</t>
+        </is>
+      </c>
+      <c r="D2002" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/duolingo</t>
+        </is>
+      </c>
+      <c r="E2002" t="inlineStr">
+        <is>
+          <t>2 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F2002" t="inlineStr"/>
+      <c r="G2002" t="inlineStr"/>
+      <c r="H2002" t="inlineStr"/>
+    </row>
+    <row r="2003">
+      <c r="A2003" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B2003" t="inlineStr">
+        <is>
+          <t>MTCH</t>
+        </is>
+      </c>
+      <c r="C2003" t="inlineStr">
+        <is>
+          <t>Match Group Inc.</t>
+        </is>
+      </c>
+      <c r="D2003" t="inlineStr">
+        <is>
+          <t>https://mtch.com/news</t>
+        </is>
+      </c>
+      <c r="E2003" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F2003" t="inlineStr"/>
+      <c r="G2003" t="inlineStr"/>
+      <c r="H2003" t="inlineStr"/>
+    </row>
+    <row r="2004">
+      <c r="A2004" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B2004" t="inlineStr">
+        <is>
+          <t>COMP</t>
+        </is>
+      </c>
+      <c r="C2004" t="inlineStr">
+        <is>
+          <t>Compass Inc.</t>
+        </is>
+      </c>
+      <c r="D2004" t="inlineStr">
+        <is>
+          <t>https://www.compass.com/careers/</t>
+        </is>
+      </c>
+      <c r="E2004" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F2004" t="inlineStr"/>
+      <c r="G2004" t="inlineStr"/>
+      <c r="H2004" t="inlineStr"/>
+    </row>
+    <row r="2005">
+      <c r="A2005" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B2005" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C2005" t="inlineStr">
+        <is>
+          <t>Block Inc. (fmr. Square)</t>
+        </is>
+      </c>
+      <c r="D2005" t="inlineStr">
+        <is>
+          <t>https://investors.block.xyz</t>
+        </is>
+      </c>
+      <c r="E2005" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+      <c r="F2005" t="inlineStr"/>
+      <c r="G2005" t="inlineStr"/>
+      <c r="H2005" t="inlineStr"/>
+    </row>
+    <row r="2006">
+      <c r="A2006" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B2006" t="inlineStr">
+        <is>
+          <t>TOST</t>
+        </is>
+      </c>
+      <c r="C2006" t="inlineStr">
+        <is>
+          <t>Toast Inc.</t>
+        </is>
+      </c>
+      <c r="D2006" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/toast</t>
+        </is>
+      </c>
+      <c r="E2006" t="inlineStr">
+        <is>
+          <t>8 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F2006" t="inlineStr"/>
+      <c r="G2006" t="inlineStr"/>
+      <c r="H2006" t="inlineStr"/>
+    </row>
+    <row r="2007">
+      <c r="A2007" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B2007" t="inlineStr">
+        <is>
+          <t>AFRM</t>
+        </is>
+      </c>
+      <c r="C2007" t="inlineStr">
+        <is>
+          <t>Affirm Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D2007" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/affirm</t>
+        </is>
+      </c>
+      <c r="E2007" t="inlineStr">
+        <is>
+          <t>3 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F2007" t="inlineStr"/>
+      <c r="G2007" t="inlineStr"/>
+      <c r="H2007" t="inlineStr"/>
+    </row>
+    <row r="2008">
+      <c r="A2008" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B2008" t="inlineStr">
+        <is>
+          <t>UPST</t>
+        </is>
+      </c>
+      <c r="C2008" t="inlineStr">
+        <is>
+          <t>Upstart Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D2008" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/upstart</t>
+        </is>
+      </c>
+      <c r="E2008" t="inlineStr">
+        <is>
+          <t>2 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F2008" t="inlineStr"/>
+      <c r="G2008" t="inlineStr"/>
+      <c r="H2008" t="inlineStr"/>
+    </row>
+    <row r="2009">
+      <c r="A2009" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B2009" t="inlineStr">
+        <is>
+          <t>ONON</t>
+        </is>
+      </c>
+      <c r="C2009" t="inlineStr">
+        <is>
+          <t>On Holding AG</t>
+        </is>
+      </c>
+      <c r="D2009" t="inlineStr">
+        <is>
+          <t>https://www.on-running.com/en-us/articles/</t>
+        </is>
+      </c>
+      <c r="E2009" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F2009" t="inlineStr"/>
+      <c r="G2009" t="inlineStr"/>
+      <c r="H2009" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/config/company_urls_jc.xlsx
+++ b/config/company_urls_jc.xlsx
@@ -7203,7 +7203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2009"/>
+  <dimension ref="A1:H2047"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -61133,9 +61133,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F1999" t="inlineStr"/>
-      <c r="G1999" t="inlineStr"/>
-      <c r="H1999" t="inlineStr"/>
     </row>
     <row r="2000">
       <c r="A2000" t="inlineStr">
@@ -61163,9 +61160,6 @@
           <t>terms: change detected</t>
         </is>
       </c>
-      <c r="F2000" t="inlineStr"/>
-      <c r="G2000" t="inlineStr"/>
-      <c r="H2000" t="inlineStr"/>
     </row>
     <row r="2001">
       <c r="A2001" t="inlineStr">
@@ -61193,9 +61187,6 @@
           <t>pricing: change detected</t>
         </is>
       </c>
-      <c r="F2001" t="inlineStr"/>
-      <c r="G2001" t="inlineStr"/>
-      <c r="H2001" t="inlineStr"/>
     </row>
     <row r="2002">
       <c r="A2002" t="inlineStr">
@@ -61223,9 +61214,6 @@
           <t>2 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F2002" t="inlineStr"/>
-      <c r="G2002" t="inlineStr"/>
-      <c r="H2002" t="inlineStr"/>
     </row>
     <row r="2003">
       <c r="A2003" t="inlineStr">
@@ -61253,9 +61241,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F2003" t="inlineStr"/>
-      <c r="G2003" t="inlineStr"/>
-      <c r="H2003" t="inlineStr"/>
     </row>
     <row r="2004">
       <c r="A2004" t="inlineStr">
@@ -61283,9 +61268,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F2004" t="inlineStr"/>
-      <c r="G2004" t="inlineStr"/>
-      <c r="H2004" t="inlineStr"/>
     </row>
     <row r="2005">
       <c r="A2005" t="inlineStr">
@@ -61313,9 +61295,6 @@
           <t>investor_relations: change detected</t>
         </is>
       </c>
-      <c r="F2005" t="inlineStr"/>
-      <c r="G2005" t="inlineStr"/>
-      <c r="H2005" t="inlineStr"/>
     </row>
     <row r="2006">
       <c r="A2006" t="inlineStr">
@@ -61343,9 +61322,6 @@
           <t>8 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F2006" t="inlineStr"/>
-      <c r="G2006" t="inlineStr"/>
-      <c r="H2006" t="inlineStr"/>
     </row>
     <row r="2007">
       <c r="A2007" t="inlineStr">
@@ -61373,9 +61349,6 @@
           <t>3 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F2007" t="inlineStr"/>
-      <c r="G2007" t="inlineStr"/>
-      <c r="H2007" t="inlineStr"/>
     </row>
     <row r="2008">
       <c r="A2008" t="inlineStr">
@@ -61403,9 +61376,6 @@
           <t>2 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F2008" t="inlineStr"/>
-      <c r="G2008" t="inlineStr"/>
-      <c r="H2008" t="inlineStr"/>
     </row>
     <row r="2009">
       <c r="A2009" t="inlineStr">
@@ -61433,9 +61403,1080 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F2009" t="inlineStr"/>
-      <c r="G2009" t="inlineStr"/>
-      <c r="H2009" t="inlineStr"/>
+    </row>
+    <row r="2010">
+      <c r="A2010" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B2010" t="inlineStr">
+        <is>
+          <t>UBER</t>
+        </is>
+      </c>
+      <c r="C2010" t="inlineStr">
+        <is>
+          <t>Uber Technologies, Inc.</t>
+        </is>
+      </c>
+      <c r="D2010" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1543151/000207176126000011/xslF345X06/primarydocument.xml</t>
+        </is>
+      </c>
+      <c r="E2010" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Macdonald Andrew (See Remarks) BOUGHT 70,000 shares @ $75.83 ($5.31M) on 2026-09-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="2011">
+      <c r="A2011" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B2011" t="inlineStr">
+        <is>
+          <t>UBER</t>
+        </is>
+      </c>
+      <c r="C2011" t="inlineStr">
+        <is>
+          <t>Uber Technologies, Inc.</t>
+        </is>
+      </c>
+      <c r="D2011" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1543151/000155278126000469/e26355_uber-euro424b3.htm</t>
+        </is>
+      </c>
+      <c r="E2011" t="inlineStr">
+        <is>
+          <t>[UNKNOWN] Form 424B3</t>
+        </is>
+      </c>
+    </row>
+    <row r="2012">
+      <c r="A2012" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B2012" t="inlineStr">
+        <is>
+          <t>EXPE</t>
+        </is>
+      </c>
+      <c r="C2012" t="inlineStr">
+        <is>
+          <t>Expedia Group, Inc.</t>
+        </is>
+      </c>
+      <c r="D2012" t="inlineStr">
+        <is>
+          <t>https://careers.expediagroup.com</t>
+        </is>
+      </c>
+      <c r="E2012" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2013">
+      <c r="A2013" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B2013" t="inlineStr">
+        <is>
+          <t>BKNG</t>
+        </is>
+      </c>
+      <c r="C2013" t="inlineStr">
+        <is>
+          <t>Booking Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D2013" t="inlineStr">
+        <is>
+          <t>https://www.booking.com/content/terms.html</t>
+        </is>
+      </c>
+      <c r="E2013" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2014">
+      <c r="A2014" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B2014" t="inlineStr">
+        <is>
+          <t>ABNB</t>
+        </is>
+      </c>
+      <c r="C2014" t="inlineStr">
+        <is>
+          <t>Airbnb, Inc.</t>
+        </is>
+      </c>
+      <c r="D2014" t="inlineStr">
+        <is>
+          <t>https://careers.airbnb.com</t>
+        </is>
+      </c>
+      <c r="E2014" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2015">
+      <c r="A2015" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B2015" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="C2015" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="D2015" t="inlineStr">
+        <is>
+          <t>https://investor.atmeta.com</t>
+        </is>
+      </c>
+      <c r="E2015" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2016">
+      <c r="A2016" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B2016" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="C2016" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="D2016" t="inlineStr">
+        <is>
+          <t>https://blog.google</t>
+        </is>
+      </c>
+      <c r="E2016" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2017">
+      <c r="A2017" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B2017" t="inlineStr">
+        <is>
+          <t>RDDT</t>
+        </is>
+      </c>
+      <c r="C2017" t="inlineStr">
+        <is>
+          <t>Reddit, Inc.</t>
+        </is>
+      </c>
+      <c r="D2017" t="inlineStr">
+        <is>
+          <t>https://redditinc.com/careers</t>
+        </is>
+      </c>
+      <c r="E2017" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2018">
+      <c r="A2018" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B2018" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="C2018" t="inlineStr">
+        <is>
+          <t>Unity Software Inc.</t>
+        </is>
+      </c>
+      <c r="D2018" t="inlineStr">
+        <is>
+          <t>https://careers.unity.com</t>
+        </is>
+      </c>
+      <c r="E2018" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2019">
+      <c r="A2019" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B2019" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="C2019" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="D2019" t="inlineStr">
+        <is>
+          <t>https://about.netflix.com/newsroom</t>
+        </is>
+      </c>
+      <c r="E2019" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2020">
+      <c r="A2020" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B2020" t="inlineStr">
+        <is>
+          <t>SPOT</t>
+        </is>
+      </c>
+      <c r="C2020" t="inlineStr">
+        <is>
+          <t>Spotify Technology S.A.</t>
+        </is>
+      </c>
+      <c r="D2020" t="inlineStr">
+        <is>
+          <t>https://www.spotify.com/premium</t>
+        </is>
+      </c>
+      <c r="E2020" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2021">
+      <c r="A2021" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B2021" t="inlineStr">
+        <is>
+          <t>SPOT</t>
+        </is>
+      </c>
+      <c r="C2021" t="inlineStr">
+        <is>
+          <t>Spotify Technology S.A.</t>
+        </is>
+      </c>
+      <c r="D2021" t="inlineStr">
+        <is>
+          <t>https://newsroom.spotify.com</t>
+        </is>
+      </c>
+      <c r="E2021" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2022">
+      <c r="A2022" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B2022" t="inlineStr">
+        <is>
+          <t>SPOT</t>
+        </is>
+      </c>
+      <c r="C2022" t="inlineStr">
+        <is>
+          <t>Spotify Technology S.A.</t>
+        </is>
+      </c>
+      <c r="D2022" t="inlineStr">
+        <is>
+          <t>https://www.lifeatspotify.com</t>
+        </is>
+      </c>
+      <c r="E2022" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2023">
+      <c r="A2023" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B2023" t="inlineStr">
+        <is>
+          <t>BBY</t>
+        </is>
+      </c>
+      <c r="C2023" t="inlineStr">
+        <is>
+          <t>Best Buy Co., Inc.</t>
+        </is>
+      </c>
+      <c r="D2023" t="inlineStr">
+        <is>
+          <t>https://www.bestbuy.com/site/help-topics/terms-and-conditions/pcmcat204400050067.c</t>
+        </is>
+      </c>
+      <c r="E2023" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2024">
+      <c r="A2024" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B2024" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="C2024" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="D2024" t="inlineStr">
+        <is>
+          <t>https://www.disneyplus.com/welcome</t>
+        </is>
+      </c>
+      <c r="E2024" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2025">
+      <c r="A2025" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B2025" t="inlineStr">
+        <is>
+          <t>FOXA</t>
+        </is>
+      </c>
+      <c r="C2025" t="inlineStr">
+        <is>
+          <t>Fox Corporation</t>
+        </is>
+      </c>
+      <c r="D2025" t="inlineStr">
+        <is>
+          <t>https://www.fox.com/terms-of-use</t>
+        </is>
+      </c>
+      <c r="E2025" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2026">
+      <c r="A2026" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B2026" t="inlineStr">
+        <is>
+          <t>FOXA</t>
+        </is>
+      </c>
+      <c r="C2026" t="inlineStr">
+        <is>
+          <t>Fox Corporation</t>
+        </is>
+      </c>
+      <c r="D2026" t="inlineStr">
+        <is>
+          <t>https://foxcareers.com</t>
+        </is>
+      </c>
+      <c r="E2026" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2027">
+      <c r="A2027" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B2027" t="inlineStr">
+        <is>
+          <t>LYV</t>
+        </is>
+      </c>
+      <c r="C2027" t="inlineStr">
+        <is>
+          <t>Live Nation Entertainment, Inc.</t>
+        </is>
+      </c>
+      <c r="D2027" t="inlineStr">
+        <is>
+          <t>https://investors.livenationentertainment.com</t>
+        </is>
+      </c>
+      <c r="E2027" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2028">
+      <c r="A2028" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B2028" t="inlineStr">
+        <is>
+          <t>LYV</t>
+        </is>
+      </c>
+      <c r="C2028" t="inlineStr">
+        <is>
+          <t>Live Nation Entertainment, Inc.</t>
+        </is>
+      </c>
+      <c r="D2028" t="inlineStr">
+        <is>
+          <t>https://www.livenationentertainment.com/careers</t>
+        </is>
+      </c>
+      <c r="E2028" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2029">
+      <c r="A2029" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B2029" t="inlineStr">
+        <is>
+          <t>STUB</t>
+        </is>
+      </c>
+      <c r="C2029" t="inlineStr">
+        <is>
+          <t>StubHub Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="D2029" t="inlineStr">
+        <is>
+          <t>https://www.stubhub.com/careers/</t>
+        </is>
+      </c>
+      <c r="E2029" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2030">
+      <c r="A2030" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B2030" t="inlineStr">
+        <is>
+          <t>TTWO</t>
+        </is>
+      </c>
+      <c r="C2030" t="inlineStr">
+        <is>
+          <t>Take-Two Interactive Software, Inc.</t>
+        </is>
+      </c>
+      <c r="D2030" t="inlineStr">
+        <is>
+          <t>https://ir.take2games.com</t>
+        </is>
+      </c>
+      <c r="E2030" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2031">
+      <c r="A2031" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B2031" t="inlineStr">
+        <is>
+          <t>ADP</t>
+        </is>
+      </c>
+      <c r="C2031" t="inlineStr">
+        <is>
+          <t>Automatic Data Processing, Inc.</t>
+        </is>
+      </c>
+      <c r="D2031" t="inlineStr">
+        <is>
+          <t>https://mediacenter.adp.com</t>
+        </is>
+      </c>
+      <c r="E2031" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2032">
+      <c r="A2032" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B2032" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C2032" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D2032" t="inlineStr">
+        <is>
+          <t>https://www.shopify.com/pricing</t>
+        </is>
+      </c>
+      <c r="E2032" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+      <c r="F2032" t="inlineStr"/>
+      <c r="G2032" t="inlineStr"/>
+      <c r="H2032" t="inlineStr"/>
+    </row>
+    <row r="2033">
+      <c r="A2033" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B2033" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C2033" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D2033" t="inlineStr">
+        <is>
+          <t>https://www.shopify.com/careers</t>
+        </is>
+      </c>
+      <c r="E2033" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F2033" t="inlineStr"/>
+      <c r="G2033" t="inlineStr"/>
+      <c r="H2033" t="inlineStr"/>
+    </row>
+    <row r="2034">
+      <c r="A2034" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B2034" t="inlineStr">
+        <is>
+          <t>GLBE</t>
+        </is>
+      </c>
+      <c r="C2034" t="inlineStr">
+        <is>
+          <t>Global-E Online Ltd.</t>
+        </is>
+      </c>
+      <c r="D2034" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1835963/000119312526384350/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E2034" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Tamari Shahar (COO) sold 24,999 shares @ $38.41 ($960.3K) on 2026-09-03</t>
+        </is>
+      </c>
+      <c r="F2034" t="inlineStr"/>
+      <c r="G2034" t="inlineStr"/>
+      <c r="H2034" t="inlineStr"/>
+    </row>
+    <row r="2035">
+      <c r="A2035" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B2035" t="inlineStr">
+        <is>
+          <t>GLBE</t>
+        </is>
+      </c>
+      <c r="C2035" t="inlineStr">
+        <is>
+          <t>Global-E Online Ltd.</t>
+        </is>
+      </c>
+      <c r="D2035" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1835963/000119312526384342/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E2035" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Debbi Nir (President) sold 228 shares @ $39.21 ($8.9K) on 2026-09-04</t>
+        </is>
+      </c>
+      <c r="F2035" t="inlineStr"/>
+      <c r="G2035" t="inlineStr"/>
+      <c r="H2035" t="inlineStr"/>
+    </row>
+    <row r="2036">
+      <c r="A2036" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B2036" t="inlineStr">
+        <is>
+          <t>EBAY</t>
+        </is>
+      </c>
+      <c r="C2036" t="inlineStr">
+        <is>
+          <t>eBay Inc.</t>
+        </is>
+      </c>
+      <c r="D2036" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/help/policies/member-behaviour-policies/user-agreement?id=4259</t>
+        </is>
+      </c>
+      <c r="E2036" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+      <c r="F2036" t="inlineStr"/>
+      <c r="G2036" t="inlineStr"/>
+      <c r="H2036" t="inlineStr"/>
+    </row>
+    <row r="2037">
+      <c r="A2037" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B2037" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C2037" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D2037" t="inlineStr">
+        <is>
+          <t>https://about.doordash.com/en-us/news</t>
+        </is>
+      </c>
+      <c r="E2037" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F2037" t="inlineStr"/>
+      <c r="G2037" t="inlineStr"/>
+      <c r="H2037" t="inlineStr"/>
+    </row>
+    <row r="2038">
+      <c r="A2038" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B2038" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C2038" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D2038" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/instacart</t>
+        </is>
+      </c>
+      <c r="E2038" t="inlineStr">
+        <is>
+          <t>1 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F2038" t="inlineStr"/>
+      <c r="G2038" t="inlineStr"/>
+      <c r="H2038" t="inlineStr"/>
+    </row>
+    <row r="2039">
+      <c r="A2039" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B2039" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C2039" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D2039" t="inlineStr">
+        <is>
+          <t>https://www.instacart.com/instacart-plus</t>
+        </is>
+      </c>
+      <c r="E2039" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+      <c r="F2039" t="inlineStr"/>
+      <c r="G2039" t="inlineStr"/>
+      <c r="H2039" t="inlineStr"/>
+    </row>
+    <row r="2040">
+      <c r="A2040" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B2040" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C2040" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D2040" t="inlineStr">
+        <is>
+          <t>https://www.instacart.com/company/newsroom</t>
+        </is>
+      </c>
+      <c r="E2040" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F2040" t="inlineStr"/>
+      <c r="G2040" t="inlineStr"/>
+      <c r="H2040" t="inlineStr"/>
+    </row>
+    <row r="2041">
+      <c r="A2041" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B2041" t="inlineStr">
+        <is>
+          <t>DUOL</t>
+        </is>
+      </c>
+      <c r="C2041" t="inlineStr">
+        <is>
+          <t>Duolingo Inc.</t>
+        </is>
+      </c>
+      <c r="D2041" t="inlineStr">
+        <is>
+          <t>https://blog.duolingo.com/</t>
+        </is>
+      </c>
+      <c r="E2041" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F2041" t="inlineStr"/>
+      <c r="G2041" t="inlineStr"/>
+      <c r="H2041" t="inlineStr"/>
+    </row>
+    <row r="2042">
+      <c r="A2042" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B2042" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="C2042" t="inlineStr">
+        <is>
+          <t>Zillow Group Inc.</t>
+        </is>
+      </c>
+      <c r="D2042" t="inlineStr">
+        <is>
+          <t>https://zillow.mediaroom.com</t>
+        </is>
+      </c>
+      <c r="E2042" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F2042" t="inlineStr"/>
+      <c r="G2042" t="inlineStr"/>
+      <c r="H2042" t="inlineStr"/>
+    </row>
+    <row r="2043">
+      <c r="A2043" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B2043" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C2043" t="inlineStr">
+        <is>
+          <t>Block Inc. (fmr. Square)</t>
+        </is>
+      </c>
+      <c r="D2043" t="inlineStr">
+        <is>
+          <t>https://investors.block.xyz</t>
+        </is>
+      </c>
+      <c r="E2043" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+      <c r="F2043" t="inlineStr"/>
+      <c r="G2043" t="inlineStr"/>
+      <c r="H2043" t="inlineStr"/>
+    </row>
+    <row r="2044">
+      <c r="A2044" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B2044" t="inlineStr">
+        <is>
+          <t>TOST</t>
+        </is>
+      </c>
+      <c r="C2044" t="inlineStr">
+        <is>
+          <t>Toast Inc.</t>
+        </is>
+      </c>
+      <c r="D2044" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/toast</t>
+        </is>
+      </c>
+      <c r="E2044" t="inlineStr">
+        <is>
+          <t>9 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F2044" t="inlineStr"/>
+      <c r="G2044" t="inlineStr"/>
+      <c r="H2044" t="inlineStr"/>
+    </row>
+    <row r="2045">
+      <c r="A2045" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B2045" t="inlineStr">
+        <is>
+          <t>HOOD</t>
+        </is>
+      </c>
+      <c r="C2045" t="inlineStr">
+        <is>
+          <t>Robinhood Markets Inc.</t>
+        </is>
+      </c>
+      <c r="D2045" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/robinhood</t>
+        </is>
+      </c>
+      <c r="E2045" t="inlineStr">
+        <is>
+          <t>1 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F2045" t="inlineStr"/>
+      <c r="G2045" t="inlineStr"/>
+      <c r="H2045" t="inlineStr"/>
+    </row>
+    <row r="2046">
+      <c r="A2046" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B2046" t="inlineStr">
+        <is>
+          <t>HOOD</t>
+        </is>
+      </c>
+      <c r="C2046" t="inlineStr">
+        <is>
+          <t>Robinhood Markets Inc.</t>
+        </is>
+      </c>
+      <c r="D2046" t="inlineStr">
+        <is>
+          <t>https://newsroom.aboutrobinhood.com</t>
+        </is>
+      </c>
+      <c r="E2046" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F2046" t="inlineStr"/>
+      <c r="G2046" t="inlineStr"/>
+      <c r="H2046" t="inlineStr"/>
+    </row>
+    <row r="2047">
+      <c r="A2047" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B2047" t="inlineStr">
+        <is>
+          <t>ONON</t>
+        </is>
+      </c>
+      <c r="C2047" t="inlineStr">
+        <is>
+          <t>On Holding AG</t>
+        </is>
+      </c>
+      <c r="D2047" t="inlineStr">
+        <is>
+          <t>https://www.on-running.com/en-us/articles/</t>
+        </is>
+      </c>
+      <c r="E2047" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F2047" t="inlineStr"/>
+      <c r="G2047" t="inlineStr"/>
+      <c r="H2047" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/config/company_urls_jc.xlsx
+++ b/config/company_urls_jc.xlsx
@@ -7203,7 +7203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2047"/>
+  <dimension ref="A1:H2139"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -62024,9 +62024,6 @@
           <t>pricing: change detected</t>
         </is>
       </c>
-      <c r="F2032" t="inlineStr"/>
-      <c r="G2032" t="inlineStr"/>
-      <c r="H2032" t="inlineStr"/>
     </row>
     <row r="2033">
       <c r="A2033" t="inlineStr">
@@ -62054,9 +62051,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F2033" t="inlineStr"/>
-      <c r="G2033" t="inlineStr"/>
-      <c r="H2033" t="inlineStr"/>
     </row>
     <row r="2034">
       <c r="A2034" t="inlineStr">
@@ -62084,9 +62078,6 @@
           <t>[ROUTINE] Insider trade — Tamari Shahar (COO) sold 24,999 shares @ $38.41 ($960.3K) on 2026-09-03</t>
         </is>
       </c>
-      <c r="F2034" t="inlineStr"/>
-      <c r="G2034" t="inlineStr"/>
-      <c r="H2034" t="inlineStr"/>
     </row>
     <row r="2035">
       <c r="A2035" t="inlineStr">
@@ -62114,9 +62105,6 @@
           <t>[ROUTINE] Insider trade — Debbi Nir (President) sold 228 shares @ $39.21 ($8.9K) on 2026-09-04</t>
         </is>
       </c>
-      <c r="F2035" t="inlineStr"/>
-      <c r="G2035" t="inlineStr"/>
-      <c r="H2035" t="inlineStr"/>
     </row>
     <row r="2036">
       <c r="A2036" t="inlineStr">
@@ -62144,9 +62132,6 @@
           <t>terms: change detected</t>
         </is>
       </c>
-      <c r="F2036" t="inlineStr"/>
-      <c r="G2036" t="inlineStr"/>
-      <c r="H2036" t="inlineStr"/>
     </row>
     <row r="2037">
       <c r="A2037" t="inlineStr">
@@ -62174,9 +62159,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F2037" t="inlineStr"/>
-      <c r="G2037" t="inlineStr"/>
-      <c r="H2037" t="inlineStr"/>
     </row>
     <row r="2038">
       <c r="A2038" t="inlineStr">
@@ -62204,9 +62186,6 @@
           <t>1 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F2038" t="inlineStr"/>
-      <c r="G2038" t="inlineStr"/>
-      <c r="H2038" t="inlineStr"/>
     </row>
     <row r="2039">
       <c r="A2039" t="inlineStr">
@@ -62234,9 +62213,6 @@
           <t>pricing: change detected</t>
         </is>
       </c>
-      <c r="F2039" t="inlineStr"/>
-      <c r="G2039" t="inlineStr"/>
-      <c r="H2039" t="inlineStr"/>
     </row>
     <row r="2040">
       <c r="A2040" t="inlineStr">
@@ -62264,9 +62240,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F2040" t="inlineStr"/>
-      <c r="G2040" t="inlineStr"/>
-      <c r="H2040" t="inlineStr"/>
     </row>
     <row r="2041">
       <c r="A2041" t="inlineStr">
@@ -62294,9 +62267,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F2041" t="inlineStr"/>
-      <c r="G2041" t="inlineStr"/>
-      <c r="H2041" t="inlineStr"/>
     </row>
     <row r="2042">
       <c r="A2042" t="inlineStr">
@@ -62324,9 +62294,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F2042" t="inlineStr"/>
-      <c r="G2042" t="inlineStr"/>
-      <c r="H2042" t="inlineStr"/>
     </row>
     <row r="2043">
       <c r="A2043" t="inlineStr">
@@ -62354,9 +62321,6 @@
           <t>investor_relations: change detected</t>
         </is>
       </c>
-      <c r="F2043" t="inlineStr"/>
-      <c r="G2043" t="inlineStr"/>
-      <c r="H2043" t="inlineStr"/>
     </row>
     <row r="2044">
       <c r="A2044" t="inlineStr">
@@ -62384,9 +62348,6 @@
           <t>9 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F2044" t="inlineStr"/>
-      <c r="G2044" t="inlineStr"/>
-      <c r="H2044" t="inlineStr"/>
     </row>
     <row r="2045">
       <c r="A2045" t="inlineStr">
@@ -62414,9 +62375,6 @@
           <t>1 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F2045" t="inlineStr"/>
-      <c r="G2045" t="inlineStr"/>
-      <c r="H2045" t="inlineStr"/>
     </row>
     <row r="2046">
       <c r="A2046" t="inlineStr">
@@ -62444,9 +62402,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F2046" t="inlineStr"/>
-      <c r="G2046" t="inlineStr"/>
-      <c r="H2046" t="inlineStr"/>
     </row>
     <row r="2047">
       <c r="A2047" t="inlineStr">
@@ -62474,9 +62429,2625 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F2047" t="inlineStr"/>
-      <c r="G2047" t="inlineStr"/>
-      <c r="H2047" t="inlineStr"/>
+    </row>
+    <row r="2048">
+      <c r="A2048" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B2048" t="inlineStr">
+        <is>
+          <t>LOGI</t>
+        </is>
+      </c>
+      <c r="C2048" t="inlineStr">
+        <is>
+          <t>Logitech International S.A.</t>
+        </is>
+      </c>
+      <c r="D2048" t="inlineStr">
+        <is>
+          <t>https://www.logitech.com/press</t>
+        </is>
+      </c>
+      <c r="E2048" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2049">
+      <c r="A2049" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B2049" t="inlineStr">
+        <is>
+          <t>GRMN</t>
+        </is>
+      </c>
+      <c r="C2049" t="inlineStr">
+        <is>
+          <t>Garmin Ltd.</t>
+        </is>
+      </c>
+      <c r="D2049" t="inlineStr">
+        <is>
+          <t>https://newsroom.garmin.com</t>
+        </is>
+      </c>
+      <c r="E2049" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2050">
+      <c r="A2050" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B2050" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="C2050" t="inlineStr">
+        <is>
+          <t>Tesla, Inc.</t>
+        </is>
+      </c>
+      <c r="D2050" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1318605/000195004726009212/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E2050" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Taneja Vaibhav (Officer) plans to sell 2,606 shares (~$938.5K) on/after 09/08/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2051">
+      <c r="A2051" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B2051" t="inlineStr">
+        <is>
+          <t>LYFT</t>
+        </is>
+      </c>
+      <c r="C2051" t="inlineStr">
+        <is>
+          <t>Lyft, Inc.</t>
+        </is>
+      </c>
+      <c r="D2051" t="inlineStr">
+        <is>
+          <t>https://www.lyft.com/blog</t>
+        </is>
+      </c>
+      <c r="E2051" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2052">
+      <c r="A2052" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B2052" t="inlineStr">
+        <is>
+          <t>LYFT</t>
+        </is>
+      </c>
+      <c r="C2052" t="inlineStr">
+        <is>
+          <t>Lyft, Inc.</t>
+        </is>
+      </c>
+      <c r="D2052" t="inlineStr">
+        <is>
+          <t>https://investor.lyft.com</t>
+        </is>
+      </c>
+      <c r="E2052" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2053">
+      <c r="A2053" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B2053" t="inlineStr">
+        <is>
+          <t>LYFT</t>
+        </is>
+      </c>
+      <c r="C2053" t="inlineStr">
+        <is>
+          <t>Lyft, Inc.</t>
+        </is>
+      </c>
+      <c r="D2053" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1759509/000162828026061020/lyft-20260906.htm</t>
+        </is>
+      </c>
+      <c r="E2053" t="inlineStr">
+        <is>
+          <t>[MATERIAL] Material event disclosure</t>
+        </is>
+      </c>
+    </row>
+    <row r="2054">
+      <c r="A2054" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B2054" t="inlineStr">
+        <is>
+          <t>EXPE</t>
+        </is>
+      </c>
+      <c r="C2054" t="inlineStr">
+        <is>
+          <t>Expedia Group, Inc.</t>
+        </is>
+      </c>
+      <c r="D2054" t="inlineStr">
+        <is>
+          <t>https://careers.expediagroup.com</t>
+        </is>
+      </c>
+      <c r="E2054" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2055">
+      <c r="A2055" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B2055" t="inlineStr">
+        <is>
+          <t>BKNG</t>
+        </is>
+      </c>
+      <c r="C2055" t="inlineStr">
+        <is>
+          <t>Booking Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D2055" t="inlineStr">
+        <is>
+          <t>https://www.booking.com/content/terms.html</t>
+        </is>
+      </c>
+      <c r="E2055" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2056">
+      <c r="A2056" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B2056" t="inlineStr">
+        <is>
+          <t>ABNB</t>
+        </is>
+      </c>
+      <c r="C2056" t="inlineStr">
+        <is>
+          <t>Airbnb, Inc.</t>
+        </is>
+      </c>
+      <c r="D2056" t="inlineStr">
+        <is>
+          <t>https://news.airbnb.com</t>
+        </is>
+      </c>
+      <c r="E2056" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2057">
+      <c r="A2057" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B2057" t="inlineStr">
+        <is>
+          <t>ABNB</t>
+        </is>
+      </c>
+      <c r="C2057" t="inlineStr">
+        <is>
+          <t>Airbnb, Inc.</t>
+        </is>
+      </c>
+      <c r="D2057" t="inlineStr">
+        <is>
+          <t>https://careers.airbnb.com</t>
+        </is>
+      </c>
+      <c r="E2057" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2058">
+      <c r="A2058" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B2058" t="inlineStr">
+        <is>
+          <t>YOU</t>
+        </is>
+      </c>
+      <c r="C2058" t="inlineStr">
+        <is>
+          <t>Clear Secure, Inc.</t>
+        </is>
+      </c>
+      <c r="D2058" t="inlineStr">
+        <is>
+          <t>https://ir.clearme.com</t>
+        </is>
+      </c>
+      <c r="E2058" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2059">
+      <c r="A2059" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B2059" t="inlineStr">
+        <is>
+          <t>CHH</t>
+        </is>
+      </c>
+      <c r="C2059" t="inlineStr">
+        <is>
+          <t>Choice Hotels International, Inc.</t>
+        </is>
+      </c>
+      <c r="D2059" t="inlineStr">
+        <is>
+          <t>https://careers.choicehotels.com</t>
+        </is>
+      </c>
+      <c r="E2059" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2060">
+      <c r="A2060" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B2060" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="C2060" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="D2060" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1326801/000095010326013672/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E2060" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Anderson Aaron (Chief Accounting Officer) sold 3,240 shares @ $618.06 ($2.00M) on 2026-09-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="2061">
+      <c r="A2061" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B2061" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="C2061" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="D2061" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1326801/000192109426001000/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E2061" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Olivan Javier (Officer) plans to sell 5,354 shares (~$3.30M) on/after 09/08/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2062">
+      <c r="A2062" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B2062" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="C2062" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="D2062" t="inlineStr">
+        <is>
+          <t>https://policies.google.com/terms</t>
+        </is>
+      </c>
+      <c r="E2062" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2063">
+      <c r="A2063" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B2063" t="inlineStr">
+        <is>
+          <t>SNAP</t>
+        </is>
+      </c>
+      <c r="C2063" t="inlineStr">
+        <is>
+          <t>Snap Inc.</t>
+        </is>
+      </c>
+      <c r="D2063" t="inlineStr">
+        <is>
+          <t>https://investor.snap.com/governance/leadership</t>
+        </is>
+      </c>
+      <c r="E2063" t="inlineStr">
+        <is>
+          <t>management_team: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2064">
+      <c r="A2064" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B2064" t="inlineStr">
+        <is>
+          <t>SNAP</t>
+        </is>
+      </c>
+      <c r="C2064" t="inlineStr">
+        <is>
+          <t>Snap Inc.</t>
+        </is>
+      </c>
+      <c r="D2064" t="inlineStr">
+        <is>
+          <t>https://newsroom.snap.com</t>
+        </is>
+      </c>
+      <c r="E2064" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2065">
+      <c r="A2065" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B2065" t="inlineStr">
+        <is>
+          <t>SNAP</t>
+        </is>
+      </c>
+      <c r="C2065" t="inlineStr">
+        <is>
+          <t>Snap Inc.</t>
+        </is>
+      </c>
+      <c r="D2065" t="inlineStr">
+        <is>
+          <t>https://investor.snap.com</t>
+        </is>
+      </c>
+      <c r="E2065" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2066">
+      <c r="A2066" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B2066" t="inlineStr">
+        <is>
+          <t>SNAP</t>
+        </is>
+      </c>
+      <c r="C2066" t="inlineStr">
+        <is>
+          <t>Snap Inc.</t>
+        </is>
+      </c>
+      <c r="D2066" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1564408/000119312526385468/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E2066" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Briers Zachary M (General Counsel) sold 11,257 shares @ $6.00 ($67.5K) on 2026-09-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="2067">
+      <c r="A2067" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B2067" t="inlineStr">
+        <is>
+          <t>SNAP</t>
+        </is>
+      </c>
+      <c r="C2067" t="inlineStr">
+        <is>
+          <t>Snap Inc.</t>
+        </is>
+      </c>
+      <c r="D2067" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1564408/000119312526385199/d129201d8k.htm</t>
+        </is>
+      </c>
+      <c r="E2067" t="inlineStr">
+        <is>
+          <t>[MATERIAL] Material event disclosure</t>
+        </is>
+      </c>
+    </row>
+    <row r="2068">
+      <c r="A2068" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B2068" t="inlineStr">
+        <is>
+          <t>PINS</t>
+        </is>
+      </c>
+      <c r="C2068" t="inlineStr">
+        <is>
+          <t>Pinterest, Inc.</t>
+        </is>
+      </c>
+      <c r="D2068" t="inlineStr">
+        <is>
+          <t>https://newsroom.pinterest.com</t>
+        </is>
+      </c>
+      <c r="E2068" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2069">
+      <c r="A2069" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B2069" t="inlineStr">
+        <is>
+          <t>PINS</t>
+        </is>
+      </c>
+      <c r="C2069" t="inlineStr">
+        <is>
+          <t>Pinterest, Inc.</t>
+        </is>
+      </c>
+      <c r="D2069" t="inlineStr">
+        <is>
+          <t>https://www.pinterestcareers.com</t>
+        </is>
+      </c>
+      <c r="E2069" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2070">
+      <c r="A2070" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B2070" t="inlineStr">
+        <is>
+          <t>PINS</t>
+        </is>
+      </c>
+      <c r="C2070" t="inlineStr">
+        <is>
+          <t>Pinterest, Inc.</t>
+        </is>
+      </c>
+      <c r="D2070" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1506293/000192109426000998/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E2070" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Silbermann Benjamin (Director) plans to sell 46,875 shares (~$940.6K) on/after 09/08/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2071">
+      <c r="A2071" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B2071" t="inlineStr">
+        <is>
+          <t>RDDT</t>
+        </is>
+      </c>
+      <c r="C2071" t="inlineStr">
+        <is>
+          <t>Reddit, Inc.</t>
+        </is>
+      </c>
+      <c r="D2071" t="inlineStr">
+        <is>
+          <t>https://redditinc.com/careers</t>
+        </is>
+      </c>
+      <c r="E2071" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2072">
+      <c r="A2072" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B2072" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="C2072" t="inlineStr">
+        <is>
+          <t>Unity Software Inc.</t>
+        </is>
+      </c>
+      <c r="D2072" t="inlineStr">
+        <is>
+          <t>https://careers.unity.com</t>
+        </is>
+      </c>
+      <c r="E2072" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2073">
+      <c r="A2073" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B2073" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="C2073" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="D2073" t="inlineStr">
+        <is>
+          <t>https://about.netflix.com/newsroom</t>
+        </is>
+      </c>
+      <c r="E2073" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2074">
+      <c r="A2074" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B2074" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="C2074" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="D2074" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1065280/000162828026060922/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E2074" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Richard Barton (Director) plans to sell 720 shares (~$55.9K) on/after 09/08/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2075">
+      <c r="A2075" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B2075" t="inlineStr">
+        <is>
+          <t>SPOT</t>
+        </is>
+      </c>
+      <c r="C2075" t="inlineStr">
+        <is>
+          <t>Spotify Technology S.A.</t>
+        </is>
+      </c>
+      <c r="D2075" t="inlineStr">
+        <is>
+          <t>https://www.spotify.com/premium</t>
+        </is>
+      </c>
+      <c r="E2075" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2076">
+      <c r="A2076" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B2076" t="inlineStr">
+        <is>
+          <t>SPOT</t>
+        </is>
+      </c>
+      <c r="C2076" t="inlineStr">
+        <is>
+          <t>Spotify Technology S.A.</t>
+        </is>
+      </c>
+      <c r="D2076" t="inlineStr">
+        <is>
+          <t>https://www.lifeatspotify.com</t>
+        </is>
+      </c>
+      <c r="E2076" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2077">
+      <c r="A2077" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B2077" t="inlineStr">
+        <is>
+          <t>NYT</t>
+        </is>
+      </c>
+      <c r="C2077" t="inlineStr">
+        <is>
+          <t>The New York Times Company</t>
+        </is>
+      </c>
+      <c r="D2077" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/71691/000119312526386067/d118790d8k.htm</t>
+        </is>
+      </c>
+      <c r="E2077" t="inlineStr">
+        <is>
+          <t>[MATERIAL] Material event disclosure</t>
+        </is>
+      </c>
+    </row>
+    <row r="2078">
+      <c r="A2078" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B2078" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="C2078" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="D2078" t="inlineStr">
+        <is>
+          <t>https://www.disneyplus.com/welcome</t>
+        </is>
+      </c>
+      <c r="E2078" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2079">
+      <c r="A2079" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B2079" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="C2079" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="D2079" t="inlineStr">
+        <is>
+          <t>https://thewaltdisneycompany.com/news/</t>
+        </is>
+      </c>
+      <c r="E2079" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2080">
+      <c r="A2080" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B2080" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="C2080" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="D2080" t="inlineStr">
+        <is>
+          <t>https://jobs.disneycareers.com</t>
+        </is>
+      </c>
+      <c r="E2080" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2081">
+      <c r="A2081" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B2081" t="inlineStr">
+        <is>
+          <t>FOXA</t>
+        </is>
+      </c>
+      <c r="C2081" t="inlineStr">
+        <is>
+          <t>Fox Corporation</t>
+        </is>
+      </c>
+      <c r="D2081" t="inlineStr">
+        <is>
+          <t>https://www.fox.com/terms-of-use</t>
+        </is>
+      </c>
+      <c r="E2081" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2082">
+      <c r="A2082" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B2082" t="inlineStr">
+        <is>
+          <t>FOXA</t>
+        </is>
+      </c>
+      <c r="C2082" t="inlineStr">
+        <is>
+          <t>Fox Corporation</t>
+        </is>
+      </c>
+      <c r="D2082" t="inlineStr">
+        <is>
+          <t>https://foxcareers.com</t>
+        </is>
+      </c>
+      <c r="E2082" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2083">
+      <c r="A2083" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B2083" t="inlineStr">
+        <is>
+          <t>FOXA</t>
+        </is>
+      </c>
+      <c r="C2083" t="inlineStr">
+        <is>
+          <t>Fox Corporation</t>
+        </is>
+      </c>
+      <c r="D2083" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1754301/000119312526385985/d176496d425.htm</t>
+        </is>
+      </c>
+      <c r="E2083" t="inlineStr">
+        <is>
+          <t>[UNKNOWN] Form 425</t>
+        </is>
+      </c>
+    </row>
+    <row r="2084">
+      <c r="A2084" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B2084" t="inlineStr">
+        <is>
+          <t>FOXA</t>
+        </is>
+      </c>
+      <c r="C2084" t="inlineStr">
+        <is>
+          <t>Fox Corporation</t>
+        </is>
+      </c>
+      <c r="D2084" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1754301/000119312526385979/d176496d8k.htm</t>
+        </is>
+      </c>
+      <c r="E2084" t="inlineStr">
+        <is>
+          <t>[MATERIAL] Material event disclosure</t>
+        </is>
+      </c>
+    </row>
+    <row r="2085">
+      <c r="A2085" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B2085" t="inlineStr">
+        <is>
+          <t>WMG</t>
+        </is>
+      </c>
+      <c r="C2085" t="inlineStr">
+        <is>
+          <t>Warner Music Group Corp.</t>
+        </is>
+      </c>
+      <c r="D2085" t="inlineStr">
+        <is>
+          <t>https://www.wmg.com/news/</t>
+        </is>
+      </c>
+      <c r="E2085" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2086">
+      <c r="A2086" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B2086" t="inlineStr">
+        <is>
+          <t>LYV</t>
+        </is>
+      </c>
+      <c r="C2086" t="inlineStr">
+        <is>
+          <t>Live Nation Entertainment, Inc.</t>
+        </is>
+      </c>
+      <c r="D2086" t="inlineStr">
+        <is>
+          <t>https://investors.livenationentertainment.com</t>
+        </is>
+      </c>
+      <c r="E2086" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2087">
+      <c r="A2087" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B2087" t="inlineStr">
+        <is>
+          <t>LYV</t>
+        </is>
+      </c>
+      <c r="C2087" t="inlineStr">
+        <is>
+          <t>Live Nation Entertainment, Inc.</t>
+        </is>
+      </c>
+      <c r="D2087" t="inlineStr">
+        <is>
+          <t>https://www.livenationentertainment.com/careers</t>
+        </is>
+      </c>
+      <c r="E2087" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2088">
+      <c r="A2088" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B2088" t="inlineStr">
+        <is>
+          <t>STUB</t>
+        </is>
+      </c>
+      <c r="C2088" t="inlineStr">
+        <is>
+          <t>StubHub Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="D2088" t="inlineStr">
+        <is>
+          <t>https://www.stubhub.com/careers/</t>
+        </is>
+      </c>
+      <c r="E2088" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2089">
+      <c r="A2089" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B2089" t="inlineStr">
+        <is>
+          <t>TTWO</t>
+        </is>
+      </c>
+      <c r="C2089" t="inlineStr">
+        <is>
+          <t>Take-Two Interactive Software, Inc.</t>
+        </is>
+      </c>
+      <c r="D2089" t="inlineStr">
+        <is>
+          <t>https://ir.take2games.com</t>
+        </is>
+      </c>
+      <c r="E2089" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2090">
+      <c r="A2090" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B2090" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="C2090" t="inlineStr">
+        <is>
+          <t>Electronic Arts Inc.</t>
+        </is>
+      </c>
+      <c r="D2090" t="inlineStr">
+        <is>
+          <t>https://www.ea.com/news</t>
+        </is>
+      </c>
+      <c r="E2090" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2091">
+      <c r="A2091" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B2091" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="C2091" t="inlineStr">
+        <is>
+          <t>Electronic Arts Inc.</t>
+        </is>
+      </c>
+      <c r="D2091" t="inlineStr">
+        <is>
+          <t>https://ir.ea.com</t>
+        </is>
+      </c>
+      <c r="E2091" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2092">
+      <c r="A2092" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B2092" t="inlineStr">
+        <is>
+          <t>RBLX</t>
+        </is>
+      </c>
+      <c r="C2092" t="inlineStr">
+        <is>
+          <t>Roblox Corporation</t>
+        </is>
+      </c>
+      <c r="D2092" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1315098/000195004726009219/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E2092" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Reinstra Mark (Officer) plans to sell 5,773 shares (~$250.0K) on/after 09/08/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2093">
+      <c r="A2093" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B2093" t="inlineStr">
+        <is>
+          <t>ADP</t>
+        </is>
+      </c>
+      <c r="C2093" t="inlineStr">
+        <is>
+          <t>Automatic Data Processing, Inc.</t>
+        </is>
+      </c>
+      <c r="D2093" t="inlineStr">
+        <is>
+          <t>https://mediacenter.adp.com</t>
+        </is>
+      </c>
+      <c r="E2093" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2094">
+      <c r="A2094" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B2094" t="inlineStr">
+        <is>
+          <t>PAYX</t>
+        </is>
+      </c>
+      <c r="C2094" t="inlineStr">
+        <is>
+          <t>Paychex, Inc.</t>
+        </is>
+      </c>
+      <c r="D2094" t="inlineStr">
+        <is>
+          <t>https://investor.paychex.com</t>
+        </is>
+      </c>
+      <c r="E2094" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2095">
+      <c r="A2095" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B2095" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C2095" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D2095" t="inlineStr">
+        <is>
+          <t>https://www.shopify.com/pricing</t>
+        </is>
+      </c>
+      <c r="E2095" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+      <c r="F2095" t="inlineStr"/>
+      <c r="G2095" t="inlineStr"/>
+      <c r="H2095" t="inlineStr"/>
+    </row>
+    <row r="2096">
+      <c r="A2096" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B2096" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C2096" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D2096" t="inlineStr">
+        <is>
+          <t>https://www.shopify.com/careers</t>
+        </is>
+      </c>
+      <c r="E2096" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F2096" t="inlineStr"/>
+      <c r="G2096" t="inlineStr"/>
+      <c r="H2096" t="inlineStr"/>
+    </row>
+    <row r="2097">
+      <c r="A2097" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B2097" t="inlineStr">
+        <is>
+          <t>WIX</t>
+        </is>
+      </c>
+      <c r="C2097" t="inlineStr">
+        <is>
+          <t>Wix.com Ltd.</t>
+        </is>
+      </c>
+      <c r="D2097" t="inlineStr">
+        <is>
+          <t>https://www.wix.com/press-room/home/post/base44-integrates-native-google-ads-campaign-management-for-app-builders</t>
+        </is>
+      </c>
+      <c r="E2097" t="inlineStr">
+        <is>
+          <t>newsroom: Base44 Integrates Native Google Ads Campaign Management for App Builders</t>
+        </is>
+      </c>
+      <c r="F2097" t="inlineStr"/>
+      <c r="G2097" t="inlineStr"/>
+      <c r="H2097" t="inlineStr"/>
+    </row>
+    <row r="2098">
+      <c r="A2098" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B2098" t="inlineStr">
+        <is>
+          <t>WIX</t>
+        </is>
+      </c>
+      <c r="C2098" t="inlineStr">
+        <is>
+          <t>Wix.com Ltd.</t>
+        </is>
+      </c>
+      <c r="D2098" t="inlineStr">
+        <is>
+          <t>https://www.wix.com/jobs/home</t>
+        </is>
+      </c>
+      <c r="E2098" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F2098" t="inlineStr"/>
+      <c r="G2098" t="inlineStr"/>
+      <c r="H2098" t="inlineStr"/>
+    </row>
+    <row r="2099">
+      <c r="A2099" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B2099" t="inlineStr">
+        <is>
+          <t>GLBE</t>
+        </is>
+      </c>
+      <c r="C2099" t="inlineStr">
+        <is>
+          <t>Global-E Online Ltd.</t>
+        </is>
+      </c>
+      <c r="D2099" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1835963/000195004726009198/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E2099" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Koren Ofer (Officer) plans to sell 12,500 shares (~$479.6K) on/after 09/08/2026</t>
+        </is>
+      </c>
+      <c r="F2099" t="inlineStr"/>
+      <c r="G2099" t="inlineStr"/>
+      <c r="H2099" t="inlineStr"/>
+    </row>
+    <row r="2100">
+      <c r="A2100" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B2100" t="inlineStr">
+        <is>
+          <t>EBAY</t>
+        </is>
+      </c>
+      <c r="C2100" t="inlineStr">
+        <is>
+          <t>eBay Inc.</t>
+        </is>
+      </c>
+      <c r="D2100" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/help/policies/member-behaviour-policies/user-agreement?id=4259</t>
+        </is>
+      </c>
+      <c r="E2100" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+      <c r="F2100" t="inlineStr"/>
+      <c r="G2100" t="inlineStr"/>
+      <c r="H2100" t="inlineStr"/>
+    </row>
+    <row r="2101">
+      <c r="A2101" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B2101" t="inlineStr">
+        <is>
+          <t>EBAY</t>
+        </is>
+      </c>
+      <c r="C2101" t="inlineStr">
+        <is>
+          <t>eBay Inc.</t>
+        </is>
+      </c>
+      <c r="D2101" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1065088/000195824426000578/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E2101" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — James Joseph Iannone (Officer) plans to sell 22,220 shares (~$2.32M) on/after 09/08/2026</t>
+        </is>
+      </c>
+      <c r="F2101" t="inlineStr"/>
+      <c r="G2101" t="inlineStr"/>
+      <c r="H2101" t="inlineStr"/>
+    </row>
+    <row r="2102">
+      <c r="A2102" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B2102" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="C2102" t="inlineStr">
+        <is>
+          <t>Wayfair Inc.</t>
+        </is>
+      </c>
+      <c r="D2102" t="inlineStr">
+        <is>
+          <t>https://investor.wayfair.com/news</t>
+        </is>
+      </c>
+      <c r="E2102" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F2102" t="inlineStr"/>
+      <c r="G2102" t="inlineStr"/>
+      <c r="H2102" t="inlineStr"/>
+    </row>
+    <row r="2103">
+      <c r="A2103" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B2103" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="C2103" t="inlineStr">
+        <is>
+          <t>Wayfair Inc.</t>
+        </is>
+      </c>
+      <c r="D2103" t="inlineStr">
+        <is>
+          <t>https://investor.wayfair.com</t>
+        </is>
+      </c>
+      <c r="E2103" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+      <c r="F2103" t="inlineStr"/>
+      <c r="G2103" t="inlineStr"/>
+      <c r="H2103" t="inlineStr"/>
+    </row>
+    <row r="2104">
+      <c r="A2104" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B2104" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="C2104" t="inlineStr">
+        <is>
+          <t>Wayfair Inc.</t>
+        </is>
+      </c>
+      <c r="D2104" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1616707/000195917326006781/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E2104" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Blotner Jon (Officer) plans to sell 6,968 shares (~$698.3K) on/after 09/08/2026</t>
+        </is>
+      </c>
+      <c r="F2104" t="inlineStr"/>
+      <c r="G2104" t="inlineStr"/>
+      <c r="H2104" t="inlineStr"/>
+    </row>
+    <row r="2105">
+      <c r="A2105" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B2105" t="inlineStr">
+        <is>
+          <t>CHWY</t>
+        </is>
+      </c>
+      <c r="C2105" t="inlineStr">
+        <is>
+          <t>Chewy Inc.</t>
+        </is>
+      </c>
+      <c r="D2105" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1766502/000162828026061018/chwy-20260802.htm</t>
+        </is>
+      </c>
+      <c r="E2105" t="inlineStr">
+        <is>
+          <t>[MATERIAL] Quarterly report</t>
+        </is>
+      </c>
+      <c r="F2105" t="inlineStr"/>
+      <c r="G2105" t="inlineStr"/>
+      <c r="H2105" t="inlineStr"/>
+    </row>
+    <row r="2106">
+      <c r="A2106" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B2106" t="inlineStr">
+        <is>
+          <t>CHWY</t>
+        </is>
+      </c>
+      <c r="C2106" t="inlineStr">
+        <is>
+          <t>Chewy Inc.</t>
+        </is>
+      </c>
+      <c r="D2106" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1766502/000162828026061011/chwy-20260909.htm</t>
+        </is>
+      </c>
+      <c r="E2106" t="inlineStr">
+        <is>
+          <t>[MATERIAL] Material event disclosure</t>
+        </is>
+      </c>
+      <c r="F2106" t="inlineStr"/>
+      <c r="G2106" t="inlineStr"/>
+      <c r="H2106" t="inlineStr"/>
+    </row>
+    <row r="2107">
+      <c r="A2107" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B2107" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C2107" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D2107" t="inlineStr">
+        <is>
+          <t>https://ir.doordash.com/governance/management/default.aspx</t>
+        </is>
+      </c>
+      <c r="E2107" t="inlineStr">
+        <is>
+          <t>management_team: change detected</t>
+        </is>
+      </c>
+      <c r="F2107" t="inlineStr"/>
+      <c r="G2107" t="inlineStr"/>
+      <c r="H2107" t="inlineStr"/>
+    </row>
+    <row r="2108">
+      <c r="A2108" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B2108" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C2108" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D2108" t="inlineStr">
+        <is>
+          <t>https://ir.doordash.com</t>
+        </is>
+      </c>
+      <c r="E2108" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+      <c r="F2108" t="inlineStr"/>
+      <c r="G2108" t="inlineStr"/>
+      <c r="H2108" t="inlineStr"/>
+    </row>
+    <row r="2109">
+      <c r="A2109" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B2109" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C2109" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D2109" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1792789/000183261726000012/xslF345X06/form4-09082026_040901.xml</t>
+        </is>
+      </c>
+      <c r="E2109" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Xu Tony (CHIEF EXECUTIVE OFFICER) other: 31,428 shares on 2026-09-03</t>
+        </is>
+      </c>
+      <c r="F2109" t="inlineStr"/>
+      <c r="G2109" t="inlineStr"/>
+      <c r="H2109" t="inlineStr"/>
+    </row>
+    <row r="2110">
+      <c r="A2110" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B2110" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C2110" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D2110" t="inlineStr">
+        <is>
+          <t>https://www.instacart.com/instacart-plus</t>
+        </is>
+      </c>
+      <c r="E2110" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+      <c r="F2110" t="inlineStr"/>
+      <c r="G2110" t="inlineStr"/>
+      <c r="H2110" t="inlineStr"/>
+    </row>
+    <row r="2111">
+      <c r="A2111" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B2111" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C2111" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D2111" t="inlineStr">
+        <is>
+          <t>https://www.instacart.com/company/newsroom</t>
+        </is>
+      </c>
+      <c r="E2111" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F2111" t="inlineStr"/>
+      <c r="G2111" t="inlineStr"/>
+      <c r="H2111" t="inlineStr"/>
+    </row>
+    <row r="2112">
+      <c r="A2112" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B2112" t="inlineStr">
+        <is>
+          <t>DUOL</t>
+        </is>
+      </c>
+      <c r="C2112" t="inlineStr">
+        <is>
+          <t>Duolingo Inc.</t>
+        </is>
+      </c>
+      <c r="D2112" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1562088/000195004726009183/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E2112" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — B. Gordon William (Director) plans to sell 20,000 shares (~$3.09M) on/after 09/08/2026</t>
+        </is>
+      </c>
+      <c r="F2112" t="inlineStr"/>
+      <c r="G2112" t="inlineStr"/>
+      <c r="H2112" t="inlineStr"/>
+    </row>
+    <row r="2113">
+      <c r="A2113" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B2113" t="inlineStr">
+        <is>
+          <t>RKT</t>
+        </is>
+      </c>
+      <c r="C2113" t="inlineStr">
+        <is>
+          <t>Rocket Companies Inc.</t>
+        </is>
+      </c>
+      <c r="D2113" t="inlineStr">
+        <is>
+          <t>https://ir.rocketcompanies.com</t>
+        </is>
+      </c>
+      <c r="E2113" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+      <c r="F2113" t="inlineStr"/>
+      <c r="G2113" t="inlineStr"/>
+      <c r="H2113" t="inlineStr"/>
+    </row>
+    <row r="2114">
+      <c r="A2114" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B2114" t="inlineStr">
+        <is>
+          <t>COMP</t>
+        </is>
+      </c>
+      <c r="C2114" t="inlineStr">
+        <is>
+          <t>Compass Inc.</t>
+        </is>
+      </c>
+      <c r="D2114" t="inlineStr">
+        <is>
+          <t>https://investors.compass.com</t>
+        </is>
+      </c>
+      <c r="E2114" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+      <c r="F2114" t="inlineStr"/>
+      <c r="G2114" t="inlineStr"/>
+      <c r="H2114" t="inlineStr"/>
+    </row>
+    <row r="2115">
+      <c r="A2115" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B2115" t="inlineStr">
+        <is>
+          <t>COMP</t>
+        </is>
+      </c>
+      <c r="C2115" t="inlineStr">
+        <is>
+          <t>Compass Inc.</t>
+        </is>
+      </c>
+      <c r="D2115" t="inlineStr">
+        <is>
+          <t>https://www.compass.com/careers/</t>
+        </is>
+      </c>
+      <c r="E2115" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F2115" t="inlineStr"/>
+      <c r="G2115" t="inlineStr"/>
+      <c r="H2115" t="inlineStr"/>
+    </row>
+    <row r="2116">
+      <c r="A2116" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B2116" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C2116" t="inlineStr">
+        <is>
+          <t>Block Inc. (fmr. Square)</t>
+        </is>
+      </c>
+      <c r="D2116" t="inlineStr">
+        <is>
+          <t>https://investors.block.xyz/governance/leadership/default.aspx</t>
+        </is>
+      </c>
+      <c r="E2116" t="inlineStr">
+        <is>
+          <t>management_team: change detected</t>
+        </is>
+      </c>
+      <c r="F2116" t="inlineStr"/>
+      <c r="G2116" t="inlineStr"/>
+      <c r="H2116" t="inlineStr"/>
+    </row>
+    <row r="2117">
+      <c r="A2117" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B2117" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C2117" t="inlineStr">
+        <is>
+          <t>Block Inc. (fmr. Square)</t>
+        </is>
+      </c>
+      <c r="D2117" t="inlineStr">
+        <is>
+          <t>https://investors.block.xyz</t>
+        </is>
+      </c>
+      <c r="E2117" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+      <c r="F2117" t="inlineStr"/>
+      <c r="G2117" t="inlineStr"/>
+      <c r="H2117" t="inlineStr"/>
+    </row>
+    <row r="2118">
+      <c r="A2118" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B2118" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C2118" t="inlineStr">
+        <is>
+          <t>Block Inc. (fmr. Square)</t>
+        </is>
+      </c>
+      <c r="D2118" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1512673/000195004726009221/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E2118" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — M Eisen Anthony (Director) plans to sell 6,000 shares (~$493.1K) on/after 09/08/2026</t>
+        </is>
+      </c>
+      <c r="F2118" t="inlineStr"/>
+      <c r="G2118" t="inlineStr"/>
+      <c r="H2118" t="inlineStr"/>
+    </row>
+    <row r="2119">
+      <c r="A2119" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B2119" t="inlineStr">
+        <is>
+          <t>BILL</t>
+        </is>
+      </c>
+      <c r="C2119" t="inlineStr">
+        <is>
+          <t>BILL Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D2119" t="inlineStr">
+        <is>
+          <t>https://investor.bill.com</t>
+        </is>
+      </c>
+      <c r="E2119" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+      <c r="F2119" t="inlineStr"/>
+      <c r="G2119" t="inlineStr"/>
+      <c r="H2119" t="inlineStr"/>
+    </row>
+    <row r="2120">
+      <c r="A2120" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B2120" t="inlineStr">
+        <is>
+          <t>PYPL</t>
+        </is>
+      </c>
+      <c r="C2120" t="inlineStr">
+        <is>
+          <t>PayPal Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D2120" t="inlineStr">
+        <is>
+          <t>https://about.pypl.com/who-we-are/executive-leadership/default.aspx</t>
+        </is>
+      </c>
+      <c r="E2120" t="inlineStr">
+        <is>
+          <t>management_team: change detected</t>
+        </is>
+      </c>
+      <c r="F2120" t="inlineStr"/>
+      <c r="G2120" t="inlineStr"/>
+      <c r="H2120" t="inlineStr"/>
+    </row>
+    <row r="2121">
+      <c r="A2121" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B2121" t="inlineStr">
+        <is>
+          <t>PYPL</t>
+        </is>
+      </c>
+      <c r="C2121" t="inlineStr">
+        <is>
+          <t>PayPal Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D2121" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1633917/000190527226000016/xslF345X06/edgardoc.xml</t>
+        </is>
+      </c>
+      <c r="E2121" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Natali Chris (SVP, Chief Accounting Officer) sold 552 shares @ $54.80 ($30.2K) on 2026-09-03</t>
+        </is>
+      </c>
+      <c r="F2121" t="inlineStr"/>
+      <c r="G2121" t="inlineStr"/>
+      <c r="H2121" t="inlineStr"/>
+    </row>
+    <row r="2122">
+      <c r="A2122" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B2122" t="inlineStr">
+        <is>
+          <t>PYPL</t>
+        </is>
+      </c>
+      <c r="C2122" t="inlineStr">
+        <is>
+          <t>PayPal Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D2122" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1633917/000189608626000016/xslF345X06/edgardoc.xml</t>
+        </is>
+      </c>
+      <c r="E2122" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Kereere Suzan (President, Global Markets) sold 3,379 shares @ $55.72 ($188.3K) on 2026-09-03</t>
+        </is>
+      </c>
+      <c r="F2122" t="inlineStr"/>
+      <c r="G2122" t="inlineStr"/>
+      <c r="H2122" t="inlineStr"/>
+    </row>
+    <row r="2123">
+      <c r="A2123" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B2123" t="inlineStr">
+        <is>
+          <t>PYPL</t>
+        </is>
+      </c>
+      <c r="C2123" t="inlineStr">
+        <is>
+          <t>PayPal Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D2123" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1633917/000200641626000017/xslF345X06/edgardoc.xml</t>
+        </is>
+      </c>
+      <c r="E2123" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Keller Frank (Pres., Checkout Sol. &amp; PayPal) sold 4,612 shares @ $55.43 ($255.7K) on 2026-09-03</t>
+        </is>
+      </c>
+      <c r="F2123" t="inlineStr"/>
+      <c r="G2123" t="inlineStr"/>
+      <c r="H2123" t="inlineStr"/>
+    </row>
+    <row r="2124">
+      <c r="A2124" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B2124" t="inlineStr">
+        <is>
+          <t>TOST</t>
+        </is>
+      </c>
+      <c r="C2124" t="inlineStr">
+        <is>
+          <t>Toast Inc.</t>
+        </is>
+      </c>
+      <c r="D2124" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/toast</t>
+        </is>
+      </c>
+      <c r="E2124" t="inlineStr">
+        <is>
+          <t>34 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F2124" t="inlineStr"/>
+      <c r="G2124" t="inlineStr"/>
+      <c r="H2124" t="inlineStr"/>
+    </row>
+    <row r="2125">
+      <c r="A2125" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B2125" t="inlineStr">
+        <is>
+          <t>TOST</t>
+        </is>
+      </c>
+      <c r="C2125" t="inlineStr">
+        <is>
+          <t>Toast Inc.</t>
+        </is>
+      </c>
+      <c r="D2125" t="inlineStr">
+        <is>
+          <t>https://investors.toasttab.com</t>
+        </is>
+      </c>
+      <c r="E2125" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+      <c r="F2125" t="inlineStr"/>
+      <c r="G2125" t="inlineStr"/>
+      <c r="H2125" t="inlineStr"/>
+    </row>
+    <row r="2126">
+      <c r="A2126" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B2126" t="inlineStr">
+        <is>
+          <t>DAVE</t>
+        </is>
+      </c>
+      <c r="C2126" t="inlineStr">
+        <is>
+          <t>Dave Inc.</t>
+        </is>
+      </c>
+      <c r="D2126" t="inlineStr">
+        <is>
+          <t>https://dave.com/careers</t>
+        </is>
+      </c>
+      <c r="E2126" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F2126" t="inlineStr"/>
+      <c r="G2126" t="inlineStr"/>
+      <c r="H2126" t="inlineStr"/>
+    </row>
+    <row r="2127">
+      <c r="A2127" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B2127" t="inlineStr">
+        <is>
+          <t>DAVE</t>
+        </is>
+      </c>
+      <c r="C2127" t="inlineStr">
+        <is>
+          <t>Dave Inc.</t>
+        </is>
+      </c>
+      <c r="D2127" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1841408/000195004726009187/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E2127" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Rozov Yadin (Director) plans to sell 11,184 shares (~$4.26M) on/after 09/08/2026</t>
+        </is>
+      </c>
+      <c r="F2127" t="inlineStr"/>
+      <c r="G2127" t="inlineStr"/>
+      <c r="H2127" t="inlineStr"/>
+    </row>
+    <row r="2128">
+      <c r="A2128" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B2128" t="inlineStr">
+        <is>
+          <t>AFRM</t>
+        </is>
+      </c>
+      <c r="C2128" t="inlineStr">
+        <is>
+          <t>Affirm Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D2128" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/affirm</t>
+        </is>
+      </c>
+      <c r="E2128" t="inlineStr">
+        <is>
+          <t>3 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F2128" t="inlineStr"/>
+      <c r="G2128" t="inlineStr"/>
+      <c r="H2128" t="inlineStr"/>
+    </row>
+    <row r="2129">
+      <c r="A2129" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B2129" t="inlineStr">
+        <is>
+          <t>HOOD</t>
+        </is>
+      </c>
+      <c r="C2129" t="inlineStr">
+        <is>
+          <t>Robinhood Markets Inc.</t>
+        </is>
+      </c>
+      <c r="D2129" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/robinhood</t>
+        </is>
+      </c>
+      <c r="E2129" t="inlineStr">
+        <is>
+          <t>1 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F2129" t="inlineStr"/>
+      <c r="G2129" t="inlineStr"/>
+      <c r="H2129" t="inlineStr"/>
+    </row>
+    <row r="2130">
+      <c r="A2130" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B2130" t="inlineStr">
+        <is>
+          <t>HOOD</t>
+        </is>
+      </c>
+      <c r="C2130" t="inlineStr">
+        <is>
+          <t>Robinhood Markets Inc.</t>
+        </is>
+      </c>
+      <c r="D2130" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1783879/000195004726009205/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E2130" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Johnson Treseder Oluwadara (Director) plans to sell 1,875 shares (~$229.0K) on/after 09/08/2026</t>
+        </is>
+      </c>
+      <c r="F2130" t="inlineStr"/>
+      <c r="G2130" t="inlineStr"/>
+      <c r="H2130" t="inlineStr"/>
+    </row>
+    <row r="2131">
+      <c r="A2131" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B2131" t="inlineStr">
+        <is>
+          <t>UPST</t>
+        </is>
+      </c>
+      <c r="C2131" t="inlineStr">
+        <is>
+          <t>Upstart Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D2131" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/upstart</t>
+        </is>
+      </c>
+      <c r="E2131" t="inlineStr">
+        <is>
+          <t>5 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F2131" t="inlineStr"/>
+      <c r="G2131" t="inlineStr"/>
+      <c r="H2131" t="inlineStr"/>
+    </row>
+    <row r="2132">
+      <c r="A2132" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B2132" t="inlineStr">
+        <is>
+          <t>UPST</t>
+        </is>
+      </c>
+      <c r="C2132" t="inlineStr">
+        <is>
+          <t>Upstart Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D2132" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1647639/000192109426001001/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E2132" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Datta Sanjay (Officer) plans to sell 116,000 shares (~$3.17M) on/after 09/08/2026</t>
+        </is>
+      </c>
+      <c r="F2132" t="inlineStr"/>
+      <c r="G2132" t="inlineStr"/>
+      <c r="H2132" t="inlineStr"/>
+    </row>
+    <row r="2133">
+      <c r="A2133" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B2133" t="inlineStr">
+        <is>
+          <t>WSM</t>
+        </is>
+      </c>
+      <c r="C2133" t="inlineStr">
+        <is>
+          <t>Williams-Sonoma Inc.</t>
+        </is>
+      </c>
+      <c r="D2133" t="inlineStr">
+        <is>
+          <t>https://ir.williams-sonomainc.com</t>
+        </is>
+      </c>
+      <c r="E2133" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+      <c r="F2133" t="inlineStr"/>
+      <c r="G2133" t="inlineStr"/>
+      <c r="H2133" t="inlineStr"/>
+    </row>
+    <row r="2134">
+      <c r="A2134" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B2134" t="inlineStr">
+        <is>
+          <t>SGI</t>
+        </is>
+      </c>
+      <c r="C2134" t="inlineStr">
+        <is>
+          <t>Somnigroup International Inc. (fmr. Tempur Sealy)</t>
+        </is>
+      </c>
+      <c r="D2134" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1206264/000162828026060918/somnigroup-sx8.htm</t>
+        </is>
+      </c>
+      <c r="E2134" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Employee stock plan registration</t>
+        </is>
+      </c>
+      <c r="F2134" t="inlineStr"/>
+      <c r="G2134" t="inlineStr"/>
+      <c r="H2134" t="inlineStr"/>
+    </row>
+    <row r="2135">
+      <c r="A2135" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B2135" t="inlineStr">
+        <is>
+          <t>SGI</t>
+        </is>
+      </c>
+      <c r="C2135" t="inlineStr">
+        <is>
+          <t>Somnigroup International Inc. (fmr. Tempur Sealy)</t>
+        </is>
+      </c>
+      <c r="D2135" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1206264/000162828026060917/somnigroup-formsx8pos.htm</t>
+        </is>
+      </c>
+      <c r="E2135" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Employee stock plan amendment</t>
+        </is>
+      </c>
+      <c r="F2135" t="inlineStr"/>
+      <c r="G2135" t="inlineStr"/>
+      <c r="H2135" t="inlineStr"/>
+    </row>
+    <row r="2136">
+      <c r="A2136" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B2136" t="inlineStr">
+        <is>
+          <t>ENVA</t>
+        </is>
+      </c>
+      <c r="C2136" t="inlineStr">
+        <is>
+          <t>Enova International Inc.</t>
+        </is>
+      </c>
+      <c r="D2136" t="inlineStr">
+        <is>
+          <t>https://www.enova.com/newsroom</t>
+        </is>
+      </c>
+      <c r="E2136" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F2136" t="inlineStr"/>
+      <c r="G2136" t="inlineStr"/>
+      <c r="H2136" t="inlineStr"/>
+    </row>
+    <row r="2137">
+      <c r="A2137" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B2137" t="inlineStr">
+        <is>
+          <t>ONON</t>
+        </is>
+      </c>
+      <c r="C2137" t="inlineStr">
+        <is>
+          <t>On Holding AG</t>
+        </is>
+      </c>
+      <c r="D2137" t="inlineStr">
+        <is>
+          <t>https://www.on-running.com/en-us/articles/</t>
+        </is>
+      </c>
+      <c r="E2137" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F2137" t="inlineStr"/>
+      <c r="G2137" t="inlineStr"/>
+      <c r="H2137" t="inlineStr"/>
+    </row>
+    <row r="2138">
+      <c r="A2138" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B2138" t="inlineStr">
+        <is>
+          <t>ONON</t>
+        </is>
+      </c>
+      <c r="C2138" t="inlineStr">
+        <is>
+          <t>On Holding AG</t>
+        </is>
+      </c>
+      <c r="D2138" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1858985/000212977226000006/xslF345X06/form4-09092026_010940.xml</t>
+        </is>
+      </c>
+      <c r="E2138" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Maguire Scott Andrew (COO) sold 1,475 shares @ $27.74 ($40.9K) on 2026-09-08</t>
+        </is>
+      </c>
+      <c r="F2138" t="inlineStr"/>
+      <c r="G2138" t="inlineStr"/>
+      <c r="H2138" t="inlineStr"/>
+    </row>
+    <row r="2139">
+      <c r="A2139" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B2139" t="inlineStr">
+        <is>
+          <t>ONON</t>
+        </is>
+      </c>
+      <c r="C2139" t="inlineStr">
+        <is>
+          <t>On Holding AG</t>
+        </is>
+      </c>
+      <c r="D2139" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1858985/000212657626000006/xslF345X06/form4-09092026_010908.xml</t>
+        </is>
+      </c>
+      <c r="E2139" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Sluis Frank (CFO) sold 687 shares @ $27.74 ($19.1K) on 2026-09-08</t>
+        </is>
+      </c>
+      <c r="F2139" t="inlineStr"/>
+      <c r="G2139" t="inlineStr"/>
+      <c r="H2139" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/config/company_urls_jc.xlsx
+++ b/config/company_urls_jc.xlsx
@@ -7203,7 +7203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2139"/>
+  <dimension ref="A1:H2214"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -63725,9 +63725,6 @@
           <t>pricing: change detected</t>
         </is>
       </c>
-      <c r="F2095" t="inlineStr"/>
-      <c r="G2095" t="inlineStr"/>
-      <c r="H2095" t="inlineStr"/>
     </row>
     <row r="2096">
       <c r="A2096" t="inlineStr">
@@ -63755,9 +63752,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F2096" t="inlineStr"/>
-      <c r="G2096" t="inlineStr"/>
-      <c r="H2096" t="inlineStr"/>
     </row>
     <row r="2097">
       <c r="A2097" t="inlineStr">
@@ -63785,9 +63779,6 @@
           <t>newsroom: Base44 Integrates Native Google Ads Campaign Management for App Builders</t>
         </is>
       </c>
-      <c r="F2097" t="inlineStr"/>
-      <c r="G2097" t="inlineStr"/>
-      <c r="H2097" t="inlineStr"/>
     </row>
     <row r="2098">
       <c r="A2098" t="inlineStr">
@@ -63815,9 +63806,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F2098" t="inlineStr"/>
-      <c r="G2098" t="inlineStr"/>
-      <c r="H2098" t="inlineStr"/>
     </row>
     <row r="2099">
       <c r="A2099" t="inlineStr">
@@ -63845,9 +63833,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Koren Ofer (Officer) plans to sell 12,500 shares (~$479.6K) on/after 09/08/2026</t>
         </is>
       </c>
-      <c r="F2099" t="inlineStr"/>
-      <c r="G2099" t="inlineStr"/>
-      <c r="H2099" t="inlineStr"/>
     </row>
     <row r="2100">
       <c r="A2100" t="inlineStr">
@@ -63875,9 +63860,6 @@
           <t>terms: change detected</t>
         </is>
       </c>
-      <c r="F2100" t="inlineStr"/>
-      <c r="G2100" t="inlineStr"/>
-      <c r="H2100" t="inlineStr"/>
     </row>
     <row r="2101">
       <c r="A2101" t="inlineStr">
@@ -63905,9 +63887,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — James Joseph Iannone (Officer) plans to sell 22,220 shares (~$2.32M) on/after 09/08/2026</t>
         </is>
       </c>
-      <c r="F2101" t="inlineStr"/>
-      <c r="G2101" t="inlineStr"/>
-      <c r="H2101" t="inlineStr"/>
     </row>
     <row r="2102">
       <c r="A2102" t="inlineStr">
@@ -63935,9 +63914,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F2102" t="inlineStr"/>
-      <c r="G2102" t="inlineStr"/>
-      <c r="H2102" t="inlineStr"/>
     </row>
     <row r="2103">
       <c r="A2103" t="inlineStr">
@@ -63965,9 +63941,6 @@
           <t>investor_relations: change detected</t>
         </is>
       </c>
-      <c r="F2103" t="inlineStr"/>
-      <c r="G2103" t="inlineStr"/>
-      <c r="H2103" t="inlineStr"/>
     </row>
     <row r="2104">
       <c r="A2104" t="inlineStr">
@@ -63995,9 +63968,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Blotner Jon (Officer) plans to sell 6,968 shares (~$698.3K) on/after 09/08/2026</t>
         </is>
       </c>
-      <c r="F2104" t="inlineStr"/>
-      <c r="G2104" t="inlineStr"/>
-      <c r="H2104" t="inlineStr"/>
     </row>
     <row r="2105">
       <c r="A2105" t="inlineStr">
@@ -64025,9 +63995,6 @@
           <t>[MATERIAL] Quarterly report</t>
         </is>
       </c>
-      <c r="F2105" t="inlineStr"/>
-      <c r="G2105" t="inlineStr"/>
-      <c r="H2105" t="inlineStr"/>
     </row>
     <row r="2106">
       <c r="A2106" t="inlineStr">
@@ -64055,9 +64022,6 @@
           <t>[MATERIAL] Material event disclosure</t>
         </is>
       </c>
-      <c r="F2106" t="inlineStr"/>
-      <c r="G2106" t="inlineStr"/>
-      <c r="H2106" t="inlineStr"/>
     </row>
     <row r="2107">
       <c r="A2107" t="inlineStr">
@@ -64085,9 +64049,6 @@
           <t>management_team: change detected</t>
         </is>
       </c>
-      <c r="F2107" t="inlineStr"/>
-      <c r="G2107" t="inlineStr"/>
-      <c r="H2107" t="inlineStr"/>
     </row>
     <row r="2108">
       <c r="A2108" t="inlineStr">
@@ -64115,9 +64076,6 @@
           <t>investor_relations: change detected</t>
         </is>
       </c>
-      <c r="F2108" t="inlineStr"/>
-      <c r="G2108" t="inlineStr"/>
-      <c r="H2108" t="inlineStr"/>
     </row>
     <row r="2109">
       <c r="A2109" t="inlineStr">
@@ -64145,9 +64103,6 @@
           <t>[ROUTINE] Insider trade — Xu Tony (CHIEF EXECUTIVE OFFICER) other: 31,428 shares on 2026-09-03</t>
         </is>
       </c>
-      <c r="F2109" t="inlineStr"/>
-      <c r="G2109" t="inlineStr"/>
-      <c r="H2109" t="inlineStr"/>
     </row>
     <row r="2110">
       <c r="A2110" t="inlineStr">
@@ -64175,9 +64130,6 @@
           <t>pricing: change detected</t>
         </is>
       </c>
-      <c r="F2110" t="inlineStr"/>
-      <c r="G2110" t="inlineStr"/>
-      <c r="H2110" t="inlineStr"/>
     </row>
     <row r="2111">
       <c r="A2111" t="inlineStr">
@@ -64205,9 +64157,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F2111" t="inlineStr"/>
-      <c r="G2111" t="inlineStr"/>
-      <c r="H2111" t="inlineStr"/>
     </row>
     <row r="2112">
       <c r="A2112" t="inlineStr">
@@ -64235,9 +64184,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — B. Gordon William (Director) plans to sell 20,000 shares (~$3.09M) on/after 09/08/2026</t>
         </is>
       </c>
-      <c r="F2112" t="inlineStr"/>
-      <c r="G2112" t="inlineStr"/>
-      <c r="H2112" t="inlineStr"/>
     </row>
     <row r="2113">
       <c r="A2113" t="inlineStr">
@@ -64265,9 +64211,6 @@
           <t>investor_relations: change detected</t>
         </is>
       </c>
-      <c r="F2113" t="inlineStr"/>
-      <c r="G2113" t="inlineStr"/>
-      <c r="H2113" t="inlineStr"/>
     </row>
     <row r="2114">
       <c r="A2114" t="inlineStr">
@@ -64295,9 +64238,6 @@
           <t>investor_relations: change detected</t>
         </is>
       </c>
-      <c r="F2114" t="inlineStr"/>
-      <c r="G2114" t="inlineStr"/>
-      <c r="H2114" t="inlineStr"/>
     </row>
     <row r="2115">
       <c r="A2115" t="inlineStr">
@@ -64325,9 +64265,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F2115" t="inlineStr"/>
-      <c r="G2115" t="inlineStr"/>
-      <c r="H2115" t="inlineStr"/>
     </row>
     <row r="2116">
       <c r="A2116" t="inlineStr">
@@ -64355,9 +64292,6 @@
           <t>management_team: change detected</t>
         </is>
       </c>
-      <c r="F2116" t="inlineStr"/>
-      <c r="G2116" t="inlineStr"/>
-      <c r="H2116" t="inlineStr"/>
     </row>
     <row r="2117">
       <c r="A2117" t="inlineStr">
@@ -64385,9 +64319,6 @@
           <t>investor_relations: change detected</t>
         </is>
       </c>
-      <c r="F2117" t="inlineStr"/>
-      <c r="G2117" t="inlineStr"/>
-      <c r="H2117" t="inlineStr"/>
     </row>
     <row r="2118">
       <c r="A2118" t="inlineStr">
@@ -64415,9 +64346,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — M Eisen Anthony (Director) plans to sell 6,000 shares (~$493.1K) on/after 09/08/2026</t>
         </is>
       </c>
-      <c r="F2118" t="inlineStr"/>
-      <c r="G2118" t="inlineStr"/>
-      <c r="H2118" t="inlineStr"/>
     </row>
     <row r="2119">
       <c r="A2119" t="inlineStr">
@@ -64445,9 +64373,6 @@
           <t>investor_relations: change detected</t>
         </is>
       </c>
-      <c r="F2119" t="inlineStr"/>
-      <c r="G2119" t="inlineStr"/>
-      <c r="H2119" t="inlineStr"/>
     </row>
     <row r="2120">
       <c r="A2120" t="inlineStr">
@@ -64475,9 +64400,6 @@
           <t>management_team: change detected</t>
         </is>
       </c>
-      <c r="F2120" t="inlineStr"/>
-      <c r="G2120" t="inlineStr"/>
-      <c r="H2120" t="inlineStr"/>
     </row>
     <row r="2121">
       <c r="A2121" t="inlineStr">
@@ -64505,9 +64427,6 @@
           <t>[ROUTINE] Insider trade — Natali Chris (SVP, Chief Accounting Officer) sold 552 shares @ $54.80 ($30.2K) on 2026-09-03</t>
         </is>
       </c>
-      <c r="F2121" t="inlineStr"/>
-      <c r="G2121" t="inlineStr"/>
-      <c r="H2121" t="inlineStr"/>
     </row>
     <row r="2122">
       <c r="A2122" t="inlineStr">
@@ -64535,9 +64454,6 @@
           <t>[ROUTINE] Insider trade — Kereere Suzan (President, Global Markets) sold 3,379 shares @ $55.72 ($188.3K) on 2026-09-03</t>
         </is>
       </c>
-      <c r="F2122" t="inlineStr"/>
-      <c r="G2122" t="inlineStr"/>
-      <c r="H2122" t="inlineStr"/>
     </row>
     <row r="2123">
       <c r="A2123" t="inlineStr">
@@ -64565,9 +64481,6 @@
           <t>[ROUTINE] Insider trade — Keller Frank (Pres., Checkout Sol. &amp; PayPal) sold 4,612 shares @ $55.43 ($255.7K) on 2026-09-03</t>
         </is>
       </c>
-      <c r="F2123" t="inlineStr"/>
-      <c r="G2123" t="inlineStr"/>
-      <c r="H2123" t="inlineStr"/>
     </row>
     <row r="2124">
       <c r="A2124" t="inlineStr">
@@ -64595,9 +64508,6 @@
           <t>34 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F2124" t="inlineStr"/>
-      <c r="G2124" t="inlineStr"/>
-      <c r="H2124" t="inlineStr"/>
     </row>
     <row r="2125">
       <c r="A2125" t="inlineStr">
@@ -64625,9 +64535,6 @@
           <t>investor_relations: change detected</t>
         </is>
       </c>
-      <c r="F2125" t="inlineStr"/>
-      <c r="G2125" t="inlineStr"/>
-      <c r="H2125" t="inlineStr"/>
     </row>
     <row r="2126">
       <c r="A2126" t="inlineStr">
@@ -64655,9 +64562,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F2126" t="inlineStr"/>
-      <c r="G2126" t="inlineStr"/>
-      <c r="H2126" t="inlineStr"/>
     </row>
     <row r="2127">
       <c r="A2127" t="inlineStr">
@@ -64685,9 +64589,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Rozov Yadin (Director) plans to sell 11,184 shares (~$4.26M) on/after 09/08/2026</t>
         </is>
       </c>
-      <c r="F2127" t="inlineStr"/>
-      <c r="G2127" t="inlineStr"/>
-      <c r="H2127" t="inlineStr"/>
     </row>
     <row r="2128">
       <c r="A2128" t="inlineStr">
@@ -64715,9 +64616,6 @@
           <t>3 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F2128" t="inlineStr"/>
-      <c r="G2128" t="inlineStr"/>
-      <c r="H2128" t="inlineStr"/>
     </row>
     <row r="2129">
       <c r="A2129" t="inlineStr">
@@ -64745,9 +64643,6 @@
           <t>1 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F2129" t="inlineStr"/>
-      <c r="G2129" t="inlineStr"/>
-      <c r="H2129" t="inlineStr"/>
     </row>
     <row r="2130">
       <c r="A2130" t="inlineStr">
@@ -64775,9 +64670,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Johnson Treseder Oluwadara (Director) plans to sell 1,875 shares (~$229.0K) on/after 09/08/2026</t>
         </is>
       </c>
-      <c r="F2130" t="inlineStr"/>
-      <c r="G2130" t="inlineStr"/>
-      <c r="H2130" t="inlineStr"/>
     </row>
     <row r="2131">
       <c r="A2131" t="inlineStr">
@@ -64805,9 +64697,6 @@
           <t>5 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F2131" t="inlineStr"/>
-      <c r="G2131" t="inlineStr"/>
-      <c r="H2131" t="inlineStr"/>
     </row>
     <row r="2132">
       <c r="A2132" t="inlineStr">
@@ -64835,9 +64724,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Datta Sanjay (Officer) plans to sell 116,000 shares (~$3.17M) on/after 09/08/2026</t>
         </is>
       </c>
-      <c r="F2132" t="inlineStr"/>
-      <c r="G2132" t="inlineStr"/>
-      <c r="H2132" t="inlineStr"/>
     </row>
     <row r="2133">
       <c r="A2133" t="inlineStr">
@@ -64865,9 +64751,6 @@
           <t>investor_relations: change detected</t>
         </is>
       </c>
-      <c r="F2133" t="inlineStr"/>
-      <c r="G2133" t="inlineStr"/>
-      <c r="H2133" t="inlineStr"/>
     </row>
     <row r="2134">
       <c r="A2134" t="inlineStr">
@@ -64895,9 +64778,6 @@
           <t>[ROUTINE] Employee stock plan registration</t>
         </is>
       </c>
-      <c r="F2134" t="inlineStr"/>
-      <c r="G2134" t="inlineStr"/>
-      <c r="H2134" t="inlineStr"/>
     </row>
     <row r="2135">
       <c r="A2135" t="inlineStr">
@@ -64925,9 +64805,6 @@
           <t>[ROUTINE] Employee stock plan amendment</t>
         </is>
       </c>
-      <c r="F2135" t="inlineStr"/>
-      <c r="G2135" t="inlineStr"/>
-      <c r="H2135" t="inlineStr"/>
     </row>
     <row r="2136">
       <c r="A2136" t="inlineStr">
@@ -64955,9 +64832,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F2136" t="inlineStr"/>
-      <c r="G2136" t="inlineStr"/>
-      <c r="H2136" t="inlineStr"/>
     </row>
     <row r="2137">
       <c r="A2137" t="inlineStr">
@@ -64985,9 +64859,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F2137" t="inlineStr"/>
-      <c r="G2137" t="inlineStr"/>
-      <c r="H2137" t="inlineStr"/>
     </row>
     <row r="2138">
       <c r="A2138" t="inlineStr">
@@ -65015,9 +64886,6 @@
           <t>[ROUTINE] Insider trade — Maguire Scott Andrew (COO) sold 1,475 shares @ $27.74 ($40.9K) on 2026-09-08</t>
         </is>
       </c>
-      <c r="F2138" t="inlineStr"/>
-      <c r="G2138" t="inlineStr"/>
-      <c r="H2138" t="inlineStr"/>
     </row>
     <row r="2139">
       <c r="A2139" t="inlineStr">
@@ -65045,9 +64913,2127 @@
           <t>[ROUTINE] Insider trade — Sluis Frank (CFO) sold 687 shares @ $27.74 ($19.1K) on 2026-09-08</t>
         </is>
       </c>
-      <c r="F2139" t="inlineStr"/>
-      <c r="G2139" t="inlineStr"/>
-      <c r="H2139" t="inlineStr"/>
+    </row>
+    <row r="2140">
+      <c r="A2140" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B2140" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="C2140" t="inlineStr">
+        <is>
+          <t>Tesla, Inc.</t>
+        </is>
+      </c>
+      <c r="D2140" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1318605/000110465926106432/xslF345X06/tm2625055d1_4seq1.xml</t>
+        </is>
+      </c>
+      <c r="E2140" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Taneja Vaibhav (Chief Financial Officer) sold 2,606 shares @ $360.13 ($938.4K) on 2026-09-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="2141">
+      <c r="A2141" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B2141" t="inlineStr">
+        <is>
+          <t>LYFT</t>
+        </is>
+      </c>
+      <c r="C2141" t="inlineStr">
+        <is>
+          <t>Lyft, Inc.</t>
+        </is>
+      </c>
+      <c r="D2141" t="inlineStr">
+        <is>
+          <t>https://www.lyft.com/blog</t>
+        </is>
+      </c>
+      <c r="E2141" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2142">
+      <c r="A2142" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B2142" t="inlineStr">
+        <is>
+          <t>UBER</t>
+        </is>
+      </c>
+      <c r="C2142" t="inlineStr">
+        <is>
+          <t>Uber Technologies, Inc.</t>
+        </is>
+      </c>
+      <c r="D2142" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1543151/000155278126000479/e26381_uber-fwp.htm</t>
+        </is>
+      </c>
+      <c r="E2142" t="inlineStr">
+        <is>
+          <t>[UNKNOWN] Form FWP</t>
+        </is>
+      </c>
+    </row>
+    <row r="2143">
+      <c r="A2143" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B2143" t="inlineStr">
+        <is>
+          <t>EXPE</t>
+        </is>
+      </c>
+      <c r="C2143" t="inlineStr">
+        <is>
+          <t>Expedia Group, Inc.</t>
+        </is>
+      </c>
+      <c r="D2143" t="inlineStr">
+        <is>
+          <t>https://careers.expediagroup.com</t>
+        </is>
+      </c>
+      <c r="E2143" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2144">
+      <c r="A2144" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B2144" t="inlineStr">
+        <is>
+          <t>BKNG</t>
+        </is>
+      </c>
+      <c r="C2144" t="inlineStr">
+        <is>
+          <t>Booking Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D2144" t="inlineStr">
+        <is>
+          <t>https://www.booking.com/content/terms.html</t>
+        </is>
+      </c>
+      <c r="E2144" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2145">
+      <c r="A2145" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B2145" t="inlineStr">
+        <is>
+          <t>BKNG</t>
+        </is>
+      </c>
+      <c r="C2145" t="inlineStr">
+        <is>
+          <t>Booking Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D2145" t="inlineStr">
+        <is>
+          <t>https://www.bookingholdings.com/careers</t>
+        </is>
+      </c>
+      <c r="E2145" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2146">
+      <c r="A2146" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B2146" t="inlineStr">
+        <is>
+          <t>ABNB</t>
+        </is>
+      </c>
+      <c r="C2146" t="inlineStr">
+        <is>
+          <t>Airbnb, Inc.</t>
+        </is>
+      </c>
+      <c r="D2146" t="inlineStr">
+        <is>
+          <t>https://news.airbnb.com</t>
+        </is>
+      </c>
+      <c r="E2146" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2147">
+      <c r="A2147" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B2147" t="inlineStr">
+        <is>
+          <t>ABNB</t>
+        </is>
+      </c>
+      <c r="C2147" t="inlineStr">
+        <is>
+          <t>Airbnb, Inc.</t>
+        </is>
+      </c>
+      <c r="D2147" t="inlineStr">
+        <is>
+          <t>https://careers.airbnb.com</t>
+        </is>
+      </c>
+      <c r="E2147" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2148">
+      <c r="A2148" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B2148" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="C2148" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="D2148" t="inlineStr">
+        <is>
+          <t>https://investor.atmeta.com</t>
+        </is>
+      </c>
+      <c r="E2148" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2149">
+      <c r="A2149" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B2149" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="C2149" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="D2149" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1326801/000192109426001004/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E2149" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Cox Christopher K (Officer) plans to sell 20,000 shares (~$13.01M) on/after 09/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2150">
+      <c r="A2150" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B2150" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="C2150" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="D2150" t="inlineStr">
+        <is>
+          <t>https://blog.google</t>
+        </is>
+      </c>
+      <c r="E2150" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2151">
+      <c r="A2151" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B2151" t="inlineStr">
+        <is>
+          <t>SNAP</t>
+        </is>
+      </c>
+      <c r="C2151" t="inlineStr">
+        <is>
+          <t>Snap Inc.</t>
+        </is>
+      </c>
+      <c r="D2151" t="inlineStr">
+        <is>
+          <t>https://newsroom.snap.com</t>
+        </is>
+      </c>
+      <c r="E2151" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2152">
+      <c r="A2152" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B2152" t="inlineStr">
+        <is>
+          <t>SNAP</t>
+        </is>
+      </c>
+      <c r="C2152" t="inlineStr">
+        <is>
+          <t>Snap Inc.</t>
+        </is>
+      </c>
+      <c r="D2152" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1564408/000192109426001002/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E2152" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Morrow Rebecca (Officer) plans to sell 20,000 shares (~$107.0K) on/after 09/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2153">
+      <c r="A2153" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B2153" t="inlineStr">
+        <is>
+          <t>PINS</t>
+        </is>
+      </c>
+      <c r="C2153" t="inlineStr">
+        <is>
+          <t>Pinterest, Inc.</t>
+        </is>
+      </c>
+      <c r="D2153" t="inlineStr">
+        <is>
+          <t>https://newsroom.pinterest.com</t>
+        </is>
+      </c>
+      <c r="E2153" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2154">
+      <c r="A2154" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B2154" t="inlineStr">
+        <is>
+          <t>PINS</t>
+        </is>
+      </c>
+      <c r="C2154" t="inlineStr">
+        <is>
+          <t>Pinterest, Inc.</t>
+        </is>
+      </c>
+      <c r="D2154" t="inlineStr">
+        <is>
+          <t>https://www.pinterestcareers.com</t>
+        </is>
+      </c>
+      <c r="E2154" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2155">
+      <c r="A2155" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B2155" t="inlineStr">
+        <is>
+          <t>PINS</t>
+        </is>
+      </c>
+      <c r="C2155" t="inlineStr">
+        <is>
+          <t>Pinterest, Inc.</t>
+        </is>
+      </c>
+      <c r="D2155" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1506293/000177391426000025/xslF345X06/wk-form4_1788989476.xml</t>
+        </is>
+      </c>
+      <c r="E2155" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Silbermann Benjamin (Director) sold 93,750 shares @ $20.05 ($1.88M) on 2026-09-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="2156">
+      <c r="A2156" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B2156" t="inlineStr">
+        <is>
+          <t>PINS</t>
+        </is>
+      </c>
+      <c r="C2156" t="inlineStr">
+        <is>
+          <t>Pinterest, Inc.</t>
+        </is>
+      </c>
+      <c r="D2156" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1506293/000192109426001003/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E2156" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Silbermann Benjamin (Director) plans to sell 46,875 shares (~$939.5K) on/after 09/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2157">
+      <c r="A2157" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B2157" t="inlineStr">
+        <is>
+          <t>RDDT</t>
+        </is>
+      </c>
+      <c r="C2157" t="inlineStr">
+        <is>
+          <t>Reddit, Inc.</t>
+        </is>
+      </c>
+      <c r="D2157" t="inlineStr">
+        <is>
+          <t>https://redditinc.com/careers</t>
+        </is>
+      </c>
+      <c r="E2157" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2158">
+      <c r="A2158" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B2158" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="C2158" t="inlineStr">
+        <is>
+          <t>Unity Software Inc.</t>
+        </is>
+      </c>
+      <c r="D2158" t="inlineStr">
+        <is>
+          <t>https://careers.unity.com</t>
+        </is>
+      </c>
+      <c r="E2158" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2159">
+      <c r="A2159" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B2159" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="C2159" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="D2159" t="inlineStr">
+        <is>
+          <t>https://about.netflix.com/newsroom</t>
+        </is>
+      </c>
+      <c r="E2159" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2160">
+      <c r="A2160" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B2160" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="C2160" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="D2160" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1065280/000106528026000269/xslF345X06/wk-form4_1788984509.xml</t>
+        </is>
+      </c>
+      <c r="E2160" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Richard N Barton (Director) sold 720 shares @ $77.60 ($55.9K) on 2026-09-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="2161">
+      <c r="A2161" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B2161" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="C2161" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="D2161" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1065280/000162828026061075/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E2161" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Richard Barton (Director) plans to sell 720 shares (~$54.9K) on/after 09/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2162">
+      <c r="A2162" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B2162" t="inlineStr">
+        <is>
+          <t>SPOT</t>
+        </is>
+      </c>
+      <c r="C2162" t="inlineStr">
+        <is>
+          <t>Spotify Technology S.A.</t>
+        </is>
+      </c>
+      <c r="D2162" t="inlineStr">
+        <is>
+          <t>https://www.spotify.com/premium</t>
+        </is>
+      </c>
+      <c r="E2162" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2163">
+      <c r="A2163" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B2163" t="inlineStr">
+        <is>
+          <t>SPOT</t>
+        </is>
+      </c>
+      <c r="C2163" t="inlineStr">
+        <is>
+          <t>Spotify Technology S.A.</t>
+        </is>
+      </c>
+      <c r="D2163" t="inlineStr">
+        <is>
+          <t>https://newsroom.spotify.com</t>
+        </is>
+      </c>
+      <c r="E2163" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2164">
+      <c r="A2164" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B2164" t="inlineStr">
+        <is>
+          <t>SPOT</t>
+        </is>
+      </c>
+      <c r="C2164" t="inlineStr">
+        <is>
+          <t>Spotify Technology S.A.</t>
+        </is>
+      </c>
+      <c r="D2164" t="inlineStr">
+        <is>
+          <t>https://www.lifeatspotify.com</t>
+        </is>
+      </c>
+      <c r="E2164" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2165">
+      <c r="A2165" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B2165" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="C2165" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="D2165" t="inlineStr">
+        <is>
+          <t>https://www.disneyplus.com/welcome</t>
+        </is>
+      </c>
+      <c r="E2165" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2166">
+      <c r="A2166" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B2166" t="inlineStr">
+        <is>
+          <t>FOXA</t>
+        </is>
+      </c>
+      <c r="C2166" t="inlineStr">
+        <is>
+          <t>Fox Corporation</t>
+        </is>
+      </c>
+      <c r="D2166" t="inlineStr">
+        <is>
+          <t>https://foxcareers.com</t>
+        </is>
+      </c>
+      <c r="E2166" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2167">
+      <c r="A2167" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B2167" t="inlineStr">
+        <is>
+          <t>UMG</t>
+        </is>
+      </c>
+      <c r="C2167" t="inlineStr">
+        <is>
+          <t>Universal Music Group N.V.</t>
+        </is>
+      </c>
+      <c r="D2167" t="inlineStr">
+        <is>
+          <t>https://www.universalmusic.com/news/</t>
+        </is>
+      </c>
+      <c r="E2167" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2168">
+      <c r="A2168" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B2168" t="inlineStr">
+        <is>
+          <t>UMG</t>
+        </is>
+      </c>
+      <c r="C2168" t="inlineStr">
+        <is>
+          <t>Universal Music Group N.V.</t>
+        </is>
+      </c>
+      <c r="D2168" t="inlineStr">
+        <is>
+          <t>https://www.universalmusic.com/careers/</t>
+        </is>
+      </c>
+      <c r="E2168" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2169">
+      <c r="A2169" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B2169" t="inlineStr">
+        <is>
+          <t>WMG</t>
+        </is>
+      </c>
+      <c r="C2169" t="inlineStr">
+        <is>
+          <t>Warner Music Group Corp.</t>
+        </is>
+      </c>
+      <c r="D2169" t="inlineStr">
+        <is>
+          <t>https://www.wmg.com/news/</t>
+        </is>
+      </c>
+      <c r="E2169" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2170">
+      <c r="A2170" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B2170" t="inlineStr">
+        <is>
+          <t>LYV</t>
+        </is>
+      </c>
+      <c r="C2170" t="inlineStr">
+        <is>
+          <t>Live Nation Entertainment, Inc.</t>
+        </is>
+      </c>
+      <c r="D2170" t="inlineStr">
+        <is>
+          <t>https://investors.livenationentertainment.com</t>
+        </is>
+      </c>
+      <c r="E2170" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2171">
+      <c r="A2171" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B2171" t="inlineStr">
+        <is>
+          <t>LYV</t>
+        </is>
+      </c>
+      <c r="C2171" t="inlineStr">
+        <is>
+          <t>Live Nation Entertainment, Inc.</t>
+        </is>
+      </c>
+      <c r="D2171" t="inlineStr">
+        <is>
+          <t>https://www.livenationentertainment.com/careers</t>
+        </is>
+      </c>
+      <c r="E2171" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2172">
+      <c r="A2172" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B2172" t="inlineStr">
+        <is>
+          <t>STUB</t>
+        </is>
+      </c>
+      <c r="C2172" t="inlineStr">
+        <is>
+          <t>StubHub Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="D2172" t="inlineStr">
+        <is>
+          <t>https://www.stubhub.com/careers/</t>
+        </is>
+      </c>
+      <c r="E2172" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2173">
+      <c r="A2173" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B2173" t="inlineStr">
+        <is>
+          <t>TTWO</t>
+        </is>
+      </c>
+      <c r="C2173" t="inlineStr">
+        <is>
+          <t>Take-Two Interactive Software, Inc.</t>
+        </is>
+      </c>
+      <c r="D2173" t="inlineStr">
+        <is>
+          <t>https://ir.take2games.com</t>
+        </is>
+      </c>
+      <c r="E2173" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2174">
+      <c r="A2174" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B2174" t="inlineStr">
+        <is>
+          <t>RBLX</t>
+        </is>
+      </c>
+      <c r="C2174" t="inlineStr">
+        <is>
+          <t>Roblox Corporation</t>
+        </is>
+      </c>
+      <c r="D2174" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1315098/000131509826000184/xslF345X06/wk-form4_1788996536.xml</t>
+        </is>
+      </c>
+      <c r="E2174" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Reinstra Mark (Chief Legal Off. &amp; Corp. Sec.) sold 5,773 shares @ $44.80 ($258.6K) on 2026-09-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="2175">
+      <c r="A2175" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B2175" t="inlineStr">
+        <is>
+          <t>INTU</t>
+        </is>
+      </c>
+      <c r="C2175" t="inlineStr">
+        <is>
+          <t>Intuit Inc.</t>
+        </is>
+      </c>
+      <c r="D2175" t="inlineStr">
+        <is>
+          <t>https://www.intuit.com/company/press-room/</t>
+        </is>
+      </c>
+      <c r="E2175" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2176">
+      <c r="A2176" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B2176" t="inlineStr">
+        <is>
+          <t>INTU</t>
+        </is>
+      </c>
+      <c r="C2176" t="inlineStr">
+        <is>
+          <t>Intuit Inc.</t>
+        </is>
+      </c>
+      <c r="D2176" t="inlineStr">
+        <is>
+          <t>https://investors.intuit.com</t>
+        </is>
+      </c>
+      <c r="E2176" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2177">
+      <c r="A2177" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B2177" t="inlineStr">
+        <is>
+          <t>INTU</t>
+        </is>
+      </c>
+      <c r="C2177" t="inlineStr">
+        <is>
+          <t>Intuit Inc.</t>
+        </is>
+      </c>
+      <c r="D2177" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/896878/000162828026061198/xslF345X06/wk-form4_1788997194.xml</t>
+        </is>
+      </c>
+      <c r="E2177" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Richard L Dalzell (Director) sold 285 shares @ $325.36 ($92.7K) on 2026-09-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="2178">
+      <c r="A2178" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B2178" t="inlineStr">
+        <is>
+          <t>INTU</t>
+        </is>
+      </c>
+      <c r="C2178" t="inlineStr">
+        <is>
+          <t>Intuit Inc.</t>
+        </is>
+      </c>
+      <c r="D2178" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/896878/000119312526386562/d141696ds3asr.htm</t>
+        </is>
+      </c>
+      <c r="E2178" t="inlineStr">
+        <is>
+          <t>[UNKNOWN] Form S-3ASR</t>
+        </is>
+      </c>
+    </row>
+    <row r="2179">
+      <c r="A2179" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B2179" t="inlineStr">
+        <is>
+          <t>INTU</t>
+        </is>
+      </c>
+      <c r="C2179" t="inlineStr">
+        <is>
+          <t>Intuit Inc.</t>
+        </is>
+      </c>
+      <c r="D2179" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/896878/000089687826000037/intu-20260731.htm</t>
+        </is>
+      </c>
+      <c r="E2179" t="inlineStr">
+        <is>
+          <t>[MATERIAL] Annual report</t>
+        </is>
+      </c>
+    </row>
+    <row r="2180">
+      <c r="A2180" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B2180" t="inlineStr">
+        <is>
+          <t>INTU</t>
+        </is>
+      </c>
+      <c r="C2180" t="inlineStr">
+        <is>
+          <t>Intuit Inc.</t>
+        </is>
+      </c>
+      <c r="D2180" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/896878/000089687826000035/s-8posshell2026x09.htm</t>
+        </is>
+      </c>
+      <c r="E2180" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Employee stock plan amendment</t>
+        </is>
+      </c>
+    </row>
+    <row r="2181">
+      <c r="A2181" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B2181" t="inlineStr">
+        <is>
+          <t>ADP</t>
+        </is>
+      </c>
+      <c r="C2181" t="inlineStr">
+        <is>
+          <t>Automatic Data Processing, Inc.</t>
+        </is>
+      </c>
+      <c r="D2181" t="inlineStr">
+        <is>
+          <t>https://mediacenter.adp.com</t>
+        </is>
+      </c>
+      <c r="E2181" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2182">
+      <c r="A2182" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B2182" t="inlineStr">
+        <is>
+          <t>PCTY</t>
+        </is>
+      </c>
+      <c r="C2182" t="inlineStr">
+        <is>
+          <t>Paylocity Holding Corporation</t>
+        </is>
+      </c>
+      <c r="D2182" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1591698/000174275826000010/xslF345X06/wk-form4_1788984147.xml</t>
+        </is>
+      </c>
+      <c r="E2182" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Cappotelli Andrew (Sr Vice President Operations) sold 69 shares @ $152.37 ($10.5K) on 2026-09-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="2183">
+      <c r="A2183" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B2183" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C2183" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D2183" t="inlineStr">
+        <is>
+          <t>https://www.shopify.com/careers</t>
+        </is>
+      </c>
+      <c r="E2183" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F2183" t="inlineStr"/>
+      <c r="G2183" t="inlineStr"/>
+      <c r="H2183" t="inlineStr"/>
+    </row>
+    <row r="2184">
+      <c r="A2184" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B2184" t="inlineStr">
+        <is>
+          <t>EBAY</t>
+        </is>
+      </c>
+      <c r="C2184" t="inlineStr">
+        <is>
+          <t>eBay Inc.</t>
+        </is>
+      </c>
+      <c r="D2184" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/help/policies/member-behaviour-policies/user-agreement?id=4259</t>
+        </is>
+      </c>
+      <c r="E2184" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+      <c r="F2184" t="inlineStr"/>
+      <c r="G2184" t="inlineStr"/>
+      <c r="H2184" t="inlineStr"/>
+    </row>
+    <row r="2185">
+      <c r="A2185" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B2185" t="inlineStr">
+        <is>
+          <t>EBAY</t>
+        </is>
+      </c>
+      <c r="C2185" t="inlineStr">
+        <is>
+          <t>eBay Inc.</t>
+        </is>
+      </c>
+      <c r="D2185" t="inlineStr">
+        <is>
+          <t>https://www.ebayinc.com/stories/news/</t>
+        </is>
+      </c>
+      <c r="E2185" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F2185" t="inlineStr"/>
+      <c r="G2185" t="inlineStr"/>
+      <c r="H2185" t="inlineStr"/>
+    </row>
+    <row r="2186">
+      <c r="A2186" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B2186" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="C2186" t="inlineStr">
+        <is>
+          <t>Wayfair Inc.</t>
+        </is>
+      </c>
+      <c r="D2186" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1616707/000195917326006849/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E2186" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Shah Niraj (Officer) plans to sell 5,000 shares (~$490.4K) on/after 09/10/2026</t>
+        </is>
+      </c>
+      <c r="F2186" t="inlineStr"/>
+      <c r="G2186" t="inlineStr"/>
+      <c r="H2186" t="inlineStr"/>
+    </row>
+    <row r="2187">
+      <c r="A2187" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B2187" t="inlineStr">
+        <is>
+          <t>ETSY</t>
+        </is>
+      </c>
+      <c r="C2187" t="inlineStr">
+        <is>
+          <t>Etsy Inc.</t>
+        </is>
+      </c>
+      <c r="D2187" t="inlineStr">
+        <is>
+          <t>https://investors.etsy.com</t>
+        </is>
+      </c>
+      <c r="E2187" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+      <c r="F2187" t="inlineStr"/>
+      <c r="G2187" t="inlineStr"/>
+      <c r="H2187" t="inlineStr"/>
+    </row>
+    <row r="2188">
+      <c r="A2188" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B2188" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C2188" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D2188" t="inlineStr">
+        <is>
+          <t>https://about.doordash.com/en-us/news</t>
+        </is>
+      </c>
+      <c r="E2188" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F2188" t="inlineStr"/>
+      <c r="G2188" t="inlineStr"/>
+      <c r="H2188" t="inlineStr"/>
+    </row>
+    <row r="2189">
+      <c r="A2189" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B2189" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C2189" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D2189" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1792789/000163564826000016/xslF345X06/form4-09092026_040902.xml</t>
+        </is>
+      </c>
+      <c r="E2189" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Lee Gordon S (CHIEF ACCOUNTING OFFICER) sold 413 shares @ $221.50 ($91.5K) on 2026-09-04</t>
+        </is>
+      </c>
+      <c r="F2189" t="inlineStr"/>
+      <c r="G2189" t="inlineStr"/>
+      <c r="H2189" t="inlineStr"/>
+    </row>
+    <row r="2190">
+      <c r="A2190" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B2190" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C2190" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D2190" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/instacart</t>
+        </is>
+      </c>
+      <c r="E2190" t="inlineStr">
+        <is>
+          <t>1 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F2190" t="inlineStr"/>
+      <c r="G2190" t="inlineStr"/>
+      <c r="H2190" t="inlineStr"/>
+    </row>
+    <row r="2191">
+      <c r="A2191" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B2191" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C2191" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D2191" t="inlineStr">
+        <is>
+          <t>https://www.instacart.com/instacart-plus</t>
+        </is>
+      </c>
+      <c r="E2191" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+      <c r="F2191" t="inlineStr"/>
+      <c r="G2191" t="inlineStr"/>
+      <c r="H2191" t="inlineStr"/>
+    </row>
+    <row r="2192">
+      <c r="A2192" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B2192" t="inlineStr">
+        <is>
+          <t>DUOL</t>
+        </is>
+      </c>
+      <c r="C2192" t="inlineStr">
+        <is>
+          <t>Duolingo Inc.</t>
+        </is>
+      </c>
+      <c r="D2192" t="inlineStr">
+        <is>
+          <t>https://blog.duolingo.com/</t>
+        </is>
+      </c>
+      <c r="E2192" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F2192" t="inlineStr"/>
+      <c r="G2192" t="inlineStr"/>
+      <c r="H2192" t="inlineStr"/>
+    </row>
+    <row r="2193">
+      <c r="A2193" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B2193" t="inlineStr">
+        <is>
+          <t>MTCH</t>
+        </is>
+      </c>
+      <c r="C2193" t="inlineStr">
+        <is>
+          <t>Match Group Inc.</t>
+        </is>
+      </c>
+      <c r="D2193" t="inlineStr">
+        <is>
+          <t>https://mtch.com/news</t>
+        </is>
+      </c>
+      <c r="E2193" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F2193" t="inlineStr"/>
+      <c r="G2193" t="inlineStr"/>
+      <c r="H2193" t="inlineStr"/>
+    </row>
+    <row r="2194">
+      <c r="A2194" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B2194" t="inlineStr">
+        <is>
+          <t>RKT</t>
+        </is>
+      </c>
+      <c r="C2194" t="inlineStr">
+        <is>
+          <t>Rocket Companies Inc.</t>
+        </is>
+      </c>
+      <c r="D2194" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1805284/000180528426000105/xslF345X06/wk-form4_1788995560.xml</t>
+        </is>
+      </c>
+      <c r="E2194" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Banfield William D. (Chief Business Officer) 61,315 shares withheld for taxes (vest event) on 2026-09-07</t>
+        </is>
+      </c>
+      <c r="F2194" t="inlineStr"/>
+      <c r="G2194" t="inlineStr"/>
+      <c r="H2194" t="inlineStr"/>
+    </row>
+    <row r="2195">
+      <c r="A2195" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B2195" t="inlineStr">
+        <is>
+          <t>RKT</t>
+        </is>
+      </c>
+      <c r="C2195" t="inlineStr">
+        <is>
+          <t>Rocket Companies Inc.</t>
+        </is>
+      </c>
+      <c r="D2195" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1805284/000180528426000104/xslF345X06/wk-form4_1788995556.xml</t>
+        </is>
+      </c>
+      <c r="E2195" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Edwards Noah A. (Chief Accounting Officer) 12,009 shares withheld for taxes (vest event) on 2026-09-07</t>
+        </is>
+      </c>
+      <c r="F2195" t="inlineStr"/>
+      <c r="G2195" t="inlineStr"/>
+      <c r="H2195" t="inlineStr"/>
+    </row>
+    <row r="2196">
+      <c r="A2196" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B2196" t="inlineStr">
+        <is>
+          <t>RKT</t>
+        </is>
+      </c>
+      <c r="C2196" t="inlineStr">
+        <is>
+          <t>Rocket Companies Inc.</t>
+        </is>
+      </c>
+      <c r="D2196" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1805284/000180528426000103/xslF345X06/wk-form4_1788995550.xml</t>
+        </is>
+      </c>
+      <c r="E2196" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Brown Brian Nicholas (President  &amp; Chief Fin Officer) 58,717 shares withheld for taxes (vest event) on 2026-09-07</t>
+        </is>
+      </c>
+      <c r="F2196" t="inlineStr"/>
+      <c r="G2196" t="inlineStr"/>
+      <c r="H2196" t="inlineStr"/>
+    </row>
+    <row r="2197">
+      <c r="A2197" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B2197" t="inlineStr">
+        <is>
+          <t>RKT</t>
+        </is>
+      </c>
+      <c r="C2197" t="inlineStr">
+        <is>
+          <t>Rocket Companies Inc.</t>
+        </is>
+      </c>
+      <c r="D2197" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1805284/000180528426000102/xslF345X06/wk-form4_1788995544.xml</t>
+        </is>
+      </c>
+      <c r="E2197" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Malhotra Shawn (Chief Technology Officer) 37,930 shares withheld for taxes (vest event) on 2026-09-07</t>
+        </is>
+      </c>
+      <c r="F2197" t="inlineStr"/>
+      <c r="G2197" t="inlineStr"/>
+      <c r="H2197" t="inlineStr"/>
+    </row>
+    <row r="2198">
+      <c r="A2198" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B2198" t="inlineStr">
+        <is>
+          <t>RKT</t>
+        </is>
+      </c>
+      <c r="C2198" t="inlineStr">
+        <is>
+          <t>Rocket Companies Inc.</t>
+        </is>
+      </c>
+      <c r="D2198" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1805284/000180528426000101/xslF345X06/wk-form4_1788995539.xml</t>
+        </is>
+      </c>
+      <c r="E2198" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Bray Jesse K (Pres &amp; CEO, Rocket Mortgage) 29,279 shares withheld for taxes (vest event) on 2026-09-07</t>
+        </is>
+      </c>
+      <c r="F2198" t="inlineStr"/>
+      <c r="G2198" t="inlineStr"/>
+      <c r="H2198" t="inlineStr"/>
+    </row>
+    <row r="2199">
+      <c r="A2199" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B2199" t="inlineStr">
+        <is>
+          <t>RKT</t>
+        </is>
+      </c>
+      <c r="C2199" t="inlineStr">
+        <is>
+          <t>Rocket Companies Inc.</t>
+        </is>
+      </c>
+      <c r="D2199" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1805284/000180528426000100/xslF345X06/wk-form4_1788995533.xml</t>
+        </is>
+      </c>
+      <c r="E2199" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Lovier Heather M. (Chief Operating Officer) 61,669 shares withheld for taxes (vest event) on 2026-09-07</t>
+        </is>
+      </c>
+      <c r="F2199" t="inlineStr"/>
+      <c r="G2199" t="inlineStr"/>
+      <c r="H2199" t="inlineStr"/>
+    </row>
+    <row r="2200">
+      <c r="A2200" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B2200" t="inlineStr">
+        <is>
+          <t>RKT</t>
+        </is>
+      </c>
+      <c r="C2200" t="inlineStr">
+        <is>
+          <t>Rocket Companies Inc.</t>
+        </is>
+      </c>
+      <c r="D2200" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1805284/000180528426000099/xslF345X06/wk-form4_1788995526.xml</t>
+        </is>
+      </c>
+      <c r="E2200" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Krishna Varun (Chief Executive Officer) 185,258 shares withheld for taxes (vest event) on 2026-09-07</t>
+        </is>
+      </c>
+      <c r="F2200" t="inlineStr"/>
+      <c r="G2200" t="inlineStr"/>
+      <c r="H2200" t="inlineStr"/>
+    </row>
+    <row r="2201">
+      <c r="A2201" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B2201" t="inlineStr">
+        <is>
+          <t>RKT</t>
+        </is>
+      </c>
+      <c r="C2201" t="inlineStr">
+        <is>
+          <t>Rocket Companies Inc.</t>
+        </is>
+      </c>
+      <c r="D2201" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1805284/000180528426000098/xslF345X06/wk-form4_1788995521.xml</t>
+        </is>
+      </c>
+      <c r="E2201" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Rizik Matthew (Director) option exercise: 14,796 shares on 2026-09-07</t>
+        </is>
+      </c>
+      <c r="F2201" t="inlineStr"/>
+      <c r="G2201" t="inlineStr"/>
+      <c r="H2201" t="inlineStr"/>
+    </row>
+    <row r="2202">
+      <c r="A2202" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B2202" t="inlineStr">
+        <is>
+          <t>RKT</t>
+        </is>
+      </c>
+      <c r="C2202" t="inlineStr">
+        <is>
+          <t>Rocket Companies Inc.</t>
+        </is>
+      </c>
+      <c r="D2202" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1805284/000180528426000097/xslF345X06/wk-form4_1788995515.xml</t>
+        </is>
+      </c>
+      <c r="E2202" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Mildenhall Jonathan (Chief Marketing Officer) 80,287 shares withheld for taxes (vest event) on 2026-09-07</t>
+        </is>
+      </c>
+      <c r="F2202" t="inlineStr"/>
+      <c r="G2202" t="inlineStr"/>
+      <c r="H2202" t="inlineStr"/>
+    </row>
+    <row r="2203">
+      <c r="A2203" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B2203" t="inlineStr">
+        <is>
+          <t>COMP</t>
+        </is>
+      </c>
+      <c r="C2203" t="inlineStr">
+        <is>
+          <t>Compass Inc.</t>
+        </is>
+      </c>
+      <c r="D2203" t="inlineStr">
+        <is>
+          <t>https://www.compass.com/careers/</t>
+        </is>
+      </c>
+      <c r="E2203" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F2203" t="inlineStr"/>
+      <c r="G2203" t="inlineStr"/>
+      <c r="H2203" t="inlineStr"/>
+    </row>
+    <row r="2204">
+      <c r="A2204" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B2204" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C2204" t="inlineStr">
+        <is>
+          <t>Block Inc. (fmr. Square)</t>
+        </is>
+      </c>
+      <c r="D2204" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1512673/000195004726009235/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E2204" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — M Eisen Anthony (Director) plans to sell 6,000 shares (~$475.6K) on/after 09/09/2026</t>
+        </is>
+      </c>
+      <c r="F2204" t="inlineStr"/>
+      <c r="G2204" t="inlineStr"/>
+      <c r="H2204" t="inlineStr"/>
+    </row>
+    <row r="2205">
+      <c r="A2205" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B2205" t="inlineStr">
+        <is>
+          <t>BILL</t>
+        </is>
+      </c>
+      <c r="C2205" t="inlineStr">
+        <is>
+          <t>BILL Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D2205" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1786352/000195004726009244/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E2205" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Rettig John (Officer) plans to sell 19,893 shares (~$946.9K) on/after 09/09/2026</t>
+        </is>
+      </c>
+      <c r="F2205" t="inlineStr"/>
+      <c r="G2205" t="inlineStr"/>
+      <c r="H2205" t="inlineStr"/>
+    </row>
+    <row r="2206">
+      <c r="A2206" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B2206" t="inlineStr">
+        <is>
+          <t>TOST</t>
+        </is>
+      </c>
+      <c r="C2206" t="inlineStr">
+        <is>
+          <t>Toast Inc.</t>
+        </is>
+      </c>
+      <c r="D2206" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/toast</t>
+        </is>
+      </c>
+      <c r="E2206" t="inlineStr">
+        <is>
+          <t>13 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F2206" t="inlineStr"/>
+      <c r="G2206" t="inlineStr"/>
+      <c r="H2206" t="inlineStr"/>
+    </row>
+    <row r="2207">
+      <c r="A2207" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B2207" t="inlineStr">
+        <is>
+          <t>DAVE</t>
+        </is>
+      </c>
+      <c r="C2207" t="inlineStr">
+        <is>
+          <t>Dave Inc.</t>
+        </is>
+      </c>
+      <c r="D2207" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1841408/000119312526386706/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E2207" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Carroll Brendan (Director) sold 300,000 shares @ $1.98 ($594.0K) on 2026-09-04</t>
+        </is>
+      </c>
+      <c r="F2207" t="inlineStr"/>
+      <c r="G2207" t="inlineStr"/>
+      <c r="H2207" t="inlineStr"/>
+    </row>
+    <row r="2208">
+      <c r="A2208" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B2208" t="inlineStr">
+        <is>
+          <t>AFRM</t>
+        </is>
+      </c>
+      <c r="C2208" t="inlineStr">
+        <is>
+          <t>Affirm Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D2208" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1820953/000162828026061117/xslF345X06/wk-form4_1788984005.xml</t>
+        </is>
+      </c>
+      <c r="E2208" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Jiyane Siphelele (Chief Accounting Officer) sold 25,000 shares @ $72.41 ($1.81M) on 2026-09-04</t>
+        </is>
+      </c>
+      <c r="F2208" t="inlineStr"/>
+      <c r="G2208" t="inlineStr"/>
+      <c r="H2208" t="inlineStr"/>
+    </row>
+    <row r="2209">
+      <c r="A2209" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B2209" t="inlineStr">
+        <is>
+          <t>HOOD</t>
+        </is>
+      </c>
+      <c r="C2209" t="inlineStr">
+        <is>
+          <t>Robinhood Markets Inc.</t>
+        </is>
+      </c>
+      <c r="D2209" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/robinhood</t>
+        </is>
+      </c>
+      <c r="E2209" t="inlineStr">
+        <is>
+          <t>9 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F2209" t="inlineStr"/>
+      <c r="G2209" t="inlineStr"/>
+      <c r="H2209" t="inlineStr"/>
+    </row>
+    <row r="2210">
+      <c r="A2210" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B2210" t="inlineStr">
+        <is>
+          <t>UPST</t>
+        </is>
+      </c>
+      <c r="C2210" t="inlineStr">
+        <is>
+          <t>Upstart Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D2210" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/upstart</t>
+        </is>
+      </c>
+      <c r="E2210" t="inlineStr">
+        <is>
+          <t>3 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F2210" t="inlineStr"/>
+      <c r="G2210" t="inlineStr"/>
+      <c r="H2210" t="inlineStr"/>
+    </row>
+    <row r="2211">
+      <c r="A2211" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B2211" t="inlineStr">
+        <is>
+          <t>UPST</t>
+        </is>
+      </c>
+      <c r="C2211" t="inlineStr">
+        <is>
+          <t>Upstart Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D2211" t="inlineStr">
+        <is>
+          <t>https://www.upstart.com/</t>
+        </is>
+      </c>
+      <c r="E2211" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+      <c r="F2211" t="inlineStr"/>
+      <c r="G2211" t="inlineStr"/>
+      <c r="H2211" t="inlineStr"/>
+    </row>
+    <row r="2212">
+      <c r="A2212" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B2212" t="inlineStr">
+        <is>
+          <t>UPST</t>
+        </is>
+      </c>
+      <c r="C2212" t="inlineStr">
+        <is>
+          <t>Upstart Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D2212" t="inlineStr">
+        <is>
+          <t>https://www.upstart.com/blog</t>
+        </is>
+      </c>
+      <c r="E2212" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F2212" t="inlineStr"/>
+      <c r="G2212" t="inlineStr"/>
+      <c r="H2212" t="inlineStr"/>
+    </row>
+    <row r="2213">
+      <c r="A2213" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B2213" t="inlineStr">
+        <is>
+          <t>ENVA</t>
+        </is>
+      </c>
+      <c r="C2213" t="inlineStr">
+        <is>
+          <t>Enova International Inc.</t>
+        </is>
+      </c>
+      <c r="D2213" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1529864/000119312526386483/enva-20260909.htm</t>
+        </is>
+      </c>
+      <c r="E2213" t="inlineStr">
+        <is>
+          <t>[MATERIAL] Material event disclosure</t>
+        </is>
+      </c>
+      <c r="F2213" t="inlineStr"/>
+      <c r="G2213" t="inlineStr"/>
+      <c r="H2213" t="inlineStr"/>
+    </row>
+    <row r="2214">
+      <c r="A2214" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B2214" t="inlineStr">
+        <is>
+          <t>ONON</t>
+        </is>
+      </c>
+      <c r="C2214" t="inlineStr">
+        <is>
+          <t>On Holding AG</t>
+        </is>
+      </c>
+      <c r="D2214" t="inlineStr">
+        <is>
+          <t>https://www.on-running.com/en-us/articles/</t>
+        </is>
+      </c>
+      <c r="E2214" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F2214" t="inlineStr"/>
+      <c r="G2214" t="inlineStr"/>
+      <c r="H2214" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/config/company_urls_jc.xlsx
+++ b/config/company_urls_jc.xlsx
@@ -7203,7 +7203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2214"/>
+  <dimension ref="A1:H2288"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -66101,9 +66101,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F2183" t="inlineStr"/>
-      <c r="G2183" t="inlineStr"/>
-      <c r="H2183" t="inlineStr"/>
     </row>
     <row r="2184">
       <c r="A2184" t="inlineStr">
@@ -66131,9 +66128,6 @@
           <t>terms: change detected</t>
         </is>
       </c>
-      <c r="F2184" t="inlineStr"/>
-      <c r="G2184" t="inlineStr"/>
-      <c r="H2184" t="inlineStr"/>
     </row>
     <row r="2185">
       <c r="A2185" t="inlineStr">
@@ -66161,9 +66155,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F2185" t="inlineStr"/>
-      <c r="G2185" t="inlineStr"/>
-      <c r="H2185" t="inlineStr"/>
     </row>
     <row r="2186">
       <c r="A2186" t="inlineStr">
@@ -66191,9 +66182,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Shah Niraj (Officer) plans to sell 5,000 shares (~$490.4K) on/after 09/10/2026</t>
         </is>
       </c>
-      <c r="F2186" t="inlineStr"/>
-      <c r="G2186" t="inlineStr"/>
-      <c r="H2186" t="inlineStr"/>
     </row>
     <row r="2187">
       <c r="A2187" t="inlineStr">
@@ -66221,9 +66209,6 @@
           <t>investor_relations: change detected</t>
         </is>
       </c>
-      <c r="F2187" t="inlineStr"/>
-      <c r="G2187" t="inlineStr"/>
-      <c r="H2187" t="inlineStr"/>
     </row>
     <row r="2188">
       <c r="A2188" t="inlineStr">
@@ -66251,9 +66236,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F2188" t="inlineStr"/>
-      <c r="G2188" t="inlineStr"/>
-      <c r="H2188" t="inlineStr"/>
     </row>
     <row r="2189">
       <c r="A2189" t="inlineStr">
@@ -66281,9 +66263,6 @@
           <t>[ROUTINE] Insider trade — Lee Gordon S (CHIEF ACCOUNTING OFFICER) sold 413 shares @ $221.50 ($91.5K) on 2026-09-04</t>
         </is>
       </c>
-      <c r="F2189" t="inlineStr"/>
-      <c r="G2189" t="inlineStr"/>
-      <c r="H2189" t="inlineStr"/>
     </row>
     <row r="2190">
       <c r="A2190" t="inlineStr">
@@ -66311,9 +66290,6 @@
           <t>1 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F2190" t="inlineStr"/>
-      <c r="G2190" t="inlineStr"/>
-      <c r="H2190" t="inlineStr"/>
     </row>
     <row r="2191">
       <c r="A2191" t="inlineStr">
@@ -66341,9 +66317,6 @@
           <t>pricing: change detected</t>
         </is>
       </c>
-      <c r="F2191" t="inlineStr"/>
-      <c r="G2191" t="inlineStr"/>
-      <c r="H2191" t="inlineStr"/>
     </row>
     <row r="2192">
       <c r="A2192" t="inlineStr">
@@ -66371,9 +66344,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F2192" t="inlineStr"/>
-      <c r="G2192" t="inlineStr"/>
-      <c r="H2192" t="inlineStr"/>
     </row>
     <row r="2193">
       <c r="A2193" t="inlineStr">
@@ -66401,9 +66371,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F2193" t="inlineStr"/>
-      <c r="G2193" t="inlineStr"/>
-      <c r="H2193" t="inlineStr"/>
     </row>
     <row r="2194">
       <c r="A2194" t="inlineStr">
@@ -66431,9 +66398,6 @@
           <t>[ROUTINE] Insider trade — Banfield William D. (Chief Business Officer) 61,315 shares withheld for taxes (vest event) on 2026-09-07</t>
         </is>
       </c>
-      <c r="F2194" t="inlineStr"/>
-      <c r="G2194" t="inlineStr"/>
-      <c r="H2194" t="inlineStr"/>
     </row>
     <row r="2195">
       <c r="A2195" t="inlineStr">
@@ -66461,9 +66425,6 @@
           <t>[ROUTINE] Insider trade — Edwards Noah A. (Chief Accounting Officer) 12,009 shares withheld for taxes (vest event) on 2026-09-07</t>
         </is>
       </c>
-      <c r="F2195" t="inlineStr"/>
-      <c r="G2195" t="inlineStr"/>
-      <c r="H2195" t="inlineStr"/>
     </row>
     <row r="2196">
       <c r="A2196" t="inlineStr">
@@ -66491,9 +66452,6 @@
           <t>[ROUTINE] Insider trade — Brown Brian Nicholas (President  &amp; Chief Fin Officer) 58,717 shares withheld for taxes (vest event) on 2026-09-07</t>
         </is>
       </c>
-      <c r="F2196" t="inlineStr"/>
-      <c r="G2196" t="inlineStr"/>
-      <c r="H2196" t="inlineStr"/>
     </row>
     <row r="2197">
       <c r="A2197" t="inlineStr">
@@ -66521,9 +66479,6 @@
           <t>[ROUTINE] Insider trade — Malhotra Shawn (Chief Technology Officer) 37,930 shares withheld for taxes (vest event) on 2026-09-07</t>
         </is>
       </c>
-      <c r="F2197" t="inlineStr"/>
-      <c r="G2197" t="inlineStr"/>
-      <c r="H2197" t="inlineStr"/>
     </row>
     <row r="2198">
       <c r="A2198" t="inlineStr">
@@ -66551,9 +66506,6 @@
           <t>[ROUTINE] Insider trade — Bray Jesse K (Pres &amp; CEO, Rocket Mortgage) 29,279 shares withheld for taxes (vest event) on 2026-09-07</t>
         </is>
       </c>
-      <c r="F2198" t="inlineStr"/>
-      <c r="G2198" t="inlineStr"/>
-      <c r="H2198" t="inlineStr"/>
     </row>
     <row r="2199">
       <c r="A2199" t="inlineStr">
@@ -66581,9 +66533,6 @@
           <t>[ROUTINE] Insider trade — Lovier Heather M. (Chief Operating Officer) 61,669 shares withheld for taxes (vest event) on 2026-09-07</t>
         </is>
       </c>
-      <c r="F2199" t="inlineStr"/>
-      <c r="G2199" t="inlineStr"/>
-      <c r="H2199" t="inlineStr"/>
     </row>
     <row r="2200">
       <c r="A2200" t="inlineStr">
@@ -66611,9 +66560,6 @@
           <t>[ROUTINE] Insider trade — Krishna Varun (Chief Executive Officer) 185,258 shares withheld for taxes (vest event) on 2026-09-07</t>
         </is>
       </c>
-      <c r="F2200" t="inlineStr"/>
-      <c r="G2200" t="inlineStr"/>
-      <c r="H2200" t="inlineStr"/>
     </row>
     <row r="2201">
       <c r="A2201" t="inlineStr">
@@ -66641,9 +66587,6 @@
           <t>[ROUTINE] Insider trade — Rizik Matthew (Director) option exercise: 14,796 shares on 2026-09-07</t>
         </is>
       </c>
-      <c r="F2201" t="inlineStr"/>
-      <c r="G2201" t="inlineStr"/>
-      <c r="H2201" t="inlineStr"/>
     </row>
     <row r="2202">
       <c r="A2202" t="inlineStr">
@@ -66671,9 +66614,6 @@
           <t>[ROUTINE] Insider trade — Mildenhall Jonathan (Chief Marketing Officer) 80,287 shares withheld for taxes (vest event) on 2026-09-07</t>
         </is>
       </c>
-      <c r="F2202" t="inlineStr"/>
-      <c r="G2202" t="inlineStr"/>
-      <c r="H2202" t="inlineStr"/>
     </row>
     <row r="2203">
       <c r="A2203" t="inlineStr">
@@ -66701,9 +66641,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F2203" t="inlineStr"/>
-      <c r="G2203" t="inlineStr"/>
-      <c r="H2203" t="inlineStr"/>
     </row>
     <row r="2204">
       <c r="A2204" t="inlineStr">
@@ -66731,9 +66668,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — M Eisen Anthony (Director) plans to sell 6,000 shares (~$475.6K) on/after 09/09/2026</t>
         </is>
       </c>
-      <c r="F2204" t="inlineStr"/>
-      <c r="G2204" t="inlineStr"/>
-      <c r="H2204" t="inlineStr"/>
     </row>
     <row r="2205">
       <c r="A2205" t="inlineStr">
@@ -66761,9 +66695,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Rettig John (Officer) plans to sell 19,893 shares (~$946.9K) on/after 09/09/2026</t>
         </is>
       </c>
-      <c r="F2205" t="inlineStr"/>
-      <c r="G2205" t="inlineStr"/>
-      <c r="H2205" t="inlineStr"/>
     </row>
     <row r="2206">
       <c r="A2206" t="inlineStr">
@@ -66791,9 +66722,6 @@
           <t>13 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F2206" t="inlineStr"/>
-      <c r="G2206" t="inlineStr"/>
-      <c r="H2206" t="inlineStr"/>
     </row>
     <row r="2207">
       <c r="A2207" t="inlineStr">
@@ -66821,9 +66749,6 @@
           <t>[ROUTINE] Insider trade — Carroll Brendan (Director) sold 300,000 shares @ $1.98 ($594.0K) on 2026-09-04</t>
         </is>
       </c>
-      <c r="F2207" t="inlineStr"/>
-      <c r="G2207" t="inlineStr"/>
-      <c r="H2207" t="inlineStr"/>
     </row>
     <row r="2208">
       <c r="A2208" t="inlineStr">
@@ -66851,9 +66776,6 @@
           <t>[ROUTINE] Insider trade — Jiyane Siphelele (Chief Accounting Officer) sold 25,000 shares @ $72.41 ($1.81M) on 2026-09-04</t>
         </is>
       </c>
-      <c r="F2208" t="inlineStr"/>
-      <c r="G2208" t="inlineStr"/>
-      <c r="H2208" t="inlineStr"/>
     </row>
     <row r="2209">
       <c r="A2209" t="inlineStr">
@@ -66881,9 +66803,6 @@
           <t>9 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F2209" t="inlineStr"/>
-      <c r="G2209" t="inlineStr"/>
-      <c r="H2209" t="inlineStr"/>
     </row>
     <row r="2210">
       <c r="A2210" t="inlineStr">
@@ -66911,9 +66830,6 @@
           <t>3 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F2210" t="inlineStr"/>
-      <c r="G2210" t="inlineStr"/>
-      <c r="H2210" t="inlineStr"/>
     </row>
     <row r="2211">
       <c r="A2211" t="inlineStr">
@@ -66941,9 +66857,6 @@
           <t>pricing: change detected</t>
         </is>
       </c>
-      <c r="F2211" t="inlineStr"/>
-      <c r="G2211" t="inlineStr"/>
-      <c r="H2211" t="inlineStr"/>
     </row>
     <row r="2212">
       <c r="A2212" t="inlineStr">
@@ -66971,9 +66884,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F2212" t="inlineStr"/>
-      <c r="G2212" t="inlineStr"/>
-      <c r="H2212" t="inlineStr"/>
     </row>
     <row r="2213">
       <c r="A2213" t="inlineStr">
@@ -67001,9 +66911,6 @@
           <t>[MATERIAL] Material event disclosure</t>
         </is>
       </c>
-      <c r="F2213" t="inlineStr"/>
-      <c r="G2213" t="inlineStr"/>
-      <c r="H2213" t="inlineStr"/>
     </row>
     <row r="2214">
       <c r="A2214" t="inlineStr">
@@ -67031,9 +66938,2088 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F2214" t="inlineStr"/>
-      <c r="G2214" t="inlineStr"/>
-      <c r="H2214" t="inlineStr"/>
+    </row>
+    <row r="2215">
+      <c r="A2215" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B2215" t="inlineStr">
+        <is>
+          <t>LOGI</t>
+        </is>
+      </c>
+      <c r="C2215" t="inlineStr">
+        <is>
+          <t>Logitech International S.A.</t>
+        </is>
+      </c>
+      <c r="D2215" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1032975/000194378926000001/xslF345X06/form4-09102026_080947.xml</t>
+        </is>
+      </c>
+      <c r="E2215" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Zahnd Sascha (Director) granted 2,518 Registered Shares on 2026-09-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="2216">
+      <c r="A2216" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B2216" t="inlineStr">
+        <is>
+          <t>LOGI</t>
+        </is>
+      </c>
+      <c r="C2216" t="inlineStr">
+        <is>
+          <t>Logitech International S.A.</t>
+        </is>
+      </c>
+      <c r="D2216" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1032975/000123404826000001/xslF345X06/form4-09102026_080913.xml</t>
+        </is>
+      </c>
+      <c r="E2216" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Thomas Deborah (Director) granted 2,518 Registered Shares on 2026-09-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="2217">
+      <c r="A2217" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B2217" t="inlineStr">
+        <is>
+          <t>LOGI</t>
+        </is>
+      </c>
+      <c r="C2217" t="inlineStr">
+        <is>
+          <t>Logitech International S.A.</t>
+        </is>
+      </c>
+      <c r="D2217" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1032975/000194437526000001/xslF345X06/form4-09102026_080942.xml</t>
+        </is>
+      </c>
+      <c r="E2217" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Ng Kwok Wang (Director) granted 2,518 Registered Shares on 2026-09-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="2218">
+      <c r="A2218" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B2218" t="inlineStr">
+        <is>
+          <t>LOGI</t>
+        </is>
+      </c>
+      <c r="C2218" t="inlineStr">
+        <is>
+          <t>Logitech International S.A.</t>
+        </is>
+      </c>
+      <c r="D2218" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1032975/000171604826000001/xslF345X06/form4-09102026_080922.xml</t>
+        </is>
+      </c>
+      <c r="E2218" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Montgomery Neela (Director) granted 2,518 Registered Shares on 2026-09-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="2219">
+      <c r="A2219" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B2219" t="inlineStr">
+        <is>
+          <t>LOGI</t>
+        </is>
+      </c>
+      <c r="C2219" t="inlineStr">
+        <is>
+          <t>Logitech International S.A.</t>
+        </is>
+      </c>
+      <c r="D2219" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1032975/000201623626000003/xslF345X06/form4-09102026_080910.xml</t>
+        </is>
+      </c>
+      <c r="E2219" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Mahoney Owen (Director) granted 3,331 Registered Shares on 2026-09-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="2220">
+      <c r="A2220" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B2220" t="inlineStr">
+        <is>
+          <t>LOGI</t>
+        </is>
+      </c>
+      <c r="C2220" t="inlineStr">
+        <is>
+          <t>Logitech International S.A.</t>
+        </is>
+      </c>
+      <c r="D2220" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1032975/000175025826000001/xslF345X06/form4-09102026_080932.xml</t>
+        </is>
+      </c>
+      <c r="E2220" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Marjorie Lao (Director) granted 2,518 Registered Shares on 2026-09-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="2221">
+      <c r="A2221" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B2221" t="inlineStr">
+        <is>
+          <t>LOGI</t>
+        </is>
+      </c>
+      <c r="C2221" t="inlineStr">
+        <is>
+          <t>Logitech International S.A.</t>
+        </is>
+      </c>
+      <c r="D2221" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1032975/000167962426000001/xslF345X06/form4-09102026_080922.xml</t>
+        </is>
+      </c>
+      <c r="E2221" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Jones Christopher Richardson (Director) granted 2,518 Registered Shares on 2026-09-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="2222">
+      <c r="A2222" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B2222" t="inlineStr">
+        <is>
+          <t>LOGI</t>
+        </is>
+      </c>
+      <c r="C2222" t="inlineStr">
+        <is>
+          <t>Logitech International S.A.</t>
+        </is>
+      </c>
+      <c r="D2222" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1032975/000111623326000001/xslF345X06/form4-09102026_080922.xml</t>
+        </is>
+      </c>
+      <c r="E2222" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Guy Gecht (Director) granted 2,518 Registered Shares on 2026-09-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="2223">
+      <c r="A2223" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B2223" t="inlineStr">
+        <is>
+          <t>LOGI</t>
+        </is>
+      </c>
+      <c r="C2223" t="inlineStr">
+        <is>
+          <t>Logitech International S.A.</t>
+        </is>
+      </c>
+      <c r="D2223" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1032975/000165255026000001/xslF345X06/form4-09102026_080923.xml</t>
+        </is>
+      </c>
+      <c r="E2223" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Bugnion Edouard (Director) granted 2,518 Registered Shares on 2026-09-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="2224">
+      <c r="A2224" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B2224" t="inlineStr">
+        <is>
+          <t>LOGI</t>
+        </is>
+      </c>
+      <c r="C2224" t="inlineStr">
+        <is>
+          <t>Logitech International S.A.</t>
+        </is>
+      </c>
+      <c r="D2224" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1032975/000137911126000001/xslF345X06/form4-09102026_080930.xml</t>
+        </is>
+      </c>
+      <c r="E2224" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Allan Donald (Director) granted 3,540 Registered Shares on 2026-09-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="2225">
+      <c r="A2225" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B2225" t="inlineStr">
+        <is>
+          <t>LOGI</t>
+        </is>
+      </c>
+      <c r="C2225" t="inlineStr">
+        <is>
+          <t>Logitech International S.A.</t>
+        </is>
+      </c>
+      <c r="D2225" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1032975/000103297526000053/logi-20260908.htm</t>
+        </is>
+      </c>
+      <c r="E2225" t="inlineStr">
+        <is>
+          <t>[MATERIAL] Material event disclosure</t>
+        </is>
+      </c>
+    </row>
+    <row r="2226">
+      <c r="A2226" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B2226" t="inlineStr">
+        <is>
+          <t>LYFT</t>
+        </is>
+      </c>
+      <c r="C2226" t="inlineStr">
+        <is>
+          <t>Lyft, Inc.</t>
+        </is>
+      </c>
+      <c r="D2226" t="inlineStr">
+        <is>
+          <t>https://www.lyft.com/blog</t>
+        </is>
+      </c>
+      <c r="E2226" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2227">
+      <c r="A2227" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B2227" t="inlineStr">
+        <is>
+          <t>UBER</t>
+        </is>
+      </c>
+      <c r="C2227" t="inlineStr">
+        <is>
+          <t>Uber Technologies, Inc.</t>
+        </is>
+      </c>
+      <c r="D2227" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1543151/000118423726000008/xslF345X06/primarydocument.xml</t>
+        </is>
+      </c>
+      <c r="E2227" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Dara Khosrowshahi (Chief Executive Officer) BOUGHT 141,000 shares @ $70.96 ($10.01M) on 2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="2228">
+      <c r="A2228" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B2228" t="inlineStr">
+        <is>
+          <t>EXPE</t>
+        </is>
+      </c>
+      <c r="C2228" t="inlineStr">
+        <is>
+          <t>Expedia Group, Inc.</t>
+        </is>
+      </c>
+      <c r="D2228" t="inlineStr">
+        <is>
+          <t>https://careers.expediagroup.com</t>
+        </is>
+      </c>
+      <c r="E2228" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2229">
+      <c r="A2229" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B2229" t="inlineStr">
+        <is>
+          <t>BKNG</t>
+        </is>
+      </c>
+      <c r="C2229" t="inlineStr">
+        <is>
+          <t>Booking Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D2229" t="inlineStr">
+        <is>
+          <t>https://www.booking.com/content/terms.html</t>
+        </is>
+      </c>
+      <c r="E2229" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2230">
+      <c r="A2230" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B2230" t="inlineStr">
+        <is>
+          <t>ABNB</t>
+        </is>
+      </c>
+      <c r="C2230" t="inlineStr">
+        <is>
+          <t>Airbnb, Inc.</t>
+        </is>
+      </c>
+      <c r="D2230" t="inlineStr">
+        <is>
+          <t>https://news.airbnb.com</t>
+        </is>
+      </c>
+      <c r="E2230" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2231">
+      <c r="A2231" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B2231" t="inlineStr">
+        <is>
+          <t>ABNB</t>
+        </is>
+      </c>
+      <c r="C2231" t="inlineStr">
+        <is>
+          <t>Airbnb, Inc.</t>
+        </is>
+      </c>
+      <c r="D2231" t="inlineStr">
+        <is>
+          <t>https://careers.airbnb.com</t>
+        </is>
+      </c>
+      <c r="E2231" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2232">
+      <c r="A2232" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B2232" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="C2232" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="D2232" t="inlineStr">
+        <is>
+          <t>https://investor.atmeta.com</t>
+        </is>
+      </c>
+      <c r="E2232" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2233">
+      <c r="A2233" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B2233" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="C2233" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="D2233" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1326801/000095010326013794/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E2233" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Olivan Javier (Chief Operating Officer) sold 5,354 shares @ $616.58 ($3.30M) on 2026-09-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="2234">
+      <c r="A2234" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B2234" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="C2234" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="D2234" t="inlineStr">
+        <is>
+          <t>https://blog.google</t>
+        </is>
+      </c>
+      <c r="E2234" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2235">
+      <c r="A2235" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B2235" t="inlineStr">
+        <is>
+          <t>SNAP</t>
+        </is>
+      </c>
+      <c r="C2235" t="inlineStr">
+        <is>
+          <t>Snap Inc.</t>
+        </is>
+      </c>
+      <c r="D2235" t="inlineStr">
+        <is>
+          <t>https://newsroom.snap.com</t>
+        </is>
+      </c>
+      <c r="E2235" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2236">
+      <c r="A2236" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B2236" t="inlineStr">
+        <is>
+          <t>PINS</t>
+        </is>
+      </c>
+      <c r="C2236" t="inlineStr">
+        <is>
+          <t>Pinterest, Inc.</t>
+        </is>
+      </c>
+      <c r="D2236" t="inlineStr">
+        <is>
+          <t>https://newsroom.pinterest.com</t>
+        </is>
+      </c>
+      <c r="E2236" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2237">
+      <c r="A2237" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B2237" t="inlineStr">
+        <is>
+          <t>RDDT</t>
+        </is>
+      </c>
+      <c r="C2237" t="inlineStr">
+        <is>
+          <t>Reddit, Inc.</t>
+        </is>
+      </c>
+      <c r="D2237" t="inlineStr">
+        <is>
+          <t>https://redditinc.com/careers</t>
+        </is>
+      </c>
+      <c r="E2237" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2238">
+      <c r="A2238" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B2238" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="C2238" t="inlineStr">
+        <is>
+          <t>Unity Software Inc.</t>
+        </is>
+      </c>
+      <c r="D2238" t="inlineStr">
+        <is>
+          <t>https://careers.unity.com</t>
+        </is>
+      </c>
+      <c r="E2238" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2239">
+      <c r="A2239" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B2239" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="C2239" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="D2239" t="inlineStr">
+        <is>
+          <t>https://about.netflix.com/newsroom</t>
+        </is>
+      </c>
+      <c r="E2239" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2240">
+      <c r="A2240" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B2240" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="C2240" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="D2240" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1065280/000106528026000271/xslF345X06/wk-form4_1789085087.xml</t>
+        </is>
+      </c>
+      <c r="E2240" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Richard N Barton (Director) sold 1,440 shares @ $75.77 ($109.1K) on 2026-09-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="2241">
+      <c r="A2241" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B2241" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="C2241" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="D2241" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1065280/000162828026061301/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E2241" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Richard Barton (Director) plans to sell 720 shares (~$54.2K) on/after 09/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2242">
+      <c r="A2242" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B2242" t="inlineStr">
+        <is>
+          <t>SPOT</t>
+        </is>
+      </c>
+      <c r="C2242" t="inlineStr">
+        <is>
+          <t>Spotify Technology S.A.</t>
+        </is>
+      </c>
+      <c r="D2242" t="inlineStr">
+        <is>
+          <t>https://newsroom.spotify.com</t>
+        </is>
+      </c>
+      <c r="E2242" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2243">
+      <c r="A2243" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B2243" t="inlineStr">
+        <is>
+          <t>SPOT</t>
+        </is>
+      </c>
+      <c r="C2243" t="inlineStr">
+        <is>
+          <t>Spotify Technology S.A.</t>
+        </is>
+      </c>
+      <c r="D2243" t="inlineStr">
+        <is>
+          <t>https://www.lifeatspotify.com</t>
+        </is>
+      </c>
+      <c r="E2243" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2244">
+      <c r="A2244" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B2244" t="inlineStr">
+        <is>
+          <t>LIF</t>
+        </is>
+      </c>
+      <c r="C2244" t="inlineStr">
+        <is>
+          <t>LIF (verify ticker)</t>
+        </is>
+      </c>
+      <c r="D2244" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1581760/000158176026000161/xslF345X06/wk-form4_1789083052.xml</t>
+        </is>
+      </c>
+      <c r="E2244" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Hulls Chris (Director) 7,545 shares withheld for taxes (vest event) on 2026-09-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="2245">
+      <c r="A2245" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B2245" t="inlineStr">
+        <is>
+          <t>LIF</t>
+        </is>
+      </c>
+      <c r="C2245" t="inlineStr">
+        <is>
+          <t>LIF (verify ticker)</t>
+        </is>
+      </c>
+      <c r="D2245" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1581760/000158176026000159/xslF345X06/wk-form4_1789082875.xml</t>
+        </is>
+      </c>
+      <c r="E2245" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Antonoff Lauren (Chief Executive Officer) 6,291 shares withheld for taxes (vest event) on 2026-09-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="2246">
+      <c r="A2246" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B2246" t="inlineStr">
+        <is>
+          <t>LIF</t>
+        </is>
+      </c>
+      <c r="C2246" t="inlineStr">
+        <is>
+          <t>LIF (verify ticker)</t>
+        </is>
+      </c>
+      <c r="D2246" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1581760/000158176026000157/xslF345X06/wk-form4_1789082836.xml</t>
+        </is>
+      </c>
+      <c r="E2246" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Burke Russell John (Chief Financial Officer) 5,314 shares withheld for taxes (vest event) on 2026-09-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="2247">
+      <c r="A2247" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B2247" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="C2247" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="D2247" t="inlineStr">
+        <is>
+          <t>https://www.disneyplus.com/welcome</t>
+        </is>
+      </c>
+      <c r="E2247" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2248">
+      <c r="A2248" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B2248" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="C2248" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="D2248" t="inlineStr">
+        <is>
+          <t>https://jobs.disneycareers.com</t>
+        </is>
+      </c>
+      <c r="E2248" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2249">
+      <c r="A2249" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B2249" t="inlineStr">
+        <is>
+          <t>FOXA</t>
+        </is>
+      </c>
+      <c r="C2249" t="inlineStr">
+        <is>
+          <t>Fox Corporation</t>
+        </is>
+      </c>
+      <c r="D2249" t="inlineStr">
+        <is>
+          <t>https://investor.foxcorporation.com</t>
+        </is>
+      </c>
+      <c r="E2249" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2250">
+      <c r="A2250" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B2250" t="inlineStr">
+        <is>
+          <t>FOXA</t>
+        </is>
+      </c>
+      <c r="C2250" t="inlineStr">
+        <is>
+          <t>Fox Corporation</t>
+        </is>
+      </c>
+      <c r="D2250" t="inlineStr">
+        <is>
+          <t>https://foxcareers.com</t>
+        </is>
+      </c>
+      <c r="E2250" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2251">
+      <c r="A2251" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B2251" t="inlineStr">
+        <is>
+          <t>FOXA</t>
+        </is>
+      </c>
+      <c r="C2251" t="inlineStr">
+        <is>
+          <t>Fox Corporation</t>
+        </is>
+      </c>
+      <c r="D2251" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1754301/000119312526387859/d114415d425.htm</t>
+        </is>
+      </c>
+      <c r="E2251" t="inlineStr">
+        <is>
+          <t>[UNKNOWN] Form 425</t>
+        </is>
+      </c>
+    </row>
+    <row r="2252">
+      <c r="A2252" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B2252" t="inlineStr">
+        <is>
+          <t>WMG</t>
+        </is>
+      </c>
+      <c r="C2252" t="inlineStr">
+        <is>
+          <t>Warner Music Group Corp.</t>
+        </is>
+      </c>
+      <c r="D2252" t="inlineStr">
+        <is>
+          <t>https://www.wmg.com/news/</t>
+        </is>
+      </c>
+      <c r="E2252" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2253">
+      <c r="A2253" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B2253" t="inlineStr">
+        <is>
+          <t>LYV</t>
+        </is>
+      </c>
+      <c r="C2253" t="inlineStr">
+        <is>
+          <t>Live Nation Entertainment, Inc.</t>
+        </is>
+      </c>
+      <c r="D2253" t="inlineStr">
+        <is>
+          <t>https://www.livenationentertainment.com/careers</t>
+        </is>
+      </c>
+      <c r="E2253" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2254">
+      <c r="A2254" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B2254" t="inlineStr">
+        <is>
+          <t>STUB</t>
+        </is>
+      </c>
+      <c r="C2254" t="inlineStr">
+        <is>
+          <t>StubHub Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="D2254" t="inlineStr">
+        <is>
+          <t>https://www.stubhub.com/careers/</t>
+        </is>
+      </c>
+      <c r="E2254" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2255">
+      <c r="A2255" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B2255" t="inlineStr">
+        <is>
+          <t>TTWO</t>
+        </is>
+      </c>
+      <c r="C2255" t="inlineStr">
+        <is>
+          <t>Take-Two Interactive Software, Inc.</t>
+        </is>
+      </c>
+      <c r="D2255" t="inlineStr">
+        <is>
+          <t>https://ir.take2games.com</t>
+        </is>
+      </c>
+      <c r="E2255" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2256">
+      <c r="A2256" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B2256" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="C2256" t="inlineStr">
+        <is>
+          <t>Electronic Arts Inc.</t>
+        </is>
+      </c>
+      <c r="D2256" t="inlineStr">
+        <is>
+          <t>https://www.ea.com/news</t>
+        </is>
+      </c>
+      <c r="E2256" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2257">
+      <c r="A2257" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B2257" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="C2257" t="inlineStr">
+        <is>
+          <t>Electronic Arts Inc.</t>
+        </is>
+      </c>
+      <c r="D2257" t="inlineStr">
+        <is>
+          <t>https://ir.ea.com</t>
+        </is>
+      </c>
+      <c r="E2257" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2258">
+      <c r="A2258" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B2258" t="inlineStr">
+        <is>
+          <t>INTU</t>
+        </is>
+      </c>
+      <c r="C2258" t="inlineStr">
+        <is>
+          <t>Intuit Inc.</t>
+        </is>
+      </c>
+      <c r="D2258" t="inlineStr">
+        <is>
+          <t>https://investors.intuit.com</t>
+        </is>
+      </c>
+      <c r="E2258" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2259">
+      <c r="A2259" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B2259" t="inlineStr">
+        <is>
+          <t>ADP</t>
+        </is>
+      </c>
+      <c r="C2259" t="inlineStr">
+        <is>
+          <t>Automatic Data Processing, Inc.</t>
+        </is>
+      </c>
+      <c r="D2259" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/8670/000122520826007726/xslF345X06/doc4.xml</t>
+        </is>
+      </c>
+      <c r="E2259" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Sugla Vishwas (Chief Strategy Officer) granted 4,900 shares on 2026-09-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="2260">
+      <c r="A2260" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B2260" t="inlineStr">
+        <is>
+          <t>ADP</t>
+        </is>
+      </c>
+      <c r="C2260" t="inlineStr">
+        <is>
+          <t>Automatic Data Processing, Inc.</t>
+        </is>
+      </c>
+      <c r="D2260" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/8670/000122520826007723/xslF345X06/doc3.xml</t>
+        </is>
+      </c>
+      <c r="E2260" t="inlineStr">
+        <is>
+          <t>[ROUTINE] New insider — initial ownership statement</t>
+        </is>
+      </c>
+    </row>
+    <row r="2261">
+      <c r="A2261" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B2261" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C2261" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D2261" t="inlineStr">
+        <is>
+          <t>https://www.shopify.com/careers</t>
+        </is>
+      </c>
+      <c r="E2261" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F2261" t="inlineStr"/>
+      <c r="G2261" t="inlineStr"/>
+      <c r="H2261" t="inlineStr"/>
+    </row>
+    <row r="2262">
+      <c r="A2262" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B2262" t="inlineStr">
+        <is>
+          <t>EBAY</t>
+        </is>
+      </c>
+      <c r="C2262" t="inlineStr">
+        <is>
+          <t>eBay Inc.</t>
+        </is>
+      </c>
+      <c r="D2262" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/help/policies/member-behaviour-policies/user-agreement?id=4259</t>
+        </is>
+      </c>
+      <c r="E2262" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+      <c r="F2262" t="inlineStr"/>
+      <c r="G2262" t="inlineStr"/>
+      <c r="H2262" t="inlineStr"/>
+    </row>
+    <row r="2263">
+      <c r="A2263" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B2263" t="inlineStr">
+        <is>
+          <t>EBAY</t>
+        </is>
+      </c>
+      <c r="C2263" t="inlineStr">
+        <is>
+          <t>eBay Inc.</t>
+        </is>
+      </c>
+      <c r="D2263" t="inlineStr">
+        <is>
+          <t>https://careers.ebayinc.com</t>
+        </is>
+      </c>
+      <c r="E2263" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F2263" t="inlineStr"/>
+      <c r="G2263" t="inlineStr"/>
+      <c r="H2263" t="inlineStr"/>
+    </row>
+    <row r="2264">
+      <c r="A2264" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B2264" t="inlineStr">
+        <is>
+          <t>EBAY</t>
+        </is>
+      </c>
+      <c r="C2264" t="inlineStr">
+        <is>
+          <t>eBay Inc.</t>
+        </is>
+      </c>
+      <c r="D2264" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1065088/000106508826000190/xslF345X06/form4.xml</t>
+        </is>
+      </c>
+      <c r="E2264" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Jamie Iannone (President and CEO) sold 22,220 shares @ $103.17 ($2.29M) on 2026-09-08</t>
+        </is>
+      </c>
+      <c r="F2264" t="inlineStr"/>
+      <c r="G2264" t="inlineStr"/>
+      <c r="H2264" t="inlineStr"/>
+    </row>
+    <row r="2265">
+      <c r="A2265" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B2265" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="C2265" t="inlineStr">
+        <is>
+          <t>Wayfair Inc.</t>
+        </is>
+      </c>
+      <c r="D2265" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1616707/000161670726000160/xslF345X06/wk-form4_1789072041.xml</t>
+        </is>
+      </c>
+      <c r="E2265" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Blotner Jon (Pres., Commercial &amp; Operations) sold 6,968 shares @ $100.22 ($698.3K) on 2026-09-08</t>
+        </is>
+      </c>
+      <c r="F2265" t="inlineStr"/>
+      <c r="G2265" t="inlineStr"/>
+      <c r="H2265" t="inlineStr"/>
+    </row>
+    <row r="2266">
+      <c r="A2266" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B2266" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="C2266" t="inlineStr">
+        <is>
+          <t>Wayfair Inc.</t>
+        </is>
+      </c>
+      <c r="D2266" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1616707/000195917326006851/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E2266" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Conine Steven (Officer) plans to sell 5,000 shares (~$490.4K) on/after 09/10/2026</t>
+        </is>
+      </c>
+      <c r="F2266" t="inlineStr"/>
+      <c r="G2266" t="inlineStr"/>
+      <c r="H2266" t="inlineStr"/>
+    </row>
+    <row r="2267">
+      <c r="A2267" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B2267" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C2267" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D2267" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/instacart</t>
+        </is>
+      </c>
+      <c r="E2267" t="inlineStr">
+        <is>
+          <t>5 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F2267" t="inlineStr"/>
+      <c r="G2267" t="inlineStr"/>
+      <c r="H2267" t="inlineStr"/>
+    </row>
+    <row r="2268">
+      <c r="A2268" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B2268" t="inlineStr">
+        <is>
+          <t>DUOL</t>
+        </is>
+      </c>
+      <c r="C2268" t="inlineStr">
+        <is>
+          <t>Duolingo Inc.</t>
+        </is>
+      </c>
+      <c r="D2268" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1562088/000162828026061361/xslF345X06/wk-form4_1789071780.xml</t>
+        </is>
+      </c>
+      <c r="E2268" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — William B Gordon (Director) sold 10,000 shares @ $145.67 ($1.46M) on 2026-09-08</t>
+        </is>
+      </c>
+      <c r="F2268" t="inlineStr"/>
+      <c r="G2268" t="inlineStr"/>
+      <c r="H2268" t="inlineStr"/>
+    </row>
+    <row r="2269">
+      <c r="A2269" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B2269" t="inlineStr">
+        <is>
+          <t>MTCH</t>
+        </is>
+      </c>
+      <c r="C2269" t="inlineStr">
+        <is>
+          <t>Match Group Inc.</t>
+        </is>
+      </c>
+      <c r="D2269" t="inlineStr">
+        <is>
+          <t>https://mtch.com/news</t>
+        </is>
+      </c>
+      <c r="E2269" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F2269" t="inlineStr"/>
+      <c r="G2269" t="inlineStr"/>
+      <c r="H2269" t="inlineStr"/>
+    </row>
+    <row r="2270">
+      <c r="A2270" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B2270" t="inlineStr">
+        <is>
+          <t>COMP</t>
+        </is>
+      </c>
+      <c r="C2270" t="inlineStr">
+        <is>
+          <t>Compass Inc.</t>
+        </is>
+      </c>
+      <c r="D2270" t="inlineStr">
+        <is>
+          <t>https://www.compass.com/careers/</t>
+        </is>
+      </c>
+      <c r="E2270" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F2270" t="inlineStr"/>
+      <c r="G2270" t="inlineStr"/>
+      <c r="H2270" t="inlineStr"/>
+    </row>
+    <row r="2271">
+      <c r="A2271" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B2271" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C2271" t="inlineStr">
+        <is>
+          <t>Block Inc. (fmr. Square)</t>
+        </is>
+      </c>
+      <c r="D2271" t="inlineStr">
+        <is>
+          <t>https://squareup.com/us/en/legal/general/ua</t>
+        </is>
+      </c>
+      <c r="E2271" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+      <c r="F2271" t="inlineStr"/>
+      <c r="G2271" t="inlineStr"/>
+      <c r="H2271" t="inlineStr"/>
+    </row>
+    <row r="2272">
+      <c r="A2272" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B2272" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C2272" t="inlineStr">
+        <is>
+          <t>Block Inc. (fmr. Square)</t>
+        </is>
+      </c>
+      <c r="D2272" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1512673/000162828026061433/xslF345X06/wk-form4_1789077758.xml</t>
+        </is>
+      </c>
+      <c r="E2272" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Eisen Anthony Mathew (Director) sold 18,000 shares @ $79.95 ($1.44M) on 2026-09-08</t>
+        </is>
+      </c>
+      <c r="F2272" t="inlineStr"/>
+      <c r="G2272" t="inlineStr"/>
+      <c r="H2272" t="inlineStr"/>
+    </row>
+    <row r="2273">
+      <c r="A2273" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B2273" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C2273" t="inlineStr">
+        <is>
+          <t>Block Inc. (fmr. Square)</t>
+        </is>
+      </c>
+      <c r="D2273" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1512673/000195004726009283/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E2273" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — M Eisen Anthony (Director) plans to sell 6,000 shares (~$470.3K) on/after 09/10/2026</t>
+        </is>
+      </c>
+      <c r="F2273" t="inlineStr"/>
+      <c r="G2273" t="inlineStr"/>
+      <c r="H2273" t="inlineStr"/>
+    </row>
+    <row r="2274">
+      <c r="A2274" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B2274" t="inlineStr">
+        <is>
+          <t>TOST</t>
+        </is>
+      </c>
+      <c r="C2274" t="inlineStr">
+        <is>
+          <t>Toast Inc.</t>
+        </is>
+      </c>
+      <c r="D2274" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/toast</t>
+        </is>
+      </c>
+      <c r="E2274" t="inlineStr">
+        <is>
+          <t>17 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F2274" t="inlineStr"/>
+      <c r="G2274" t="inlineStr"/>
+      <c r="H2274" t="inlineStr"/>
+    </row>
+    <row r="2275">
+      <c r="A2275" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B2275" t="inlineStr">
+        <is>
+          <t>DAVE</t>
+        </is>
+      </c>
+      <c r="C2275" t="inlineStr">
+        <is>
+          <t>Dave Inc.</t>
+        </is>
+      </c>
+      <c r="D2275" t="inlineStr">
+        <is>
+          <t>https://dave.com/careers</t>
+        </is>
+      </c>
+      <c r="E2275" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F2275" t="inlineStr"/>
+      <c r="G2275" t="inlineStr"/>
+      <c r="H2275" t="inlineStr"/>
+    </row>
+    <row r="2276">
+      <c r="A2276" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B2276" t="inlineStr">
+        <is>
+          <t>AFRM</t>
+        </is>
+      </c>
+      <c r="C2276" t="inlineStr">
+        <is>
+          <t>Affirm Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D2276" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/affirm</t>
+        </is>
+      </c>
+      <c r="E2276" t="inlineStr">
+        <is>
+          <t>5 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F2276" t="inlineStr"/>
+      <c r="G2276" t="inlineStr"/>
+      <c r="H2276" t="inlineStr"/>
+    </row>
+    <row r="2277">
+      <c r="A2277" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B2277" t="inlineStr">
+        <is>
+          <t>HOOD</t>
+        </is>
+      </c>
+      <c r="C2277" t="inlineStr">
+        <is>
+          <t>Robinhood Markets Inc.</t>
+        </is>
+      </c>
+      <c r="D2277" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/robinhood</t>
+        </is>
+      </c>
+      <c r="E2277" t="inlineStr">
+        <is>
+          <t>3 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F2277" t="inlineStr"/>
+      <c r="G2277" t="inlineStr"/>
+      <c r="H2277" t="inlineStr"/>
+    </row>
+    <row r="2278">
+      <c r="A2278" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B2278" t="inlineStr">
+        <is>
+          <t>HOOD</t>
+        </is>
+      </c>
+      <c r="C2278" t="inlineStr">
+        <is>
+          <t>Robinhood Markets Inc.</t>
+        </is>
+      </c>
+      <c r="D2278" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1783879/000181742526000012/xslF345X06/wk-form4_1789074490.xml</t>
+        </is>
+      </c>
+      <c r="E2278" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Treseder Oluwadara Johnson (Director) sold 1,875 shares @ $125.00 ($234.4K) on 2026-09-08</t>
+        </is>
+      </c>
+      <c r="F2278" t="inlineStr"/>
+      <c r="G2278" t="inlineStr"/>
+      <c r="H2278" t="inlineStr"/>
+    </row>
+    <row r="2279">
+      <c r="A2279" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B2279" t="inlineStr">
+        <is>
+          <t>HOOD</t>
+        </is>
+      </c>
+      <c r="C2279" t="inlineStr">
+        <is>
+          <t>Robinhood Markets Inc.</t>
+        </is>
+      </c>
+      <c r="D2279" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1783879/000195004726009302/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E2279" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Baiju Prafulkumar Bhatt Living Trust (Director) plans to sell 43,373 shares (~$5.00M) on/after 09/10/2026</t>
+        </is>
+      </c>
+      <c r="F2279" t="inlineStr"/>
+      <c r="G2279" t="inlineStr"/>
+      <c r="H2279" t="inlineStr"/>
+    </row>
+    <row r="2280">
+      <c r="A2280" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B2280" t="inlineStr">
+        <is>
+          <t>UPST</t>
+        </is>
+      </c>
+      <c r="C2280" t="inlineStr">
+        <is>
+          <t>Upstart Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D2280" t="inlineStr">
+        <is>
+          <t>https://careers.upstart.com/jobs?gh_jid=8095582</t>
+        </is>
+      </c>
+      <c r="E2280" t="inlineStr">
+        <is>
+          <t>New senior role: Director of Lifecycle Marketing</t>
+        </is>
+      </c>
+      <c r="F2280" t="inlineStr"/>
+      <c r="G2280" t="inlineStr"/>
+      <c r="H2280" t="inlineStr"/>
+    </row>
+    <row r="2281">
+      <c r="A2281" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B2281" t="inlineStr">
+        <is>
+          <t>UPST</t>
+        </is>
+      </c>
+      <c r="C2281" t="inlineStr">
+        <is>
+          <t>Upstart Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D2281" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/upstart</t>
+        </is>
+      </c>
+      <c r="E2281" t="inlineStr">
+        <is>
+          <t>2 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F2281" t="inlineStr"/>
+      <c r="G2281" t="inlineStr"/>
+      <c r="H2281" t="inlineStr"/>
+    </row>
+    <row r="2282">
+      <c r="A2282" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B2282" t="inlineStr">
+        <is>
+          <t>UPST</t>
+        </is>
+      </c>
+      <c r="C2282" t="inlineStr">
+        <is>
+          <t>Upstart Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D2282" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1647639/000183281226000010/xslF345X06/wk-form4_1789082008.xml</t>
+        </is>
+      </c>
+      <c r="E2282" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Gu Paul (Chief Executive Officer) BOUGHT 50,000 shares @ $25.55 ($1.28M) on 2026-09-10</t>
+        </is>
+      </c>
+      <c r="F2282" t="inlineStr"/>
+      <c r="G2282" t="inlineStr"/>
+      <c r="H2282" t="inlineStr"/>
+    </row>
+    <row r="2283">
+      <c r="A2283" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B2283" t="inlineStr">
+        <is>
+          <t>UPST</t>
+        </is>
+      </c>
+      <c r="C2283" t="inlineStr">
+        <is>
+          <t>Upstart Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D2283" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1647639/000183280826000020/xslF345X06/wk-form4_1789081939.xml</t>
+        </is>
+      </c>
+      <c r="E2283" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Datta Sanjay (President, Capital&amp; Enterprise) sold 116,000 shares @ $27.29 ($3.17M) on 2026-09-08</t>
+        </is>
+      </c>
+      <c r="F2283" t="inlineStr"/>
+      <c r="G2283" t="inlineStr"/>
+      <c r="H2283" t="inlineStr"/>
+    </row>
+    <row r="2284">
+      <c r="A2284" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B2284" t="inlineStr">
+        <is>
+          <t>RH</t>
+        </is>
+      </c>
+      <c r="C2284" t="inlineStr">
+        <is>
+          <t>RH (Restoration Hardware)</t>
+        </is>
+      </c>
+      <c r="D2284" t="inlineStr">
+        <is>
+          <t>https://ir.rh.com/news-releases</t>
+        </is>
+      </c>
+      <c r="E2284" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F2284" t="inlineStr"/>
+      <c r="G2284" t="inlineStr"/>
+      <c r="H2284" t="inlineStr"/>
+    </row>
+    <row r="2285">
+      <c r="A2285" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B2285" t="inlineStr">
+        <is>
+          <t>RH</t>
+        </is>
+      </c>
+      <c r="C2285" t="inlineStr">
+        <is>
+          <t>RH (Restoration Hardware)</t>
+        </is>
+      </c>
+      <c r="D2285" t="inlineStr">
+        <is>
+          <t>https://ir.rh.com</t>
+        </is>
+      </c>
+      <c r="E2285" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+      <c r="F2285" t="inlineStr"/>
+      <c r="G2285" t="inlineStr"/>
+      <c r="H2285" t="inlineStr"/>
+    </row>
+    <row r="2286">
+      <c r="A2286" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B2286" t="inlineStr">
+        <is>
+          <t>RH</t>
+        </is>
+      </c>
+      <c r="C2286" t="inlineStr">
+        <is>
+          <t>RH (Restoration Hardware)</t>
+        </is>
+      </c>
+      <c r="D2286" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1528849/000110465926106764/rh-20260801x10q.htm</t>
+        </is>
+      </c>
+      <c r="E2286" t="inlineStr">
+        <is>
+          <t>[MATERIAL] Quarterly report</t>
+        </is>
+      </c>
+      <c r="F2286" t="inlineStr"/>
+      <c r="G2286" t="inlineStr"/>
+      <c r="H2286" t="inlineStr"/>
+    </row>
+    <row r="2287">
+      <c r="A2287" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B2287" t="inlineStr">
+        <is>
+          <t>RH</t>
+        </is>
+      </c>
+      <c r="C2287" t="inlineStr">
+        <is>
+          <t>RH (Restoration Hardware)</t>
+        </is>
+      </c>
+      <c r="D2287" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1528849/000110465926106743/rh-20260910x8k.htm</t>
+        </is>
+      </c>
+      <c r="E2287" t="inlineStr">
+        <is>
+          <t>[MATERIAL] Material event disclosure</t>
+        </is>
+      </c>
+      <c r="F2287" t="inlineStr"/>
+      <c r="G2287" t="inlineStr"/>
+      <c r="H2287" t="inlineStr"/>
+    </row>
+    <row r="2288">
+      <c r="A2288" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B2288" t="inlineStr">
+        <is>
+          <t>ONON</t>
+        </is>
+      </c>
+      <c r="C2288" t="inlineStr">
+        <is>
+          <t>On Holding AG</t>
+        </is>
+      </c>
+      <c r="D2288" t="inlineStr">
+        <is>
+          <t>https://www.on-running.com/en-us/articles/</t>
+        </is>
+      </c>
+      <c r="E2288" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F2288" t="inlineStr"/>
+      <c r="G2288" t="inlineStr"/>
+      <c r="H2288" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/config/company_urls_jc.xlsx
+++ b/config/company_urls_jc.xlsx
@@ -7203,7 +7203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2288"/>
+  <dimension ref="A1:H2329"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -68207,9 +68207,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F2261" t="inlineStr"/>
-      <c r="G2261" t="inlineStr"/>
-      <c r="H2261" t="inlineStr"/>
     </row>
     <row r="2262">
       <c r="A2262" t="inlineStr">
@@ -68237,9 +68234,6 @@
           <t>terms: change detected</t>
         </is>
       </c>
-      <c r="F2262" t="inlineStr"/>
-      <c r="G2262" t="inlineStr"/>
-      <c r="H2262" t="inlineStr"/>
     </row>
     <row r="2263">
       <c r="A2263" t="inlineStr">
@@ -68267,9 +68261,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F2263" t="inlineStr"/>
-      <c r="G2263" t="inlineStr"/>
-      <c r="H2263" t="inlineStr"/>
     </row>
     <row r="2264">
       <c r="A2264" t="inlineStr">
@@ -68297,9 +68288,6 @@
           <t>[ROUTINE] Insider trade — Jamie Iannone (President and CEO) sold 22,220 shares @ $103.17 ($2.29M) on 2026-09-08</t>
         </is>
       </c>
-      <c r="F2264" t="inlineStr"/>
-      <c r="G2264" t="inlineStr"/>
-      <c r="H2264" t="inlineStr"/>
     </row>
     <row r="2265">
       <c r="A2265" t="inlineStr">
@@ -68327,9 +68315,6 @@
           <t>[ROUTINE] Insider trade — Blotner Jon (Pres., Commercial &amp; Operations) sold 6,968 shares @ $100.22 ($698.3K) on 2026-09-08</t>
         </is>
       </c>
-      <c r="F2265" t="inlineStr"/>
-      <c r="G2265" t="inlineStr"/>
-      <c r="H2265" t="inlineStr"/>
     </row>
     <row r="2266">
       <c r="A2266" t="inlineStr">
@@ -68357,9 +68342,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Conine Steven (Officer) plans to sell 5,000 shares (~$490.4K) on/after 09/10/2026</t>
         </is>
       </c>
-      <c r="F2266" t="inlineStr"/>
-      <c r="G2266" t="inlineStr"/>
-      <c r="H2266" t="inlineStr"/>
     </row>
     <row r="2267">
       <c r="A2267" t="inlineStr">
@@ -68387,9 +68369,6 @@
           <t>5 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F2267" t="inlineStr"/>
-      <c r="G2267" t="inlineStr"/>
-      <c r="H2267" t="inlineStr"/>
     </row>
     <row r="2268">
       <c r="A2268" t="inlineStr">
@@ -68417,9 +68396,6 @@
           <t>[ROUTINE] Insider trade — William B Gordon (Director) sold 10,000 shares @ $145.67 ($1.46M) on 2026-09-08</t>
         </is>
       </c>
-      <c r="F2268" t="inlineStr"/>
-      <c r="G2268" t="inlineStr"/>
-      <c r="H2268" t="inlineStr"/>
     </row>
     <row r="2269">
       <c r="A2269" t="inlineStr">
@@ -68447,9 +68423,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F2269" t="inlineStr"/>
-      <c r="G2269" t="inlineStr"/>
-      <c r="H2269" t="inlineStr"/>
     </row>
     <row r="2270">
       <c r="A2270" t="inlineStr">
@@ -68477,9 +68450,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F2270" t="inlineStr"/>
-      <c r="G2270" t="inlineStr"/>
-      <c r="H2270" t="inlineStr"/>
     </row>
     <row r="2271">
       <c r="A2271" t="inlineStr">
@@ -68507,9 +68477,6 @@
           <t>terms: change detected</t>
         </is>
       </c>
-      <c r="F2271" t="inlineStr"/>
-      <c r="G2271" t="inlineStr"/>
-      <c r="H2271" t="inlineStr"/>
     </row>
     <row r="2272">
       <c r="A2272" t="inlineStr">
@@ -68537,9 +68504,6 @@
           <t>[ROUTINE] Insider trade — Eisen Anthony Mathew (Director) sold 18,000 shares @ $79.95 ($1.44M) on 2026-09-08</t>
         </is>
       </c>
-      <c r="F2272" t="inlineStr"/>
-      <c r="G2272" t="inlineStr"/>
-      <c r="H2272" t="inlineStr"/>
     </row>
     <row r="2273">
       <c r="A2273" t="inlineStr">
@@ -68567,9 +68531,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — M Eisen Anthony (Director) plans to sell 6,000 shares (~$470.3K) on/after 09/10/2026</t>
         </is>
       </c>
-      <c r="F2273" t="inlineStr"/>
-      <c r="G2273" t="inlineStr"/>
-      <c r="H2273" t="inlineStr"/>
     </row>
     <row r="2274">
       <c r="A2274" t="inlineStr">
@@ -68597,9 +68558,6 @@
           <t>17 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F2274" t="inlineStr"/>
-      <c r="G2274" t="inlineStr"/>
-      <c r="H2274" t="inlineStr"/>
     </row>
     <row r="2275">
       <c r="A2275" t="inlineStr">
@@ -68627,9 +68585,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F2275" t="inlineStr"/>
-      <c r="G2275" t="inlineStr"/>
-      <c r="H2275" t="inlineStr"/>
     </row>
     <row r="2276">
       <c r="A2276" t="inlineStr">
@@ -68657,9 +68612,6 @@
           <t>5 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F2276" t="inlineStr"/>
-      <c r="G2276" t="inlineStr"/>
-      <c r="H2276" t="inlineStr"/>
     </row>
     <row r="2277">
       <c r="A2277" t="inlineStr">
@@ -68687,9 +68639,6 @@
           <t>3 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F2277" t="inlineStr"/>
-      <c r="G2277" t="inlineStr"/>
-      <c r="H2277" t="inlineStr"/>
     </row>
     <row r="2278">
       <c r="A2278" t="inlineStr">
@@ -68717,9 +68666,6 @@
           <t>[ROUTINE] Insider trade — Treseder Oluwadara Johnson (Director) sold 1,875 shares @ $125.00 ($234.4K) on 2026-09-08</t>
         </is>
       </c>
-      <c r="F2278" t="inlineStr"/>
-      <c r="G2278" t="inlineStr"/>
-      <c r="H2278" t="inlineStr"/>
     </row>
     <row r="2279">
       <c r="A2279" t="inlineStr">
@@ -68747,9 +68693,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Baiju Prafulkumar Bhatt Living Trust (Director) plans to sell 43,373 shares (~$5.00M) on/after 09/10/2026</t>
         </is>
       </c>
-      <c r="F2279" t="inlineStr"/>
-      <c r="G2279" t="inlineStr"/>
-      <c r="H2279" t="inlineStr"/>
     </row>
     <row r="2280">
       <c r="A2280" t="inlineStr">
@@ -68777,9 +68720,6 @@
           <t>New senior role: Director of Lifecycle Marketing</t>
         </is>
       </c>
-      <c r="F2280" t="inlineStr"/>
-      <c r="G2280" t="inlineStr"/>
-      <c r="H2280" t="inlineStr"/>
     </row>
     <row r="2281">
       <c r="A2281" t="inlineStr">
@@ -68807,9 +68747,6 @@
           <t>2 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F2281" t="inlineStr"/>
-      <c r="G2281" t="inlineStr"/>
-      <c r="H2281" t="inlineStr"/>
     </row>
     <row r="2282">
       <c r="A2282" t="inlineStr">
@@ -68837,9 +68774,6 @@
           <t>[ROUTINE] Insider trade — Gu Paul (Chief Executive Officer) BOUGHT 50,000 shares @ $25.55 ($1.28M) on 2026-09-10</t>
         </is>
       </c>
-      <c r="F2282" t="inlineStr"/>
-      <c r="G2282" t="inlineStr"/>
-      <c r="H2282" t="inlineStr"/>
     </row>
     <row r="2283">
       <c r="A2283" t="inlineStr">
@@ -68867,9 +68801,6 @@
           <t>[ROUTINE] Insider trade — Datta Sanjay (President, Capital&amp; Enterprise) sold 116,000 shares @ $27.29 ($3.17M) on 2026-09-08</t>
         </is>
       </c>
-      <c r="F2283" t="inlineStr"/>
-      <c r="G2283" t="inlineStr"/>
-      <c r="H2283" t="inlineStr"/>
     </row>
     <row r="2284">
       <c r="A2284" t="inlineStr">
@@ -68897,9 +68828,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F2284" t="inlineStr"/>
-      <c r="G2284" t="inlineStr"/>
-      <c r="H2284" t="inlineStr"/>
     </row>
     <row r="2285">
       <c r="A2285" t="inlineStr">
@@ -68927,9 +68855,6 @@
           <t>investor_relations: change detected</t>
         </is>
       </c>
-      <c r="F2285" t="inlineStr"/>
-      <c r="G2285" t="inlineStr"/>
-      <c r="H2285" t="inlineStr"/>
     </row>
     <row r="2286">
       <c r="A2286" t="inlineStr">
@@ -68957,9 +68882,6 @@
           <t>[MATERIAL] Quarterly report</t>
         </is>
       </c>
-      <c r="F2286" t="inlineStr"/>
-      <c r="G2286" t="inlineStr"/>
-      <c r="H2286" t="inlineStr"/>
     </row>
     <row r="2287">
       <c r="A2287" t="inlineStr">
@@ -68987,9 +68909,6 @@
           <t>[MATERIAL] Material event disclosure</t>
         </is>
       </c>
-      <c r="F2287" t="inlineStr"/>
-      <c r="G2287" t="inlineStr"/>
-      <c r="H2287" t="inlineStr"/>
     </row>
     <row r="2288">
       <c r="A2288" t="inlineStr">
@@ -69017,9 +68936,1164 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F2288" t="inlineStr"/>
-      <c r="G2288" t="inlineStr"/>
-      <c r="H2288" t="inlineStr"/>
+    </row>
+    <row r="2289">
+      <c r="A2289" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B2289" t="inlineStr">
+        <is>
+          <t>LYFT</t>
+        </is>
+      </c>
+      <c r="C2289" t="inlineStr">
+        <is>
+          <t>Lyft, Inc.</t>
+        </is>
+      </c>
+      <c r="D2289" t="inlineStr">
+        <is>
+          <t>https://www.lyft.com/blog</t>
+        </is>
+      </c>
+      <c r="E2289" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2290">
+      <c r="A2290" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B2290" t="inlineStr">
+        <is>
+          <t>LYFT</t>
+        </is>
+      </c>
+      <c r="C2290" t="inlineStr">
+        <is>
+          <t>Lyft, Inc.</t>
+        </is>
+      </c>
+      <c r="D2290" t="inlineStr">
+        <is>
+          <t>https://investor.lyft.com</t>
+        </is>
+      </c>
+      <c r="E2290" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2291">
+      <c r="A2291" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B2291" t="inlineStr">
+        <is>
+          <t>EXPE</t>
+        </is>
+      </c>
+      <c r="C2291" t="inlineStr">
+        <is>
+          <t>Expedia Group, Inc.</t>
+        </is>
+      </c>
+      <c r="D2291" t="inlineStr">
+        <is>
+          <t>https://careers.expediagroup.com</t>
+        </is>
+      </c>
+      <c r="E2291" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2292">
+      <c r="A2292" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B2292" t="inlineStr">
+        <is>
+          <t>BKNG</t>
+        </is>
+      </c>
+      <c r="C2292" t="inlineStr">
+        <is>
+          <t>Booking Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D2292" t="inlineStr">
+        <is>
+          <t>https://www.booking.com/content/terms.html</t>
+        </is>
+      </c>
+      <c r="E2292" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2293">
+      <c r="A2293" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B2293" t="inlineStr">
+        <is>
+          <t>BKNG</t>
+        </is>
+      </c>
+      <c r="C2293" t="inlineStr">
+        <is>
+          <t>Booking Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D2293" t="inlineStr">
+        <is>
+          <t>https://www.bookingholdings.com/careers</t>
+        </is>
+      </c>
+      <c r="E2293" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2294">
+      <c r="A2294" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B2294" t="inlineStr">
+        <is>
+          <t>ABNB</t>
+        </is>
+      </c>
+      <c r="C2294" t="inlineStr">
+        <is>
+          <t>Airbnb, Inc.</t>
+        </is>
+      </c>
+      <c r="D2294" t="inlineStr">
+        <is>
+          <t>https://news.airbnb.com</t>
+        </is>
+      </c>
+      <c r="E2294" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2295">
+      <c r="A2295" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B2295" t="inlineStr">
+        <is>
+          <t>ABNB</t>
+        </is>
+      </c>
+      <c r="C2295" t="inlineStr">
+        <is>
+          <t>Airbnb, Inc.</t>
+        </is>
+      </c>
+      <c r="D2295" t="inlineStr">
+        <is>
+          <t>https://careers.airbnb.com</t>
+        </is>
+      </c>
+      <c r="E2295" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2296">
+      <c r="A2296" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B2296" t="inlineStr">
+        <is>
+          <t>RDDT</t>
+        </is>
+      </c>
+      <c r="C2296" t="inlineStr">
+        <is>
+          <t>Reddit, Inc.</t>
+        </is>
+      </c>
+      <c r="D2296" t="inlineStr">
+        <is>
+          <t>https://redditinc.com/careers</t>
+        </is>
+      </c>
+      <c r="E2296" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2297">
+      <c r="A2297" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B2297" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="C2297" t="inlineStr">
+        <is>
+          <t>Unity Software Inc.</t>
+        </is>
+      </c>
+      <c r="D2297" t="inlineStr">
+        <is>
+          <t>https://careers.unity.com</t>
+        </is>
+      </c>
+      <c r="E2297" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2298">
+      <c r="A2298" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B2298" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="C2298" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="D2298" t="inlineStr">
+        <is>
+          <t>https://about.netflix.com/newsroom</t>
+        </is>
+      </c>
+      <c r="E2298" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2299">
+      <c r="A2299" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B2299" t="inlineStr">
+        <is>
+          <t>SPOT</t>
+        </is>
+      </c>
+      <c r="C2299" t="inlineStr">
+        <is>
+          <t>Spotify Technology S.A.</t>
+        </is>
+      </c>
+      <c r="D2299" t="inlineStr">
+        <is>
+          <t>https://www.spotify.com/legal/end-user-agreement/</t>
+        </is>
+      </c>
+      <c r="E2299" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2300">
+      <c r="A2300" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B2300" t="inlineStr">
+        <is>
+          <t>SPOT</t>
+        </is>
+      </c>
+      <c r="C2300" t="inlineStr">
+        <is>
+          <t>Spotify Technology S.A.</t>
+        </is>
+      </c>
+      <c r="D2300" t="inlineStr">
+        <is>
+          <t>https://newsroom.spotify.com</t>
+        </is>
+      </c>
+      <c r="E2300" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2301">
+      <c r="A2301" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B2301" t="inlineStr">
+        <is>
+          <t>LIF</t>
+        </is>
+      </c>
+      <c r="C2301" t="inlineStr">
+        <is>
+          <t>LIF (verify ticker)</t>
+        </is>
+      </c>
+      <c r="D2301" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1581760/000195917326006914/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E2301" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Prober Charles J. (Director) plans to sell 7,930 shares (~$334.0K) on/after 09/14/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2302">
+      <c r="A2302" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B2302" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="C2302" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="D2302" t="inlineStr">
+        <is>
+          <t>https://www.disneyplus.com/welcome</t>
+        </is>
+      </c>
+      <c r="E2302" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2303">
+      <c r="A2303" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B2303" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="C2303" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="D2303" t="inlineStr">
+        <is>
+          <t>https://thewaltdisneycompany.com/news/</t>
+        </is>
+      </c>
+      <c r="E2303" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2304">
+      <c r="A2304" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B2304" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="C2304" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="D2304" t="inlineStr">
+        <is>
+          <t>https://jobs.disneycareers.com</t>
+        </is>
+      </c>
+      <c r="E2304" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2305">
+      <c r="A2305" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B2305" t="inlineStr">
+        <is>
+          <t>FOXA</t>
+        </is>
+      </c>
+      <c r="C2305" t="inlineStr">
+        <is>
+          <t>Fox Corporation</t>
+        </is>
+      </c>
+      <c r="D2305" t="inlineStr">
+        <is>
+          <t>https://investor.foxcorporation.com</t>
+        </is>
+      </c>
+      <c r="E2305" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2306">
+      <c r="A2306" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B2306" t="inlineStr">
+        <is>
+          <t>FOXA</t>
+        </is>
+      </c>
+      <c r="C2306" t="inlineStr">
+        <is>
+          <t>Fox Corporation</t>
+        </is>
+      </c>
+      <c r="D2306" t="inlineStr">
+        <is>
+          <t>https://foxcareers.com</t>
+        </is>
+      </c>
+      <c r="E2306" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2307">
+      <c r="A2307" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B2307" t="inlineStr">
+        <is>
+          <t>LYV</t>
+        </is>
+      </c>
+      <c r="C2307" t="inlineStr">
+        <is>
+          <t>Live Nation Entertainment, Inc.</t>
+        </is>
+      </c>
+      <c r="D2307" t="inlineStr">
+        <is>
+          <t>https://investors.livenationentertainment.com</t>
+        </is>
+      </c>
+      <c r="E2307" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2308">
+      <c r="A2308" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B2308" t="inlineStr">
+        <is>
+          <t>STUB</t>
+        </is>
+      </c>
+      <c r="C2308" t="inlineStr">
+        <is>
+          <t>StubHub Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="D2308" t="inlineStr">
+        <is>
+          <t>https://www.stubhub.com/careers/</t>
+        </is>
+      </c>
+      <c r="E2308" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2309">
+      <c r="A2309" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B2309" t="inlineStr">
+        <is>
+          <t>TTWO</t>
+        </is>
+      </c>
+      <c r="C2309" t="inlineStr">
+        <is>
+          <t>Take-Two Interactive Software, Inc.</t>
+        </is>
+      </c>
+      <c r="D2309" t="inlineStr">
+        <is>
+          <t>https://ir.take2games.com</t>
+        </is>
+      </c>
+      <c r="E2309" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2310">
+      <c r="A2310" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B2310" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="C2310" t="inlineStr">
+        <is>
+          <t>Electronic Arts Inc.</t>
+        </is>
+      </c>
+      <c r="D2310" t="inlineStr">
+        <is>
+          <t>https://www.ea.com/news</t>
+        </is>
+      </c>
+      <c r="E2310" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2311">
+      <c r="A2311" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B2311" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="C2311" t="inlineStr">
+        <is>
+          <t>Electronic Arts Inc.</t>
+        </is>
+      </c>
+      <c r="D2311" t="inlineStr">
+        <is>
+          <t>https://ir.ea.com</t>
+        </is>
+      </c>
+      <c r="E2311" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2312">
+      <c r="A2312" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B2312" t="inlineStr">
+        <is>
+          <t>CDW</t>
+        </is>
+      </c>
+      <c r="C2312" t="inlineStr">
+        <is>
+          <t>CDW Corporation</t>
+        </is>
+      </c>
+      <c r="D2312" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1402057/000119312526389920/d141326d424b5.htm</t>
+        </is>
+      </c>
+      <c r="E2312" t="inlineStr">
+        <is>
+          <t>[UNKNOWN] Form 424B5</t>
+        </is>
+      </c>
+    </row>
+    <row r="2313">
+      <c r="A2313" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B2313" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C2313" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D2313" t="inlineStr">
+        <is>
+          <t>https://www.shopify.com/careers</t>
+        </is>
+      </c>
+      <c r="E2313" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F2313" t="inlineStr"/>
+      <c r="G2313" t="inlineStr"/>
+      <c r="H2313" t="inlineStr"/>
+    </row>
+    <row r="2314">
+      <c r="A2314" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B2314" t="inlineStr">
+        <is>
+          <t>EBAY</t>
+        </is>
+      </c>
+      <c r="C2314" t="inlineStr">
+        <is>
+          <t>eBay Inc.</t>
+        </is>
+      </c>
+      <c r="D2314" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/help/policies/member-behaviour-policies/user-agreement?id=4259</t>
+        </is>
+      </c>
+      <c r="E2314" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+      <c r="F2314" t="inlineStr"/>
+      <c r="G2314" t="inlineStr"/>
+      <c r="H2314" t="inlineStr"/>
+    </row>
+    <row r="2315">
+      <c r="A2315" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B2315" t="inlineStr">
+        <is>
+          <t>EBAY</t>
+        </is>
+      </c>
+      <c r="C2315" t="inlineStr">
+        <is>
+          <t>eBay Inc.</t>
+        </is>
+      </c>
+      <c r="D2315" t="inlineStr">
+        <is>
+          <t>https://www.ebayinc.com/stories/news/</t>
+        </is>
+      </c>
+      <c r="E2315" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F2315" t="inlineStr"/>
+      <c r="G2315" t="inlineStr"/>
+      <c r="H2315" t="inlineStr"/>
+    </row>
+    <row r="2316">
+      <c r="A2316" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B2316" t="inlineStr">
+        <is>
+          <t>CHWY</t>
+        </is>
+      </c>
+      <c r="C2316" t="inlineStr">
+        <is>
+          <t>Chewy Inc.</t>
+        </is>
+      </c>
+      <c r="D2316" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1766502/000119312526389818/d175085ds3asr.htm</t>
+        </is>
+      </c>
+      <c r="E2316" t="inlineStr">
+        <is>
+          <t>[UNKNOWN] Form S-3ASR</t>
+        </is>
+      </c>
+      <c r="F2316" t="inlineStr"/>
+      <c r="G2316" t="inlineStr"/>
+      <c r="H2316" t="inlineStr"/>
+    </row>
+    <row r="2317">
+      <c r="A2317" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B2317" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C2317" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D2317" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/instacart</t>
+        </is>
+      </c>
+      <c r="E2317" t="inlineStr">
+        <is>
+          <t>1 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F2317" t="inlineStr"/>
+      <c r="G2317" t="inlineStr"/>
+      <c r="H2317" t="inlineStr"/>
+    </row>
+    <row r="2318">
+      <c r="A2318" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B2318" t="inlineStr">
+        <is>
+          <t>MTCH</t>
+        </is>
+      </c>
+      <c r="C2318" t="inlineStr">
+        <is>
+          <t>Match Group Inc.</t>
+        </is>
+      </c>
+      <c r="D2318" t="inlineStr">
+        <is>
+          <t>https://mtch.com/news</t>
+        </is>
+      </c>
+      <c r="E2318" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F2318" t="inlineStr"/>
+      <c r="G2318" t="inlineStr"/>
+      <c r="H2318" t="inlineStr"/>
+    </row>
+    <row r="2319">
+      <c r="A2319" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B2319" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="C2319" t="inlineStr">
+        <is>
+          <t>Zillow Group Inc.</t>
+        </is>
+      </c>
+      <c r="D2319" t="inlineStr">
+        <is>
+          <t>https://zillow.mediaroom.com</t>
+        </is>
+      </c>
+      <c r="E2319" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F2319" t="inlineStr"/>
+      <c r="G2319" t="inlineStr"/>
+      <c r="H2319" t="inlineStr"/>
+    </row>
+    <row r="2320">
+      <c r="A2320" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B2320" t="inlineStr">
+        <is>
+          <t>COMP</t>
+        </is>
+      </c>
+      <c r="C2320" t="inlineStr">
+        <is>
+          <t>Compass Inc.</t>
+        </is>
+      </c>
+      <c r="D2320" t="inlineStr">
+        <is>
+          <t>https://www.compass.com/careers/</t>
+        </is>
+      </c>
+      <c r="E2320" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F2320" t="inlineStr"/>
+      <c r="G2320" t="inlineStr"/>
+      <c r="H2320" t="inlineStr"/>
+    </row>
+    <row r="2321">
+      <c r="A2321" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B2321" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C2321" t="inlineStr">
+        <is>
+          <t>Block Inc. (fmr. Square)</t>
+        </is>
+      </c>
+      <c r="D2321" t="inlineStr">
+        <is>
+          <t>https://investors.block.xyz</t>
+        </is>
+      </c>
+      <c r="E2321" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+      <c r="F2321" t="inlineStr"/>
+      <c r="G2321" t="inlineStr"/>
+      <c r="H2321" t="inlineStr"/>
+    </row>
+    <row r="2322">
+      <c r="A2322" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B2322" t="inlineStr">
+        <is>
+          <t>PYPL</t>
+        </is>
+      </c>
+      <c r="C2322" t="inlineStr">
+        <is>
+          <t>PayPal Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D2322" t="inlineStr">
+        <is>
+          <t>https://www.paypal.com/us/legalhub/paypal/useragreement-full</t>
+        </is>
+      </c>
+      <c r="E2322" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+      <c r="F2322" t="inlineStr"/>
+      <c r="G2322" t="inlineStr"/>
+      <c r="H2322" t="inlineStr"/>
+    </row>
+    <row r="2323">
+      <c r="A2323" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B2323" t="inlineStr">
+        <is>
+          <t>TOST</t>
+        </is>
+      </c>
+      <c r="C2323" t="inlineStr">
+        <is>
+          <t>Toast Inc.</t>
+        </is>
+      </c>
+      <c r="D2323" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/toast</t>
+        </is>
+      </c>
+      <c r="E2323" t="inlineStr">
+        <is>
+          <t>8 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F2323" t="inlineStr"/>
+      <c r="G2323" t="inlineStr"/>
+      <c r="H2323" t="inlineStr"/>
+    </row>
+    <row r="2324">
+      <c r="A2324" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B2324" t="inlineStr">
+        <is>
+          <t>AFRM</t>
+        </is>
+      </c>
+      <c r="C2324" t="inlineStr">
+        <is>
+          <t>Affirm Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D2324" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/affirm</t>
+        </is>
+      </c>
+      <c r="E2324" t="inlineStr">
+        <is>
+          <t>5 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F2324" t="inlineStr"/>
+      <c r="G2324" t="inlineStr"/>
+      <c r="H2324" t="inlineStr"/>
+    </row>
+    <row r="2325">
+      <c r="A2325" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B2325" t="inlineStr">
+        <is>
+          <t>KLAR</t>
+        </is>
+      </c>
+      <c r="C2325" t="inlineStr">
+        <is>
+          <t>Klarna Group plc</t>
+        </is>
+      </c>
+      <c r="D2325" t="inlineStr">
+        <is>
+          <t>https://investors.klarna.com/governance/leadership/default.aspx</t>
+        </is>
+      </c>
+      <c r="E2325" t="inlineStr">
+        <is>
+          <t>management_team: change detected</t>
+        </is>
+      </c>
+      <c r="F2325" t="inlineStr"/>
+      <c r="G2325" t="inlineStr"/>
+      <c r="H2325" t="inlineStr"/>
+    </row>
+    <row r="2326">
+      <c r="A2326" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B2326" t="inlineStr">
+        <is>
+          <t>HOOD</t>
+        </is>
+      </c>
+      <c r="C2326" t="inlineStr">
+        <is>
+          <t>Robinhood Markets Inc.</t>
+        </is>
+      </c>
+      <c r="D2326" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/robinhood</t>
+        </is>
+      </c>
+      <c r="E2326" t="inlineStr">
+        <is>
+          <t>29 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F2326" t="inlineStr"/>
+      <c r="G2326" t="inlineStr"/>
+      <c r="H2326" t="inlineStr"/>
+    </row>
+    <row r="2327">
+      <c r="A2327" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B2327" t="inlineStr">
+        <is>
+          <t>UPST</t>
+        </is>
+      </c>
+      <c r="C2327" t="inlineStr">
+        <is>
+          <t>Upstart Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D2327" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/upstart</t>
+        </is>
+      </c>
+      <c r="E2327" t="inlineStr">
+        <is>
+          <t>1 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F2327" t="inlineStr"/>
+      <c r="G2327" t="inlineStr"/>
+      <c r="H2327" t="inlineStr"/>
+    </row>
+    <row r="2328">
+      <c r="A2328" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B2328" t="inlineStr">
+        <is>
+          <t>SGI</t>
+        </is>
+      </c>
+      <c r="C2328" t="inlineStr">
+        <is>
+          <t>Somnigroup International Inc. (fmr. Tempur Sealy)</t>
+        </is>
+      </c>
+      <c r="D2328" t="inlineStr">
+        <is>
+          <t>https://www.somnigroup.com/terms</t>
+        </is>
+      </c>
+      <c r="E2328" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+      <c r="F2328" t="inlineStr"/>
+      <c r="G2328" t="inlineStr"/>
+      <c r="H2328" t="inlineStr"/>
+    </row>
+    <row r="2329">
+      <c r="A2329" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B2329" t="inlineStr">
+        <is>
+          <t>SGI</t>
+        </is>
+      </c>
+      <c r="C2329" t="inlineStr">
+        <is>
+          <t>Somnigroup International Inc. (fmr. Tempur Sealy)</t>
+        </is>
+      </c>
+      <c r="D2329" t="inlineStr">
+        <is>
+          <t>https://www.somnigroup.com/news</t>
+        </is>
+      </c>
+      <c r="E2329" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F2329" t="inlineStr"/>
+      <c r="G2329" t="inlineStr"/>
+      <c r="H2329" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/config/company_urls_jc.xlsx
+++ b/config/company_urls_jc.xlsx
@@ -7203,7 +7203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2329"/>
+  <dimension ref="A1:H2404"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -69611,9 +69611,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F2313" t="inlineStr"/>
-      <c r="G2313" t="inlineStr"/>
-      <c r="H2313" t="inlineStr"/>
     </row>
     <row r="2314">
       <c r="A2314" t="inlineStr">
@@ -69641,9 +69638,6 @@
           <t>terms: change detected</t>
         </is>
       </c>
-      <c r="F2314" t="inlineStr"/>
-      <c r="G2314" t="inlineStr"/>
-      <c r="H2314" t="inlineStr"/>
     </row>
     <row r="2315">
       <c r="A2315" t="inlineStr">
@@ -69671,9 +69665,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F2315" t="inlineStr"/>
-      <c r="G2315" t="inlineStr"/>
-      <c r="H2315" t="inlineStr"/>
     </row>
     <row r="2316">
       <c r="A2316" t="inlineStr">
@@ -69701,9 +69692,6 @@
           <t>[UNKNOWN] Form S-3ASR</t>
         </is>
       </c>
-      <c r="F2316" t="inlineStr"/>
-      <c r="G2316" t="inlineStr"/>
-      <c r="H2316" t="inlineStr"/>
     </row>
     <row r="2317">
       <c r="A2317" t="inlineStr">
@@ -69731,9 +69719,6 @@
           <t>1 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F2317" t="inlineStr"/>
-      <c r="G2317" t="inlineStr"/>
-      <c r="H2317" t="inlineStr"/>
     </row>
     <row r="2318">
       <c r="A2318" t="inlineStr">
@@ -69761,9 +69746,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F2318" t="inlineStr"/>
-      <c r="G2318" t="inlineStr"/>
-      <c r="H2318" t="inlineStr"/>
     </row>
     <row r="2319">
       <c r="A2319" t="inlineStr">
@@ -69791,9 +69773,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F2319" t="inlineStr"/>
-      <c r="G2319" t="inlineStr"/>
-      <c r="H2319" t="inlineStr"/>
     </row>
     <row r="2320">
       <c r="A2320" t="inlineStr">
@@ -69821,9 +69800,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F2320" t="inlineStr"/>
-      <c r="G2320" t="inlineStr"/>
-      <c r="H2320" t="inlineStr"/>
     </row>
     <row r="2321">
       <c r="A2321" t="inlineStr">
@@ -69851,9 +69827,6 @@
           <t>investor_relations: change detected</t>
         </is>
       </c>
-      <c r="F2321" t="inlineStr"/>
-      <c r="G2321" t="inlineStr"/>
-      <c r="H2321" t="inlineStr"/>
     </row>
     <row r="2322">
       <c r="A2322" t="inlineStr">
@@ -69881,9 +69854,6 @@
           <t>terms: change detected</t>
         </is>
       </c>
-      <c r="F2322" t="inlineStr"/>
-      <c r="G2322" t="inlineStr"/>
-      <c r="H2322" t="inlineStr"/>
     </row>
     <row r="2323">
       <c r="A2323" t="inlineStr">
@@ -69911,9 +69881,6 @@
           <t>8 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F2323" t="inlineStr"/>
-      <c r="G2323" t="inlineStr"/>
-      <c r="H2323" t="inlineStr"/>
     </row>
     <row r="2324">
       <c r="A2324" t="inlineStr">
@@ -69941,9 +69908,6 @@
           <t>5 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F2324" t="inlineStr"/>
-      <c r="G2324" t="inlineStr"/>
-      <c r="H2324" t="inlineStr"/>
     </row>
     <row r="2325">
       <c r="A2325" t="inlineStr">
@@ -69971,9 +69935,6 @@
           <t>management_team: change detected</t>
         </is>
       </c>
-      <c r="F2325" t="inlineStr"/>
-      <c r="G2325" t="inlineStr"/>
-      <c r="H2325" t="inlineStr"/>
     </row>
     <row r="2326">
       <c r="A2326" t="inlineStr">
@@ -70001,9 +69962,6 @@
           <t>29 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F2326" t="inlineStr"/>
-      <c r="G2326" t="inlineStr"/>
-      <c r="H2326" t="inlineStr"/>
     </row>
     <row r="2327">
       <c r="A2327" t="inlineStr">
@@ -70031,9 +69989,6 @@
           <t>1 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F2327" t="inlineStr"/>
-      <c r="G2327" t="inlineStr"/>
-      <c r="H2327" t="inlineStr"/>
     </row>
     <row r="2328">
       <c r="A2328" t="inlineStr">
@@ -70061,9 +70016,6 @@
           <t>terms: change detected</t>
         </is>
       </c>
-      <c r="F2328" t="inlineStr"/>
-      <c r="G2328" t="inlineStr"/>
-      <c r="H2328" t="inlineStr"/>
     </row>
     <row r="2329">
       <c r="A2329" t="inlineStr">
@@ -70091,9 +70043,2118 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F2329" t="inlineStr"/>
-      <c r="G2329" t="inlineStr"/>
-      <c r="H2329" t="inlineStr"/>
+    </row>
+    <row r="2330">
+      <c r="A2330" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B2330" t="inlineStr">
+        <is>
+          <t>LOGI</t>
+        </is>
+      </c>
+      <c r="C2330" t="inlineStr">
+        <is>
+          <t>Logitech International S.A.</t>
+        </is>
+      </c>
+      <c r="D2330" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1032975/000147522326000004/xslF345X06/form4-09142026_090946.xml</t>
+        </is>
+      </c>
+      <c r="E2330" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Harnett Samantha (CHIEF LEGAL OFFICER) sold 16,265 shares @ $101.35 ($1.65M) on 2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="2331">
+      <c r="A2331" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B2331" t="inlineStr">
+        <is>
+          <t>EXPE</t>
+        </is>
+      </c>
+      <c r="C2331" t="inlineStr">
+        <is>
+          <t>Expedia Group, Inc.</t>
+        </is>
+      </c>
+      <c r="D2331" t="inlineStr">
+        <is>
+          <t>https://careers.expediagroup.com</t>
+        </is>
+      </c>
+      <c r="E2331" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2332">
+      <c r="A2332" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B2332" t="inlineStr">
+        <is>
+          <t>BKNG</t>
+        </is>
+      </c>
+      <c r="C2332" t="inlineStr">
+        <is>
+          <t>Booking Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D2332" t="inlineStr">
+        <is>
+          <t>https://www.bookingholdings.com/careers</t>
+        </is>
+      </c>
+      <c r="E2332" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2333">
+      <c r="A2333" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B2333" t="inlineStr">
+        <is>
+          <t>ABNB</t>
+        </is>
+      </c>
+      <c r="C2333" t="inlineStr">
+        <is>
+          <t>Airbnb, Inc.</t>
+        </is>
+      </c>
+      <c r="D2333" t="inlineStr">
+        <is>
+          <t>https://careers.airbnb.com</t>
+        </is>
+      </c>
+      <c r="E2333" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2334">
+      <c r="A2334" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B2334" t="inlineStr">
+        <is>
+          <t>ABNB</t>
+        </is>
+      </c>
+      <c r="C2334" t="inlineStr">
+        <is>
+          <t>Airbnb, Inc.</t>
+        </is>
+      </c>
+      <c r="D2334" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1559720/000195917326006965/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E2334" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Bernstein David C (Officer) plans to sell 1,489 shares (~$251.5K) on/after 09/15/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2335">
+      <c r="A2335" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B2335" t="inlineStr">
+        <is>
+          <t>ABNB</t>
+        </is>
+      </c>
+      <c r="C2335" t="inlineStr">
+        <is>
+          <t>Airbnb, Inc.</t>
+        </is>
+      </c>
+      <c r="D2335" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1559720/000195917326006951/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E2335" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Blecharczyk Nathan (Officer) plans to sell 13,615 shares (~$2.35M) on/after 09/14/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2336">
+      <c r="A2336" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B2336" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="C2336" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="D2336" t="inlineStr">
+        <is>
+          <t>https://investor.atmeta.com</t>
+        </is>
+      </c>
+      <c r="E2336" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2337">
+      <c r="A2337" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B2337" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="C2337" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="D2337" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1326801/000192109426001013/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E2337" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Olivan Javier (Officer) plans to sell 1,575 shares (~$1.04M) on/after 09/14/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2338">
+      <c r="A2338" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B2338" t="inlineStr">
+        <is>
+          <t>PINS</t>
+        </is>
+      </c>
+      <c r="C2338" t="inlineStr">
+        <is>
+          <t>Pinterest, Inc.</t>
+        </is>
+      </c>
+      <c r="D2338" t="inlineStr">
+        <is>
+          <t>https://newsroom.pinterest.com</t>
+        </is>
+      </c>
+      <c r="E2338" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2339">
+      <c r="A2339" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B2339" t="inlineStr">
+        <is>
+          <t>PINS</t>
+        </is>
+      </c>
+      <c r="C2339" t="inlineStr">
+        <is>
+          <t>Pinterest, Inc.</t>
+        </is>
+      </c>
+      <c r="D2339" t="inlineStr">
+        <is>
+          <t>https://www.pinterestcareers.com</t>
+        </is>
+      </c>
+      <c r="E2339" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2340">
+      <c r="A2340" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B2340" t="inlineStr">
+        <is>
+          <t>RDDT</t>
+        </is>
+      </c>
+      <c r="C2340" t="inlineStr">
+        <is>
+          <t>Reddit, Inc.</t>
+        </is>
+      </c>
+      <c r="D2340" t="inlineStr">
+        <is>
+          <t>https://redditinc.com/careers</t>
+        </is>
+      </c>
+      <c r="E2340" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2341">
+      <c r="A2341" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B2341" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="C2341" t="inlineStr">
+        <is>
+          <t>Unity Software Inc.</t>
+        </is>
+      </c>
+      <c r="D2341" t="inlineStr">
+        <is>
+          <t>https://careers.unity.com</t>
+        </is>
+      </c>
+      <c r="E2341" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2342">
+      <c r="A2342" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B2342" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="C2342" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="D2342" t="inlineStr">
+        <is>
+          <t>https://about.netflix.com/newsroom</t>
+        </is>
+      </c>
+      <c r="E2342" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2343">
+      <c r="A2343" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B2343" t="inlineStr">
+        <is>
+          <t>SPOT</t>
+        </is>
+      </c>
+      <c r="C2343" t="inlineStr">
+        <is>
+          <t>Spotify Technology S.A.</t>
+        </is>
+      </c>
+      <c r="D2343" t="inlineStr">
+        <is>
+          <t>https://www.spotify.com/premium</t>
+        </is>
+      </c>
+      <c r="E2343" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2344">
+      <c r="A2344" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B2344" t="inlineStr">
+        <is>
+          <t>SPOT</t>
+        </is>
+      </c>
+      <c r="C2344" t="inlineStr">
+        <is>
+          <t>Spotify Technology S.A.</t>
+        </is>
+      </c>
+      <c r="D2344" t="inlineStr">
+        <is>
+          <t>https://newsroom.spotify.com</t>
+        </is>
+      </c>
+      <c r="E2344" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2345">
+      <c r="A2345" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B2345" t="inlineStr">
+        <is>
+          <t>SPOT</t>
+        </is>
+      </c>
+      <c r="C2345" t="inlineStr">
+        <is>
+          <t>Spotify Technology S.A.</t>
+        </is>
+      </c>
+      <c r="D2345" t="inlineStr">
+        <is>
+          <t>https://www.lifeatspotify.com</t>
+        </is>
+      </c>
+      <c r="E2345" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2346">
+      <c r="A2346" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B2346" t="inlineStr">
+        <is>
+          <t>SPOT</t>
+        </is>
+      </c>
+      <c r="C2346" t="inlineStr">
+        <is>
+          <t>Spotify Technology S.A.</t>
+        </is>
+      </c>
+      <c r="D2346" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1639920/000195824426000596/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E2346" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Stig Gustav Victor Soderstrom (Officer) plans to sell 83,643 shares (~$46.53M) on/after 09/14/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2347">
+      <c r="A2347" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B2347" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="C2347" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="D2347" t="inlineStr">
+        <is>
+          <t>https://www.disneyplus.com/welcome</t>
+        </is>
+      </c>
+      <c r="E2347" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2348">
+      <c r="A2348" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B2348" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="C2348" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="D2348" t="inlineStr">
+        <is>
+          <t>https://thewaltdisneycompany.com/news/</t>
+        </is>
+      </c>
+      <c r="E2348" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2349">
+      <c r="A2349" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B2349" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="C2349" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="D2349" t="inlineStr">
+        <is>
+          <t>https://jobs.disneycareers.com</t>
+        </is>
+      </c>
+      <c r="E2349" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2350">
+      <c r="A2350" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B2350" t="inlineStr">
+        <is>
+          <t>FOXA</t>
+        </is>
+      </c>
+      <c r="C2350" t="inlineStr">
+        <is>
+          <t>Fox Corporation</t>
+        </is>
+      </c>
+      <c r="D2350" t="inlineStr">
+        <is>
+          <t>https://foxcareers.com</t>
+        </is>
+      </c>
+      <c r="E2350" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2351">
+      <c r="A2351" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B2351" t="inlineStr">
+        <is>
+          <t>WMG</t>
+        </is>
+      </c>
+      <c r="C2351" t="inlineStr">
+        <is>
+          <t>Warner Music Group Corp.</t>
+        </is>
+      </c>
+      <c r="D2351" t="inlineStr">
+        <is>
+          <t>https://www.wmg.com/news/</t>
+        </is>
+      </c>
+      <c r="E2351" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2352">
+      <c r="A2352" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B2352" t="inlineStr">
+        <is>
+          <t>LYV</t>
+        </is>
+      </c>
+      <c r="C2352" t="inlineStr">
+        <is>
+          <t>Live Nation Entertainment, Inc.</t>
+        </is>
+      </c>
+      <c r="D2352" t="inlineStr">
+        <is>
+          <t>https://www.livenationentertainment.com/careers</t>
+        </is>
+      </c>
+      <c r="E2352" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2353">
+      <c r="A2353" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B2353" t="inlineStr">
+        <is>
+          <t>STUB</t>
+        </is>
+      </c>
+      <c r="C2353" t="inlineStr">
+        <is>
+          <t>StubHub Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="D2353" t="inlineStr">
+        <is>
+          <t>https://www.stubhub.com/careers/</t>
+        </is>
+      </c>
+      <c r="E2353" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2354">
+      <c r="A2354" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B2354" t="inlineStr">
+        <is>
+          <t>LAMR</t>
+        </is>
+      </c>
+      <c r="C2354" t="inlineStr">
+        <is>
+          <t>Lamar Advertising Company</t>
+        </is>
+      </c>
+      <c r="D2354" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1090425/000196858226000968/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E2354" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Thomas V.  Reifenheiser (Director) plans to sell 8,099 shares (~$1.21M) on/after 09/14/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2355">
+      <c r="A2355" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B2355" t="inlineStr">
+        <is>
+          <t>TTWO</t>
+        </is>
+      </c>
+      <c r="C2355" t="inlineStr">
+        <is>
+          <t>Take-Two Interactive Software, Inc.</t>
+        </is>
+      </c>
+      <c r="D2355" t="inlineStr">
+        <is>
+          <t>https://ir.take2games.com</t>
+        </is>
+      </c>
+      <c r="E2355" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2356">
+      <c r="A2356" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B2356" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="C2356" t="inlineStr">
+        <is>
+          <t>Electronic Arts Inc.</t>
+        </is>
+      </c>
+      <c r="D2356" t="inlineStr">
+        <is>
+          <t>https://www.ea.com/news</t>
+        </is>
+      </c>
+      <c r="E2356" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2357">
+      <c r="A2357" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B2357" t="inlineStr">
+        <is>
+          <t>ADP</t>
+        </is>
+      </c>
+      <c r="C2357" t="inlineStr">
+        <is>
+          <t>Automatic Data Processing, Inc.</t>
+        </is>
+      </c>
+      <c r="D2357" t="inlineStr">
+        <is>
+          <t>https://mediacenter.adp.com</t>
+        </is>
+      </c>
+      <c r="E2357" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2358">
+      <c r="A2358" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B2358" t="inlineStr">
+        <is>
+          <t>PAYX</t>
+        </is>
+      </c>
+      <c r="C2358" t="inlineStr">
+        <is>
+          <t>Paychex, Inc.</t>
+        </is>
+      </c>
+      <c r="D2358" t="inlineStr">
+        <is>
+          <t>https://www.paychex.com/newsroom</t>
+        </is>
+      </c>
+      <c r="E2358" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2359">
+      <c r="A2359" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B2359" t="inlineStr">
+        <is>
+          <t>CDW</t>
+        </is>
+      </c>
+      <c r="C2359" t="inlineStr">
+        <is>
+          <t>CDW Corporation</t>
+        </is>
+      </c>
+      <c r="D2359" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1402057/000119312526390802/d108370dfwp.htm</t>
+        </is>
+      </c>
+      <c r="E2359" t="inlineStr">
+        <is>
+          <t>[UNKNOWN] Form FWP</t>
+        </is>
+      </c>
+    </row>
+    <row r="2360">
+      <c r="A2360" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B2360" t="inlineStr">
+        <is>
+          <t>CDW</t>
+        </is>
+      </c>
+      <c r="C2360" t="inlineStr">
+        <is>
+          <t>CDW Corporation</t>
+        </is>
+      </c>
+      <c r="D2360" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1402057/000140205726000102/xslF345X06/wk-form4_1789416744.xml</t>
+        </is>
+      </c>
+      <c r="E2360" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Jones Marc Ellis (Director) granted 20 Common Stock, par value $0.01 on 2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="2361">
+      <c r="A2361" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B2361" t="inlineStr">
+        <is>
+          <t>CDW</t>
+        </is>
+      </c>
+      <c r="C2361" t="inlineStr">
+        <is>
+          <t>CDW Corporation</t>
+        </is>
+      </c>
+      <c r="D2361" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1402057/000140205726000101/xslF345X06/wk-form4_1789416739.xml</t>
+        </is>
+      </c>
+      <c r="E2361" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — David W Nelms (Director) granted 148 Common Stock, par value $0.01 on 2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="2362">
+      <c r="A2362" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B2362" t="inlineStr">
+        <is>
+          <t>CDW</t>
+        </is>
+      </c>
+      <c r="C2362" t="inlineStr">
+        <is>
+          <t>CDW Corporation</t>
+        </is>
+      </c>
+      <c r="D2362" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1402057/000140205726000100/xslF345X06/wk-form4_1789416732.xml</t>
+        </is>
+      </c>
+      <c r="E2362" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Kumar Mukesh (See Remarks) granted 192 Common Stock, par value $0.01 on 2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="2363">
+      <c r="A2363" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B2363" t="inlineStr">
+        <is>
+          <t>CDW</t>
+        </is>
+      </c>
+      <c r="C2363" t="inlineStr">
+        <is>
+          <t>CDW Corporation</t>
+        </is>
+      </c>
+      <c r="D2363" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1402057/000140205726000099/xslF345X06/wk-form4_1789416724.xml</t>
+        </is>
+      </c>
+      <c r="E2363" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Virginia C. Addicott (Director) granted 82 Common Stock, par value $0.01 on 2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="2364">
+      <c r="A2364" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B2364" t="inlineStr">
+        <is>
+          <t>CDW</t>
+        </is>
+      </c>
+      <c r="C2364" t="inlineStr">
+        <is>
+          <t>CDW Corporation</t>
+        </is>
+      </c>
+      <c r="D2364" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1402057/000140205726000098/xslF345X06/wk-form4_1789416716.xml</t>
+        </is>
+      </c>
+      <c r="E2364" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Sanderson Katherine Elizabeth (See Remarks) granted 243 Common Stock, par value $0.01 on 2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="2365">
+      <c r="A2365" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B2365" t="inlineStr">
+        <is>
+          <t>CDW</t>
+        </is>
+      </c>
+      <c r="C2365" t="inlineStr">
+        <is>
+          <t>CDW Corporation</t>
+        </is>
+      </c>
+      <c r="D2365" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1402057/000140205726000097/xslF345X06/wk-form4_1789416709.xml</t>
+        </is>
+      </c>
+      <c r="E2365" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Frederick J. Kulevich (See Remarks) granted 185 Common Stock, par value $0.01 on 2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="2366">
+      <c r="A2366" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B2366" t="inlineStr">
+        <is>
+          <t>CDW</t>
+        </is>
+      </c>
+      <c r="C2366" t="inlineStr">
+        <is>
+          <t>CDW Corporation</t>
+        </is>
+      </c>
+      <c r="D2366" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1402057/000140205726000096/xslF345X06/wk-form4_1789416701.xml</t>
+        </is>
+      </c>
+      <c r="E2366" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Lynda M Clarizio (Director) granted 7 Common Stock, par value $0.01 on 2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="2367">
+      <c r="A2367" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B2367" t="inlineStr">
+        <is>
+          <t>CDW</t>
+        </is>
+      </c>
+      <c r="C2367" t="inlineStr">
+        <is>
+          <t>CDW Corporation</t>
+        </is>
+      </c>
+      <c r="D2367" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1402057/000140205726000095/xslF345X06/wk-form4_1789416693.xml</t>
+        </is>
+      </c>
+      <c r="E2367" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Hang Tan (See Remarks) granted 213 Common Stock, par value $0.01 on 2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="2368">
+      <c r="A2368" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B2368" t="inlineStr">
+        <is>
+          <t>CDW</t>
+        </is>
+      </c>
+      <c r="C2368" t="inlineStr">
+        <is>
+          <t>CDW Corporation</t>
+        </is>
+      </c>
+      <c r="D2368" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1402057/000140205726000094/xslF345X06/wk-form4_1789416685.xml</t>
+        </is>
+      </c>
+      <c r="E2368" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Foxx Anthony R (Director) granted 30 Common Stock, par value $0.01 on 2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="2369">
+      <c r="A2369" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B2369" t="inlineStr">
+        <is>
+          <t>CDW</t>
+        </is>
+      </c>
+      <c r="C2369" t="inlineStr">
+        <is>
+          <t>CDW Corporation</t>
+        </is>
+      </c>
+      <c r="D2369" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1402057/000140205726000093/xslF345X06/wk-form4_1789416680.xml</t>
+        </is>
+      </c>
+      <c r="E2369" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Albert Joseph Jr Miralles (See Remarks) granted 299 Common Stock, par value $0.01 on 2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="2370">
+      <c r="A2370" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B2370" t="inlineStr">
+        <is>
+          <t>CDW</t>
+        </is>
+      </c>
+      <c r="C2370" t="inlineStr">
+        <is>
+          <t>CDW Corporation</t>
+        </is>
+      </c>
+      <c r="D2370" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1402057/000140205726000092/xslF345X06/wk-form4_1789416671.xml</t>
+        </is>
+      </c>
+      <c r="E2370" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Peter R Locy (See Remarks) granted 29 Common Stock, par value $0.01 on 2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="2371">
+      <c r="A2371" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B2371" t="inlineStr">
+        <is>
+          <t>CDW</t>
+        </is>
+      </c>
+      <c r="C2371" t="inlineStr">
+        <is>
+          <t>CDW Corporation</t>
+        </is>
+      </c>
+      <c r="D2371" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1402057/000140205726000091/xslF345X06/wk-form4_1789416665.xml</t>
+        </is>
+      </c>
+      <c r="E2371" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Christine A Leahy (See Remarks) granted 825 Common Stock, par value $0.01 on 2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="2372">
+      <c r="A2372" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B2372" t="inlineStr">
+        <is>
+          <t>CDW</t>
+        </is>
+      </c>
+      <c r="C2372" t="inlineStr">
+        <is>
+          <t>CDW Corporation</t>
+        </is>
+      </c>
+      <c r="D2372" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1402057/000140205726000090/xslF345X06/wk-form4_1789416660.xml</t>
+        </is>
+      </c>
+      <c r="E2372" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Swedish Joseph (Director) granted 29 Common Stock, par value $0.01 on 2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="2373">
+      <c r="A2373" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B2373" t="inlineStr">
+        <is>
+          <t>CDW</t>
+        </is>
+      </c>
+      <c r="C2373" t="inlineStr">
+        <is>
+          <t>CDW Corporation</t>
+        </is>
+      </c>
+      <c r="D2373" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1402057/000140205726000089/xslF345X06/wk-form4_1789416654.xml</t>
+        </is>
+      </c>
+      <c r="E2373" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Grier Kelly J (Director) granted 7 Common Stock, par value $0.01 on 2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="2374">
+      <c r="A2374" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B2374" t="inlineStr">
+        <is>
+          <t>CDW</t>
+        </is>
+      </c>
+      <c r="C2374" t="inlineStr">
+        <is>
+          <t>CDW Corporation</t>
+        </is>
+      </c>
+      <c r="D2374" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1402057/000140205726000088/xslF345X06/wk-form4_1789416648.xml</t>
+        </is>
+      </c>
+      <c r="E2374" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Elizabeth H. Connelly (See Remarks) granted 238 Common Stock, par value $0.01 on 2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="2375">
+      <c r="A2375" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B2375" t="inlineStr">
+        <is>
+          <t>CDW</t>
+        </is>
+      </c>
+      <c r="C2375" t="inlineStr">
+        <is>
+          <t>CDW Corporation</t>
+        </is>
+      </c>
+      <c r="D2375" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1402057/000140205726000087/xslF345X06/wk-form4_1789416642.xml</t>
+        </is>
+      </c>
+      <c r="E2375" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — James A Bell (Director) granted 96 Common Stock, par value $0.01 on 2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="2376">
+      <c r="A2376" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B2376" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C2376" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D2376" t="inlineStr">
+        <is>
+          <t>https://www.shopify.com/pricing</t>
+        </is>
+      </c>
+      <c r="E2376" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+      <c r="F2376" t="inlineStr"/>
+      <c r="G2376" t="inlineStr"/>
+      <c r="H2376" t="inlineStr"/>
+    </row>
+    <row r="2377">
+      <c r="A2377" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B2377" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C2377" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D2377" t="inlineStr">
+        <is>
+          <t>https://www.shopify.com/careers</t>
+        </is>
+      </c>
+      <c r="E2377" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F2377" t="inlineStr"/>
+      <c r="G2377" t="inlineStr"/>
+      <c r="H2377" t="inlineStr"/>
+    </row>
+    <row r="2378">
+      <c r="A2378" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B2378" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C2378" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D2378" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1594805/000195004726009436/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E2378" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Hoffmeister Jeff (Officer) plans to sell 11,647 shares (~$1.50M) on/after 09/14/2026</t>
+        </is>
+      </c>
+      <c r="F2378" t="inlineStr"/>
+      <c r="G2378" t="inlineStr"/>
+      <c r="H2378" t="inlineStr"/>
+    </row>
+    <row r="2379">
+      <c r="A2379" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B2379" t="inlineStr">
+        <is>
+          <t>WIX</t>
+        </is>
+      </c>
+      <c r="C2379" t="inlineStr">
+        <is>
+          <t>Wix.com Ltd.</t>
+        </is>
+      </c>
+      <c r="D2379" t="inlineStr">
+        <is>
+          <t>https://www.wix.com/press-room/home/post/wix-releases-latest-esg-report-1</t>
+        </is>
+      </c>
+      <c r="E2379" t="inlineStr">
+        <is>
+          <t>newsroom: Wix Releases Latest ESG Report</t>
+        </is>
+      </c>
+      <c r="F2379" t="inlineStr"/>
+      <c r="G2379" t="inlineStr"/>
+      <c r="H2379" t="inlineStr"/>
+    </row>
+    <row r="2380">
+      <c r="A2380" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B2380" t="inlineStr">
+        <is>
+          <t>GLBE</t>
+        </is>
+      </c>
+      <c r="C2380" t="inlineStr">
+        <is>
+          <t>Global-E Online Ltd.</t>
+        </is>
+      </c>
+      <c r="D2380" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1835963/000195004726009443/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E2380" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Koren Ofer (Officer) plans to sell 12,500 shares (~$464.8K) on/after 09/14/2026</t>
+        </is>
+      </c>
+      <c r="F2380" t="inlineStr"/>
+      <c r="G2380" t="inlineStr"/>
+      <c r="H2380" t="inlineStr"/>
+    </row>
+    <row r="2381">
+      <c r="A2381" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B2381" t="inlineStr">
+        <is>
+          <t>GLBE</t>
+        </is>
+      </c>
+      <c r="C2381" t="inlineStr">
+        <is>
+          <t>Global-E Online Ltd.</t>
+        </is>
+      </c>
+      <c r="D2381" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1835963/000119312526390620/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E2381" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Koren Ofer (CFO) sold 12,500 shares @ $36.68 ($458.4K) on 2026-09-08</t>
+        </is>
+      </c>
+      <c r="F2381" t="inlineStr"/>
+      <c r="G2381" t="inlineStr"/>
+      <c r="H2381" t="inlineStr"/>
+    </row>
+    <row r="2382">
+      <c r="A2382" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B2382" t="inlineStr">
+        <is>
+          <t>EBAY</t>
+        </is>
+      </c>
+      <c r="C2382" t="inlineStr">
+        <is>
+          <t>eBay Inc.</t>
+        </is>
+      </c>
+      <c r="D2382" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/help/policies/member-behaviour-policies/user-agreement?id=4259</t>
+        </is>
+      </c>
+      <c r="E2382" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+      <c r="F2382" t="inlineStr"/>
+      <c r="G2382" t="inlineStr"/>
+      <c r="H2382" t="inlineStr"/>
+    </row>
+    <row r="2383">
+      <c r="A2383" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B2383" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="C2383" t="inlineStr">
+        <is>
+          <t>Wayfair Inc.</t>
+        </is>
+      </c>
+      <c r="D2383" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1616707/000195917326006949/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E2383" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Shah Niraj (Officer) plans to sell 69,000 shares (~$7.13M) on/after 09/14/2026</t>
+        </is>
+      </c>
+      <c r="F2383" t="inlineStr"/>
+      <c r="G2383" t="inlineStr"/>
+      <c r="H2383" t="inlineStr"/>
+    </row>
+    <row r="2384">
+      <c r="A2384" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B2384" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="C2384" t="inlineStr">
+        <is>
+          <t>Wayfair Inc.</t>
+        </is>
+      </c>
+      <c r="D2384" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1616707/000195917326006948/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E2384" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Conine Steven (Officer) plans to sell 69,000 shares (~$7.13M) on/after 09/14/2026</t>
+        </is>
+      </c>
+      <c r="F2384" t="inlineStr"/>
+      <c r="G2384" t="inlineStr"/>
+      <c r="H2384" t="inlineStr"/>
+    </row>
+    <row r="2385">
+      <c r="A2385" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B2385" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="C2385" t="inlineStr">
+        <is>
+          <t>Wayfair Inc.</t>
+        </is>
+      </c>
+      <c r="D2385" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1616707/000195917326006925/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E2385" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Shah Niraj (Officer) plans to sell 1,000 shares (~$100.0K) on/after 09/14/2026</t>
+        </is>
+      </c>
+      <c r="F2385" t="inlineStr"/>
+      <c r="G2385" t="inlineStr"/>
+      <c r="H2385" t="inlineStr"/>
+    </row>
+    <row r="2386">
+      <c r="A2386" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B2386" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="C2386" t="inlineStr">
+        <is>
+          <t>Wayfair Inc.</t>
+        </is>
+      </c>
+      <c r="D2386" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1616707/000195917326006923/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E2386" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Conine Steven (Officer) plans to sell 1,000 shares (~$100.0K) on/after 09/14/2026</t>
+        </is>
+      </c>
+      <c r="F2386" t="inlineStr"/>
+      <c r="G2386" t="inlineStr"/>
+      <c r="H2386" t="inlineStr"/>
+    </row>
+    <row r="2387">
+      <c r="A2387" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B2387" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C2387" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D2387" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/instacart</t>
+        </is>
+      </c>
+      <c r="E2387" t="inlineStr">
+        <is>
+          <t>5 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F2387" t="inlineStr"/>
+      <c r="G2387" t="inlineStr"/>
+      <c r="H2387" t="inlineStr"/>
+    </row>
+    <row r="2388">
+      <c r="A2388" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B2388" t="inlineStr">
+        <is>
+          <t>DUOL</t>
+        </is>
+      </c>
+      <c r="C2388" t="inlineStr">
+        <is>
+          <t>Duolingo Inc.</t>
+        </is>
+      </c>
+      <c r="D2388" t="inlineStr">
+        <is>
+          <t>https://blog.duolingo.com/</t>
+        </is>
+      </c>
+      <c r="E2388" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F2388" t="inlineStr"/>
+      <c r="G2388" t="inlineStr"/>
+      <c r="H2388" t="inlineStr"/>
+    </row>
+    <row r="2389">
+      <c r="A2389" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B2389" t="inlineStr">
+        <is>
+          <t>DUOL</t>
+        </is>
+      </c>
+      <c r="C2389" t="inlineStr">
+        <is>
+          <t>Duolingo Inc.</t>
+        </is>
+      </c>
+      <c r="D2389" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1562088/000195004726009429/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E2389" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Chen Stephen (Officer) plans to sell 8,072 shares (~$1.16M) on/after 09/14/2026</t>
+        </is>
+      </c>
+      <c r="F2389" t="inlineStr"/>
+      <c r="G2389" t="inlineStr"/>
+      <c r="H2389" t="inlineStr"/>
+    </row>
+    <row r="2390">
+      <c r="A2390" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B2390" t="inlineStr">
+        <is>
+          <t>COMP</t>
+        </is>
+      </c>
+      <c r="C2390" t="inlineStr">
+        <is>
+          <t>Compass Inc.</t>
+        </is>
+      </c>
+      <c r="D2390" t="inlineStr">
+        <is>
+          <t>https://www.compass.com/careers/</t>
+        </is>
+      </c>
+      <c r="E2390" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F2390" t="inlineStr"/>
+      <c r="G2390" t="inlineStr"/>
+      <c r="H2390" t="inlineStr"/>
+    </row>
+    <row r="2391">
+      <c r="A2391" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B2391" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C2391" t="inlineStr">
+        <is>
+          <t>Block Inc. (fmr. Square)</t>
+        </is>
+      </c>
+      <c r="D2391" t="inlineStr">
+        <is>
+          <t>https://squareup.com/us/en/legal/general/ua</t>
+        </is>
+      </c>
+      <c r="E2391" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+      <c r="F2391" t="inlineStr"/>
+      <c r="G2391" t="inlineStr"/>
+      <c r="H2391" t="inlineStr"/>
+    </row>
+    <row r="2392">
+      <c r="A2392" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B2392" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C2392" t="inlineStr">
+        <is>
+          <t>Block Inc. (fmr. Square)</t>
+        </is>
+      </c>
+      <c r="D2392" t="inlineStr">
+        <is>
+          <t>https://investors.block.xyz</t>
+        </is>
+      </c>
+      <c r="E2392" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+      <c r="F2392" t="inlineStr"/>
+      <c r="G2392" t="inlineStr"/>
+      <c r="H2392" t="inlineStr"/>
+    </row>
+    <row r="2393">
+      <c r="A2393" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B2393" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C2393" t="inlineStr">
+        <is>
+          <t>Block Inc. (fmr. Square)</t>
+        </is>
+      </c>
+      <c r="D2393" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1512673/000195004726009420/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E2393" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — M Eisen Anthony (Director) plans to sell 6,000 shares (~$473.8K) on/after 09/14/2026</t>
+        </is>
+      </c>
+      <c r="F2393" t="inlineStr"/>
+      <c r="G2393" t="inlineStr"/>
+      <c r="H2393" t="inlineStr"/>
+    </row>
+    <row r="2394">
+      <c r="A2394" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B2394" t="inlineStr">
+        <is>
+          <t>TOST</t>
+        </is>
+      </c>
+      <c r="C2394" t="inlineStr">
+        <is>
+          <t>Toast Inc.</t>
+        </is>
+      </c>
+      <c r="D2394" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/toast</t>
+        </is>
+      </c>
+      <c r="E2394" t="inlineStr">
+        <is>
+          <t>5 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F2394" t="inlineStr"/>
+      <c r="G2394" t="inlineStr"/>
+      <c r="H2394" t="inlineStr"/>
+    </row>
+    <row r="2395">
+      <c r="A2395" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B2395" t="inlineStr">
+        <is>
+          <t>SEZL</t>
+        </is>
+      </c>
+      <c r="C2395" t="inlineStr">
+        <is>
+          <t>Sezzle Inc.</t>
+        </is>
+      </c>
+      <c r="D2395" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1662991/000166299126000156/xslF345X06/wk-form4_1789422445.xml</t>
+        </is>
+      </c>
+      <c r="E2395" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Youakim Charles (Executive Chairman and CEO) other: 1,508,454 Common Stock, par value $0.00001 per share on 2026-09-02</t>
+        </is>
+      </c>
+      <c r="F2395" t="inlineStr"/>
+      <c r="G2395" t="inlineStr"/>
+      <c r="H2395" t="inlineStr"/>
+    </row>
+    <row r="2396">
+      <c r="A2396" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B2396" t="inlineStr">
+        <is>
+          <t>SEZL</t>
+        </is>
+      </c>
+      <c r="C2396" t="inlineStr">
+        <is>
+          <t>Sezzle Inc.</t>
+        </is>
+      </c>
+      <c r="D2396" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1662991/000166299126000155/xslSCHEDULE_13D_X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E2396" t="inlineStr">
+        <is>
+          <t>[MATERIAL] Update to 5%+ active owner disclosure</t>
+        </is>
+      </c>
+      <c r="F2396" t="inlineStr"/>
+      <c r="G2396" t="inlineStr"/>
+      <c r="H2396" t="inlineStr"/>
+    </row>
+    <row r="2397">
+      <c r="A2397" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B2397" t="inlineStr">
+        <is>
+          <t>DAVE</t>
+        </is>
+      </c>
+      <c r="C2397" t="inlineStr">
+        <is>
+          <t>Dave Inc.</t>
+        </is>
+      </c>
+      <c r="D2397" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1841408/000119312526390839/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E2397" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Carroll Brendan (Director) sold 64,991 shares @ $1.60 ($103.7K) on 2026-09-10</t>
+        </is>
+      </c>
+      <c r="F2397" t="inlineStr"/>
+      <c r="G2397" t="inlineStr"/>
+      <c r="H2397" t="inlineStr"/>
+    </row>
+    <row r="2398">
+      <c r="A2398" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B2398" t="inlineStr">
+        <is>
+          <t>AFRM</t>
+        </is>
+      </c>
+      <c r="C2398" t="inlineStr">
+        <is>
+          <t>Affirm Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D2398" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/affirm</t>
+        </is>
+      </c>
+      <c r="E2398" t="inlineStr">
+        <is>
+          <t>1 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F2398" t="inlineStr"/>
+      <c r="G2398" t="inlineStr"/>
+      <c r="H2398" t="inlineStr"/>
+    </row>
+    <row r="2399">
+      <c r="A2399" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B2399" t="inlineStr">
+        <is>
+          <t>AFRM</t>
+        </is>
+      </c>
+      <c r="C2399" t="inlineStr">
+        <is>
+          <t>Affirm Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D2399" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1820953/000195004726009394/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E2399" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Jiyane Siphelele (Officer) plans to sell 26,980 shares (~$1.95M) on/after 09/14/2026</t>
+        </is>
+      </c>
+      <c r="F2399" t="inlineStr"/>
+      <c r="G2399" t="inlineStr"/>
+      <c r="H2399" t="inlineStr"/>
+    </row>
+    <row r="2400">
+      <c r="A2400" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B2400" t="inlineStr">
+        <is>
+          <t>HOOD</t>
+        </is>
+      </c>
+      <c r="C2400" t="inlineStr">
+        <is>
+          <t>Robinhood Markets Inc.</t>
+        </is>
+      </c>
+      <c r="D2400" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/robinhood</t>
+        </is>
+      </c>
+      <c r="E2400" t="inlineStr">
+        <is>
+          <t>4 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F2400" t="inlineStr"/>
+      <c r="G2400" t="inlineStr"/>
+      <c r="H2400" t="inlineStr"/>
+    </row>
+    <row r="2401">
+      <c r="A2401" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B2401" t="inlineStr">
+        <is>
+          <t>HOOD</t>
+        </is>
+      </c>
+      <c r="C2401" t="inlineStr">
+        <is>
+          <t>Robinhood Markets Inc.</t>
+        </is>
+      </c>
+      <c r="D2401" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1783879/000187091426000025/xslF345X06/wk-form4_1789417999.xml</t>
+        </is>
+      </c>
+      <c r="E2401" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Bhatt Baiju (Director) sold 43,373 shares @ $114.28 ($4.96M) on 2026-09-10</t>
+        </is>
+      </c>
+      <c r="F2401" t="inlineStr"/>
+      <c r="G2401" t="inlineStr"/>
+      <c r="H2401" t="inlineStr"/>
+    </row>
+    <row r="2402">
+      <c r="A2402" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B2402" t="inlineStr">
+        <is>
+          <t>UPST</t>
+        </is>
+      </c>
+      <c r="C2402" t="inlineStr">
+        <is>
+          <t>Upstart Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D2402" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/upstart</t>
+        </is>
+      </c>
+      <c r="E2402" t="inlineStr">
+        <is>
+          <t>2 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F2402" t="inlineStr"/>
+      <c r="G2402" t="inlineStr"/>
+      <c r="H2402" t="inlineStr"/>
+    </row>
+    <row r="2403">
+      <c r="A2403" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B2403" t="inlineStr">
+        <is>
+          <t>ENVA</t>
+        </is>
+      </c>
+      <c r="C2403" t="inlineStr">
+        <is>
+          <t>Enova International Inc.</t>
+        </is>
+      </c>
+      <c r="D2403" t="inlineStr">
+        <is>
+          <t>https://ir.enova.com</t>
+        </is>
+      </c>
+      <c r="E2403" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+      <c r="F2403" t="inlineStr"/>
+      <c r="G2403" t="inlineStr"/>
+      <c r="H2403" t="inlineStr"/>
+    </row>
+    <row r="2404">
+      <c r="A2404" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B2404" t="inlineStr">
+        <is>
+          <t>ENVA</t>
+        </is>
+      </c>
+      <c r="C2404" t="inlineStr">
+        <is>
+          <t>Enova International Inc.</t>
+        </is>
+      </c>
+      <c r="D2404" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1529864/000119312526390599/enva-20260914.htm</t>
+        </is>
+      </c>
+      <c r="E2404" t="inlineStr">
+        <is>
+          <t>[MATERIAL] Material event disclosure</t>
+        </is>
+      </c>
+      <c r="F2404" t="inlineStr"/>
+      <c r="G2404" t="inlineStr"/>
+      <c r="H2404" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/config/company_urls_jc.xlsx
+++ b/config/company_urls_jc.xlsx
@@ -7203,7 +7203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2404"/>
+  <dimension ref="A1:H2469"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -71312,9 +71312,6 @@
           <t>pricing: change detected</t>
         </is>
       </c>
-      <c r="F2376" t="inlineStr"/>
-      <c r="G2376" t="inlineStr"/>
-      <c r="H2376" t="inlineStr"/>
     </row>
     <row r="2377">
       <c r="A2377" t="inlineStr">
@@ -71342,9 +71339,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F2377" t="inlineStr"/>
-      <c r="G2377" t="inlineStr"/>
-      <c r="H2377" t="inlineStr"/>
     </row>
     <row r="2378">
       <c r="A2378" t="inlineStr">
@@ -71372,9 +71366,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Hoffmeister Jeff (Officer) plans to sell 11,647 shares (~$1.50M) on/after 09/14/2026</t>
         </is>
       </c>
-      <c r="F2378" t="inlineStr"/>
-      <c r="G2378" t="inlineStr"/>
-      <c r="H2378" t="inlineStr"/>
     </row>
     <row r="2379">
       <c r="A2379" t="inlineStr">
@@ -71402,9 +71393,6 @@
           <t>newsroom: Wix Releases Latest ESG Report</t>
         </is>
       </c>
-      <c r="F2379" t="inlineStr"/>
-      <c r="G2379" t="inlineStr"/>
-      <c r="H2379" t="inlineStr"/>
     </row>
     <row r="2380">
       <c r="A2380" t="inlineStr">
@@ -71432,9 +71420,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Koren Ofer (Officer) plans to sell 12,500 shares (~$464.8K) on/after 09/14/2026</t>
         </is>
       </c>
-      <c r="F2380" t="inlineStr"/>
-      <c r="G2380" t="inlineStr"/>
-      <c r="H2380" t="inlineStr"/>
     </row>
     <row r="2381">
       <c r="A2381" t="inlineStr">
@@ -71462,9 +71447,6 @@
           <t>[ROUTINE] Insider trade — Koren Ofer (CFO) sold 12,500 shares @ $36.68 ($458.4K) on 2026-09-08</t>
         </is>
       </c>
-      <c r="F2381" t="inlineStr"/>
-      <c r="G2381" t="inlineStr"/>
-      <c r="H2381" t="inlineStr"/>
     </row>
     <row r="2382">
       <c r="A2382" t="inlineStr">
@@ -71492,9 +71474,6 @@
           <t>terms: change detected</t>
         </is>
       </c>
-      <c r="F2382" t="inlineStr"/>
-      <c r="G2382" t="inlineStr"/>
-      <c r="H2382" t="inlineStr"/>
     </row>
     <row r="2383">
       <c r="A2383" t="inlineStr">
@@ -71522,9 +71501,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Shah Niraj (Officer) plans to sell 69,000 shares (~$7.13M) on/after 09/14/2026</t>
         </is>
       </c>
-      <c r="F2383" t="inlineStr"/>
-      <c r="G2383" t="inlineStr"/>
-      <c r="H2383" t="inlineStr"/>
     </row>
     <row r="2384">
       <c r="A2384" t="inlineStr">
@@ -71552,9 +71528,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Conine Steven (Officer) plans to sell 69,000 shares (~$7.13M) on/after 09/14/2026</t>
         </is>
       </c>
-      <c r="F2384" t="inlineStr"/>
-      <c r="G2384" t="inlineStr"/>
-      <c r="H2384" t="inlineStr"/>
     </row>
     <row r="2385">
       <c r="A2385" t="inlineStr">
@@ -71582,9 +71555,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Shah Niraj (Officer) plans to sell 1,000 shares (~$100.0K) on/after 09/14/2026</t>
         </is>
       </c>
-      <c r="F2385" t="inlineStr"/>
-      <c r="G2385" t="inlineStr"/>
-      <c r="H2385" t="inlineStr"/>
     </row>
     <row r="2386">
       <c r="A2386" t="inlineStr">
@@ -71612,9 +71582,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Conine Steven (Officer) plans to sell 1,000 shares (~$100.0K) on/after 09/14/2026</t>
         </is>
       </c>
-      <c r="F2386" t="inlineStr"/>
-      <c r="G2386" t="inlineStr"/>
-      <c r="H2386" t="inlineStr"/>
     </row>
     <row r="2387">
       <c r="A2387" t="inlineStr">
@@ -71642,9 +71609,6 @@
           <t>5 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F2387" t="inlineStr"/>
-      <c r="G2387" t="inlineStr"/>
-      <c r="H2387" t="inlineStr"/>
     </row>
     <row r="2388">
       <c r="A2388" t="inlineStr">
@@ -71672,9 +71636,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F2388" t="inlineStr"/>
-      <c r="G2388" t="inlineStr"/>
-      <c r="H2388" t="inlineStr"/>
     </row>
     <row r="2389">
       <c r="A2389" t="inlineStr">
@@ -71702,9 +71663,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Chen Stephen (Officer) plans to sell 8,072 shares (~$1.16M) on/after 09/14/2026</t>
         </is>
       </c>
-      <c r="F2389" t="inlineStr"/>
-      <c r="G2389" t="inlineStr"/>
-      <c r="H2389" t="inlineStr"/>
     </row>
     <row r="2390">
       <c r="A2390" t="inlineStr">
@@ -71732,9 +71690,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F2390" t="inlineStr"/>
-      <c r="G2390" t="inlineStr"/>
-      <c r="H2390" t="inlineStr"/>
     </row>
     <row r="2391">
       <c r="A2391" t="inlineStr">
@@ -71762,9 +71717,6 @@
           <t>terms: change detected</t>
         </is>
       </c>
-      <c r="F2391" t="inlineStr"/>
-      <c r="G2391" t="inlineStr"/>
-      <c r="H2391" t="inlineStr"/>
     </row>
     <row r="2392">
       <c r="A2392" t="inlineStr">
@@ -71792,9 +71744,6 @@
           <t>investor_relations: change detected</t>
         </is>
       </c>
-      <c r="F2392" t="inlineStr"/>
-      <c r="G2392" t="inlineStr"/>
-      <c r="H2392" t="inlineStr"/>
     </row>
     <row r="2393">
       <c r="A2393" t="inlineStr">
@@ -71822,9 +71771,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — M Eisen Anthony (Director) plans to sell 6,000 shares (~$473.8K) on/after 09/14/2026</t>
         </is>
       </c>
-      <c r="F2393" t="inlineStr"/>
-      <c r="G2393" t="inlineStr"/>
-      <c r="H2393" t="inlineStr"/>
     </row>
     <row r="2394">
       <c r="A2394" t="inlineStr">
@@ -71852,9 +71798,6 @@
           <t>5 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F2394" t="inlineStr"/>
-      <c r="G2394" t="inlineStr"/>
-      <c r="H2394" t="inlineStr"/>
     </row>
     <row r="2395">
       <c r="A2395" t="inlineStr">
@@ -71882,9 +71825,6 @@
           <t>[ROUTINE] Insider trade — Youakim Charles (Executive Chairman and CEO) other: 1,508,454 Common Stock, par value $0.00001 per share on 2026-09-02</t>
         </is>
       </c>
-      <c r="F2395" t="inlineStr"/>
-      <c r="G2395" t="inlineStr"/>
-      <c r="H2395" t="inlineStr"/>
     </row>
     <row r="2396">
       <c r="A2396" t="inlineStr">
@@ -71912,9 +71852,6 @@
           <t>[MATERIAL] Update to 5%+ active owner disclosure</t>
         </is>
       </c>
-      <c r="F2396" t="inlineStr"/>
-      <c r="G2396" t="inlineStr"/>
-      <c r="H2396" t="inlineStr"/>
     </row>
     <row r="2397">
       <c r="A2397" t="inlineStr">
@@ -71942,9 +71879,6 @@
           <t>[ROUTINE] Insider trade — Carroll Brendan (Director) sold 64,991 shares @ $1.60 ($103.7K) on 2026-09-10</t>
         </is>
       </c>
-      <c r="F2397" t="inlineStr"/>
-      <c r="G2397" t="inlineStr"/>
-      <c r="H2397" t="inlineStr"/>
     </row>
     <row r="2398">
       <c r="A2398" t="inlineStr">
@@ -71972,9 +71906,6 @@
           <t>1 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F2398" t="inlineStr"/>
-      <c r="G2398" t="inlineStr"/>
-      <c r="H2398" t="inlineStr"/>
     </row>
     <row r="2399">
       <c r="A2399" t="inlineStr">
@@ -72002,9 +71933,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Jiyane Siphelele (Officer) plans to sell 26,980 shares (~$1.95M) on/after 09/14/2026</t>
         </is>
       </c>
-      <c r="F2399" t="inlineStr"/>
-      <c r="G2399" t="inlineStr"/>
-      <c r="H2399" t="inlineStr"/>
     </row>
     <row r="2400">
       <c r="A2400" t="inlineStr">
@@ -72032,9 +71960,6 @@
           <t>4 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F2400" t="inlineStr"/>
-      <c r="G2400" t="inlineStr"/>
-      <c r="H2400" t="inlineStr"/>
     </row>
     <row r="2401">
       <c r="A2401" t="inlineStr">
@@ -72062,9 +71987,6 @@
           <t>[ROUTINE] Insider trade — Bhatt Baiju (Director) sold 43,373 shares @ $114.28 ($4.96M) on 2026-09-10</t>
         </is>
       </c>
-      <c r="F2401" t="inlineStr"/>
-      <c r="G2401" t="inlineStr"/>
-      <c r="H2401" t="inlineStr"/>
     </row>
     <row r="2402">
       <c r="A2402" t="inlineStr">
@@ -72092,9 +72014,6 @@
           <t>2 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F2402" t="inlineStr"/>
-      <c r="G2402" t="inlineStr"/>
-      <c r="H2402" t="inlineStr"/>
     </row>
     <row r="2403">
       <c r="A2403" t="inlineStr">
@@ -72122,9 +72041,6 @@
           <t>investor_relations: change detected</t>
         </is>
       </c>
-      <c r="F2403" t="inlineStr"/>
-      <c r="G2403" t="inlineStr"/>
-      <c r="H2403" t="inlineStr"/>
     </row>
     <row r="2404">
       <c r="A2404" t="inlineStr">
@@ -72152,9 +72068,1854 @@
           <t>[MATERIAL] Material event disclosure</t>
         </is>
       </c>
-      <c r="F2404" t="inlineStr"/>
-      <c r="G2404" t="inlineStr"/>
-      <c r="H2404" t="inlineStr"/>
+    </row>
+    <row r="2405">
+      <c r="A2405" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B2405" t="inlineStr">
+        <is>
+          <t>LYFT</t>
+        </is>
+      </c>
+      <c r="C2405" t="inlineStr">
+        <is>
+          <t>Lyft, Inc.</t>
+        </is>
+      </c>
+      <c r="D2405" t="inlineStr">
+        <is>
+          <t>https://www.lyft.com/blog</t>
+        </is>
+      </c>
+      <c r="E2405" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2406">
+      <c r="A2406" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B2406" t="inlineStr">
+        <is>
+          <t>UBER</t>
+        </is>
+      </c>
+      <c r="C2406" t="inlineStr">
+        <is>
+          <t>Uber Technologies, Inc.</t>
+        </is>
+      </c>
+      <c r="D2406" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1543151/000177529726000012/xslF345X06/primarydocument.xml</t>
+        </is>
+      </c>
+      <c r="E2406" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Hazelbaker Jill (See Remarks) sold 28,170 shares @ $71.31 ($2.01M) on 2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="2407">
+      <c r="A2407" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B2407" t="inlineStr">
+        <is>
+          <t>UBER</t>
+        </is>
+      </c>
+      <c r="C2407" t="inlineStr">
+        <is>
+          <t>Uber Technologies, Inc.</t>
+        </is>
+      </c>
+      <c r="D2407" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1543151/000155278126000487/e26384_uber-8a12b.htm</t>
+        </is>
+      </c>
+      <c r="E2407" t="inlineStr">
+        <is>
+          <t>[UNKNOWN] Form 8-A12B</t>
+        </is>
+      </c>
+    </row>
+    <row r="2408">
+      <c r="A2408" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B2408" t="inlineStr">
+        <is>
+          <t>UBER</t>
+        </is>
+      </c>
+      <c r="C2408" t="inlineStr">
+        <is>
+          <t>Uber Technologies, Inc.</t>
+        </is>
+      </c>
+      <c r="D2408" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1543151/000155278126000486/e26383_uber-8k.htm</t>
+        </is>
+      </c>
+      <c r="E2408" t="inlineStr">
+        <is>
+          <t>[MATERIAL] Material event disclosure</t>
+        </is>
+      </c>
+    </row>
+    <row r="2409">
+      <c r="A2409" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B2409" t="inlineStr">
+        <is>
+          <t>EXPE</t>
+        </is>
+      </c>
+      <c r="C2409" t="inlineStr">
+        <is>
+          <t>Expedia Group, Inc.</t>
+        </is>
+      </c>
+      <c r="D2409" t="inlineStr">
+        <is>
+          <t>https://careers.expediagroup.com</t>
+        </is>
+      </c>
+      <c r="E2409" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2410">
+      <c r="A2410" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B2410" t="inlineStr">
+        <is>
+          <t>BKNG</t>
+        </is>
+      </c>
+      <c r="C2410" t="inlineStr">
+        <is>
+          <t>Booking Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D2410" t="inlineStr">
+        <is>
+          <t>https://www.booking.com/content/terms.html</t>
+        </is>
+      </c>
+      <c r="E2410" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2411">
+      <c r="A2411" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B2411" t="inlineStr">
+        <is>
+          <t>ABNB</t>
+        </is>
+      </c>
+      <c r="C2411" t="inlineStr">
+        <is>
+          <t>Airbnb, Inc.</t>
+        </is>
+      </c>
+      <c r="D2411" t="inlineStr">
+        <is>
+          <t>https://careers.airbnb.com</t>
+        </is>
+      </c>
+      <c r="E2411" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2412">
+      <c r="A2412" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B2412" t="inlineStr">
+        <is>
+          <t>YOU</t>
+        </is>
+      </c>
+      <c r="C2412" t="inlineStr">
+        <is>
+          <t>Clear Secure, Inc.</t>
+        </is>
+      </c>
+      <c r="D2412" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1856314/000095014226002552/eh260830672_8k.htm</t>
+        </is>
+      </c>
+      <c r="E2412" t="inlineStr">
+        <is>
+          <t>[MATERIAL] Material event disclosure</t>
+        </is>
+      </c>
+    </row>
+    <row r="2413">
+      <c r="A2413" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B2413" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="C2413" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="D2413" t="inlineStr">
+        <is>
+          <t>https://investor.atmeta.com</t>
+        </is>
+      </c>
+      <c r="E2413" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2414">
+      <c r="A2414" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B2414" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="C2414" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="D2414" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1326801/000192109426001023/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E2414" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Cox Christopher K (Officer) plans to sell 20,000 shares (~$13.50M) on/after 09/15/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2415">
+      <c r="A2415" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B2415" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="C2415" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="D2415" t="inlineStr">
+        <is>
+          <t>https://blog.google</t>
+        </is>
+      </c>
+      <c r="E2415" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2416">
+      <c r="A2416" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B2416" t="inlineStr">
+        <is>
+          <t>SNAP</t>
+        </is>
+      </c>
+      <c r="C2416" t="inlineStr">
+        <is>
+          <t>Snap Inc.</t>
+        </is>
+      </c>
+      <c r="D2416" t="inlineStr">
+        <is>
+          <t>https://careers.snap.com</t>
+        </is>
+      </c>
+      <c r="E2416" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2417">
+      <c r="A2417" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B2417" t="inlineStr">
+        <is>
+          <t>PINS</t>
+        </is>
+      </c>
+      <c r="C2417" t="inlineStr">
+        <is>
+          <t>Pinterest, Inc.</t>
+        </is>
+      </c>
+      <c r="D2417" t="inlineStr">
+        <is>
+          <t>https://newsroom.pinterest.com</t>
+        </is>
+      </c>
+      <c r="E2417" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2418">
+      <c r="A2418" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B2418" t="inlineStr">
+        <is>
+          <t>PINS</t>
+        </is>
+      </c>
+      <c r="C2418" t="inlineStr">
+        <is>
+          <t>Pinterest, Inc.</t>
+        </is>
+      </c>
+      <c r="D2418" t="inlineStr">
+        <is>
+          <t>https://www.pinterestcareers.com</t>
+        </is>
+      </c>
+      <c r="E2418" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2419">
+      <c r="A2419" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B2419" t="inlineStr">
+        <is>
+          <t>PINS</t>
+        </is>
+      </c>
+      <c r="C2419" t="inlineStr">
+        <is>
+          <t>Pinterest, Inc.</t>
+        </is>
+      </c>
+      <c r="D2419" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1506293/000192109426001025/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E2419" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Silbermann Benjamin (Director) plans to sell 46,875 shares (~$900.9K) on/after 09/15/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2420">
+      <c r="A2420" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B2420" t="inlineStr">
+        <is>
+          <t>RDDT</t>
+        </is>
+      </c>
+      <c r="C2420" t="inlineStr">
+        <is>
+          <t>Reddit, Inc.</t>
+        </is>
+      </c>
+      <c r="D2420" t="inlineStr">
+        <is>
+          <t>https://redditinc.com/careers</t>
+        </is>
+      </c>
+      <c r="E2420" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2421">
+      <c r="A2421" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B2421" t="inlineStr">
+        <is>
+          <t>RDDT</t>
+        </is>
+      </c>
+      <c r="C2421" t="inlineStr">
+        <is>
+          <t>Reddit, Inc.</t>
+        </is>
+      </c>
+      <c r="D2421" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1713445/000195004726009529/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E2421" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — The XYZ Revocable Trust (Director) plans to sell 121,156 shares (~$19.67M) on/after 09/15/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2422">
+      <c r="A2422" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B2422" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="C2422" t="inlineStr">
+        <is>
+          <t>Unity Software Inc.</t>
+        </is>
+      </c>
+      <c r="D2422" t="inlineStr">
+        <is>
+          <t>https://unity.com/legal/terms-of-service</t>
+        </is>
+      </c>
+      <c r="E2422" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2423">
+      <c r="A2423" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B2423" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="C2423" t="inlineStr">
+        <is>
+          <t>Unity Software Inc.</t>
+        </is>
+      </c>
+      <c r="D2423" t="inlineStr">
+        <is>
+          <t>https://careers.unity.com</t>
+        </is>
+      </c>
+      <c r="E2423" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2424">
+      <c r="A2424" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B2424" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="C2424" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="D2424" t="inlineStr">
+        <is>
+          <t>https://about.netflix.com/newsroom</t>
+        </is>
+      </c>
+      <c r="E2424" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2425">
+      <c r="A2425" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B2425" t="inlineStr">
+        <is>
+          <t>SPOT</t>
+        </is>
+      </c>
+      <c r="C2425" t="inlineStr">
+        <is>
+          <t>Spotify Technology S.A.</t>
+        </is>
+      </c>
+      <c r="D2425" t="inlineStr">
+        <is>
+          <t>https://newsroom.spotify.com</t>
+        </is>
+      </c>
+      <c r="E2425" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2426">
+      <c r="A2426" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B2426" t="inlineStr">
+        <is>
+          <t>SPOT</t>
+        </is>
+      </c>
+      <c r="C2426" t="inlineStr">
+        <is>
+          <t>Spotify Technology S.A.</t>
+        </is>
+      </c>
+      <c r="D2426" t="inlineStr">
+        <is>
+          <t>https://www.lifeatspotify.com</t>
+        </is>
+      </c>
+      <c r="E2426" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2427">
+      <c r="A2427" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B2427" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="C2427" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="D2427" t="inlineStr">
+        <is>
+          <t>https://www.disneyplus.com/welcome</t>
+        </is>
+      </c>
+      <c r="E2427" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2428">
+      <c r="A2428" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B2428" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="C2428" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="D2428" t="inlineStr">
+        <is>
+          <t>https://thewaltdisneycompany.com/news/</t>
+        </is>
+      </c>
+      <c r="E2428" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2429">
+      <c r="A2429" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B2429" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="C2429" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="D2429" t="inlineStr">
+        <is>
+          <t>https://jobs.disneycareers.com</t>
+        </is>
+      </c>
+      <c r="E2429" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2430">
+      <c r="A2430" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B2430" t="inlineStr">
+        <is>
+          <t>FOXA</t>
+        </is>
+      </c>
+      <c r="C2430" t="inlineStr">
+        <is>
+          <t>Fox Corporation</t>
+        </is>
+      </c>
+      <c r="D2430" t="inlineStr">
+        <is>
+          <t>https://foxcareers.com</t>
+        </is>
+      </c>
+      <c r="E2430" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2431">
+      <c r="A2431" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B2431" t="inlineStr">
+        <is>
+          <t>LYV</t>
+        </is>
+      </c>
+      <c r="C2431" t="inlineStr">
+        <is>
+          <t>Live Nation Entertainment, Inc.</t>
+        </is>
+      </c>
+      <c r="D2431" t="inlineStr">
+        <is>
+          <t>https://investors.livenationentertainment.com</t>
+        </is>
+      </c>
+      <c r="E2431" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2432">
+      <c r="A2432" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B2432" t="inlineStr">
+        <is>
+          <t>STUB</t>
+        </is>
+      </c>
+      <c r="C2432" t="inlineStr">
+        <is>
+          <t>StubHub Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="D2432" t="inlineStr">
+        <is>
+          <t>https://www.stubhub.com/careers/</t>
+        </is>
+      </c>
+      <c r="E2432" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2433">
+      <c r="A2433" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B2433" t="inlineStr">
+        <is>
+          <t>LION</t>
+        </is>
+      </c>
+      <c r="C2433" t="inlineStr">
+        <is>
+          <t>LION (verify ticker)</t>
+        </is>
+      </c>
+      <c r="D2433" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/2052959/000205295926000072/lion-20260915.htm</t>
+        </is>
+      </c>
+      <c r="E2433" t="inlineStr">
+        <is>
+          <t>[MATERIAL] Material event disclosure</t>
+        </is>
+      </c>
+    </row>
+    <row r="2434">
+      <c r="A2434" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B2434" t="inlineStr">
+        <is>
+          <t>TTWO</t>
+        </is>
+      </c>
+      <c r="C2434" t="inlineStr">
+        <is>
+          <t>Take-Two Interactive Software, Inc.</t>
+        </is>
+      </c>
+      <c r="D2434" t="inlineStr">
+        <is>
+          <t>https://ir.take2games.com</t>
+        </is>
+      </c>
+      <c r="E2434" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2435">
+      <c r="A2435" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B2435" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="C2435" t="inlineStr">
+        <is>
+          <t>Electronic Arts Inc.</t>
+        </is>
+      </c>
+      <c r="D2435" t="inlineStr">
+        <is>
+          <t>https://www.ea.com/news</t>
+        </is>
+      </c>
+      <c r="E2435" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2436">
+      <c r="A2436" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B2436" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="C2436" t="inlineStr">
+        <is>
+          <t>Electronic Arts Inc.</t>
+        </is>
+      </c>
+      <c r="D2436" t="inlineStr">
+        <is>
+          <t>https://ir.ea.com</t>
+        </is>
+      </c>
+      <c r="E2436" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2437">
+      <c r="A2437" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B2437" t="inlineStr">
+        <is>
+          <t>CDW</t>
+        </is>
+      </c>
+      <c r="C2437" t="inlineStr">
+        <is>
+          <t>CDW Corporation</t>
+        </is>
+      </c>
+      <c r="D2437" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1402057/000119312526392158/d141326d424b5.htm</t>
+        </is>
+      </c>
+      <c r="E2437" t="inlineStr">
+        <is>
+          <t>[UNKNOWN] Form 424B5</t>
+        </is>
+      </c>
+    </row>
+    <row r="2438">
+      <c r="A2438" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B2438" t="inlineStr">
+        <is>
+          <t>CDW</t>
+        </is>
+      </c>
+      <c r="C2438" t="inlineStr">
+        <is>
+          <t>CDW Corporation</t>
+        </is>
+      </c>
+      <c r="D2438" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1402057/000119312526392039/d180681d8k.htm</t>
+        </is>
+      </c>
+      <c r="E2438" t="inlineStr">
+        <is>
+          <t>[MATERIAL] Material event disclosure</t>
+        </is>
+      </c>
+    </row>
+    <row r="2439">
+      <c r="A2439" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B2439" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C2439" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D2439" t="inlineStr">
+        <is>
+          <t>https://www.shopify.com/pricing</t>
+        </is>
+      </c>
+      <c r="E2439" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+      <c r="F2439" t="inlineStr"/>
+      <c r="G2439" t="inlineStr"/>
+      <c r="H2439" t="inlineStr"/>
+    </row>
+    <row r="2440">
+      <c r="A2440" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B2440" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C2440" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D2440" t="inlineStr">
+        <is>
+          <t>https://www.shopify.com/careers</t>
+        </is>
+      </c>
+      <c r="E2440" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F2440" t="inlineStr"/>
+      <c r="G2440" t="inlineStr"/>
+      <c r="H2440" t="inlineStr"/>
+    </row>
+    <row r="2441">
+      <c r="A2441" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B2441" t="inlineStr">
+        <is>
+          <t>EBAY</t>
+        </is>
+      </c>
+      <c r="C2441" t="inlineStr">
+        <is>
+          <t>eBay Inc.</t>
+        </is>
+      </c>
+      <c r="D2441" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/help/policies/member-behaviour-policies/user-agreement?id=4259</t>
+        </is>
+      </c>
+      <c r="E2441" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+      <c r="F2441" t="inlineStr"/>
+      <c r="G2441" t="inlineStr"/>
+      <c r="H2441" t="inlineStr"/>
+    </row>
+    <row r="2442">
+      <c r="A2442" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B2442" t="inlineStr">
+        <is>
+          <t>EBAY</t>
+        </is>
+      </c>
+      <c r="C2442" t="inlineStr">
+        <is>
+          <t>eBay Inc.</t>
+        </is>
+      </c>
+      <c r="D2442" t="inlineStr">
+        <is>
+          <t>https://careers.ebayinc.com</t>
+        </is>
+      </c>
+      <c r="E2442" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F2442" t="inlineStr"/>
+      <c r="G2442" t="inlineStr"/>
+      <c r="H2442" t="inlineStr"/>
+    </row>
+    <row r="2443">
+      <c r="A2443" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B2443" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C2443" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D2443" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/instacart</t>
+        </is>
+      </c>
+      <c r="E2443" t="inlineStr">
+        <is>
+          <t>3 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F2443" t="inlineStr"/>
+      <c r="G2443" t="inlineStr"/>
+      <c r="H2443" t="inlineStr"/>
+    </row>
+    <row r="2444">
+      <c r="A2444" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B2444" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C2444" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D2444" t="inlineStr">
+        <is>
+          <t>https://www.instacart.com/instacart-plus</t>
+        </is>
+      </c>
+      <c r="E2444" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+      <c r="F2444" t="inlineStr"/>
+      <c r="G2444" t="inlineStr"/>
+      <c r="H2444" t="inlineStr"/>
+    </row>
+    <row r="2445">
+      <c r="A2445" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B2445" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C2445" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D2445" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1579091/000192109426001017/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E2445" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Lisa Blackwood-Kapral (Officer) plans to sell 3,017 shares (~$142.0K) on/after 09/15/2026</t>
+        </is>
+      </c>
+      <c r="F2445" t="inlineStr"/>
+      <c r="G2445" t="inlineStr"/>
+      <c r="H2445" t="inlineStr"/>
+    </row>
+    <row r="2446">
+      <c r="A2446" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B2446" t="inlineStr">
+        <is>
+          <t>DUOL</t>
+        </is>
+      </c>
+      <c r="C2446" t="inlineStr">
+        <is>
+          <t>Duolingo Inc.</t>
+        </is>
+      </c>
+      <c r="D2446" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/duolingo</t>
+        </is>
+      </c>
+      <c r="E2446" t="inlineStr">
+        <is>
+          <t>3 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F2446" t="inlineStr"/>
+      <c r="G2446" t="inlineStr"/>
+      <c r="H2446" t="inlineStr"/>
+    </row>
+    <row r="2447">
+      <c r="A2447" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B2447" t="inlineStr">
+        <is>
+          <t>DUOL</t>
+        </is>
+      </c>
+      <c r="C2447" t="inlineStr">
+        <is>
+          <t>Duolingo Inc.</t>
+        </is>
+      </c>
+      <c r="D2447" t="inlineStr">
+        <is>
+          <t>https://blog.duolingo.com/</t>
+        </is>
+      </c>
+      <c r="E2447" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F2447" t="inlineStr"/>
+      <c r="G2447" t="inlineStr"/>
+      <c r="H2447" t="inlineStr"/>
+    </row>
+    <row r="2448">
+      <c r="A2448" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B2448" t="inlineStr">
+        <is>
+          <t>DUOL</t>
+        </is>
+      </c>
+      <c r="C2448" t="inlineStr">
+        <is>
+          <t>Duolingo Inc.</t>
+        </is>
+      </c>
+      <c r="D2448" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1562088/000162828026062115/xslF345X06/wk-form4_1789512674.xml</t>
+        </is>
+      </c>
+      <c r="E2448" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Chen Stephen C. (General Counsel) sold 8,072 shares @ $149.33 ($1.21M) on 2026-09-14</t>
+        </is>
+      </c>
+      <c r="F2448" t="inlineStr"/>
+      <c r="G2448" t="inlineStr"/>
+      <c r="H2448" t="inlineStr"/>
+    </row>
+    <row r="2449">
+      <c r="A2449" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B2449" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="C2449" t="inlineStr">
+        <is>
+          <t>Zillow Group Inc.</t>
+        </is>
+      </c>
+      <c r="D2449" t="inlineStr">
+        <is>
+          <t>https://zillow.mediaroom.com</t>
+        </is>
+      </c>
+      <c r="E2449" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F2449" t="inlineStr"/>
+      <c r="G2449" t="inlineStr"/>
+      <c r="H2449" t="inlineStr"/>
+    </row>
+    <row r="2450">
+      <c r="A2450" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B2450" t="inlineStr">
+        <is>
+          <t>RKT</t>
+        </is>
+      </c>
+      <c r="C2450" t="inlineStr">
+        <is>
+          <t>Rocket Companies Inc.</t>
+        </is>
+      </c>
+      <c r="D2450" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1805284/000196858226000980/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E2450" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Jesse K. Bray (Director) plans to sell 900,000 shares (~$12.10M) on/after 09/15/2026</t>
+        </is>
+      </c>
+      <c r="F2450" t="inlineStr"/>
+      <c r="G2450" t="inlineStr"/>
+      <c r="H2450" t="inlineStr"/>
+    </row>
+    <row r="2451">
+      <c r="A2451" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B2451" t="inlineStr">
+        <is>
+          <t>COMP</t>
+        </is>
+      </c>
+      <c r="C2451" t="inlineStr">
+        <is>
+          <t>Compass Inc.</t>
+        </is>
+      </c>
+      <c r="D2451" t="inlineStr">
+        <is>
+          <t>https://www.compass.com/careers/</t>
+        </is>
+      </c>
+      <c r="E2451" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F2451" t="inlineStr"/>
+      <c r="G2451" t="inlineStr"/>
+      <c r="H2451" t="inlineStr"/>
+    </row>
+    <row r="2452">
+      <c r="A2452" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B2452" t="inlineStr">
+        <is>
+          <t>COMP</t>
+        </is>
+      </c>
+      <c r="C2452" t="inlineStr">
+        <is>
+          <t>Compass Inc.</t>
+        </is>
+      </c>
+      <c r="D2452" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1563190/000156319026000144/xslFormDX01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E2452" t="inlineStr">
+        <is>
+          <t>[UNKNOWN] Form D</t>
+        </is>
+      </c>
+      <c r="F2452" t="inlineStr"/>
+      <c r="G2452" t="inlineStr"/>
+      <c r="H2452" t="inlineStr"/>
+    </row>
+    <row r="2453">
+      <c r="A2453" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B2453" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C2453" t="inlineStr">
+        <is>
+          <t>Block Inc. (fmr. Square)</t>
+        </is>
+      </c>
+      <c r="D2453" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1512673/000162828026062107/xslF345X06/wk-form4_1789510278.xml</t>
+        </is>
+      </c>
+      <c r="E2453" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Eisen Anthony Mathew (Director) sold 18,000 shares @ $79.41 ($1.43M) on 2026-09-11</t>
+        </is>
+      </c>
+      <c r="F2453" t="inlineStr"/>
+      <c r="G2453" t="inlineStr"/>
+      <c r="H2453" t="inlineStr"/>
+    </row>
+    <row r="2454">
+      <c r="A2454" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B2454" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C2454" t="inlineStr">
+        <is>
+          <t>Block Inc. (fmr. Square)</t>
+        </is>
+      </c>
+      <c r="D2454" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1512673/000195004726009475/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E2454" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — M Eisen Anthony (Director) plans to sell 6,000 shares (~$475.9K) on/after 09/15/2026</t>
+        </is>
+      </c>
+      <c r="F2454" t="inlineStr"/>
+      <c r="G2454" t="inlineStr"/>
+      <c r="H2454" t="inlineStr"/>
+    </row>
+    <row r="2455">
+      <c r="A2455" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B2455" t="inlineStr">
+        <is>
+          <t>PYPL</t>
+        </is>
+      </c>
+      <c r="C2455" t="inlineStr">
+        <is>
+          <t>PayPal Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D2455" t="inlineStr">
+        <is>
+          <t>https://careers.pypl.com</t>
+        </is>
+      </c>
+      <c r="E2455" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F2455" t="inlineStr"/>
+      <c r="G2455" t="inlineStr"/>
+      <c r="H2455" t="inlineStr"/>
+    </row>
+    <row r="2456">
+      <c r="A2456" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B2456" t="inlineStr">
+        <is>
+          <t>TOST</t>
+        </is>
+      </c>
+      <c r="C2456" t="inlineStr">
+        <is>
+          <t>Toast Inc.</t>
+        </is>
+      </c>
+      <c r="D2456" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/toast</t>
+        </is>
+      </c>
+      <c r="E2456" t="inlineStr">
+        <is>
+          <t>10 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F2456" t="inlineStr"/>
+      <c r="G2456" t="inlineStr"/>
+      <c r="H2456" t="inlineStr"/>
+    </row>
+    <row r="2457">
+      <c r="A2457" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B2457" t="inlineStr">
+        <is>
+          <t>DAVE</t>
+        </is>
+      </c>
+      <c r="C2457" t="inlineStr">
+        <is>
+          <t>Dave Inc.</t>
+        </is>
+      </c>
+      <c r="D2457" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1841408/000119312526392097/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E2457" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Wilk Jason (Chief Executive Officer) other: 37,090 Variable Prepaid Forward Contract (obligation to sell) on 2026-09-11</t>
+        </is>
+      </c>
+      <c r="F2457" t="inlineStr"/>
+      <c r="G2457" t="inlineStr"/>
+      <c r="H2457" t="inlineStr"/>
+    </row>
+    <row r="2458">
+      <c r="A2458" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B2458" t="inlineStr">
+        <is>
+          <t>DAVE</t>
+        </is>
+      </c>
+      <c r="C2458" t="inlineStr">
+        <is>
+          <t>Dave Inc.</t>
+        </is>
+      </c>
+      <c r="D2458" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1841408/000119312526392095/xslSCHEDULE_13D_X02/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E2458" t="inlineStr">
+        <is>
+          <t>[MATERIAL] Update to 5%+ active owner disclosure</t>
+        </is>
+      </c>
+      <c r="F2458" t="inlineStr"/>
+      <c r="G2458" t="inlineStr"/>
+      <c r="H2458" t="inlineStr"/>
+    </row>
+    <row r="2459">
+      <c r="A2459" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B2459" t="inlineStr">
+        <is>
+          <t>DAVE</t>
+        </is>
+      </c>
+      <c r="C2459" t="inlineStr">
+        <is>
+          <t>Dave Inc.</t>
+        </is>
+      </c>
+      <c r="D2459" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1841408/000119312526392085/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E2459" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Beilman Kyle (CFO and COO and Secretary) other: 40,000 Variable Prepaid Forward Contract (obligation to sell) on 2026-09-11</t>
+        </is>
+      </c>
+      <c r="F2459" t="inlineStr"/>
+      <c r="G2459" t="inlineStr"/>
+      <c r="H2459" t="inlineStr"/>
+    </row>
+    <row r="2460">
+      <c r="A2460" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B2460" t="inlineStr">
+        <is>
+          <t>AFRM</t>
+        </is>
+      </c>
+      <c r="C2460" t="inlineStr">
+        <is>
+          <t>Affirm Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D2460" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/affirm</t>
+        </is>
+      </c>
+      <c r="E2460" t="inlineStr">
+        <is>
+          <t>4 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F2460" t="inlineStr"/>
+      <c r="G2460" t="inlineStr"/>
+      <c r="H2460" t="inlineStr"/>
+    </row>
+    <row r="2461">
+      <c r="A2461" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B2461" t="inlineStr">
+        <is>
+          <t>HOOD</t>
+        </is>
+      </c>
+      <c r="C2461" t="inlineStr">
+        <is>
+          <t>Robinhood Markets Inc.</t>
+        </is>
+      </c>
+      <c r="D2461" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/robinhood</t>
+        </is>
+      </c>
+      <c r="E2461" t="inlineStr">
+        <is>
+          <t>7 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F2461" t="inlineStr"/>
+      <c r="G2461" t="inlineStr"/>
+      <c r="H2461" t="inlineStr"/>
+    </row>
+    <row r="2462">
+      <c r="A2462" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B2462" t="inlineStr">
+        <is>
+          <t>HOOD</t>
+        </is>
+      </c>
+      <c r="C2462" t="inlineStr">
+        <is>
+          <t>Robinhood Markets Inc.</t>
+        </is>
+      </c>
+      <c r="D2462" t="inlineStr">
+        <is>
+          <t>https://newsroom.aboutrobinhood.com</t>
+        </is>
+      </c>
+      <c r="E2462" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F2462" t="inlineStr"/>
+      <c r="G2462" t="inlineStr"/>
+      <c r="H2462" t="inlineStr"/>
+    </row>
+    <row r="2463">
+      <c r="A2463" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B2463" t="inlineStr">
+        <is>
+          <t>HOOD</t>
+        </is>
+      </c>
+      <c r="C2463" t="inlineStr">
+        <is>
+          <t>Robinhood Markets Inc.</t>
+        </is>
+      </c>
+      <c r="D2463" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1783879/000195004726009490/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E2463" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Verma Shiv (Officer) plans to sell 11,472 shares (~$1.31M) on/after 09/15/2026</t>
+        </is>
+      </c>
+      <c r="F2463" t="inlineStr"/>
+      <c r="G2463" t="inlineStr"/>
+      <c r="H2463" t="inlineStr"/>
+    </row>
+    <row r="2464">
+      <c r="A2464" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B2464" t="inlineStr">
+        <is>
+          <t>UPST</t>
+        </is>
+      </c>
+      <c r="C2464" t="inlineStr">
+        <is>
+          <t>Upstart Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D2464" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/upstart</t>
+        </is>
+      </c>
+      <c r="E2464" t="inlineStr">
+        <is>
+          <t>2 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F2464" t="inlineStr"/>
+      <c r="G2464" t="inlineStr"/>
+      <c r="H2464" t="inlineStr"/>
+    </row>
+    <row r="2465">
+      <c r="A2465" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B2465" t="inlineStr">
+        <is>
+          <t>UPST</t>
+        </is>
+      </c>
+      <c r="C2465" t="inlineStr">
+        <is>
+          <t>Upstart Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D2465" t="inlineStr">
+        <is>
+          <t>https://www.upstart.com/blog</t>
+        </is>
+      </c>
+      <c r="E2465" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F2465" t="inlineStr"/>
+      <c r="G2465" t="inlineStr"/>
+      <c r="H2465" t="inlineStr"/>
+    </row>
+    <row r="2466">
+      <c r="A2466" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B2466" t="inlineStr">
+        <is>
+          <t>WSM</t>
+        </is>
+      </c>
+      <c r="C2466" t="inlineStr">
+        <is>
+          <t>Williams-Sonoma Inc.</t>
+        </is>
+      </c>
+      <c r="D2466" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/719955/000071995526000210/xslF345X06/form4.xml</t>
+        </is>
+      </c>
+      <c r="E2466" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Howie Jeffrey (EVP CHIEF FINANCIAL OFFICER) 3,939 shares withheld for taxes (vest event) on 2026-09-12</t>
+        </is>
+      </c>
+      <c r="F2466" t="inlineStr"/>
+      <c r="G2466" t="inlineStr"/>
+      <c r="H2466" t="inlineStr"/>
+    </row>
+    <row r="2467">
+      <c r="A2467" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B2467" t="inlineStr">
+        <is>
+          <t>ENVA</t>
+        </is>
+      </c>
+      <c r="C2467" t="inlineStr">
+        <is>
+          <t>Enova International Inc.</t>
+        </is>
+      </c>
+      <c r="D2467" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1529864/000119312526392151/enva-20260915.htm</t>
+        </is>
+      </c>
+      <c r="E2467" t="inlineStr">
+        <is>
+          <t>[MATERIAL] Material event disclosure</t>
+        </is>
+      </c>
+      <c r="F2467" t="inlineStr"/>
+      <c r="G2467" t="inlineStr"/>
+      <c r="H2467" t="inlineStr"/>
+    </row>
+    <row r="2468">
+      <c r="A2468" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B2468" t="inlineStr">
+        <is>
+          <t>ONON</t>
+        </is>
+      </c>
+      <c r="C2468" t="inlineStr">
+        <is>
+          <t>On Holding AG</t>
+        </is>
+      </c>
+      <c r="D2468" t="inlineStr">
+        <is>
+          <t>https://investors.on-running.com/governance/default.aspx</t>
+        </is>
+      </c>
+      <c r="E2468" t="inlineStr">
+        <is>
+          <t>management_team: change detected</t>
+        </is>
+      </c>
+      <c r="F2468" t="inlineStr"/>
+      <c r="G2468" t="inlineStr"/>
+      <c r="H2468" t="inlineStr"/>
+    </row>
+    <row r="2469">
+      <c r="A2469" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B2469" t="inlineStr">
+        <is>
+          <t>ONON</t>
+        </is>
+      </c>
+      <c r="C2469" t="inlineStr">
+        <is>
+          <t>On Holding AG</t>
+        </is>
+      </c>
+      <c r="D2469" t="inlineStr">
+        <is>
+          <t>https://www.on-running.com/en-us/articles/</t>
+        </is>
+      </c>
+      <c r="E2469" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F2469" t="inlineStr"/>
+      <c r="G2469" t="inlineStr"/>
+      <c r="H2469" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/config/company_urls_jc.xlsx
+++ b/config/company_urls_jc.xlsx
@@ -7203,7 +7203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2469"/>
+  <dimension ref="A1:H2555"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -73013,9 +73013,6 @@
           <t>pricing: change detected</t>
         </is>
       </c>
-      <c r="F2439" t="inlineStr"/>
-      <c r="G2439" t="inlineStr"/>
-      <c r="H2439" t="inlineStr"/>
     </row>
     <row r="2440">
       <c r="A2440" t="inlineStr">
@@ -73043,9 +73040,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F2440" t="inlineStr"/>
-      <c r="G2440" t="inlineStr"/>
-      <c r="H2440" t="inlineStr"/>
     </row>
     <row r="2441">
       <c r="A2441" t="inlineStr">
@@ -73073,9 +73067,6 @@
           <t>terms: change detected</t>
         </is>
       </c>
-      <c r="F2441" t="inlineStr"/>
-      <c r="G2441" t="inlineStr"/>
-      <c r="H2441" t="inlineStr"/>
     </row>
     <row r="2442">
       <c r="A2442" t="inlineStr">
@@ -73103,9 +73094,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F2442" t="inlineStr"/>
-      <c r="G2442" t="inlineStr"/>
-      <c r="H2442" t="inlineStr"/>
     </row>
     <row r="2443">
       <c r="A2443" t="inlineStr">
@@ -73133,9 +73121,6 @@
           <t>3 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F2443" t="inlineStr"/>
-      <c r="G2443" t="inlineStr"/>
-      <c r="H2443" t="inlineStr"/>
     </row>
     <row r="2444">
       <c r="A2444" t="inlineStr">
@@ -73163,9 +73148,6 @@
           <t>pricing: change detected</t>
         </is>
       </c>
-      <c r="F2444" t="inlineStr"/>
-      <c r="G2444" t="inlineStr"/>
-      <c r="H2444" t="inlineStr"/>
     </row>
     <row r="2445">
       <c r="A2445" t="inlineStr">
@@ -73193,9 +73175,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Lisa Blackwood-Kapral (Officer) plans to sell 3,017 shares (~$142.0K) on/after 09/15/2026</t>
         </is>
       </c>
-      <c r="F2445" t="inlineStr"/>
-      <c r="G2445" t="inlineStr"/>
-      <c r="H2445" t="inlineStr"/>
     </row>
     <row r="2446">
       <c r="A2446" t="inlineStr">
@@ -73223,9 +73202,6 @@
           <t>3 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F2446" t="inlineStr"/>
-      <c r="G2446" t="inlineStr"/>
-      <c r="H2446" t="inlineStr"/>
     </row>
     <row r="2447">
       <c r="A2447" t="inlineStr">
@@ -73253,9 +73229,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F2447" t="inlineStr"/>
-      <c r="G2447" t="inlineStr"/>
-      <c r="H2447" t="inlineStr"/>
     </row>
     <row r="2448">
       <c r="A2448" t="inlineStr">
@@ -73283,9 +73256,6 @@
           <t>[ROUTINE] Insider trade — Chen Stephen C. (General Counsel) sold 8,072 shares @ $149.33 ($1.21M) on 2026-09-14</t>
         </is>
       </c>
-      <c r="F2448" t="inlineStr"/>
-      <c r="G2448" t="inlineStr"/>
-      <c r="H2448" t="inlineStr"/>
     </row>
     <row r="2449">
       <c r="A2449" t="inlineStr">
@@ -73313,9 +73283,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F2449" t="inlineStr"/>
-      <c r="G2449" t="inlineStr"/>
-      <c r="H2449" t="inlineStr"/>
     </row>
     <row r="2450">
       <c r="A2450" t="inlineStr">
@@ -73343,9 +73310,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Jesse K. Bray (Director) plans to sell 900,000 shares (~$12.10M) on/after 09/15/2026</t>
         </is>
       </c>
-      <c r="F2450" t="inlineStr"/>
-      <c r="G2450" t="inlineStr"/>
-      <c r="H2450" t="inlineStr"/>
     </row>
     <row r="2451">
       <c r="A2451" t="inlineStr">
@@ -73373,9 +73337,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F2451" t="inlineStr"/>
-      <c r="G2451" t="inlineStr"/>
-      <c r="H2451" t="inlineStr"/>
     </row>
     <row r="2452">
       <c r="A2452" t="inlineStr">
@@ -73403,9 +73364,6 @@
           <t>[UNKNOWN] Form D</t>
         </is>
       </c>
-      <c r="F2452" t="inlineStr"/>
-      <c r="G2452" t="inlineStr"/>
-      <c r="H2452" t="inlineStr"/>
     </row>
     <row r="2453">
       <c r="A2453" t="inlineStr">
@@ -73433,9 +73391,6 @@
           <t>[ROUTINE] Insider trade — Eisen Anthony Mathew (Director) sold 18,000 shares @ $79.41 ($1.43M) on 2026-09-11</t>
         </is>
       </c>
-      <c r="F2453" t="inlineStr"/>
-      <c r="G2453" t="inlineStr"/>
-      <c r="H2453" t="inlineStr"/>
     </row>
     <row r="2454">
       <c r="A2454" t="inlineStr">
@@ -73463,9 +73418,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — M Eisen Anthony (Director) plans to sell 6,000 shares (~$475.9K) on/after 09/15/2026</t>
         </is>
       </c>
-      <c r="F2454" t="inlineStr"/>
-      <c r="G2454" t="inlineStr"/>
-      <c r="H2454" t="inlineStr"/>
     </row>
     <row r="2455">
       <c r="A2455" t="inlineStr">
@@ -73493,9 +73445,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F2455" t="inlineStr"/>
-      <c r="G2455" t="inlineStr"/>
-      <c r="H2455" t="inlineStr"/>
     </row>
     <row r="2456">
       <c r="A2456" t="inlineStr">
@@ -73523,9 +73472,6 @@
           <t>10 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F2456" t="inlineStr"/>
-      <c r="G2456" t="inlineStr"/>
-      <c r="H2456" t="inlineStr"/>
     </row>
     <row r="2457">
       <c r="A2457" t="inlineStr">
@@ -73553,9 +73499,6 @@
           <t>[ROUTINE] Insider trade — Wilk Jason (Chief Executive Officer) other: 37,090 Variable Prepaid Forward Contract (obligation to sell) on 2026-09-11</t>
         </is>
       </c>
-      <c r="F2457" t="inlineStr"/>
-      <c r="G2457" t="inlineStr"/>
-      <c r="H2457" t="inlineStr"/>
     </row>
     <row r="2458">
       <c r="A2458" t="inlineStr">
@@ -73583,9 +73526,6 @@
           <t>[MATERIAL] Update to 5%+ active owner disclosure</t>
         </is>
       </c>
-      <c r="F2458" t="inlineStr"/>
-      <c r="G2458" t="inlineStr"/>
-      <c r="H2458" t="inlineStr"/>
     </row>
     <row r="2459">
       <c r="A2459" t="inlineStr">
@@ -73613,9 +73553,6 @@
           <t>[ROUTINE] Insider trade — Beilman Kyle (CFO and COO and Secretary) other: 40,000 Variable Prepaid Forward Contract (obligation to sell) on 2026-09-11</t>
         </is>
       </c>
-      <c r="F2459" t="inlineStr"/>
-      <c r="G2459" t="inlineStr"/>
-      <c r="H2459" t="inlineStr"/>
     </row>
     <row r="2460">
       <c r="A2460" t="inlineStr">
@@ -73643,9 +73580,6 @@
           <t>4 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F2460" t="inlineStr"/>
-      <c r="G2460" t="inlineStr"/>
-      <c r="H2460" t="inlineStr"/>
     </row>
     <row r="2461">
       <c r="A2461" t="inlineStr">
@@ -73673,9 +73607,6 @@
           <t>7 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F2461" t="inlineStr"/>
-      <c r="G2461" t="inlineStr"/>
-      <c r="H2461" t="inlineStr"/>
     </row>
     <row r="2462">
       <c r="A2462" t="inlineStr">
@@ -73703,9 +73634,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F2462" t="inlineStr"/>
-      <c r="G2462" t="inlineStr"/>
-      <c r="H2462" t="inlineStr"/>
     </row>
     <row r="2463">
       <c r="A2463" t="inlineStr">
@@ -73733,9 +73661,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Verma Shiv (Officer) plans to sell 11,472 shares (~$1.31M) on/after 09/15/2026</t>
         </is>
       </c>
-      <c r="F2463" t="inlineStr"/>
-      <c r="G2463" t="inlineStr"/>
-      <c r="H2463" t="inlineStr"/>
     </row>
     <row r="2464">
       <c r="A2464" t="inlineStr">
@@ -73763,9 +73688,6 @@
           <t>2 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F2464" t="inlineStr"/>
-      <c r="G2464" t="inlineStr"/>
-      <c r="H2464" t="inlineStr"/>
     </row>
     <row r="2465">
       <c r="A2465" t="inlineStr">
@@ -73793,9 +73715,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F2465" t="inlineStr"/>
-      <c r="G2465" t="inlineStr"/>
-      <c r="H2465" t="inlineStr"/>
     </row>
     <row r="2466">
       <c r="A2466" t="inlineStr">
@@ -73823,9 +73742,6 @@
           <t>[ROUTINE] Insider trade — Howie Jeffrey (EVP CHIEF FINANCIAL OFFICER) 3,939 shares withheld for taxes (vest event) on 2026-09-12</t>
         </is>
       </c>
-      <c r="F2466" t="inlineStr"/>
-      <c r="G2466" t="inlineStr"/>
-      <c r="H2466" t="inlineStr"/>
     </row>
     <row r="2467">
       <c r="A2467" t="inlineStr">
@@ -73853,9 +73769,6 @@
           <t>[MATERIAL] Material event disclosure</t>
         </is>
       </c>
-      <c r="F2467" t="inlineStr"/>
-      <c r="G2467" t="inlineStr"/>
-      <c r="H2467" t="inlineStr"/>
     </row>
     <row r="2468">
       <c r="A2468" t="inlineStr">
@@ -73883,9 +73796,6 @@
           <t>management_team: change detected</t>
         </is>
       </c>
-      <c r="F2468" t="inlineStr"/>
-      <c r="G2468" t="inlineStr"/>
-      <c r="H2468" t="inlineStr"/>
     </row>
     <row r="2469">
       <c r="A2469" t="inlineStr">
@@ -73913,9 +73823,2424 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F2469" t="inlineStr"/>
-      <c r="G2469" t="inlineStr"/>
-      <c r="H2469" t="inlineStr"/>
+    </row>
+    <row r="2470">
+      <c r="A2470" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B2470" t="inlineStr">
+        <is>
+          <t>LYFT</t>
+        </is>
+      </c>
+      <c r="C2470" t="inlineStr">
+        <is>
+          <t>Lyft, Inc.</t>
+        </is>
+      </c>
+      <c r="D2470" t="inlineStr">
+        <is>
+          <t>https://www.lyft.com/blog</t>
+        </is>
+      </c>
+      <c r="E2470" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2471">
+      <c r="A2471" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B2471" t="inlineStr">
+        <is>
+          <t>EXPE</t>
+        </is>
+      </c>
+      <c r="C2471" t="inlineStr">
+        <is>
+          <t>Expedia Group, Inc.</t>
+        </is>
+      </c>
+      <c r="D2471" t="inlineStr">
+        <is>
+          <t>https://careers.expediagroup.com</t>
+        </is>
+      </c>
+      <c r="E2471" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2472">
+      <c r="A2472" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B2472" t="inlineStr">
+        <is>
+          <t>BKNG</t>
+        </is>
+      </c>
+      <c r="C2472" t="inlineStr">
+        <is>
+          <t>Booking Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D2472" t="inlineStr">
+        <is>
+          <t>https://www.booking.com/content/terms.html</t>
+        </is>
+      </c>
+      <c r="E2472" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2473">
+      <c r="A2473" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B2473" t="inlineStr">
+        <is>
+          <t>BKNG</t>
+        </is>
+      </c>
+      <c r="C2473" t="inlineStr">
+        <is>
+          <t>Booking Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D2473" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1075531/000187574126000008/xslF345X06/form4-09162026_040901.xml</t>
+        </is>
+      </c>
+      <c r="E2473" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Pisano Paulo (CHIEF HUMAN RESOURCES OFFICER) sold 1,500 shares @ $173.02 ($259.5K) on 2026-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="2474">
+      <c r="A2474" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B2474" t="inlineStr">
+        <is>
+          <t>ABNB</t>
+        </is>
+      </c>
+      <c r="C2474" t="inlineStr">
+        <is>
+          <t>Airbnb, Inc.</t>
+        </is>
+      </c>
+      <c r="D2474" t="inlineStr">
+        <is>
+          <t>https://careers.airbnb.com</t>
+        </is>
+      </c>
+      <c r="E2474" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2475">
+      <c r="A2475" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B2475" t="inlineStr">
+        <is>
+          <t>ABNB</t>
+        </is>
+      </c>
+      <c r="C2475" t="inlineStr">
+        <is>
+          <t>Airbnb, Inc.</t>
+        </is>
+      </c>
+      <c r="D2475" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1559720/000119312526393171/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E2475" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Blecharczyk Nathan (Chief Strategy Officer) sold 13,615 shares @ $172.36 ($2.35M) on 2026-09-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="2476">
+      <c r="A2476" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B2476" t="inlineStr">
+        <is>
+          <t>CHH</t>
+        </is>
+      </c>
+      <c r="C2476" t="inlineStr">
+        <is>
+          <t>Choice Hotels International, Inc.</t>
+        </is>
+      </c>
+      <c r="D2476" t="inlineStr">
+        <is>
+          <t>https://media.choicehotels.com</t>
+        </is>
+      </c>
+      <c r="E2476" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2477">
+      <c r="A2477" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B2477" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="C2477" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="D2477" t="inlineStr">
+        <is>
+          <t>https://investor.atmeta.com</t>
+        </is>
+      </c>
+      <c r="E2477" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2478">
+      <c r="A2478" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B2478" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="C2478" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="D2478" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1326801/000095010326014061/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E2478" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Olivan Javier (Chief Operating Officer) sold 1,575 shares @ $657.73 ($1.04M) on 2026-09-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="2479">
+      <c r="A2479" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B2479" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="C2479" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="D2479" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1652044/000119312526393517/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E2479" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Frances Arnold (Director) granted 13 Class C Google Stock Units on 2026-09-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="2480">
+      <c r="A2480" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B2480" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="C2480" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="D2480" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1652044/000119312526393515/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E2480" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Washington Robin L (Director) granted 3 Class C Google Stock Units on 2026-09-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="2481">
+      <c r="A2481" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B2481" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="C2481" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="D2481" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1652044/000119312526393513/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E2481" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Shriram Kavitark Ram (Director) granted 3 Class C Google Stock Units on 2026-09-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="2482">
+      <c r="A2482" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B2482" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="C2482" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="D2482" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1652044/000119312526393511/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E2482" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Hennessy John L. (Director) granted 4 Class C Google Stock Units on 2026-09-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="2483">
+      <c r="A2483" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B2483" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="C2483" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="D2483" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1652044/000119312526393509/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E2483" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — L John Doerr (Director) granted 3 Class C Google Stock Units on 2026-09-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="2484">
+      <c r="A2484" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B2484" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="C2484" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="D2484" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1652044/000119312526393506/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E2484" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Ferguson Roger W. Jr. (Director) granted 3 Class C Google Stock Units on 2026-09-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="2485">
+      <c r="A2485" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B2485" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="C2485" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="D2485" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1652044/000119312526393503/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E2485" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — R. Martin Chavez (Director) granted 3 Class C Google Stock Units on 2026-09-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="2486">
+      <c r="A2486" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B2486" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="C2486" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="D2486" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1652044/000119312526393500/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E2486" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Saraci Marsida (VP, Chief Accounting Officer) granted 10 Class C Google Stock Units on 2026-09-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="2487">
+      <c r="A2487" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B2487" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="C2487" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="D2487" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1652044/000119312526393497/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E2487" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — John Kent Walker (President, Global Affairs, CLO) granted 82 Class C Google Stock Units on 2026-09-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="2488">
+      <c r="A2488" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B2488" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="C2488" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="D2488" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1652044/000119312526393494/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E2488" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Porat Ruth (President and CIO) granted 82 Class C Google Stock Units on 2026-09-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="2489">
+      <c r="A2489" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B2489" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="C2489" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="D2489" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1652044/000119312526393491/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E2489" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Schindler Philipp (SVP, Chief Business Officer) granted 104 Class C Google Stock Units on 2026-09-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="2490">
+      <c r="A2490" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B2490" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="C2490" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="D2490" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1652044/000119312526393485/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E2490" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Ashkenazi Anat (SVP, Chief Financial Officer) granted 82 Class C Google Stock Units on 2026-09-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="2491">
+      <c r="A2491" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B2491" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="C2491" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="D2491" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1652044/000119312526393483/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E2491" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Pichai Sundar (Chief Executive Officer) granted 131 Class C Google Stock Units on 2026-09-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="2492">
+      <c r="A2492" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B2492" t="inlineStr">
+        <is>
+          <t>SNAP</t>
+        </is>
+      </c>
+      <c r="C2492" t="inlineStr">
+        <is>
+          <t>Snap Inc.</t>
+        </is>
+      </c>
+      <c r="D2492" t="inlineStr">
+        <is>
+          <t>https://newsroom.snap.com</t>
+        </is>
+      </c>
+      <c r="E2492" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2493">
+      <c r="A2493" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B2493" t="inlineStr">
+        <is>
+          <t>SNAP</t>
+        </is>
+      </c>
+      <c r="C2493" t="inlineStr">
+        <is>
+          <t>Snap Inc.</t>
+        </is>
+      </c>
+      <c r="D2493" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1564408/000192109426001031/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E2493" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Mohan Ajit (Officer) plans to sell 6,797 shares (~$39.6K) on/after 09/16/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2494">
+      <c r="A2494" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B2494" t="inlineStr">
+        <is>
+          <t>PINS</t>
+        </is>
+      </c>
+      <c r="C2494" t="inlineStr">
+        <is>
+          <t>Pinterest, Inc.</t>
+        </is>
+      </c>
+      <c r="D2494" t="inlineStr">
+        <is>
+          <t>https://newsroom.pinterest.com</t>
+        </is>
+      </c>
+      <c r="E2494" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2495">
+      <c r="A2495" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B2495" t="inlineStr">
+        <is>
+          <t>PINS</t>
+        </is>
+      </c>
+      <c r="C2495" t="inlineStr">
+        <is>
+          <t>Pinterest, Inc.</t>
+        </is>
+      </c>
+      <c r="D2495" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1506293/000177391426000027/xslF345X06/wk-form4_1789599138.xml</t>
+        </is>
+      </c>
+      <c r="E2495" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Silbermann Benjamin (Director) sold 93,750 shares @ $18.93 ($1.77M) on 2026-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="2496">
+      <c r="A2496" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B2496" t="inlineStr">
+        <is>
+          <t>PINS</t>
+        </is>
+      </c>
+      <c r="C2496" t="inlineStr">
+        <is>
+          <t>Pinterest, Inc.</t>
+        </is>
+      </c>
+      <c r="D2496" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1506293/000192109426001030/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E2496" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Silbermann Benjamin (Director) plans to sell 46,875 shares (~$873.6K) on/after 09/16/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2497">
+      <c r="A2497" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B2497" t="inlineStr">
+        <is>
+          <t>RDDT</t>
+        </is>
+      </c>
+      <c r="C2497" t="inlineStr">
+        <is>
+          <t>Reddit, Inc.</t>
+        </is>
+      </c>
+      <c r="D2497" t="inlineStr">
+        <is>
+          <t>https://redditinc.com/careers</t>
+        </is>
+      </c>
+      <c r="E2497" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2498">
+      <c r="A2498" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B2498" t="inlineStr">
+        <is>
+          <t>RDDT</t>
+        </is>
+      </c>
+      <c r="C2498" t="inlineStr">
+        <is>
+          <t>Reddit, Inc.</t>
+        </is>
+      </c>
+      <c r="D2498" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1713445/000166365126000021/xslF345X06/wk-form4_1789596929.xml</t>
+        </is>
+      </c>
+      <c r="E2498" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Wong Jennifer L. (Chief Operating Officer) sold 60,000 shares @ $162.33 ($9.74M) on 2026-09-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="2499">
+      <c r="A2499" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B2499" t="inlineStr">
+        <is>
+          <t>APP</t>
+        </is>
+      </c>
+      <c r="C2499" t="inlineStr">
+        <is>
+          <t>AppLovin Corporation</t>
+        </is>
+      </c>
+      <c r="D2499" t="inlineStr">
+        <is>
+          <t>https://www.applovin.com/blog/</t>
+        </is>
+      </c>
+      <c r="E2499" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2500">
+      <c r="A2500" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B2500" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="C2500" t="inlineStr">
+        <is>
+          <t>Unity Software Inc.</t>
+        </is>
+      </c>
+      <c r="D2500" t="inlineStr">
+        <is>
+          <t>https://careers.unity.com</t>
+        </is>
+      </c>
+      <c r="E2500" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2501">
+      <c r="A2501" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B2501" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="C2501" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="D2501" t="inlineStr">
+        <is>
+          <t>https://about.netflix.com/newsroom</t>
+        </is>
+      </c>
+      <c r="E2501" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2502">
+      <c r="A2502" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B2502" t="inlineStr">
+        <is>
+          <t>SPOT</t>
+        </is>
+      </c>
+      <c r="C2502" t="inlineStr">
+        <is>
+          <t>Spotify Technology S.A.</t>
+        </is>
+      </c>
+      <c r="D2502" t="inlineStr">
+        <is>
+          <t>https://newsroom.spotify.com</t>
+        </is>
+      </c>
+      <c r="E2502" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2503">
+      <c r="A2503" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B2503" t="inlineStr">
+        <is>
+          <t>SPOT</t>
+        </is>
+      </c>
+      <c r="C2503" t="inlineStr">
+        <is>
+          <t>Spotify Technology S.A.</t>
+        </is>
+      </c>
+      <c r="D2503" t="inlineStr">
+        <is>
+          <t>https://www.lifeatspotify.com</t>
+        </is>
+      </c>
+      <c r="E2503" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2504">
+      <c r="A2504" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B2504" t="inlineStr">
+        <is>
+          <t>SPOT</t>
+        </is>
+      </c>
+      <c r="C2504" t="inlineStr">
+        <is>
+          <t>Spotify Technology S.A.</t>
+        </is>
+      </c>
+      <c r="D2504" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1639920/000114036126036782/xslF345X06/form4.xml</t>
+        </is>
+      </c>
+      <c r="E2504" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Soderstrom Gustav (Co-Chief Executive Officer) sold 20,913 shares @ $544.19 ($11.38M) on 2026-09-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="2505">
+      <c r="A2505" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B2505" t="inlineStr">
+        <is>
+          <t>LIF</t>
+        </is>
+      </c>
+      <c r="C2505" t="inlineStr">
+        <is>
+          <t>LIF (verify ticker)</t>
+        </is>
+      </c>
+      <c r="D2505" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1581760/000158176026000162/xslF345X06/wk-form4_1789606409.xml</t>
+        </is>
+      </c>
+      <c r="E2505" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Prober Charles J. (Director) sold 7,930 shares @ $42.12 ($334.0K) on 2026-09-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="2506">
+      <c r="A2506" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B2506" t="inlineStr">
+        <is>
+          <t>BBY</t>
+        </is>
+      </c>
+      <c r="C2506" t="inlineStr">
+        <is>
+          <t>Best Buy Co., Inc.</t>
+        </is>
+      </c>
+      <c r="D2506" t="inlineStr">
+        <is>
+          <t>https://www.bestbuy.com/site/help-topics/terms-and-conditions/pcmcat204400050067.c</t>
+        </is>
+      </c>
+      <c r="E2506" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2507">
+      <c r="A2507" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B2507" t="inlineStr">
+        <is>
+          <t>BBY</t>
+        </is>
+      </c>
+      <c r="C2507" t="inlineStr">
+        <is>
+          <t>Best Buy Co., Inc.</t>
+        </is>
+      </c>
+      <c r="D2507" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/764478/000196794026000052/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E2507" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Richard M Schulze (10% Stockholder) plans to sell 300,000 shares (~$27.97M) on/after 09/16/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2508">
+      <c r="A2508" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B2508" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="C2508" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="D2508" t="inlineStr">
+        <is>
+          <t>https://www.disneyplus.com/welcome</t>
+        </is>
+      </c>
+      <c r="E2508" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2509">
+      <c r="A2509" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B2509" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="C2509" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="D2509" t="inlineStr">
+        <is>
+          <t>https://jobs.disneycareers.com</t>
+        </is>
+      </c>
+      <c r="E2509" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2510">
+      <c r="A2510" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B2510" t="inlineStr">
+        <is>
+          <t>FOXA</t>
+        </is>
+      </c>
+      <c r="C2510" t="inlineStr">
+        <is>
+          <t>Fox Corporation</t>
+        </is>
+      </c>
+      <c r="D2510" t="inlineStr">
+        <is>
+          <t>https://foxcareers.com</t>
+        </is>
+      </c>
+      <c r="E2510" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2511">
+      <c r="A2511" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B2511" t="inlineStr">
+        <is>
+          <t>FOXA</t>
+        </is>
+      </c>
+      <c r="C2511" t="inlineStr">
+        <is>
+          <t>Fox Corporation</t>
+        </is>
+      </c>
+      <c r="D2511" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1754301/000162828026062330/xslF345X06/wk-form4_1789596176.xml</t>
+        </is>
+      </c>
+      <c r="E2511" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Lachlan K Murdoch (Executive Chair, CEO) sold 149,934 shares @ $68.53 ($10.27M) on 2026-09-15; BOUGHT 149,934 shares @ $68.53 ($10.27M) on 2026-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="2512">
+      <c r="A2512" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B2512" t="inlineStr">
+        <is>
+          <t>WMG</t>
+        </is>
+      </c>
+      <c r="C2512" t="inlineStr">
+        <is>
+          <t>Warner Music Group Corp.</t>
+        </is>
+      </c>
+      <c r="D2512" t="inlineStr">
+        <is>
+          <t>https://www.wmg.com/news/</t>
+        </is>
+      </c>
+      <c r="E2512" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2513">
+      <c r="A2513" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B2513" t="inlineStr">
+        <is>
+          <t>LYV</t>
+        </is>
+      </c>
+      <c r="C2513" t="inlineStr">
+        <is>
+          <t>Live Nation Entertainment, Inc.</t>
+        </is>
+      </c>
+      <c r="D2513" t="inlineStr">
+        <is>
+          <t>https://investors.livenationentertainment.com</t>
+        </is>
+      </c>
+      <c r="E2513" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2514">
+      <c r="A2514" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B2514" t="inlineStr">
+        <is>
+          <t>LYV</t>
+        </is>
+      </c>
+      <c r="C2514" t="inlineStr">
+        <is>
+          <t>Live Nation Entertainment, Inc.</t>
+        </is>
+      </c>
+      <c r="D2514" t="inlineStr">
+        <is>
+          <t>https://www.livenationentertainment.com/careers</t>
+        </is>
+      </c>
+      <c r="E2514" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2515">
+      <c r="A2515" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B2515" t="inlineStr">
+        <is>
+          <t>STUB</t>
+        </is>
+      </c>
+      <c r="C2515" t="inlineStr">
+        <is>
+          <t>StubHub Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="D2515" t="inlineStr">
+        <is>
+          <t>https://www.stubhub.com/careers/</t>
+        </is>
+      </c>
+      <c r="E2515" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2516">
+      <c r="A2516" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B2516" t="inlineStr">
+        <is>
+          <t>LAMR</t>
+        </is>
+      </c>
+      <c r="C2516" t="inlineStr">
+        <is>
+          <t>Lamar Advertising Company</t>
+        </is>
+      </c>
+      <c r="D2516" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1090425/000119248226000451/xslF345X06/form4.xml</t>
+        </is>
+      </c>
+      <c r="E2516" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Thomas V Reifenheiser (Director) sold 8,099 shares @ $149.03 ($1.21M) on 2026-09-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="2517">
+      <c r="A2517" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B2517" t="inlineStr">
+        <is>
+          <t>TTWO</t>
+        </is>
+      </c>
+      <c r="C2517" t="inlineStr">
+        <is>
+          <t>Take-Two Interactive Software, Inc.</t>
+        </is>
+      </c>
+      <c r="D2517" t="inlineStr">
+        <is>
+          <t>https://ir.take2games.com</t>
+        </is>
+      </c>
+      <c r="E2517" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2518">
+      <c r="A2518" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B2518" t="inlineStr">
+        <is>
+          <t>TTWO</t>
+        </is>
+      </c>
+      <c r="C2518" t="inlineStr">
+        <is>
+          <t>Take-Two Interactive Software, Inc.</t>
+        </is>
+      </c>
+      <c r="D2518" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/946581/000094658126000082/xslF345X06/form4.xml</t>
+        </is>
+      </c>
+      <c r="E2518" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Siminoff Ellen F (Director) sold 334 shares @ $219.53 ($73.3K) on 2026-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="2519">
+      <c r="A2519" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B2519" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="C2519" t="inlineStr">
+        <is>
+          <t>Electronic Arts Inc.</t>
+        </is>
+      </c>
+      <c r="D2519" t="inlineStr">
+        <is>
+          <t>https://www.ea.com/news</t>
+        </is>
+      </c>
+      <c r="E2519" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2520">
+      <c r="A2520" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B2520" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="C2520" t="inlineStr">
+        <is>
+          <t>Electronic Arts Inc.</t>
+        </is>
+      </c>
+      <c r="D2520" t="inlineStr">
+        <is>
+          <t>https://ir.ea.com</t>
+        </is>
+      </c>
+      <c r="E2520" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2521">
+      <c r="A2521" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B2521" t="inlineStr">
+        <is>
+          <t>INTU</t>
+        </is>
+      </c>
+      <c r="C2521" t="inlineStr">
+        <is>
+          <t>Intuit Inc.</t>
+        </is>
+      </c>
+      <c r="D2521" t="inlineStr">
+        <is>
+          <t>https://investors.intuit.com</t>
+        </is>
+      </c>
+      <c r="E2521" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2522">
+      <c r="A2522" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B2522" t="inlineStr">
+        <is>
+          <t>PAYX</t>
+        </is>
+      </c>
+      <c r="C2522" t="inlineStr">
+        <is>
+          <t>Paychex, Inc.</t>
+        </is>
+      </c>
+      <c r="D2522" t="inlineStr">
+        <is>
+          <t>https://investor.paychex.com</t>
+        </is>
+      </c>
+      <c r="E2522" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2523">
+      <c r="A2523" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B2523" t="inlineStr">
+        <is>
+          <t>PCTY</t>
+        </is>
+      </c>
+      <c r="C2523" t="inlineStr">
+        <is>
+          <t>Paylocity Holding Corporation</t>
+        </is>
+      </c>
+      <c r="D2523" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1591698/000131483026000002/xslF345X06/wk-form4_1789588904.xml</t>
+        </is>
+      </c>
+      <c r="E2523" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Beauchamp Steven R (Executive Chairman) sold 15,000 shares @ $147.18 ($2.21M) on 2026-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="2524">
+      <c r="A2524" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B2524" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C2524" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D2524" t="inlineStr">
+        <is>
+          <t>https://www.shopify.com/careers</t>
+        </is>
+      </c>
+      <c r="E2524" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F2524" t="inlineStr"/>
+      <c r="G2524" t="inlineStr"/>
+      <c r="H2524" t="inlineStr"/>
+    </row>
+    <row r="2525">
+      <c r="A2525" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B2525" t="inlineStr">
+        <is>
+          <t>GLBE</t>
+        </is>
+      </c>
+      <c r="C2525" t="inlineStr">
+        <is>
+          <t>Global-E Online Ltd.</t>
+        </is>
+      </c>
+      <c r="D2525" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1835963/000119312526392875/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E2525" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Koren Ofer (CFO) sold 300 shares @ $38.00 ($11.4K) on 2026-09-14</t>
+        </is>
+      </c>
+      <c r="F2525" t="inlineStr"/>
+      <c r="G2525" t="inlineStr"/>
+      <c r="H2525" t="inlineStr"/>
+    </row>
+    <row r="2526">
+      <c r="A2526" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B2526" t="inlineStr">
+        <is>
+          <t>EBAY</t>
+        </is>
+      </c>
+      <c r="C2526" t="inlineStr">
+        <is>
+          <t>eBay Inc.</t>
+        </is>
+      </c>
+      <c r="D2526" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/help/policies/member-behaviour-policies/user-agreement?id=4259</t>
+        </is>
+      </c>
+      <c r="E2526" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+      <c r="F2526" t="inlineStr"/>
+      <c r="G2526" t="inlineStr"/>
+      <c r="H2526" t="inlineStr"/>
+    </row>
+    <row r="2527">
+      <c r="A2527" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B2527" t="inlineStr">
+        <is>
+          <t>EBAY</t>
+        </is>
+      </c>
+      <c r="C2527" t="inlineStr">
+        <is>
+          <t>eBay Inc.</t>
+        </is>
+      </c>
+      <c r="D2527" t="inlineStr">
+        <is>
+          <t>https://careers.ebayinc.com</t>
+        </is>
+      </c>
+      <c r="E2527" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F2527" t="inlineStr"/>
+      <c r="G2527" t="inlineStr"/>
+      <c r="H2527" t="inlineStr"/>
+    </row>
+    <row r="2528">
+      <c r="A2528" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B2528" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="C2528" t="inlineStr">
+        <is>
+          <t>Wayfair Inc.</t>
+        </is>
+      </c>
+      <c r="D2528" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1616707/000161670726000164/xslF345X06/wk-form4_1789593755.xml</t>
+        </is>
+      </c>
+      <c r="E2528" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Conine Steven (Director) sold 69,000 shares @ $103.36 ($7.13M) on 2026-09-14</t>
+        </is>
+      </c>
+      <c r="F2528" t="inlineStr"/>
+      <c r="G2528" t="inlineStr"/>
+      <c r="H2528" t="inlineStr"/>
+    </row>
+    <row r="2529">
+      <c r="A2529" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B2529" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="C2529" t="inlineStr">
+        <is>
+          <t>Wayfair Inc.</t>
+        </is>
+      </c>
+      <c r="D2529" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1616707/000161670726000162/xslF345X06/wk-form4_1789593603.xml</t>
+        </is>
+      </c>
+      <c r="E2529" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Shah Niraj (Chief Executive Officer) sold 69,000 shares @ $103.35 ($7.13M) on 2026-09-14</t>
+        </is>
+      </c>
+      <c r="F2529" t="inlineStr"/>
+      <c r="G2529" t="inlineStr"/>
+      <c r="H2529" t="inlineStr"/>
+    </row>
+    <row r="2530">
+      <c r="A2530" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B2530" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C2530" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D2530" t="inlineStr">
+        <is>
+          <t>https://about.doordash.com/en-us/news</t>
+        </is>
+      </c>
+      <c r="E2530" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F2530" t="inlineStr"/>
+      <c r="G2530" t="inlineStr"/>
+      <c r="H2530" t="inlineStr"/>
+    </row>
+    <row r="2531">
+      <c r="A2531" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B2531" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C2531" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D2531" t="inlineStr">
+        <is>
+          <t>https://instacart.careers/job/?gh_jid=8198284</t>
+        </is>
+      </c>
+      <c r="E2531" t="inlineStr">
+        <is>
+          <t>New senior role: Director of Product, Logistics</t>
+        </is>
+      </c>
+      <c r="F2531" t="inlineStr"/>
+      <c r="G2531" t="inlineStr"/>
+      <c r="H2531" t="inlineStr"/>
+    </row>
+    <row r="2532">
+      <c r="A2532" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B2532" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C2532" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D2532" t="inlineStr">
+        <is>
+          <t>https://instacart.careers/job/?gh_jid=8198282</t>
+        </is>
+      </c>
+      <c r="E2532" t="inlineStr">
+        <is>
+          <t>New senior role: Director of Product, Logistics</t>
+        </is>
+      </c>
+      <c r="F2532" t="inlineStr"/>
+      <c r="G2532" t="inlineStr"/>
+      <c r="H2532" t="inlineStr"/>
+    </row>
+    <row r="2533">
+      <c r="A2533" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B2533" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C2533" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D2533" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/instacart</t>
+        </is>
+      </c>
+      <c r="E2533" t="inlineStr">
+        <is>
+          <t>4 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F2533" t="inlineStr"/>
+      <c r="G2533" t="inlineStr"/>
+      <c r="H2533" t="inlineStr"/>
+    </row>
+    <row r="2534">
+      <c r="A2534" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B2534" t="inlineStr">
+        <is>
+          <t>DUOL</t>
+        </is>
+      </c>
+      <c r="C2534" t="inlineStr">
+        <is>
+          <t>Duolingo Inc.</t>
+        </is>
+      </c>
+      <c r="D2534" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/duolingo</t>
+        </is>
+      </c>
+      <c r="E2534" t="inlineStr">
+        <is>
+          <t>1 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F2534" t="inlineStr"/>
+      <c r="G2534" t="inlineStr"/>
+      <c r="H2534" t="inlineStr"/>
+    </row>
+    <row r="2535">
+      <c r="A2535" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B2535" t="inlineStr">
+        <is>
+          <t>DUOL</t>
+        </is>
+      </c>
+      <c r="C2535" t="inlineStr">
+        <is>
+          <t>Duolingo Inc.</t>
+        </is>
+      </c>
+      <c r="D2535" t="inlineStr">
+        <is>
+          <t>https://blog.duolingo.com/</t>
+        </is>
+      </c>
+      <c r="E2535" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F2535" t="inlineStr"/>
+      <c r="G2535" t="inlineStr"/>
+      <c r="H2535" t="inlineStr"/>
+    </row>
+    <row r="2536">
+      <c r="A2536" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B2536" t="inlineStr">
+        <is>
+          <t>DUOL</t>
+        </is>
+      </c>
+      <c r="C2536" t="inlineStr">
+        <is>
+          <t>Duolingo Inc.</t>
+        </is>
+      </c>
+      <c r="D2536" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1562088/000195004726009563/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E2536" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Von Ahn Arellano Luis (Director) plans to sell 28,292 shares (~$4.35M) on/after 09/16/2026</t>
+        </is>
+      </c>
+      <c r="F2536" t="inlineStr"/>
+      <c r="G2536" t="inlineStr"/>
+      <c r="H2536" t="inlineStr"/>
+    </row>
+    <row r="2537">
+      <c r="A2537" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B2537" t="inlineStr">
+        <is>
+          <t>DUOL</t>
+        </is>
+      </c>
+      <c r="C2537" t="inlineStr">
+        <is>
+          <t>Duolingo Inc.</t>
+        </is>
+      </c>
+      <c r="D2537" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1562088/000195004726009562/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E2537" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Von Ahn Foundation Luis (Director) plans to sell 19,008 shares (~$2.93M) on/after 09/16/2026</t>
+        </is>
+      </c>
+      <c r="F2537" t="inlineStr"/>
+      <c r="G2537" t="inlineStr"/>
+      <c r="H2537" t="inlineStr"/>
+    </row>
+    <row r="2538">
+      <c r="A2538" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B2538" t="inlineStr">
+        <is>
+          <t>RKT</t>
+        </is>
+      </c>
+      <c r="C2538" t="inlineStr">
+        <is>
+          <t>Rocket Companies Inc.</t>
+        </is>
+      </c>
+      <c r="D2538" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1805284/000180528426000107/xslF345X06/wk-form4_1789589171.xml</t>
+        </is>
+      </c>
+      <c r="E2538" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Bray Jesse K (Pres &amp; CEO, Rocket Mortgage) sold 225,000 shares @ $13.11 ($2.95M) on 2026-09-15</t>
+        </is>
+      </c>
+      <c r="F2538" t="inlineStr"/>
+      <c r="G2538" t="inlineStr"/>
+      <c r="H2538" t="inlineStr"/>
+    </row>
+    <row r="2539">
+      <c r="A2539" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B2539" t="inlineStr">
+        <is>
+          <t>COMP</t>
+        </is>
+      </c>
+      <c r="C2539" t="inlineStr">
+        <is>
+          <t>Compass Inc.</t>
+        </is>
+      </c>
+      <c r="D2539" t="inlineStr">
+        <is>
+          <t>https://investors.compass.com</t>
+        </is>
+      </c>
+      <c r="E2539" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+      <c r="F2539" t="inlineStr"/>
+      <c r="G2539" t="inlineStr"/>
+      <c r="H2539" t="inlineStr"/>
+    </row>
+    <row r="2540">
+      <c r="A2540" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B2540" t="inlineStr">
+        <is>
+          <t>COMP</t>
+        </is>
+      </c>
+      <c r="C2540" t="inlineStr">
+        <is>
+          <t>Compass Inc.</t>
+        </is>
+      </c>
+      <c r="D2540" t="inlineStr">
+        <is>
+          <t>https://www.compass.com/careers/</t>
+        </is>
+      </c>
+      <c r="E2540" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F2540" t="inlineStr"/>
+      <c r="G2540" t="inlineStr"/>
+      <c r="H2540" t="inlineStr"/>
+    </row>
+    <row r="2541">
+      <c r="A2541" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B2541" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C2541" t="inlineStr">
+        <is>
+          <t>Block Inc. (fmr. Square)</t>
+        </is>
+      </c>
+      <c r="D2541" t="inlineStr">
+        <is>
+          <t>https://investors.block.xyz</t>
+        </is>
+      </c>
+      <c r="E2541" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+      <c r="F2541" t="inlineStr"/>
+      <c r="G2541" t="inlineStr"/>
+      <c r="H2541" t="inlineStr"/>
+    </row>
+    <row r="2542">
+      <c r="A2542" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B2542" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C2542" t="inlineStr">
+        <is>
+          <t>Block Inc. (fmr. Square)</t>
+        </is>
+      </c>
+      <c r="D2542" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1512673/000195004726009548/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E2542" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — M Eisen Anthony (Director) plans to sell 6,000 shares (~$470.2K) on/after 09/16/2026</t>
+        </is>
+      </c>
+      <c r="F2542" t="inlineStr"/>
+      <c r="G2542" t="inlineStr"/>
+      <c r="H2542" t="inlineStr"/>
+    </row>
+    <row r="2543">
+      <c r="A2543" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B2543" t="inlineStr">
+        <is>
+          <t>PYPL</t>
+        </is>
+      </c>
+      <c r="C2543" t="inlineStr">
+        <is>
+          <t>PayPal Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D2543" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1633917/000129069726000006/xslF345X06/edgardoc.xml</t>
+        </is>
+      </c>
+      <c r="E2543" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Miller Jamie S (Chief Fin &amp; Op Officer) 6,129 shares withheld for taxes (vest event) on 2026-09-15</t>
+        </is>
+      </c>
+      <c r="F2543" t="inlineStr"/>
+      <c r="G2543" t="inlineStr"/>
+      <c r="H2543" t="inlineStr"/>
+    </row>
+    <row r="2544">
+      <c r="A2544" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B2544" t="inlineStr">
+        <is>
+          <t>TOST</t>
+        </is>
+      </c>
+      <c r="C2544" t="inlineStr">
+        <is>
+          <t>Toast Inc.</t>
+        </is>
+      </c>
+      <c r="D2544" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/toast</t>
+        </is>
+      </c>
+      <c r="E2544" t="inlineStr">
+        <is>
+          <t>16 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F2544" t="inlineStr"/>
+      <c r="G2544" t="inlineStr"/>
+      <c r="H2544" t="inlineStr"/>
+    </row>
+    <row r="2545">
+      <c r="A2545" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B2545" t="inlineStr">
+        <is>
+          <t>DAVE</t>
+        </is>
+      </c>
+      <c r="C2545" t="inlineStr">
+        <is>
+          <t>Dave Inc.</t>
+        </is>
+      </c>
+      <c r="D2545" t="inlineStr">
+        <is>
+          <t>https://dave.com/careers</t>
+        </is>
+      </c>
+      <c r="E2545" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F2545" t="inlineStr"/>
+      <c r="G2545" t="inlineStr"/>
+      <c r="H2545" t="inlineStr"/>
+    </row>
+    <row r="2546">
+      <c r="A2546" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B2546" t="inlineStr">
+        <is>
+          <t>DAVE</t>
+        </is>
+      </c>
+      <c r="C2546" t="inlineStr">
+        <is>
+          <t>Dave Inc.</t>
+        </is>
+      </c>
+      <c r="D2546" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1841408/000195004726009594/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E2546" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Rozov Yadin (Former Affiliate) plans to sell 54,782 shares (~$20.26M) on/after 09/16/2026</t>
+        </is>
+      </c>
+      <c r="F2546" t="inlineStr"/>
+      <c r="G2546" t="inlineStr"/>
+      <c r="H2546" t="inlineStr"/>
+    </row>
+    <row r="2547">
+      <c r="A2547" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B2547" t="inlineStr">
+        <is>
+          <t>AFRM</t>
+        </is>
+      </c>
+      <c r="C2547" t="inlineStr">
+        <is>
+          <t>Affirm Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D2547" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1820953/000162828026062240/xslF345X06/wk-form4_1789589247.xml</t>
+        </is>
+      </c>
+      <c r="E2547" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Jiyane Siphelele (Chief Accounting Officer) sold 26,980 shares @ $72.19 ($1.95M) on 2026-09-14</t>
+        </is>
+      </c>
+      <c r="F2547" t="inlineStr"/>
+      <c r="G2547" t="inlineStr"/>
+      <c r="H2547" t="inlineStr"/>
+    </row>
+    <row r="2548">
+      <c r="A2548" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B2548" t="inlineStr">
+        <is>
+          <t>HOOD</t>
+        </is>
+      </c>
+      <c r="C2548" t="inlineStr">
+        <is>
+          <t>Robinhood Markets Inc.</t>
+        </is>
+      </c>
+      <c r="D2548" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/robinhood</t>
+        </is>
+      </c>
+      <c r="E2548" t="inlineStr">
+        <is>
+          <t>4 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F2548" t="inlineStr"/>
+      <c r="G2548" t="inlineStr"/>
+      <c r="H2548" t="inlineStr"/>
+    </row>
+    <row r="2549">
+      <c r="A2549" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B2549" t="inlineStr">
+        <is>
+          <t>UPST</t>
+        </is>
+      </c>
+      <c r="C2549" t="inlineStr">
+        <is>
+          <t>Upstart Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D2549" t="inlineStr">
+        <is>
+          <t>https://careers.upstart.com/jobs?gh_jid=8189183</t>
+        </is>
+      </c>
+      <c r="E2549" t="inlineStr">
+        <is>
+          <t>New senior role: Director of Product, Machine Learning &amp; Decisioning Platforms</t>
+        </is>
+      </c>
+      <c r="F2549" t="inlineStr"/>
+      <c r="G2549" t="inlineStr"/>
+      <c r="H2549" t="inlineStr"/>
+    </row>
+    <row r="2550">
+      <c r="A2550" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B2550" t="inlineStr">
+        <is>
+          <t>UPST</t>
+        </is>
+      </c>
+      <c r="C2550" t="inlineStr">
+        <is>
+          <t>Upstart Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D2550" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/upstart</t>
+        </is>
+      </c>
+      <c r="E2550" t="inlineStr">
+        <is>
+          <t>1 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F2550" t="inlineStr"/>
+      <c r="G2550" t="inlineStr"/>
+      <c r="H2550" t="inlineStr"/>
+    </row>
+    <row r="2551">
+      <c r="A2551" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B2551" t="inlineStr">
+        <is>
+          <t>WSM</t>
+        </is>
+      </c>
+      <c r="C2551" t="inlineStr">
+        <is>
+          <t>Williams-Sonoma Inc.</t>
+        </is>
+      </c>
+      <c r="D2551" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/719955/000195824426000612/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E2551" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Jeffrey E. Howie (Officer) plans to sell 3,045 shares (~$664.4K) on/after 09/16/2026</t>
+        </is>
+      </c>
+      <c r="F2551" t="inlineStr"/>
+      <c r="G2551" t="inlineStr"/>
+      <c r="H2551" t="inlineStr"/>
+    </row>
+    <row r="2552">
+      <c r="A2552" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B2552" t="inlineStr">
+        <is>
+          <t>WSM</t>
+        </is>
+      </c>
+      <c r="C2552" t="inlineStr">
+        <is>
+          <t>Williams-Sonoma Inc.</t>
+        </is>
+      </c>
+      <c r="D2552" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/719955/000162828026062283/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E2552" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Alber Laura (OFFICER) plans to sell 35,000 shares (~$7.74M) on/after 09/16/2026</t>
+        </is>
+      </c>
+      <c r="F2552" t="inlineStr"/>
+      <c r="G2552" t="inlineStr"/>
+      <c r="H2552" t="inlineStr"/>
+    </row>
+    <row r="2553">
+      <c r="A2553" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B2553" t="inlineStr">
+        <is>
+          <t>SGI</t>
+        </is>
+      </c>
+      <c r="C2553" t="inlineStr">
+        <is>
+          <t>Somnigroup International Inc. (fmr. Tempur Sealy)</t>
+        </is>
+      </c>
+      <c r="D2553" t="inlineStr">
+        <is>
+          <t>https://www.somnigroup.com/terms</t>
+        </is>
+      </c>
+      <c r="E2553" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+      <c r="F2553" t="inlineStr"/>
+      <c r="G2553" t="inlineStr"/>
+      <c r="H2553" t="inlineStr"/>
+    </row>
+    <row r="2554">
+      <c r="A2554" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B2554" t="inlineStr">
+        <is>
+          <t>SGI</t>
+        </is>
+      </c>
+      <c r="C2554" t="inlineStr">
+        <is>
+          <t>Somnigroup International Inc. (fmr. Tempur Sealy)</t>
+        </is>
+      </c>
+      <c r="D2554" t="inlineStr">
+        <is>
+          <t>https://www.somnigroup.com/news</t>
+        </is>
+      </c>
+      <c r="E2554" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F2554" t="inlineStr"/>
+      <c r="G2554" t="inlineStr"/>
+      <c r="H2554" t="inlineStr"/>
+    </row>
+    <row r="2555">
+      <c r="A2555" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B2555" t="inlineStr">
+        <is>
+          <t>ONON</t>
+        </is>
+      </c>
+      <c r="C2555" t="inlineStr">
+        <is>
+          <t>On Holding AG</t>
+        </is>
+      </c>
+      <c r="D2555" t="inlineStr">
+        <is>
+          <t>https://www.on-running.com/en-us/articles/</t>
+        </is>
+      </c>
+      <c r="E2555" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F2555" t="inlineStr"/>
+      <c r="G2555" t="inlineStr"/>
+      <c r="H2555" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/config/company_urls_jc.xlsx
+++ b/config/company_urls_jc.xlsx
@@ -7203,7 +7203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2555"/>
+  <dimension ref="A1:H2635"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -75308,9 +75308,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F2524" t="inlineStr"/>
-      <c r="G2524" t="inlineStr"/>
-      <c r="H2524" t="inlineStr"/>
     </row>
     <row r="2525">
       <c r="A2525" t="inlineStr">
@@ -75338,9 +75335,6 @@
           <t>[ROUTINE] Insider trade — Koren Ofer (CFO) sold 300 shares @ $38.00 ($11.4K) on 2026-09-14</t>
         </is>
       </c>
-      <c r="F2525" t="inlineStr"/>
-      <c r="G2525" t="inlineStr"/>
-      <c r="H2525" t="inlineStr"/>
     </row>
     <row r="2526">
       <c r="A2526" t="inlineStr">
@@ -75368,9 +75362,6 @@
           <t>terms: change detected</t>
         </is>
       </c>
-      <c r="F2526" t="inlineStr"/>
-      <c r="G2526" t="inlineStr"/>
-      <c r="H2526" t="inlineStr"/>
     </row>
     <row r="2527">
       <c r="A2527" t="inlineStr">
@@ -75398,9 +75389,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F2527" t="inlineStr"/>
-      <c r="G2527" t="inlineStr"/>
-      <c r="H2527" t="inlineStr"/>
     </row>
     <row r="2528">
       <c r="A2528" t="inlineStr">
@@ -75428,9 +75416,6 @@
           <t>[ROUTINE] Insider trade — Conine Steven (Director) sold 69,000 shares @ $103.36 ($7.13M) on 2026-09-14</t>
         </is>
       </c>
-      <c r="F2528" t="inlineStr"/>
-      <c r="G2528" t="inlineStr"/>
-      <c r="H2528" t="inlineStr"/>
     </row>
     <row r="2529">
       <c r="A2529" t="inlineStr">
@@ -75458,9 +75443,6 @@
           <t>[ROUTINE] Insider trade — Shah Niraj (Chief Executive Officer) sold 69,000 shares @ $103.35 ($7.13M) on 2026-09-14</t>
         </is>
       </c>
-      <c r="F2529" t="inlineStr"/>
-      <c r="G2529" t="inlineStr"/>
-      <c r="H2529" t="inlineStr"/>
     </row>
     <row r="2530">
       <c r="A2530" t="inlineStr">
@@ -75488,9 +75470,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F2530" t="inlineStr"/>
-      <c r="G2530" t="inlineStr"/>
-      <c r="H2530" t="inlineStr"/>
     </row>
     <row r="2531">
       <c r="A2531" t="inlineStr">
@@ -75518,9 +75497,6 @@
           <t>New senior role: Director of Product, Logistics</t>
         </is>
       </c>
-      <c r="F2531" t="inlineStr"/>
-      <c r="G2531" t="inlineStr"/>
-      <c r="H2531" t="inlineStr"/>
     </row>
     <row r="2532">
       <c r="A2532" t="inlineStr">
@@ -75548,9 +75524,6 @@
           <t>New senior role: Director of Product, Logistics</t>
         </is>
       </c>
-      <c r="F2532" t="inlineStr"/>
-      <c r="G2532" t="inlineStr"/>
-      <c r="H2532" t="inlineStr"/>
     </row>
     <row r="2533">
       <c r="A2533" t="inlineStr">
@@ -75578,9 +75551,6 @@
           <t>4 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F2533" t="inlineStr"/>
-      <c r="G2533" t="inlineStr"/>
-      <c r="H2533" t="inlineStr"/>
     </row>
     <row r="2534">
       <c r="A2534" t="inlineStr">
@@ -75608,9 +75578,6 @@
           <t>1 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F2534" t="inlineStr"/>
-      <c r="G2534" t="inlineStr"/>
-      <c r="H2534" t="inlineStr"/>
     </row>
     <row r="2535">
       <c r="A2535" t="inlineStr">
@@ -75638,9 +75605,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F2535" t="inlineStr"/>
-      <c r="G2535" t="inlineStr"/>
-      <c r="H2535" t="inlineStr"/>
     </row>
     <row r="2536">
       <c r="A2536" t="inlineStr">
@@ -75668,9 +75632,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Von Ahn Arellano Luis (Director) plans to sell 28,292 shares (~$4.35M) on/after 09/16/2026</t>
         </is>
       </c>
-      <c r="F2536" t="inlineStr"/>
-      <c r="G2536" t="inlineStr"/>
-      <c r="H2536" t="inlineStr"/>
     </row>
     <row r="2537">
       <c r="A2537" t="inlineStr">
@@ -75698,9 +75659,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Von Ahn Foundation Luis (Director) plans to sell 19,008 shares (~$2.93M) on/after 09/16/2026</t>
         </is>
       </c>
-      <c r="F2537" t="inlineStr"/>
-      <c r="G2537" t="inlineStr"/>
-      <c r="H2537" t="inlineStr"/>
     </row>
     <row r="2538">
       <c r="A2538" t="inlineStr">
@@ -75728,9 +75686,6 @@
           <t>[ROUTINE] Insider trade — Bray Jesse K (Pres &amp; CEO, Rocket Mortgage) sold 225,000 shares @ $13.11 ($2.95M) on 2026-09-15</t>
         </is>
       </c>
-      <c r="F2538" t="inlineStr"/>
-      <c r="G2538" t="inlineStr"/>
-      <c r="H2538" t="inlineStr"/>
     </row>
     <row r="2539">
       <c r="A2539" t="inlineStr">
@@ -75758,9 +75713,6 @@
           <t>investor_relations: change detected</t>
         </is>
       </c>
-      <c r="F2539" t="inlineStr"/>
-      <c r="G2539" t="inlineStr"/>
-      <c r="H2539" t="inlineStr"/>
     </row>
     <row r="2540">
       <c r="A2540" t="inlineStr">
@@ -75788,9 +75740,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F2540" t="inlineStr"/>
-      <c r="G2540" t="inlineStr"/>
-      <c r="H2540" t="inlineStr"/>
     </row>
     <row r="2541">
       <c r="A2541" t="inlineStr">
@@ -75818,9 +75767,6 @@
           <t>investor_relations: change detected</t>
         </is>
       </c>
-      <c r="F2541" t="inlineStr"/>
-      <c r="G2541" t="inlineStr"/>
-      <c r="H2541" t="inlineStr"/>
     </row>
     <row r="2542">
       <c r="A2542" t="inlineStr">
@@ -75848,9 +75794,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — M Eisen Anthony (Director) plans to sell 6,000 shares (~$470.2K) on/after 09/16/2026</t>
         </is>
       </c>
-      <c r="F2542" t="inlineStr"/>
-      <c r="G2542" t="inlineStr"/>
-      <c r="H2542" t="inlineStr"/>
     </row>
     <row r="2543">
       <c r="A2543" t="inlineStr">
@@ -75878,9 +75821,6 @@
           <t>[ROUTINE] Insider trade — Miller Jamie S (Chief Fin &amp; Op Officer) 6,129 shares withheld for taxes (vest event) on 2026-09-15</t>
         </is>
       </c>
-      <c r="F2543" t="inlineStr"/>
-      <c r="G2543" t="inlineStr"/>
-      <c r="H2543" t="inlineStr"/>
     </row>
     <row r="2544">
       <c r="A2544" t="inlineStr">
@@ -75908,9 +75848,6 @@
           <t>16 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F2544" t="inlineStr"/>
-      <c r="G2544" t="inlineStr"/>
-      <c r="H2544" t="inlineStr"/>
     </row>
     <row r="2545">
       <c r="A2545" t="inlineStr">
@@ -75938,9 +75875,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F2545" t="inlineStr"/>
-      <c r="G2545" t="inlineStr"/>
-      <c r="H2545" t="inlineStr"/>
     </row>
     <row r="2546">
       <c r="A2546" t="inlineStr">
@@ -75968,9 +75902,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Rozov Yadin (Former Affiliate) plans to sell 54,782 shares (~$20.26M) on/after 09/16/2026</t>
         </is>
       </c>
-      <c r="F2546" t="inlineStr"/>
-      <c r="G2546" t="inlineStr"/>
-      <c r="H2546" t="inlineStr"/>
     </row>
     <row r="2547">
       <c r="A2547" t="inlineStr">
@@ -75998,9 +75929,6 @@
           <t>[ROUTINE] Insider trade — Jiyane Siphelele (Chief Accounting Officer) sold 26,980 shares @ $72.19 ($1.95M) on 2026-09-14</t>
         </is>
       </c>
-      <c r="F2547" t="inlineStr"/>
-      <c r="G2547" t="inlineStr"/>
-      <c r="H2547" t="inlineStr"/>
     </row>
     <row r="2548">
       <c r="A2548" t="inlineStr">
@@ -76028,9 +75956,6 @@
           <t>4 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F2548" t="inlineStr"/>
-      <c r="G2548" t="inlineStr"/>
-      <c r="H2548" t="inlineStr"/>
     </row>
     <row r="2549">
       <c r="A2549" t="inlineStr">
@@ -76058,9 +75983,6 @@
           <t>New senior role: Director of Product, Machine Learning &amp; Decisioning Platforms</t>
         </is>
       </c>
-      <c r="F2549" t="inlineStr"/>
-      <c r="G2549" t="inlineStr"/>
-      <c r="H2549" t="inlineStr"/>
     </row>
     <row r="2550">
       <c r="A2550" t="inlineStr">
@@ -76088,9 +76010,6 @@
           <t>1 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F2550" t="inlineStr"/>
-      <c r="G2550" t="inlineStr"/>
-      <c r="H2550" t="inlineStr"/>
     </row>
     <row r="2551">
       <c r="A2551" t="inlineStr">
@@ -76118,9 +76037,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Jeffrey E. Howie (Officer) plans to sell 3,045 shares (~$664.4K) on/after 09/16/2026</t>
         </is>
       </c>
-      <c r="F2551" t="inlineStr"/>
-      <c r="G2551" t="inlineStr"/>
-      <c r="H2551" t="inlineStr"/>
     </row>
     <row r="2552">
       <c r="A2552" t="inlineStr">
@@ -76148,9 +76064,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Alber Laura (OFFICER) plans to sell 35,000 shares (~$7.74M) on/after 09/16/2026</t>
         </is>
       </c>
-      <c r="F2552" t="inlineStr"/>
-      <c r="G2552" t="inlineStr"/>
-      <c r="H2552" t="inlineStr"/>
     </row>
     <row r="2553">
       <c r="A2553" t="inlineStr">
@@ -76178,9 +76091,6 @@
           <t>terms: change detected</t>
         </is>
       </c>
-      <c r="F2553" t="inlineStr"/>
-      <c r="G2553" t="inlineStr"/>
-      <c r="H2553" t="inlineStr"/>
     </row>
     <row r="2554">
       <c r="A2554" t="inlineStr">
@@ -76208,9 +76118,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F2554" t="inlineStr"/>
-      <c r="G2554" t="inlineStr"/>
-      <c r="H2554" t="inlineStr"/>
     </row>
     <row r="2555">
       <c r="A2555" t="inlineStr">
@@ -76238,9 +76145,2280 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F2555" t="inlineStr"/>
-      <c r="G2555" t="inlineStr"/>
-      <c r="H2555" t="inlineStr"/>
+    </row>
+    <row r="2556">
+      <c r="A2556" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B2556" t="inlineStr">
+        <is>
+          <t>LYFT</t>
+        </is>
+      </c>
+      <c r="C2556" t="inlineStr">
+        <is>
+          <t>Lyft, Inc.</t>
+        </is>
+      </c>
+      <c r="D2556" t="inlineStr">
+        <is>
+          <t>https://www.lyft.com/blog</t>
+        </is>
+      </c>
+      <c r="E2556" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2557">
+      <c r="A2557" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B2557" t="inlineStr">
+        <is>
+          <t>UBER</t>
+        </is>
+      </c>
+      <c r="C2557" t="inlineStr">
+        <is>
+          <t>Uber Technologies, Inc.</t>
+        </is>
+      </c>
+      <c r="D2557" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1543151/000155278126000495/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E2557" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Uber Technologies, Inc (10%+ owner) sold 29,369,611 shares @ $6.21 ($182.24M) on 2026-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="2558">
+      <c r="A2558" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B2558" t="inlineStr">
+        <is>
+          <t>UBER</t>
+        </is>
+      </c>
+      <c r="C2558" t="inlineStr">
+        <is>
+          <t>Uber Technologies, Inc.</t>
+        </is>
+      </c>
+      <c r="D2558" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1543151/000155278126000494/xslSCHEDULE_13D_X02/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E2558" t="inlineStr">
+        <is>
+          <t>[MATERIAL] Update to 5%+ active owner disclosure</t>
+        </is>
+      </c>
+    </row>
+    <row r="2559">
+      <c r="A2559" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B2559" t="inlineStr">
+        <is>
+          <t>EXPE</t>
+        </is>
+      </c>
+      <c r="C2559" t="inlineStr">
+        <is>
+          <t>Expedia Group, Inc.</t>
+        </is>
+      </c>
+      <c r="D2559" t="inlineStr">
+        <is>
+          <t>https://careers.expediagroup.com</t>
+        </is>
+      </c>
+      <c r="E2559" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2560">
+      <c r="A2560" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B2560" t="inlineStr">
+        <is>
+          <t>BKNG</t>
+        </is>
+      </c>
+      <c r="C2560" t="inlineStr">
+        <is>
+          <t>Booking Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D2560" t="inlineStr">
+        <is>
+          <t>https://www.booking.com/content/terms.html</t>
+        </is>
+      </c>
+      <c r="E2560" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2561">
+      <c r="A2561" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B2561" t="inlineStr">
+        <is>
+          <t>ABNB</t>
+        </is>
+      </c>
+      <c r="C2561" t="inlineStr">
+        <is>
+          <t>Airbnb, Inc.</t>
+        </is>
+      </c>
+      <c r="D2561" t="inlineStr">
+        <is>
+          <t>https://careers.airbnb.com</t>
+        </is>
+      </c>
+      <c r="E2561" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2562">
+      <c r="A2562" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B2562" t="inlineStr">
+        <is>
+          <t>ABNB</t>
+        </is>
+      </c>
+      <c r="C2562" t="inlineStr">
+        <is>
+          <t>Airbnb, Inc.</t>
+        </is>
+      </c>
+      <c r="D2562" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1559720/000119312526394396/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E2562" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Bernstein David C (Chief Accounting Officer) sold 1,489 shares @ $168.93 ($251.5K) on 2026-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="2563">
+      <c r="A2563" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B2563" t="inlineStr">
+        <is>
+          <t>SPHR</t>
+        </is>
+      </c>
+      <c r="C2563" t="inlineStr">
+        <is>
+          <t>Sphere Entertainment Co.</t>
+        </is>
+      </c>
+      <c r="D2563" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1795250/000119312526394321/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E2563" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Koester Jennifer (President &amp; COO, Sphere) 24,284 shares withheld for taxes (vest event) on 2026-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="2564">
+      <c r="A2564" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B2564" t="inlineStr">
+        <is>
+          <t>SPHR</t>
+        </is>
+      </c>
+      <c r="C2564" t="inlineStr">
+        <is>
+          <t>Sphere Entertainment Co.</t>
+        </is>
+      </c>
+      <c r="D2564" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1795250/000119312526394327/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E2564" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Granville-Smith David (Executive Vice President) 47,456 shares withheld for taxes (vest event) on 2026-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="2565">
+      <c r="A2565" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B2565" t="inlineStr">
+        <is>
+          <t>SPHR</t>
+        </is>
+      </c>
+      <c r="C2565" t="inlineStr">
+        <is>
+          <t>Sphere Entertainment Co.</t>
+        </is>
+      </c>
+      <c r="D2565" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1795250/000119312526394326/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E2565" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — James Lawrence Dolan (Executive Chairman and CEO) 54,921 shares withheld for taxes (vest event) on 2026-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="2566">
+      <c r="A2566" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B2566" t="inlineStr">
+        <is>
+          <t>SPHR</t>
+        </is>
+      </c>
+      <c r="C2566" t="inlineStr">
+        <is>
+          <t>Sphere Entertainment Co.</t>
+        </is>
+      </c>
+      <c r="D2566" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1795250/000119312526394310/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E2566" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Dolan Ryan Thomas (Director) 894 shares withheld for taxes (vest event) on 2026-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="2567">
+      <c r="A2567" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B2567" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="C2567" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="D2567" t="inlineStr">
+        <is>
+          <t>https://investor.atmeta.com</t>
+        </is>
+      </c>
+      <c r="E2567" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2568">
+      <c r="A2568" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B2568" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="C2568" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="D2568" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1326801/000095010326014140/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E2568" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Cox Christopher K (Chief Product Officer) sold 20,000 shares @ $675.23 ($13.50M) on 2026-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="2569">
+      <c r="A2569" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B2569" t="inlineStr">
+        <is>
+          <t>RDDT</t>
+        </is>
+      </c>
+      <c r="C2569" t="inlineStr">
+        <is>
+          <t>Reddit, Inc.</t>
+        </is>
+      </c>
+      <c r="D2569" t="inlineStr">
+        <is>
+          <t>https://redditinc.com/careers</t>
+        </is>
+      </c>
+      <c r="E2569" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2570">
+      <c r="A2570" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B2570" t="inlineStr">
+        <is>
+          <t>RDDT</t>
+        </is>
+      </c>
+      <c r="C2570" t="inlineStr">
+        <is>
+          <t>Reddit, Inc.</t>
+        </is>
+      </c>
+      <c r="D2570" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1713445/000171344526000109/xslF345X06/wk-form4_1789682506.xml</t>
+        </is>
+      </c>
+      <c r="E2570" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Huffman Steve Ladd (CEO &amp; President) sold 17,308 shares @ $160.11 ($2.77M) on 2026-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="2571">
+      <c r="A2571" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B2571" t="inlineStr">
+        <is>
+          <t>APP</t>
+        </is>
+      </c>
+      <c r="C2571" t="inlineStr">
+        <is>
+          <t>AppLovin Corporation</t>
+        </is>
+      </c>
+      <c r="D2571" t="inlineStr">
+        <is>
+          <t>https://www.applovin.com/legal/</t>
+        </is>
+      </c>
+      <c r="E2571" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2572">
+      <c r="A2572" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B2572" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="C2572" t="inlineStr">
+        <is>
+          <t>Unity Software Inc.</t>
+        </is>
+      </c>
+      <c r="D2572" t="inlineStr">
+        <is>
+          <t>https://careers.unity.com</t>
+        </is>
+      </c>
+      <c r="E2572" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2573">
+      <c r="A2573" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B2573" t="inlineStr">
+        <is>
+          <t>SPOT</t>
+        </is>
+      </c>
+      <c r="C2573" t="inlineStr">
+        <is>
+          <t>Spotify Technology S.A.</t>
+        </is>
+      </c>
+      <c r="D2573" t="inlineStr">
+        <is>
+          <t>https://newsroom.spotify.com</t>
+        </is>
+      </c>
+      <c r="E2573" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2574">
+      <c r="A2574" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B2574" t="inlineStr">
+        <is>
+          <t>SPOT</t>
+        </is>
+      </c>
+      <c r="C2574" t="inlineStr">
+        <is>
+          <t>Spotify Technology S.A.</t>
+        </is>
+      </c>
+      <c r="D2574" t="inlineStr">
+        <is>
+          <t>https://www.lifeatspotify.com</t>
+        </is>
+      </c>
+      <c r="E2574" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2575">
+      <c r="A2575" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B2575" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="C2575" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="D2575" t="inlineStr">
+        <is>
+          <t>https://www.disneyplus.com/welcome</t>
+        </is>
+      </c>
+      <c r="E2575" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2576">
+      <c r="A2576" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B2576" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="C2576" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="D2576" t="inlineStr">
+        <is>
+          <t>https://thewaltdisneycompany.com/news/</t>
+        </is>
+      </c>
+      <c r="E2576" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2577">
+      <c r="A2577" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B2577" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="C2577" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="D2577" t="inlineStr">
+        <is>
+          <t>https://jobs.disneycareers.com</t>
+        </is>
+      </c>
+      <c r="E2577" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2578">
+      <c r="A2578" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B2578" t="inlineStr">
+        <is>
+          <t>FOXA</t>
+        </is>
+      </c>
+      <c r="C2578" t="inlineStr">
+        <is>
+          <t>Fox Corporation</t>
+        </is>
+      </c>
+      <c r="D2578" t="inlineStr">
+        <is>
+          <t>https://investor.foxcorporation.com</t>
+        </is>
+      </c>
+      <c r="E2578" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2579">
+      <c r="A2579" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B2579" t="inlineStr">
+        <is>
+          <t>FOXA</t>
+        </is>
+      </c>
+      <c r="C2579" t="inlineStr">
+        <is>
+          <t>Fox Corporation</t>
+        </is>
+      </c>
+      <c r="D2579" t="inlineStr">
+        <is>
+          <t>https://foxcareers.com</t>
+        </is>
+      </c>
+      <c r="E2579" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2580">
+      <c r="A2580" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B2580" t="inlineStr">
+        <is>
+          <t>FOXA</t>
+        </is>
+      </c>
+      <c r="C2580" t="inlineStr">
+        <is>
+          <t>Fox Corporation</t>
+        </is>
+      </c>
+      <c r="D2580" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1754301/000162828026062486/fox2026annualreport.htm</t>
+        </is>
+      </c>
+      <c r="E2580" t="inlineStr">
+        <is>
+          <t>[UNKNOWN] Form ARS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2581">
+      <c r="A2581" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B2581" t="inlineStr">
+        <is>
+          <t>FOXA</t>
+        </is>
+      </c>
+      <c r="C2581" t="inlineStr">
+        <is>
+          <t>Fox Corporation</t>
+        </is>
+      </c>
+      <c r="D2581" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1754301/000162828026062482/defa14a2026.htm</t>
+        </is>
+      </c>
+      <c r="E2581" t="inlineStr">
+        <is>
+          <t>[UNKNOWN] Form DEFA14A</t>
+        </is>
+      </c>
+    </row>
+    <row r="2582">
+      <c r="A2582" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B2582" t="inlineStr">
+        <is>
+          <t>FOXA</t>
+        </is>
+      </c>
+      <c r="C2582" t="inlineStr">
+        <is>
+          <t>Fox Corporation</t>
+        </is>
+      </c>
+      <c r="D2582" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1754301/000162828026062480/fox-20260917.htm</t>
+        </is>
+      </c>
+      <c r="E2582" t="inlineStr">
+        <is>
+          <t>[MATERIAL] Proxy statement (annual meeting / governance vote)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2583">
+      <c r="A2583" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B2583" t="inlineStr">
+        <is>
+          <t>LYV</t>
+        </is>
+      </c>
+      <c r="C2583" t="inlineStr">
+        <is>
+          <t>Live Nation Entertainment, Inc.</t>
+        </is>
+      </c>
+      <c r="D2583" t="inlineStr">
+        <is>
+          <t>https://investors.livenationentertainment.com</t>
+        </is>
+      </c>
+      <c r="E2583" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2584">
+      <c r="A2584" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B2584" t="inlineStr">
+        <is>
+          <t>LYV</t>
+        </is>
+      </c>
+      <c r="C2584" t="inlineStr">
+        <is>
+          <t>Live Nation Entertainment, Inc.</t>
+        </is>
+      </c>
+      <c r="D2584" t="inlineStr">
+        <is>
+          <t>https://www.livenationentertainment.com/careers</t>
+        </is>
+      </c>
+      <c r="E2584" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2585">
+      <c r="A2585" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B2585" t="inlineStr">
+        <is>
+          <t>STUB</t>
+        </is>
+      </c>
+      <c r="C2585" t="inlineStr">
+        <is>
+          <t>StubHub Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="D2585" t="inlineStr">
+        <is>
+          <t>https://www.stubhub.com/careers/</t>
+        </is>
+      </c>
+      <c r="E2585" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2586">
+      <c r="A2586" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B2586" t="inlineStr">
+        <is>
+          <t>LION</t>
+        </is>
+      </c>
+      <c r="C2586" t="inlineStr">
+        <is>
+          <t>LION (verify ticker)</t>
+        </is>
+      </c>
+      <c r="D2586" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/2052959/000125824826000014/xslF345X06/wk-form4_1789678388.xml</t>
+        </is>
+      </c>
+      <c r="E2586" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Harry Sloan (Director) granted 18,767 shares on 2026-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="2587">
+      <c r="A2587" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B2587" t="inlineStr">
+        <is>
+          <t>LION</t>
+        </is>
+      </c>
+      <c r="C2587" t="inlineStr">
+        <is>
+          <t>LION (verify ticker)</t>
+        </is>
+      </c>
+      <c r="D2587" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/2052959/000150447126000002/xslF345X06/wk-form4_1789678369.xml</t>
+        </is>
+      </c>
+      <c r="E2587" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Rosenblatt M Richard (Director) granted 17,873 shares on 2026-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="2588">
+      <c r="A2588" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B2588" t="inlineStr">
+        <is>
+          <t>LION</t>
+        </is>
+      </c>
+      <c r="C2588" t="inlineStr">
+        <is>
+          <t>LION (verify ticker)</t>
+        </is>
+      </c>
+      <c r="D2588" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/2052959/000179699926000002/xslF345X06/wk-form4_1789678351.xml</t>
+        </is>
+      </c>
+      <c r="E2588" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Ostolaza Yvette (Director) granted 18,767 shares on 2026-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="2589">
+      <c r="A2589" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B2589" t="inlineStr">
+        <is>
+          <t>LION</t>
+        </is>
+      </c>
+      <c r="C2589" t="inlineStr">
+        <is>
+          <t>LION (verify ticker)</t>
+        </is>
+      </c>
+      <c r="D2589" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/2052959/000175209926000003/xslF345X06/wk-form4_1789678330.xml</t>
+        </is>
+      </c>
+      <c r="E2589" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — McCaw Susan (Director) granted 13,405 shares on 2026-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="2590">
+      <c r="A2590" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B2590" t="inlineStr">
+        <is>
+          <t>LION</t>
+        </is>
+      </c>
+      <c r="C2590" t="inlineStr">
+        <is>
+          <t>LION (verify ticker)</t>
+        </is>
+      </c>
+      <c r="D2590" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/2052959/000123577526000002/xslF345X06/wk-form4_1789678309.xml</t>
+        </is>
+      </c>
+      <c r="E2590" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — John D Jr Harkey (Director) granted 19,214 shares on 2026-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="2591">
+      <c r="A2591" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B2591" t="inlineStr">
+        <is>
+          <t>LION</t>
+        </is>
+      </c>
+      <c r="C2591" t="inlineStr">
+        <is>
+          <t>LION (verify ticker)</t>
+        </is>
+      </c>
+      <c r="D2591" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/2052959/000156753026000003/xslF345X06/wk-form4_1789678285.xml</t>
+        </is>
+      </c>
+      <c r="E2591" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Crawford Gordon (Director) granted 17,873 shares on 2026-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="2592">
+      <c r="A2592" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B2592" t="inlineStr">
+        <is>
+          <t>LION</t>
+        </is>
+      </c>
+      <c r="C2592" t="inlineStr">
+        <is>
+          <t>LION (verify ticker)</t>
+        </is>
+      </c>
+      <c r="D2592" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/2052959/000119312526394379/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E2592" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Mark H Md Rachesky (Director) granted 20,197 shares on 2026-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="2593">
+      <c r="A2593" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B2593" t="inlineStr">
+        <is>
+          <t>LION</t>
+        </is>
+      </c>
+      <c r="C2593" t="inlineStr">
+        <is>
+          <t>LION (verify ticker)</t>
+        </is>
+      </c>
+      <c r="D2593" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/2052959/000119312526394367/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E2593" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Emily Fine (Director) granted 17,873 shares on 2026-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="2594">
+      <c r="A2594" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B2594" t="inlineStr">
+        <is>
+          <t>TTWO</t>
+        </is>
+      </c>
+      <c r="C2594" t="inlineStr">
+        <is>
+          <t>Take-Two Interactive Software, Inc.</t>
+        </is>
+      </c>
+      <c r="D2594" t="inlineStr">
+        <is>
+          <t>https://ir.take2games.com</t>
+        </is>
+      </c>
+      <c r="E2594" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2595">
+      <c r="A2595" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B2595" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="C2595" t="inlineStr">
+        <is>
+          <t>Electronic Arts Inc.</t>
+        </is>
+      </c>
+      <c r="D2595" t="inlineStr">
+        <is>
+          <t>https://www.ea.com/news</t>
+        </is>
+      </c>
+      <c r="E2595" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2596">
+      <c r="A2596" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B2596" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="C2596" t="inlineStr">
+        <is>
+          <t>Electronic Arts Inc.</t>
+        </is>
+      </c>
+      <c r="D2596" t="inlineStr">
+        <is>
+          <t>https://ir.ea.com</t>
+        </is>
+      </c>
+      <c r="E2596" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2597">
+      <c r="A2597" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B2597" t="inlineStr">
+        <is>
+          <t>PCTY</t>
+        </is>
+      </c>
+      <c r="C2597" t="inlineStr">
+        <is>
+          <t>Paylocity Holding Corporation</t>
+        </is>
+      </c>
+      <c r="D2597" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1591698/000159169826000131/pcty-20260917.htm</t>
+        </is>
+      </c>
+      <c r="E2597" t="inlineStr">
+        <is>
+          <t>[MATERIAL] Material event disclosure</t>
+        </is>
+      </c>
+    </row>
+    <row r="2598">
+      <c r="A2598" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B2598" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C2598" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D2598" t="inlineStr">
+        <is>
+          <t>https://www.shopify.com/pricing</t>
+        </is>
+      </c>
+      <c r="E2598" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+      <c r="F2598" t="inlineStr"/>
+      <c r="G2598" t="inlineStr"/>
+      <c r="H2598" t="inlineStr"/>
+    </row>
+    <row r="2599">
+      <c r="A2599" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B2599" t="inlineStr">
+        <is>
+          <t>EBAY</t>
+        </is>
+      </c>
+      <c r="C2599" t="inlineStr">
+        <is>
+          <t>eBay Inc.</t>
+        </is>
+      </c>
+      <c r="D2599" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/help/policies/member-behaviour-policies/user-agreement?id=4259</t>
+        </is>
+      </c>
+      <c r="E2599" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+      <c r="F2599" t="inlineStr"/>
+      <c r="G2599" t="inlineStr"/>
+      <c r="H2599" t="inlineStr"/>
+    </row>
+    <row r="2600">
+      <c r="A2600" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B2600" t="inlineStr">
+        <is>
+          <t>EBAY</t>
+        </is>
+      </c>
+      <c r="C2600" t="inlineStr">
+        <is>
+          <t>eBay Inc.</t>
+        </is>
+      </c>
+      <c r="D2600" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1065088/000106508826000198/xslF345X06/form4.xml</t>
+        </is>
+      </c>
+      <c r="E2600" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Jamie Iannone (President and CEO) 19,481 shares withheld for taxes (vest event) on 2026-09-15</t>
+        </is>
+      </c>
+      <c r="F2600" t="inlineStr"/>
+      <c r="G2600" t="inlineStr"/>
+      <c r="H2600" t="inlineStr"/>
+    </row>
+    <row r="2601">
+      <c r="A2601" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B2601" t="inlineStr">
+        <is>
+          <t>EBAY</t>
+        </is>
+      </c>
+      <c r="C2601" t="inlineStr">
+        <is>
+          <t>eBay Inc.</t>
+        </is>
+      </c>
+      <c r="D2601" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1065088/000106508826000197/xslF345X06/form4.xml</t>
+        </is>
+      </c>
+      <c r="E2601" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Samantha Wellington (SVP, Chief Legal Officer) 1,804 shares withheld for taxes (vest event) on 2026-09-15</t>
+        </is>
+      </c>
+      <c r="F2601" t="inlineStr"/>
+      <c r="G2601" t="inlineStr"/>
+      <c r="H2601" t="inlineStr"/>
+    </row>
+    <row r="2602">
+      <c r="A2602" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B2602" t="inlineStr">
+        <is>
+          <t>EBAY</t>
+        </is>
+      </c>
+      <c r="C2602" t="inlineStr">
+        <is>
+          <t>eBay Inc.</t>
+        </is>
+      </c>
+      <c r="D2602" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1065088/000106508826000196/xslF345X06/form4.xml</t>
+        </is>
+      </c>
+      <c r="E2602" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Boone Cornelius (SVP, Chief People Officer) 3,379 shares withheld for taxes (vest event) on 2026-09-15</t>
+        </is>
+      </c>
+      <c r="F2602" t="inlineStr"/>
+      <c r="G2602" t="inlineStr"/>
+      <c r="H2602" t="inlineStr"/>
+    </row>
+    <row r="2603">
+      <c r="A2603" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B2603" t="inlineStr">
+        <is>
+          <t>EBAY</t>
+        </is>
+      </c>
+      <c r="C2603" t="inlineStr">
+        <is>
+          <t>eBay Inc.</t>
+        </is>
+      </c>
+      <c r="D2603" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1065088/000106508826000195/xslF345X06/form4.xml</t>
+        </is>
+      </c>
+      <c r="E2603" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Loeger Julie A (SVP, Chief Growth Officer) 10,610 shares withheld for taxes (vest event) on 2026-06-15</t>
+        </is>
+      </c>
+      <c r="F2603" t="inlineStr"/>
+      <c r="G2603" t="inlineStr"/>
+      <c r="H2603" t="inlineStr"/>
+    </row>
+    <row r="2604">
+      <c r="A2604" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B2604" t="inlineStr">
+        <is>
+          <t>EBAY</t>
+        </is>
+      </c>
+      <c r="C2604" t="inlineStr">
+        <is>
+          <t>eBay Inc.</t>
+        </is>
+      </c>
+      <c r="D2604" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1065088/000106508826000194/xslF345X06/form4.xml</t>
+        </is>
+      </c>
+      <c r="E2604" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Sweetnam Jordan Douglas Bradley (SVP, Chief Commercial Officer) 3,641 shares withheld for taxes (vest event) on 2026-09-15</t>
+        </is>
+      </c>
+      <c r="F2604" t="inlineStr"/>
+      <c r="G2604" t="inlineStr"/>
+      <c r="H2604" t="inlineStr"/>
+    </row>
+    <row r="2605">
+      <c r="A2605" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B2605" t="inlineStr">
+        <is>
+          <t>EBAY</t>
+        </is>
+      </c>
+      <c r="C2605" t="inlineStr">
+        <is>
+          <t>eBay Inc.</t>
+        </is>
+      </c>
+      <c r="D2605" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1065088/000106508826000193/xslF345X06/form4.xml</t>
+        </is>
+      </c>
+      <c r="E2605" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Rebecca Spencer (VP, Chief Accounting Officer) 1,362 shares withheld for taxes (vest event) on 2026-09-15</t>
+        </is>
+      </c>
+      <c r="F2605" t="inlineStr"/>
+      <c r="G2605" t="inlineStr"/>
+      <c r="H2605" t="inlineStr"/>
+    </row>
+    <row r="2606">
+      <c r="A2606" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B2606" t="inlineStr">
+        <is>
+          <t>EBAY</t>
+        </is>
+      </c>
+      <c r="C2606" t="inlineStr">
+        <is>
+          <t>eBay Inc.</t>
+        </is>
+      </c>
+      <c r="D2606" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1065088/000106508826000192/xslF345X06/form4.xml</t>
+        </is>
+      </c>
+      <c r="E2606" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Rawashdeh Mazen (SVP, Chief Technology Officer) 5,394 shares withheld for taxes (vest event) on 2026-09-15</t>
+        </is>
+      </c>
+      <c r="F2606" t="inlineStr"/>
+      <c r="G2606" t="inlineStr"/>
+      <c r="H2606" t="inlineStr"/>
+    </row>
+    <row r="2607">
+      <c r="A2607" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B2607" t="inlineStr">
+        <is>
+          <t>EBAY</t>
+        </is>
+      </c>
+      <c r="C2607" t="inlineStr">
+        <is>
+          <t>eBay Inc.</t>
+        </is>
+      </c>
+      <c r="D2607" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1065088/000106508826000191/xslF345X06/form4.xml</t>
+        </is>
+      </c>
+      <c r="E2607" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Alford Peggy (SVP, Chief Financial Officer) 2,716 shares withheld for taxes (vest event) on 2026-09-15</t>
+        </is>
+      </c>
+      <c r="F2607" t="inlineStr"/>
+      <c r="G2607" t="inlineStr"/>
+      <c r="H2607" t="inlineStr"/>
+    </row>
+    <row r="2608">
+      <c r="A2608" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B2608" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C2608" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D2608" t="inlineStr">
+        <is>
+          <t>https://about.doordash.com/en-us/news</t>
+        </is>
+      </c>
+      <c r="E2608" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F2608" t="inlineStr"/>
+      <c r="G2608" t="inlineStr"/>
+      <c r="H2608" t="inlineStr"/>
+    </row>
+    <row r="2609">
+      <c r="A2609" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B2609" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C2609" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D2609" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1792789/000195004726009629/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E2609" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Yandell Keith (Officer) plans to sell 2,184 shares (~$429.7K) on/after 09/17/2026</t>
+        </is>
+      </c>
+      <c r="F2609" t="inlineStr"/>
+      <c r="G2609" t="inlineStr"/>
+      <c r="H2609" t="inlineStr"/>
+    </row>
+    <row r="2610">
+      <c r="A2610" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B2610" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C2610" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D2610" t="inlineStr">
+        <is>
+          <t>https://instacart.careers/job/?gh_jid=8112138</t>
+        </is>
+      </c>
+      <c r="E2610" t="inlineStr">
+        <is>
+          <t>New senior role: Chief of Staff, Online Grocery</t>
+        </is>
+      </c>
+      <c r="F2610" t="inlineStr"/>
+      <c r="G2610" t="inlineStr"/>
+      <c r="H2610" t="inlineStr"/>
+    </row>
+    <row r="2611">
+      <c r="A2611" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B2611" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C2611" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D2611" t="inlineStr">
+        <is>
+          <t>https://instacart.careers/job/?gh_jid=8112136</t>
+        </is>
+      </c>
+      <c r="E2611" t="inlineStr">
+        <is>
+          <t>New senior role: Chief of Staff, Online Grocery</t>
+        </is>
+      </c>
+      <c r="F2611" t="inlineStr"/>
+      <c r="G2611" t="inlineStr"/>
+      <c r="H2611" t="inlineStr"/>
+    </row>
+    <row r="2612">
+      <c r="A2612" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B2612" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C2612" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D2612" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/instacart</t>
+        </is>
+      </c>
+      <c r="E2612" t="inlineStr">
+        <is>
+          <t>2 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F2612" t="inlineStr"/>
+      <c r="G2612" t="inlineStr"/>
+      <c r="H2612" t="inlineStr"/>
+    </row>
+    <row r="2613">
+      <c r="A2613" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B2613" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C2613" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D2613" t="inlineStr">
+        <is>
+          <t>https://www.instacart.com/instacart-plus</t>
+        </is>
+      </c>
+      <c r="E2613" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+      <c r="F2613" t="inlineStr"/>
+      <c r="G2613" t="inlineStr"/>
+      <c r="H2613" t="inlineStr"/>
+    </row>
+    <row r="2614">
+      <c r="A2614" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B2614" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C2614" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D2614" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1579091/000165168726000019/xslF345X06/wk-form4_1789675918.xml</t>
+        </is>
+      </c>
+      <c r="E2614" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Lisa Blackwood-Kapral (Chief Accounting Officer) sold 3,017 shares @ $47.08 ($142.0K) on 2026-09-15</t>
+        </is>
+      </c>
+      <c r="F2614" t="inlineStr"/>
+      <c r="G2614" t="inlineStr"/>
+      <c r="H2614" t="inlineStr"/>
+    </row>
+    <row r="2615">
+      <c r="A2615" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B2615" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="C2615" t="inlineStr">
+        <is>
+          <t>Zillow Group Inc.</t>
+        </is>
+      </c>
+      <c r="D2615" t="inlineStr">
+        <is>
+          <t>https://zillow.mediaroom.com</t>
+        </is>
+      </c>
+      <c r="E2615" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F2615" t="inlineStr"/>
+      <c r="G2615" t="inlineStr"/>
+      <c r="H2615" t="inlineStr"/>
+    </row>
+    <row r="2616">
+      <c r="A2616" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B2616" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="C2616" t="inlineStr">
+        <is>
+          <t>Zillow Group Inc.</t>
+        </is>
+      </c>
+      <c r="D2616" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1617640/000161764026000060/z-20260916.htm</t>
+        </is>
+      </c>
+      <c r="E2616" t="inlineStr">
+        <is>
+          <t>[MATERIAL] Material event disclosure</t>
+        </is>
+      </c>
+      <c r="F2616" t="inlineStr"/>
+      <c r="G2616" t="inlineStr"/>
+      <c r="H2616" t="inlineStr"/>
+    </row>
+    <row r="2617">
+      <c r="A2617" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B2617" t="inlineStr">
+        <is>
+          <t>COMP</t>
+        </is>
+      </c>
+      <c r="C2617" t="inlineStr">
+        <is>
+          <t>Compass Inc.</t>
+        </is>
+      </c>
+      <c r="D2617" t="inlineStr">
+        <is>
+          <t>https://www.compass.com/careers/</t>
+        </is>
+      </c>
+      <c r="E2617" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F2617" t="inlineStr"/>
+      <c r="G2617" t="inlineStr"/>
+      <c r="H2617" t="inlineStr"/>
+    </row>
+    <row r="2618">
+      <c r="A2618" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B2618" t="inlineStr">
+        <is>
+          <t>COMP</t>
+        </is>
+      </c>
+      <c r="C2618" t="inlineStr">
+        <is>
+          <t>Compass Inc.</t>
+        </is>
+      </c>
+      <c r="D2618" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1563190/000156319026000150/xslF345X06/wk-form4_1789675893.xml</t>
+        </is>
+      </c>
+      <c r="E2618" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Gustavson Timothy B. (Chief Accounting Officer) 1,176 shares withheld for taxes (vest event) on 2026-09-15</t>
+        </is>
+      </c>
+      <c r="F2618" t="inlineStr"/>
+      <c r="G2618" t="inlineStr"/>
+      <c r="H2618" t="inlineStr"/>
+    </row>
+    <row r="2619">
+      <c r="A2619" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B2619" t="inlineStr">
+        <is>
+          <t>COMP</t>
+        </is>
+      </c>
+      <c r="C2619" t="inlineStr">
+        <is>
+          <t>Compass Inc.</t>
+        </is>
+      </c>
+      <c r="D2619" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1563190/000156319026000149/xslF345X06/wk-form4_1789675868.xml</t>
+        </is>
+      </c>
+      <c r="E2619" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Glass Ethan Charles (Chief Legal Officer) 50,970 shares withheld for taxes (vest event) on 2026-09-15</t>
+        </is>
+      </c>
+      <c r="F2619" t="inlineStr"/>
+      <c r="G2619" t="inlineStr"/>
+      <c r="H2619" t="inlineStr"/>
+    </row>
+    <row r="2620">
+      <c r="A2620" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B2620" t="inlineStr">
+        <is>
+          <t>COMP</t>
+        </is>
+      </c>
+      <c r="C2620" t="inlineStr">
+        <is>
+          <t>Compass Inc.</t>
+        </is>
+      </c>
+      <c r="D2620" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1563190/000156319026000148/xslF345X06/wk-form4_1789675827.xml</t>
+        </is>
+      </c>
+      <c r="E2620" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Wahlers Scott R. (CFO) 24,297 shares withheld for taxes (vest event) on 2026-09-15</t>
+        </is>
+      </c>
+      <c r="F2620" t="inlineStr"/>
+      <c r="G2620" t="inlineStr"/>
+      <c r="H2620" t="inlineStr"/>
+    </row>
+    <row r="2621">
+      <c r="A2621" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B2621" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C2621" t="inlineStr">
+        <is>
+          <t>Block Inc. (fmr. Square)</t>
+        </is>
+      </c>
+      <c r="D2621" t="inlineStr">
+        <is>
+          <t>https://squareup.com/us/en/legal/general/ua</t>
+        </is>
+      </c>
+      <c r="E2621" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+      <c r="F2621" t="inlineStr"/>
+      <c r="G2621" t="inlineStr"/>
+      <c r="H2621" t="inlineStr"/>
+    </row>
+    <row r="2622">
+      <c r="A2622" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B2622" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C2622" t="inlineStr">
+        <is>
+          <t>Block Inc. (fmr. Square)</t>
+        </is>
+      </c>
+      <c r="D2622" t="inlineStr">
+        <is>
+          <t>https://investors.block.xyz</t>
+        </is>
+      </c>
+      <c r="E2622" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+      <c r="F2622" t="inlineStr"/>
+      <c r="G2622" t="inlineStr"/>
+      <c r="H2622" t="inlineStr"/>
+    </row>
+    <row r="2623">
+      <c r="A2623" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B2623" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C2623" t="inlineStr">
+        <is>
+          <t>Block Inc. (fmr. Square)</t>
+        </is>
+      </c>
+      <c r="D2623" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1512673/000195004726009613/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E2623" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — M Eisen Anthony (Director) plans to sell 6,000 shares (~$467.8K) on/after 09/17/2026</t>
+        </is>
+      </c>
+      <c r="F2623" t="inlineStr"/>
+      <c r="G2623" t="inlineStr"/>
+      <c r="H2623" t="inlineStr"/>
+    </row>
+    <row r="2624">
+      <c r="A2624" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B2624" t="inlineStr">
+        <is>
+          <t>BILL</t>
+        </is>
+      </c>
+      <c r="C2624" t="inlineStr">
+        <is>
+          <t>BILL Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D2624" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1786352/000206742526000004/xslF345X06/form4-09172026_040909.xml</t>
+        </is>
+      </c>
+      <c r="E2624" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Cieri Michael (Chief Product Officer) granted 46,856 Restricted Stock Units on 2026-09-15</t>
+        </is>
+      </c>
+      <c r="F2624" t="inlineStr"/>
+      <c r="G2624" t="inlineStr"/>
+      <c r="H2624" t="inlineStr"/>
+    </row>
+    <row r="2625">
+      <c r="A2625" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B2625" t="inlineStr">
+        <is>
+          <t>BILL</t>
+        </is>
+      </c>
+      <c r="C2625" t="inlineStr">
+        <is>
+          <t>BILL Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D2625" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1786352/000207397026000003/xslF345X06/form4-09172026_040907.xml</t>
+        </is>
+      </c>
+      <c r="E2625" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Jain Rohini (Chief Financial Officer) granted 67,681 Restricted Stock Units on 2026-09-15</t>
+        </is>
+      </c>
+      <c r="F2625" t="inlineStr"/>
+      <c r="G2625" t="inlineStr"/>
+      <c r="H2625" t="inlineStr"/>
+    </row>
+    <row r="2626">
+      <c r="A2626" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B2626" t="inlineStr">
+        <is>
+          <t>BILL</t>
+        </is>
+      </c>
+      <c r="C2626" t="inlineStr">
+        <is>
+          <t>BILL Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D2626" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1786352/000179549726000006/xslF345X06/form4-09172026_040905.xml</t>
+        </is>
+      </c>
+      <c r="E2626" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Lacerte Rene A. (CEO) granted 116,619 Restricted Stock Units on 2026-09-15</t>
+        </is>
+      </c>
+      <c r="F2626" t="inlineStr"/>
+      <c r="G2626" t="inlineStr"/>
+      <c r="H2626" t="inlineStr"/>
+    </row>
+    <row r="2627">
+      <c r="A2627" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B2627" t="inlineStr">
+        <is>
+          <t>TOST</t>
+        </is>
+      </c>
+      <c r="C2627" t="inlineStr">
+        <is>
+          <t>Toast Inc.</t>
+        </is>
+      </c>
+      <c r="D2627" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/toast</t>
+        </is>
+      </c>
+      <c r="E2627" t="inlineStr">
+        <is>
+          <t>9 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F2627" t="inlineStr"/>
+      <c r="G2627" t="inlineStr"/>
+      <c r="H2627" t="inlineStr"/>
+    </row>
+    <row r="2628">
+      <c r="A2628" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B2628" t="inlineStr">
+        <is>
+          <t>HOOD</t>
+        </is>
+      </c>
+      <c r="C2628" t="inlineStr">
+        <is>
+          <t>Robinhood Markets Inc.</t>
+        </is>
+      </c>
+      <c r="D2628" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/robinhood</t>
+        </is>
+      </c>
+      <c r="E2628" t="inlineStr">
+        <is>
+          <t>3 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F2628" t="inlineStr"/>
+      <c r="G2628" t="inlineStr"/>
+      <c r="H2628" t="inlineStr"/>
+    </row>
+    <row r="2629">
+      <c r="A2629" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B2629" t="inlineStr">
+        <is>
+          <t>HOOD</t>
+        </is>
+      </c>
+      <c r="C2629" t="inlineStr">
+        <is>
+          <t>Robinhood Markets Inc.</t>
+        </is>
+      </c>
+      <c r="D2629" t="inlineStr">
+        <is>
+          <t>https://newsroom.aboutrobinhood.com</t>
+        </is>
+      </c>
+      <c r="E2629" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F2629" t="inlineStr"/>
+      <c r="G2629" t="inlineStr"/>
+      <c r="H2629" t="inlineStr"/>
+    </row>
+    <row r="2630">
+      <c r="A2630" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B2630" t="inlineStr">
+        <is>
+          <t>HOOD</t>
+        </is>
+      </c>
+      <c r="C2630" t="inlineStr">
+        <is>
+          <t>Robinhood Markets Inc.</t>
+        </is>
+      </c>
+      <c r="D2630" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1783879/000210858926000024/xslF345X06/wk-form4_1789677670.xml</t>
+        </is>
+      </c>
+      <c r="E2630" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Verma Shiv (Chief Financial Officer) sold 11,472 shares @ $110.42 ($1.27M) on 2026-09-15</t>
+        </is>
+      </c>
+      <c r="F2630" t="inlineStr"/>
+      <c r="G2630" t="inlineStr"/>
+      <c r="H2630" t="inlineStr"/>
+    </row>
+    <row r="2631">
+      <c r="A2631" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B2631" t="inlineStr">
+        <is>
+          <t>UPST</t>
+        </is>
+      </c>
+      <c r="C2631" t="inlineStr">
+        <is>
+          <t>Upstart Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D2631" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/upstart</t>
+        </is>
+      </c>
+      <c r="E2631" t="inlineStr">
+        <is>
+          <t>1 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F2631" t="inlineStr"/>
+      <c r="G2631" t="inlineStr"/>
+      <c r="H2631" t="inlineStr"/>
+    </row>
+    <row r="2632">
+      <c r="A2632" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B2632" t="inlineStr">
+        <is>
+          <t>RH</t>
+        </is>
+      </c>
+      <c r="C2632" t="inlineStr">
+        <is>
+          <t>RH (Restoration Hardware)</t>
+        </is>
+      </c>
+      <c r="D2632" t="inlineStr">
+        <is>
+          <t>https://ir.rh.com/news-releases</t>
+        </is>
+      </c>
+      <c r="E2632" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F2632" t="inlineStr"/>
+      <c r="G2632" t="inlineStr"/>
+      <c r="H2632" t="inlineStr"/>
+    </row>
+    <row r="2633">
+      <c r="A2633" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B2633" t="inlineStr">
+        <is>
+          <t>RH</t>
+        </is>
+      </c>
+      <c r="C2633" t="inlineStr">
+        <is>
+          <t>RH (Restoration Hardware)</t>
+        </is>
+      </c>
+      <c r="D2633" t="inlineStr">
+        <is>
+          <t>https://ir.rh.com</t>
+        </is>
+      </c>
+      <c r="E2633" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+      <c r="F2633" t="inlineStr"/>
+      <c r="G2633" t="inlineStr"/>
+      <c r="H2633" t="inlineStr"/>
+    </row>
+    <row r="2634">
+      <c r="A2634" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B2634" t="inlineStr">
+        <is>
+          <t>ENVA</t>
+        </is>
+      </c>
+      <c r="C2634" t="inlineStr">
+        <is>
+          <t>Enova International Inc.</t>
+        </is>
+      </c>
+      <c r="D2634" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1529864/000162828026062583/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E2634" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — David Fisher (Officer) plans to sell 31,163 shares (~$5.36M) on/after 09/17/2026</t>
+        </is>
+      </c>
+      <c r="F2634" t="inlineStr"/>
+      <c r="G2634" t="inlineStr"/>
+      <c r="H2634" t="inlineStr"/>
+    </row>
+    <row r="2635">
+      <c r="A2635" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B2635" t="inlineStr">
+        <is>
+          <t>ENVA</t>
+        </is>
+      </c>
+      <c r="C2635" t="inlineStr">
+        <is>
+          <t>Enova International Inc.</t>
+        </is>
+      </c>
+      <c r="D2635" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1529864/000119312526394356/enva-20260917.htm</t>
+        </is>
+      </c>
+      <c r="E2635" t="inlineStr">
+        <is>
+          <t>[MATERIAL] Material event disclosure</t>
+        </is>
+      </c>
+      <c r="F2635" t="inlineStr"/>
+      <c r="G2635" t="inlineStr"/>
+      <c r="H2635" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/config/company_urls_jc.xlsx
+++ b/config/company_urls_jc.xlsx
@@ -7203,7 +7203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2635"/>
+  <dimension ref="A1:H2673"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -77306,9 +77306,6 @@
           <t>pricing: change detected</t>
         </is>
       </c>
-      <c r="F2598" t="inlineStr"/>
-      <c r="G2598" t="inlineStr"/>
-      <c r="H2598" t="inlineStr"/>
     </row>
     <row r="2599">
       <c r="A2599" t="inlineStr">
@@ -77336,9 +77333,6 @@
           <t>terms: change detected</t>
         </is>
       </c>
-      <c r="F2599" t="inlineStr"/>
-      <c r="G2599" t="inlineStr"/>
-      <c r="H2599" t="inlineStr"/>
     </row>
     <row r="2600">
       <c r="A2600" t="inlineStr">
@@ -77366,9 +77360,6 @@
           <t>[ROUTINE] Insider trade — Jamie Iannone (President and CEO) 19,481 shares withheld for taxes (vest event) on 2026-09-15</t>
         </is>
       </c>
-      <c r="F2600" t="inlineStr"/>
-      <c r="G2600" t="inlineStr"/>
-      <c r="H2600" t="inlineStr"/>
     </row>
     <row r="2601">
       <c r="A2601" t="inlineStr">
@@ -77396,9 +77387,6 @@
           <t>[ROUTINE] Insider trade — Samantha Wellington (SVP, Chief Legal Officer) 1,804 shares withheld for taxes (vest event) on 2026-09-15</t>
         </is>
       </c>
-      <c r="F2601" t="inlineStr"/>
-      <c r="G2601" t="inlineStr"/>
-      <c r="H2601" t="inlineStr"/>
     </row>
     <row r="2602">
       <c r="A2602" t="inlineStr">
@@ -77426,9 +77414,6 @@
           <t>[ROUTINE] Insider trade — Boone Cornelius (SVP, Chief People Officer) 3,379 shares withheld for taxes (vest event) on 2026-09-15</t>
         </is>
       </c>
-      <c r="F2602" t="inlineStr"/>
-      <c r="G2602" t="inlineStr"/>
-      <c r="H2602" t="inlineStr"/>
     </row>
     <row r="2603">
       <c r="A2603" t="inlineStr">
@@ -77456,9 +77441,6 @@
           <t>[ROUTINE] Insider trade — Loeger Julie A (SVP, Chief Growth Officer) 10,610 shares withheld for taxes (vest event) on 2026-06-15</t>
         </is>
       </c>
-      <c r="F2603" t="inlineStr"/>
-      <c r="G2603" t="inlineStr"/>
-      <c r="H2603" t="inlineStr"/>
     </row>
     <row r="2604">
       <c r="A2604" t="inlineStr">
@@ -77486,9 +77468,6 @@
           <t>[ROUTINE] Insider trade — Sweetnam Jordan Douglas Bradley (SVP, Chief Commercial Officer) 3,641 shares withheld for taxes (vest event) on 2026-09-15</t>
         </is>
       </c>
-      <c r="F2604" t="inlineStr"/>
-      <c r="G2604" t="inlineStr"/>
-      <c r="H2604" t="inlineStr"/>
     </row>
     <row r="2605">
       <c r="A2605" t="inlineStr">
@@ -77516,9 +77495,6 @@
           <t>[ROUTINE] Insider trade — Rebecca Spencer (VP, Chief Accounting Officer) 1,362 shares withheld for taxes (vest event) on 2026-09-15</t>
         </is>
       </c>
-      <c r="F2605" t="inlineStr"/>
-      <c r="G2605" t="inlineStr"/>
-      <c r="H2605" t="inlineStr"/>
     </row>
     <row r="2606">
       <c r="A2606" t="inlineStr">
@@ -77546,9 +77522,6 @@
           <t>[ROUTINE] Insider trade — Rawashdeh Mazen (SVP, Chief Technology Officer) 5,394 shares withheld for taxes (vest event) on 2026-09-15</t>
         </is>
       </c>
-      <c r="F2606" t="inlineStr"/>
-      <c r="G2606" t="inlineStr"/>
-      <c r="H2606" t="inlineStr"/>
     </row>
     <row r="2607">
       <c r="A2607" t="inlineStr">
@@ -77576,9 +77549,6 @@
           <t>[ROUTINE] Insider trade — Alford Peggy (SVP, Chief Financial Officer) 2,716 shares withheld for taxes (vest event) on 2026-09-15</t>
         </is>
       </c>
-      <c r="F2607" t="inlineStr"/>
-      <c r="G2607" t="inlineStr"/>
-      <c r="H2607" t="inlineStr"/>
     </row>
     <row r="2608">
       <c r="A2608" t="inlineStr">
@@ -77606,9 +77576,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F2608" t="inlineStr"/>
-      <c r="G2608" t="inlineStr"/>
-      <c r="H2608" t="inlineStr"/>
     </row>
     <row r="2609">
       <c r="A2609" t="inlineStr">
@@ -77636,9 +77603,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Yandell Keith (Officer) plans to sell 2,184 shares (~$429.7K) on/after 09/17/2026</t>
         </is>
       </c>
-      <c r="F2609" t="inlineStr"/>
-      <c r="G2609" t="inlineStr"/>
-      <c r="H2609" t="inlineStr"/>
     </row>
     <row r="2610">
       <c r="A2610" t="inlineStr">
@@ -77666,9 +77630,6 @@
           <t>New senior role: Chief of Staff, Online Grocery</t>
         </is>
       </c>
-      <c r="F2610" t="inlineStr"/>
-      <c r="G2610" t="inlineStr"/>
-      <c r="H2610" t="inlineStr"/>
     </row>
     <row r="2611">
       <c r="A2611" t="inlineStr">
@@ -77696,9 +77657,6 @@
           <t>New senior role: Chief of Staff, Online Grocery</t>
         </is>
       </c>
-      <c r="F2611" t="inlineStr"/>
-      <c r="G2611" t="inlineStr"/>
-      <c r="H2611" t="inlineStr"/>
     </row>
     <row r="2612">
       <c r="A2612" t="inlineStr">
@@ -77726,9 +77684,6 @@
           <t>2 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F2612" t="inlineStr"/>
-      <c r="G2612" t="inlineStr"/>
-      <c r="H2612" t="inlineStr"/>
     </row>
     <row r="2613">
       <c r="A2613" t="inlineStr">
@@ -77756,9 +77711,6 @@
           <t>pricing: change detected</t>
         </is>
       </c>
-      <c r="F2613" t="inlineStr"/>
-      <c r="G2613" t="inlineStr"/>
-      <c r="H2613" t="inlineStr"/>
     </row>
     <row r="2614">
       <c r="A2614" t="inlineStr">
@@ -77786,9 +77738,6 @@
           <t>[ROUTINE] Insider trade — Lisa Blackwood-Kapral (Chief Accounting Officer) sold 3,017 shares @ $47.08 ($142.0K) on 2026-09-15</t>
         </is>
       </c>
-      <c r="F2614" t="inlineStr"/>
-      <c r="G2614" t="inlineStr"/>
-      <c r="H2614" t="inlineStr"/>
     </row>
     <row r="2615">
       <c r="A2615" t="inlineStr">
@@ -77816,9 +77765,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F2615" t="inlineStr"/>
-      <c r="G2615" t="inlineStr"/>
-      <c r="H2615" t="inlineStr"/>
     </row>
     <row r="2616">
       <c r="A2616" t="inlineStr">
@@ -77846,9 +77792,6 @@
           <t>[MATERIAL] Material event disclosure</t>
         </is>
       </c>
-      <c r="F2616" t="inlineStr"/>
-      <c r="G2616" t="inlineStr"/>
-      <c r="H2616" t="inlineStr"/>
     </row>
     <row r="2617">
       <c r="A2617" t="inlineStr">
@@ -77876,9 +77819,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F2617" t="inlineStr"/>
-      <c r="G2617" t="inlineStr"/>
-      <c r="H2617" t="inlineStr"/>
     </row>
     <row r="2618">
       <c r="A2618" t="inlineStr">
@@ -77906,9 +77846,6 @@
           <t>[ROUTINE] Insider trade — Gustavson Timothy B. (Chief Accounting Officer) 1,176 shares withheld for taxes (vest event) on 2026-09-15</t>
         </is>
       </c>
-      <c r="F2618" t="inlineStr"/>
-      <c r="G2618" t="inlineStr"/>
-      <c r="H2618" t="inlineStr"/>
     </row>
     <row r="2619">
       <c r="A2619" t="inlineStr">
@@ -77936,9 +77873,6 @@
           <t>[ROUTINE] Insider trade — Glass Ethan Charles (Chief Legal Officer) 50,970 shares withheld for taxes (vest event) on 2026-09-15</t>
         </is>
       </c>
-      <c r="F2619" t="inlineStr"/>
-      <c r="G2619" t="inlineStr"/>
-      <c r="H2619" t="inlineStr"/>
     </row>
     <row r="2620">
       <c r="A2620" t="inlineStr">
@@ -77966,9 +77900,6 @@
           <t>[ROUTINE] Insider trade — Wahlers Scott R. (CFO) 24,297 shares withheld for taxes (vest event) on 2026-09-15</t>
         </is>
       </c>
-      <c r="F2620" t="inlineStr"/>
-      <c r="G2620" t="inlineStr"/>
-      <c r="H2620" t="inlineStr"/>
     </row>
     <row r="2621">
       <c r="A2621" t="inlineStr">
@@ -77996,9 +77927,6 @@
           <t>terms: change detected</t>
         </is>
       </c>
-      <c r="F2621" t="inlineStr"/>
-      <c r="G2621" t="inlineStr"/>
-      <c r="H2621" t="inlineStr"/>
     </row>
     <row r="2622">
       <c r="A2622" t="inlineStr">
@@ -78026,9 +77954,6 @@
           <t>investor_relations: change detected</t>
         </is>
       </c>
-      <c r="F2622" t="inlineStr"/>
-      <c r="G2622" t="inlineStr"/>
-      <c r="H2622" t="inlineStr"/>
     </row>
     <row r="2623">
       <c r="A2623" t="inlineStr">
@@ -78056,9 +77981,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — M Eisen Anthony (Director) plans to sell 6,000 shares (~$467.8K) on/after 09/17/2026</t>
         </is>
       </c>
-      <c r="F2623" t="inlineStr"/>
-      <c r="G2623" t="inlineStr"/>
-      <c r="H2623" t="inlineStr"/>
     </row>
     <row r="2624">
       <c r="A2624" t="inlineStr">
@@ -78086,9 +78008,6 @@
           <t>[ROUTINE] Insider trade — Cieri Michael (Chief Product Officer) granted 46,856 Restricted Stock Units on 2026-09-15</t>
         </is>
       </c>
-      <c r="F2624" t="inlineStr"/>
-      <c r="G2624" t="inlineStr"/>
-      <c r="H2624" t="inlineStr"/>
     </row>
     <row r="2625">
       <c r="A2625" t="inlineStr">
@@ -78116,9 +78035,6 @@
           <t>[ROUTINE] Insider trade — Jain Rohini (Chief Financial Officer) granted 67,681 Restricted Stock Units on 2026-09-15</t>
         </is>
       </c>
-      <c r="F2625" t="inlineStr"/>
-      <c r="G2625" t="inlineStr"/>
-      <c r="H2625" t="inlineStr"/>
     </row>
     <row r="2626">
       <c r="A2626" t="inlineStr">
@@ -78146,9 +78062,6 @@
           <t>[ROUTINE] Insider trade — Lacerte Rene A. (CEO) granted 116,619 Restricted Stock Units on 2026-09-15</t>
         </is>
       </c>
-      <c r="F2626" t="inlineStr"/>
-      <c r="G2626" t="inlineStr"/>
-      <c r="H2626" t="inlineStr"/>
     </row>
     <row r="2627">
       <c r="A2627" t="inlineStr">
@@ -78176,9 +78089,6 @@
           <t>9 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F2627" t="inlineStr"/>
-      <c r="G2627" t="inlineStr"/>
-      <c r="H2627" t="inlineStr"/>
     </row>
     <row r="2628">
       <c r="A2628" t="inlineStr">
@@ -78206,9 +78116,6 @@
           <t>3 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F2628" t="inlineStr"/>
-      <c r="G2628" t="inlineStr"/>
-      <c r="H2628" t="inlineStr"/>
     </row>
     <row r="2629">
       <c r="A2629" t="inlineStr">
@@ -78236,9 +78143,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F2629" t="inlineStr"/>
-      <c r="G2629" t="inlineStr"/>
-      <c r="H2629" t="inlineStr"/>
     </row>
     <row r="2630">
       <c r="A2630" t="inlineStr">
@@ -78266,9 +78170,6 @@
           <t>[ROUTINE] Insider trade — Verma Shiv (Chief Financial Officer) sold 11,472 shares @ $110.42 ($1.27M) on 2026-09-15</t>
         </is>
       </c>
-      <c r="F2630" t="inlineStr"/>
-      <c r="G2630" t="inlineStr"/>
-      <c r="H2630" t="inlineStr"/>
     </row>
     <row r="2631">
       <c r="A2631" t="inlineStr">
@@ -78296,9 +78197,6 @@
           <t>1 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F2631" t="inlineStr"/>
-      <c r="G2631" t="inlineStr"/>
-      <c r="H2631" t="inlineStr"/>
     </row>
     <row r="2632">
       <c r="A2632" t="inlineStr">
@@ -78326,9 +78224,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F2632" t="inlineStr"/>
-      <c r="G2632" t="inlineStr"/>
-      <c r="H2632" t="inlineStr"/>
     </row>
     <row r="2633">
       <c r="A2633" t="inlineStr">
@@ -78356,9 +78251,6 @@
           <t>investor_relations: change detected</t>
         </is>
       </c>
-      <c r="F2633" t="inlineStr"/>
-      <c r="G2633" t="inlineStr"/>
-      <c r="H2633" t="inlineStr"/>
     </row>
     <row r="2634">
       <c r="A2634" t="inlineStr">
@@ -78386,9 +78278,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — David Fisher (Officer) plans to sell 31,163 shares (~$5.36M) on/after 09/17/2026</t>
         </is>
       </c>
-      <c r="F2634" t="inlineStr"/>
-      <c r="G2634" t="inlineStr"/>
-      <c r="H2634" t="inlineStr"/>
     </row>
     <row r="2635">
       <c r="A2635" t="inlineStr">
@@ -78416,9 +78305,1080 @@
           <t>[MATERIAL] Material event disclosure</t>
         </is>
       </c>
-      <c r="F2635" t="inlineStr"/>
-      <c r="G2635" t="inlineStr"/>
-      <c r="H2635" t="inlineStr"/>
+    </row>
+    <row r="2636">
+      <c r="A2636" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B2636" t="inlineStr">
+        <is>
+          <t>LYFT</t>
+        </is>
+      </c>
+      <c r="C2636" t="inlineStr">
+        <is>
+          <t>Lyft, Inc.</t>
+        </is>
+      </c>
+      <c r="D2636" t="inlineStr">
+        <is>
+          <t>https://www.lyft.com/blog</t>
+        </is>
+      </c>
+      <c r="E2636" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2637">
+      <c r="A2637" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B2637" t="inlineStr">
+        <is>
+          <t>EXPE</t>
+        </is>
+      </c>
+      <c r="C2637" t="inlineStr">
+        <is>
+          <t>Expedia Group, Inc.</t>
+        </is>
+      </c>
+      <c r="D2637" t="inlineStr">
+        <is>
+          <t>https://careers.expediagroup.com</t>
+        </is>
+      </c>
+      <c r="E2637" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2638">
+      <c r="A2638" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B2638" t="inlineStr">
+        <is>
+          <t>BKNG</t>
+        </is>
+      </c>
+      <c r="C2638" t="inlineStr">
+        <is>
+          <t>Booking Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D2638" t="inlineStr">
+        <is>
+          <t>https://www.booking.com/content/terms.html</t>
+        </is>
+      </c>
+      <c r="E2638" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2639">
+      <c r="A2639" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B2639" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="C2639" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="D2639" t="inlineStr">
+        <is>
+          <t>https://blog.google</t>
+        </is>
+      </c>
+      <c r="E2639" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2640">
+      <c r="A2640" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B2640" t="inlineStr">
+        <is>
+          <t>SNAP</t>
+        </is>
+      </c>
+      <c r="C2640" t="inlineStr">
+        <is>
+          <t>Snap Inc.</t>
+        </is>
+      </c>
+      <c r="D2640" t="inlineStr">
+        <is>
+          <t>https://investor.snap.com/governance/leadership</t>
+        </is>
+      </c>
+      <c r="E2640" t="inlineStr">
+        <is>
+          <t>management_team: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2641">
+      <c r="A2641" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B2641" t="inlineStr">
+        <is>
+          <t>SNAP</t>
+        </is>
+      </c>
+      <c r="C2641" t="inlineStr">
+        <is>
+          <t>Snap Inc.</t>
+        </is>
+      </c>
+      <c r="D2641" t="inlineStr">
+        <is>
+          <t>https://newsroom.snap.com</t>
+        </is>
+      </c>
+      <c r="E2641" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2642">
+      <c r="A2642" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B2642" t="inlineStr">
+        <is>
+          <t>PINS</t>
+        </is>
+      </c>
+      <c r="C2642" t="inlineStr">
+        <is>
+          <t>Pinterest, Inc.</t>
+        </is>
+      </c>
+      <c r="D2642" t="inlineStr">
+        <is>
+          <t>https://www.pinterestcareers.com</t>
+        </is>
+      </c>
+      <c r="E2642" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2643">
+      <c r="A2643" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B2643" t="inlineStr">
+        <is>
+          <t>RDDT</t>
+        </is>
+      </c>
+      <c r="C2643" t="inlineStr">
+        <is>
+          <t>Reddit, Inc.</t>
+        </is>
+      </c>
+      <c r="D2643" t="inlineStr">
+        <is>
+          <t>https://redditinc.com/careers</t>
+        </is>
+      </c>
+      <c r="E2643" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2644">
+      <c r="A2644" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B2644" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="C2644" t="inlineStr">
+        <is>
+          <t>Unity Software Inc.</t>
+        </is>
+      </c>
+      <c r="D2644" t="inlineStr">
+        <is>
+          <t>https://careers.unity.com</t>
+        </is>
+      </c>
+      <c r="E2644" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2645">
+      <c r="A2645" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B2645" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="C2645" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="D2645" t="inlineStr">
+        <is>
+          <t>https://about.netflix.com/newsroom</t>
+        </is>
+      </c>
+      <c r="E2645" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2646">
+      <c r="A2646" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B2646" t="inlineStr">
+        <is>
+          <t>SPOT</t>
+        </is>
+      </c>
+      <c r="C2646" t="inlineStr">
+        <is>
+          <t>Spotify Technology S.A.</t>
+        </is>
+      </c>
+      <c r="D2646" t="inlineStr">
+        <is>
+          <t>https://www.spotify.com/premium</t>
+        </is>
+      </c>
+      <c r="E2646" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2647">
+      <c r="A2647" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B2647" t="inlineStr">
+        <is>
+          <t>SPOT</t>
+        </is>
+      </c>
+      <c r="C2647" t="inlineStr">
+        <is>
+          <t>Spotify Technology S.A.</t>
+        </is>
+      </c>
+      <c r="D2647" t="inlineStr">
+        <is>
+          <t>https://newsroom.spotify.com</t>
+        </is>
+      </c>
+      <c r="E2647" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2648">
+      <c r="A2648" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B2648" t="inlineStr">
+        <is>
+          <t>SPOT</t>
+        </is>
+      </c>
+      <c r="C2648" t="inlineStr">
+        <is>
+          <t>Spotify Technology S.A.</t>
+        </is>
+      </c>
+      <c r="D2648" t="inlineStr">
+        <is>
+          <t>https://www.lifeatspotify.com</t>
+        </is>
+      </c>
+      <c r="E2648" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2649">
+      <c r="A2649" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B2649" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="C2649" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="D2649" t="inlineStr">
+        <is>
+          <t>https://www.disneyplus.com/welcome</t>
+        </is>
+      </c>
+      <c r="E2649" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2650">
+      <c r="A2650" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B2650" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="C2650" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="D2650" t="inlineStr">
+        <is>
+          <t>https://thewaltdisneycompany.com/news/</t>
+        </is>
+      </c>
+      <c r="E2650" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2651">
+      <c r="A2651" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B2651" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="C2651" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="D2651" t="inlineStr">
+        <is>
+          <t>https://jobs.disneycareers.com</t>
+        </is>
+      </c>
+      <c r="E2651" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2652">
+      <c r="A2652" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B2652" t="inlineStr">
+        <is>
+          <t>FOXA</t>
+        </is>
+      </c>
+      <c r="C2652" t="inlineStr">
+        <is>
+          <t>Fox Corporation</t>
+        </is>
+      </c>
+      <c r="D2652" t="inlineStr">
+        <is>
+          <t>https://foxcareers.com</t>
+        </is>
+      </c>
+      <c r="E2652" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2653">
+      <c r="A2653" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B2653" t="inlineStr">
+        <is>
+          <t>LYV</t>
+        </is>
+      </c>
+      <c r="C2653" t="inlineStr">
+        <is>
+          <t>Live Nation Entertainment, Inc.</t>
+        </is>
+      </c>
+      <c r="D2653" t="inlineStr">
+        <is>
+          <t>https://investors.livenationentertainment.com</t>
+        </is>
+      </c>
+      <c r="E2653" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2654">
+      <c r="A2654" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B2654" t="inlineStr">
+        <is>
+          <t>LYV</t>
+        </is>
+      </c>
+      <c r="C2654" t="inlineStr">
+        <is>
+          <t>Live Nation Entertainment, Inc.</t>
+        </is>
+      </c>
+      <c r="D2654" t="inlineStr">
+        <is>
+          <t>https://www.livenationentertainment.com/careers</t>
+        </is>
+      </c>
+      <c r="E2654" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2655">
+      <c r="A2655" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B2655" t="inlineStr">
+        <is>
+          <t>TTWO</t>
+        </is>
+      </c>
+      <c r="C2655" t="inlineStr">
+        <is>
+          <t>Take-Two Interactive Software, Inc.</t>
+        </is>
+      </c>
+      <c r="D2655" t="inlineStr">
+        <is>
+          <t>https://ir.take2games.com</t>
+        </is>
+      </c>
+      <c r="E2655" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2656">
+      <c r="A2656" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B2656" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="C2656" t="inlineStr">
+        <is>
+          <t>Electronic Arts Inc.</t>
+        </is>
+      </c>
+      <c r="D2656" t="inlineStr">
+        <is>
+          <t>https://www.ea.com/news</t>
+        </is>
+      </c>
+      <c r="E2656" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2657">
+      <c r="A2657" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B2657" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="C2657" t="inlineStr">
+        <is>
+          <t>Electronic Arts Inc.</t>
+        </is>
+      </c>
+      <c r="D2657" t="inlineStr">
+        <is>
+          <t>https://ir.ea.com</t>
+        </is>
+      </c>
+      <c r="E2657" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2658">
+      <c r="A2658" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B2658" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C2658" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D2658" t="inlineStr">
+        <is>
+          <t>https://www.shopify.com/careers</t>
+        </is>
+      </c>
+      <c r="E2658" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F2658" t="inlineStr"/>
+      <c r="G2658" t="inlineStr"/>
+      <c r="H2658" t="inlineStr"/>
+    </row>
+    <row r="2659">
+      <c r="A2659" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B2659" t="inlineStr">
+        <is>
+          <t>EBAY</t>
+        </is>
+      </c>
+      <c r="C2659" t="inlineStr">
+        <is>
+          <t>eBay Inc.</t>
+        </is>
+      </c>
+      <c r="D2659" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/help/policies/member-behaviour-policies/user-agreement?id=4259</t>
+        </is>
+      </c>
+      <c r="E2659" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+      <c r="F2659" t="inlineStr"/>
+      <c r="G2659" t="inlineStr"/>
+      <c r="H2659" t="inlineStr"/>
+    </row>
+    <row r="2660">
+      <c r="A2660" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B2660" t="inlineStr">
+        <is>
+          <t>CHWY</t>
+        </is>
+      </c>
+      <c r="C2660" t="inlineStr">
+        <is>
+          <t>Chewy Inc.</t>
+        </is>
+      </c>
+      <c r="D2660" t="inlineStr">
+        <is>
+          <t>https://careers.chewy.com</t>
+        </is>
+      </c>
+      <c r="E2660" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F2660" t="inlineStr"/>
+      <c r="G2660" t="inlineStr"/>
+      <c r="H2660" t="inlineStr"/>
+    </row>
+    <row r="2661">
+      <c r="A2661" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B2661" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C2661" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D2661" t="inlineStr">
+        <is>
+          <t>https://about.doordash.com/en-us/news</t>
+        </is>
+      </c>
+      <c r="E2661" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F2661" t="inlineStr"/>
+      <c r="G2661" t="inlineStr"/>
+      <c r="H2661" t="inlineStr"/>
+    </row>
+    <row r="2662">
+      <c r="A2662" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B2662" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C2662" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D2662" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/instacart</t>
+        </is>
+      </c>
+      <c r="E2662" t="inlineStr">
+        <is>
+          <t>7 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F2662" t="inlineStr"/>
+      <c r="G2662" t="inlineStr"/>
+      <c r="H2662" t="inlineStr"/>
+    </row>
+    <row r="2663">
+      <c r="A2663" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B2663" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C2663" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D2663" t="inlineStr">
+        <is>
+          <t>https://www.instacart.com/company/newsroom</t>
+        </is>
+      </c>
+      <c r="E2663" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F2663" t="inlineStr"/>
+      <c r="G2663" t="inlineStr"/>
+      <c r="H2663" t="inlineStr"/>
+    </row>
+    <row r="2664">
+      <c r="A2664" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B2664" t="inlineStr">
+        <is>
+          <t>DUOL</t>
+        </is>
+      </c>
+      <c r="C2664" t="inlineStr">
+        <is>
+          <t>Duolingo Inc.</t>
+        </is>
+      </c>
+      <c r="D2664" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/duolingo</t>
+        </is>
+      </c>
+      <c r="E2664" t="inlineStr">
+        <is>
+          <t>1 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F2664" t="inlineStr"/>
+      <c r="G2664" t="inlineStr"/>
+      <c r="H2664" t="inlineStr"/>
+    </row>
+    <row r="2665">
+      <c r="A2665" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B2665" t="inlineStr">
+        <is>
+          <t>MTCH</t>
+        </is>
+      </c>
+      <c r="C2665" t="inlineStr">
+        <is>
+          <t>Match Group Inc.</t>
+        </is>
+      </c>
+      <c r="D2665" t="inlineStr">
+        <is>
+          <t>https://ir.mtch.com/leadership/default.aspx</t>
+        </is>
+      </c>
+      <c r="E2665" t="inlineStr">
+        <is>
+          <t>management_team: change detected</t>
+        </is>
+      </c>
+      <c r="F2665" t="inlineStr"/>
+      <c r="G2665" t="inlineStr"/>
+      <c r="H2665" t="inlineStr"/>
+    </row>
+    <row r="2666">
+      <c r="A2666" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B2666" t="inlineStr">
+        <is>
+          <t>MTCH</t>
+        </is>
+      </c>
+      <c r="C2666" t="inlineStr">
+        <is>
+          <t>Match Group Inc.</t>
+        </is>
+      </c>
+      <c r="D2666" t="inlineStr">
+        <is>
+          <t>https://mtch.com/news</t>
+        </is>
+      </c>
+      <c r="E2666" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F2666" t="inlineStr"/>
+      <c r="G2666" t="inlineStr"/>
+      <c r="H2666" t="inlineStr"/>
+    </row>
+    <row r="2667">
+      <c r="A2667" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B2667" t="inlineStr">
+        <is>
+          <t>COMP</t>
+        </is>
+      </c>
+      <c r="C2667" t="inlineStr">
+        <is>
+          <t>Compass Inc.</t>
+        </is>
+      </c>
+      <c r="D2667" t="inlineStr">
+        <is>
+          <t>https://www.compass.com/careers/</t>
+        </is>
+      </c>
+      <c r="E2667" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F2667" t="inlineStr"/>
+      <c r="G2667" t="inlineStr"/>
+      <c r="H2667" t="inlineStr"/>
+    </row>
+    <row r="2668">
+      <c r="A2668" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B2668" t="inlineStr">
+        <is>
+          <t>TOST</t>
+        </is>
+      </c>
+      <c r="C2668" t="inlineStr">
+        <is>
+          <t>Toast Inc.</t>
+        </is>
+      </c>
+      <c r="D2668" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/toast</t>
+        </is>
+      </c>
+      <c r="E2668" t="inlineStr">
+        <is>
+          <t>11 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F2668" t="inlineStr"/>
+      <c r="G2668" t="inlineStr"/>
+      <c r="H2668" t="inlineStr"/>
+    </row>
+    <row r="2669">
+      <c r="A2669" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B2669" t="inlineStr">
+        <is>
+          <t>SEZL</t>
+        </is>
+      </c>
+      <c r="C2669" t="inlineStr">
+        <is>
+          <t>Sezzle Inc.</t>
+        </is>
+      </c>
+      <c r="D2669" t="inlineStr">
+        <is>
+          <t>https://investors.sezzle.com</t>
+        </is>
+      </c>
+      <c r="E2669" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+      <c r="F2669" t="inlineStr"/>
+      <c r="G2669" t="inlineStr"/>
+      <c r="H2669" t="inlineStr"/>
+    </row>
+    <row r="2670">
+      <c r="A2670" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B2670" t="inlineStr">
+        <is>
+          <t>AFRM</t>
+        </is>
+      </c>
+      <c r="C2670" t="inlineStr">
+        <is>
+          <t>Affirm Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D2670" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/affirm</t>
+        </is>
+      </c>
+      <c r="E2670" t="inlineStr">
+        <is>
+          <t>3 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F2670" t="inlineStr"/>
+      <c r="G2670" t="inlineStr"/>
+      <c r="H2670" t="inlineStr"/>
+    </row>
+    <row r="2671">
+      <c r="A2671" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B2671" t="inlineStr">
+        <is>
+          <t>HOOD</t>
+        </is>
+      </c>
+      <c r="C2671" t="inlineStr">
+        <is>
+          <t>Robinhood Markets Inc.</t>
+        </is>
+      </c>
+      <c r="D2671" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/robinhood</t>
+        </is>
+      </c>
+      <c r="E2671" t="inlineStr">
+        <is>
+          <t>4 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F2671" t="inlineStr"/>
+      <c r="G2671" t="inlineStr"/>
+      <c r="H2671" t="inlineStr"/>
+    </row>
+    <row r="2672">
+      <c r="A2672" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B2672" t="inlineStr">
+        <is>
+          <t>UPST</t>
+        </is>
+      </c>
+      <c r="C2672" t="inlineStr">
+        <is>
+          <t>Upstart Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D2672" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/upstart</t>
+        </is>
+      </c>
+      <c r="E2672" t="inlineStr">
+        <is>
+          <t>2 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F2672" t="inlineStr"/>
+      <c r="G2672" t="inlineStr"/>
+      <c r="H2672" t="inlineStr"/>
+    </row>
+    <row r="2673">
+      <c r="A2673" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B2673" t="inlineStr">
+        <is>
+          <t>ONON</t>
+        </is>
+      </c>
+      <c r="C2673" t="inlineStr">
+        <is>
+          <t>On Holding AG</t>
+        </is>
+      </c>
+      <c r="D2673" t="inlineStr">
+        <is>
+          <t>https://www.on-running.com/en-us/articles/</t>
+        </is>
+      </c>
+      <c r="E2673" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F2673" t="inlineStr"/>
+      <c r="G2673" t="inlineStr"/>
+      <c r="H2673" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
